--- a/jogos_2025-07-20.xlsx
+++ b/jogos_2025-07-20.xlsx
@@ -232,12 +232,12 @@
     <t>Japan J1 League</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
@@ -256,12 +256,12 @@
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
@@ -271,15 +271,15 @@
     <t>Chile Primera División</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
+    <t>Canada Canadian Premier League</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
-    <t>Canada Canadian Premier League</t>
-  </si>
-  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
@@ -310,42 +310,42 @@
     <t>Shimizu S-Pulse</t>
   </si>
   <si>
+    <t>Albirex Niigata</t>
+  </si>
+  <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
+  </si>
+  <si>
     <t>Fagiano Okayama</t>
   </si>
   <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Cheongju</t>
+    <t>Gamba Osaka</t>
   </si>
   <si>
     <t>Yokohama F. Marinos</t>
   </si>
   <si>
-    <t>Gamba Osaka</t>
-  </si>
-  <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
-    <t>Albirex Niigata</t>
-  </si>
-  <si>
     <t>Varberg</t>
   </si>
   <si>
+    <t>Shenzhen Juniors</t>
+  </si>
+  <si>
     <t>Nanjing City</t>
   </si>
   <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
-    <t>Shenzhen Juniors</t>
-  </si>
-  <si>
     <t>Sirius</t>
   </si>
   <si>
@@ -355,21 +355,21 @@
     <t>Vålerenga</t>
   </si>
   <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
     <t>SJK</t>
   </si>
   <si>
     <t>Kyzyl-Zhar</t>
   </si>
   <si>
-    <t>Kalmar</t>
+    <t>Internacional</t>
   </si>
   <si>
     <t>Nõmme Kalju</t>
   </si>
   <si>
-    <t>Internacional</t>
-  </si>
-  <si>
     <t>Tammeka</t>
   </si>
   <si>
@@ -379,60 +379,60 @@
     <t>Halmstad</t>
   </si>
   <si>
+    <t>Platense</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>Independiente</t>
+  </si>
+  <si>
+    <t>Barracas Central</t>
+  </si>
+  <si>
+    <t>Lanús</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
     <t>Tromsø</t>
   </si>
   <si>
-    <t>Independiente</t>
+    <t>Tigre</t>
+  </si>
+  <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Newell's Old Boys</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Boca Juniors</t>
   </si>
   <si>
     <t>Atlético Tucumán</t>
   </si>
   <si>
-    <t>Platense</t>
+    <t>Defensa y Justicia</t>
   </si>
   <si>
     <t>Instituto</t>
   </si>
   <si>
-    <t>San Lorenzo</t>
-  </si>
-  <si>
-    <t>Lanús</t>
-  </si>
-  <si>
-    <t>Barracas Central</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Estudiantes</t>
-  </si>
-  <si>
     <t>Godoy Cruz</t>
   </si>
   <si>
-    <t>Boca Juniors</t>
-  </si>
-  <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
-    <t>Tigre</t>
-  </si>
-  <si>
-    <t>Newell's Old Boys</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
-    <t>Defensa y Justicia</t>
-  </si>
-  <si>
     <t>HJK</t>
   </si>
   <si>
@@ -454,57 +454,57 @@
     <t>HamKam</t>
   </si>
   <si>
+    <t>Ñublense</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
     <t>Vitória</t>
   </si>
   <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Valour FC</t>
+  </si>
+  <si>
+    <t>Toronto II</t>
+  </si>
+  <si>
     <t>New England II</t>
   </si>
   <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Valour FC</t>
-  </si>
-  <si>
-    <t>Ñublense</t>
-  </si>
-  <si>
     <t>Magallanes</t>
   </si>
   <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
+    <t>CSA</t>
+  </si>
+  <si>
     <t>Confiança</t>
   </si>
   <si>
-    <t>CSA</t>
+    <t>Palmeiras</t>
   </si>
   <si>
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>Palmeiras</t>
+    <t>Deportes Temuco</t>
   </si>
   <si>
     <t>América Mineiro</t>
   </si>
   <si>
-    <t>Deportes Temuco</t>
+    <t>Ypiranga Erechim</t>
   </si>
   <si>
     <t>Brusque</t>
   </si>
   <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
     <t>Flamengo</t>
   </si>
   <si>
@@ -544,42 +544,42 @@
     <t>Yokohama</t>
   </si>
   <si>
+    <t>Sanfrecce Hiroshima</t>
+  </si>
+  <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
     <t>Vissel Kobe</t>
   </si>
   <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
     <t>Asan Mugunghwa</t>
   </si>
   <si>
-    <t>Cheonan City</t>
+    <t>Kawasaki Frontale</t>
   </si>
   <si>
     <t>Nagoya Grampus</t>
   </si>
   <si>
-    <t>Kawasaki Frontale</t>
-  </si>
-  <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
-    <t>Sanfrecce Hiroshima</t>
-  </si>
-  <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
+    <t>Shanghai Jiading</t>
+  </si>
+  <si>
     <t>Guangxi Baoyun</t>
   </si>
   <si>
     <t>Shaanxi Union</t>
   </si>
   <si>
-    <t>Shanghai Jiading</t>
-  </si>
-  <si>
     <t>IFK Göteborg</t>
   </si>
   <si>
@@ -589,21 +589,21 @@
     <t>Haugesund</t>
   </si>
   <si>
+    <t>Brage</t>
+  </si>
+  <si>
     <t>Gnistan</t>
   </si>
   <si>
     <t>Atyrau</t>
   </si>
   <si>
-    <t>Brage</t>
+    <t>Ceará</t>
   </si>
   <si>
     <t>Tallinna Kalev</t>
   </si>
   <si>
-    <t>Ceará</t>
-  </si>
-  <si>
     <t>Tallinna FC Flora</t>
   </si>
   <si>
@@ -613,60 +613,60 @@
     <t>Häcken</t>
   </si>
   <si>
+    <t>Vélez Sarsfield</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Talleres Córdoba</t>
+  </si>
+  <si>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>Rosario Central</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
     <t>Bryne</t>
   </si>
   <si>
-    <t>Talleres Córdoba</t>
+    <t>Argentinos Juniors</t>
+  </si>
+  <si>
+    <t>Gimnasia La Plata</t>
+  </si>
+  <si>
+    <t>Racing Club</t>
+  </si>
+  <si>
+    <t>Banfield</t>
+  </si>
+  <si>
+    <t>Huracán</t>
+  </si>
+  <si>
+    <t>Unión Santa Fe</t>
   </si>
   <si>
     <t>Central Córdoba SdE</t>
   </si>
   <si>
-    <t>Vélez Sarsfield</t>
+    <t>Aldosivi</t>
   </si>
   <si>
     <t>River Plate</t>
   </si>
   <si>
-    <t>Gimnasia La Plata</t>
-  </si>
-  <si>
-    <t>Rosario Central</t>
-  </si>
-  <si>
-    <t>Independiente Rivadavia</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Huracán</t>
-  </si>
-  <si>
     <t>Sarmiento</t>
   </si>
   <si>
-    <t>Unión Santa Fe</t>
-  </si>
-  <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Argentinos Juniors</t>
-  </si>
-  <si>
-    <t>Banfield</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Racing Club</t>
-  </si>
-  <si>
-    <t>Aldosivi</t>
-  </si>
-  <si>
     <t>Oulu</t>
   </si>
   <si>
@@ -688,55 +688,55 @@
     <t>Fredrikstad</t>
   </si>
   <si>
+    <t>Universidad Chile</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
     <t>Bragantino</t>
   </si>
   <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
+    <t>Cavalry FC</t>
+  </si>
+  <si>
+    <t>Chicago Fire II</t>
+  </si>
+  <si>
     <t>Orlando City II</t>
   </si>
   <si>
-    <t>Botafogo SP</t>
-  </si>
-  <si>
-    <t>Cavalry FC</t>
-  </si>
-  <si>
-    <t>Universidad Chile</t>
-  </si>
-  <si>
     <t>Univ. Concepción</t>
   </si>
   <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
-    <t>Juventude</t>
-  </si>
-  <si>
     <t>Valur</t>
   </si>
   <si>
+    <t>Figueirense</t>
+  </si>
+  <si>
     <t>Tombense</t>
   </si>
   <si>
-    <t>Figueirense</t>
+    <t>Atlético Mineiro</t>
   </si>
   <si>
     <t>Botafogo</t>
   </si>
   <si>
-    <t>Atlético Mineiro</t>
+    <t>Santiago Morning</t>
   </si>
   <si>
     <t>Chapecoense</t>
   </si>
   <si>
-    <t>Santiago Morning</t>
+    <t>São Bernardo</t>
   </si>
   <si>
     <t>Retrô</t>
-  </si>
-  <si>
-    <t>São Bernardo</t>
   </si>
   <si>
     <t>Fluminense</t>
@@ -1278,13 +1278,13 @@
         <v>247</v>
       </c>
       <c r="L2">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="M2">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="N2">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O2">
         <v>1.5</v>
@@ -1296,40 +1296,40 @@
         <v>3</v>
       </c>
       <c r="R2">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S2">
+        <v>2.62</v>
+      </c>
+      <c r="T2">
         <v>2.8</v>
-      </c>
-      <c r="T2">
-        <v>2.92</v>
       </c>
       <c r="U2">
         <v>1.4</v>
       </c>
       <c r="V2">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="W2">
         <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="Z2">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AA2">
         <v>3.4</v>
       </c>
       <c r="AB2">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AC2">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AD2">
         <v>3.4</v>
@@ -1338,10 +1338,10 @@
         <v>1.27</v>
       </c>
       <c r="AF2">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG2">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH2">
         <v>6.5</v>
@@ -1394,13 +1394,13 @@
         <v>247</v>
       </c>
       <c r="L3">
-        <v>2.95</v>
+        <v>4.6</v>
       </c>
       <c r="M3">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N3">
-        <v>2.02</v>
+        <v>1.61</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1510,13 +1510,13 @@
         <v>247</v>
       </c>
       <c r="L4">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="M4">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N4">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="O4">
         <v>1.44</v>
@@ -1528,7 +1528,7 @@
         <v>2.88</v>
       </c>
       <c r="R4">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S4">
         <v>3.9</v>
@@ -1540,7 +1540,7 @@
         <v>1.67</v>
       </c>
       <c r="V4">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="W4">
         <v>1.18</v>
@@ -1552,34 +1552,34 @@
         <v>12</v>
       </c>
       <c r="Z4">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AA4">
-        <v>5.45</v>
+        <v>5.55</v>
       </c>
       <c r="AB4">
         <v>1.5</v>
       </c>
       <c r="AC4">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AD4">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AE4">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH4">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AI4">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AJ4" t="s">
         <v>248</v>
@@ -1626,13 +1626,13 @@
         <v>247</v>
       </c>
       <c r="L5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M5">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>1.29</v>
@@ -1644,58 +1644,58 @@
         <v>3.5</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB5">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC5">
         <v>2.62</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ5" t="s">
         <v>248</v>
@@ -2090,76 +2090,76 @@
         <v>247</v>
       </c>
       <c r="L9">
-        <v>4.6</v>
+        <v>3.99</v>
       </c>
       <c r="M9">
-        <v>3.28</v>
+        <v>3.36</v>
       </c>
       <c r="N9">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="O9">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="P9">
-        <v>7.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q9">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="R9">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S9">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T9">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="U9">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="V9">
-        <v>8.75</v>
+        <v>8</v>
       </c>
       <c r="W9">
+        <v>1.08</v>
+      </c>
+      <c r="X9">
         <v>1.06</v>
       </c>
-      <c r="X9">
-        <v>1.08</v>
-      </c>
       <c r="Y9">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z9">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AA9">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AB9">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="AC9">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AD9">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AE9">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AF9">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AG9">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AH9">
-        <v>8.25</v>
+        <v>7</v>
       </c>
       <c r="AI9">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AJ9" t="s">
         <v>248</v>
@@ -2206,76 +2206,76 @@
         <v>247</v>
       </c>
       <c r="L10">
-        <v>5.5</v>
+        <v>2.19</v>
       </c>
       <c r="M10">
-        <v>4.1</v>
+        <v>3.13</v>
       </c>
       <c r="N10">
+        <v>2.91</v>
+      </c>
+      <c r="O10">
+        <v>1.73</v>
+      </c>
+      <c r="P10">
+        <v>7.75</v>
+      </c>
+      <c r="Q10">
+        <v>2.38</v>
+      </c>
+      <c r="R10">
         <v>1.44</v>
       </c>
-      <c r="O10">
-        <v>3.2</v>
-      </c>
-      <c r="P10">
-        <v>15.25</v>
-      </c>
-      <c r="Q10">
-        <v>1.36</v>
-      </c>
-      <c r="R10">
-        <v>1.3</v>
-      </c>
       <c r="S10">
+        <v>2.63</v>
+      </c>
+      <c r="T10">
         <v>3.25</v>
       </c>
-      <c r="T10">
-        <v>2.45</v>
-      </c>
       <c r="U10">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y10">
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="Z10">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AA10">
-        <v>4.05</v>
+        <v>2.9</v>
       </c>
       <c r="AB10">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="AC10">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AD10">
-        <v>2.59</v>
+        <v>4.2</v>
       </c>
       <c r="AE10">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG10">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH10">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="AI10">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AJ10" t="s">
         <v>248</v>
@@ -2295,7 +2295,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
         <v>90</v>
@@ -2322,76 +2322,76 @@
         <v>247</v>
       </c>
       <c r="L11">
+        <v>2.18</v>
+      </c>
+      <c r="M11">
+        <v>3.12</v>
+      </c>
+      <c r="N11">
+        <v>2.93</v>
+      </c>
+      <c r="O11">
+        <v>1.79</v>
+      </c>
+      <c r="P11">
+        <v>10.5</v>
+      </c>
+      <c r="Q11">
         <v>2.16</v>
       </c>
-      <c r="M11">
-        <v>3.32</v>
-      </c>
-      <c r="N11">
+      <c r="R11">
+        <v>1.4</v>
+      </c>
+      <c r="S11">
+        <v>2.8</v>
+      </c>
+      <c r="T11">
+        <v>2.9</v>
+      </c>
+      <c r="U11">
+        <v>1.36</v>
+      </c>
+      <c r="V11">
+        <v>8.5</v>
+      </c>
+      <c r="W11">
+        <v>1.07</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
+        <v>9</v>
+      </c>
+      <c r="Z11">
+        <v>1.28</v>
+      </c>
+      <c r="AA11">
         <v>3.08</v>
       </c>
-      <c r="O11">
-        <v>1.8</v>
-      </c>
-      <c r="P11">
-        <v>9.1</v>
-      </c>
-      <c r="Q11">
-        <v>2.22</v>
-      </c>
-      <c r="R11">
-        <v>1.36</v>
-      </c>
-      <c r="S11">
-        <v>2.9</v>
-      </c>
-      <c r="T11">
-        <v>2.8</v>
-      </c>
-      <c r="U11">
-        <v>1.4</v>
-      </c>
-      <c r="V11">
-        <v>7</v>
-      </c>
-      <c r="W11">
-        <v>1.08</v>
-      </c>
-      <c r="X11">
-        <v>1</v>
-      </c>
-      <c r="Y11">
-        <v>9.1</v>
-      </c>
-      <c r="Z11">
-        <v>1.26</v>
-      </c>
-      <c r="AA11">
-        <v>3.22</v>
-      </c>
       <c r="AB11">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC11">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AD11">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="AE11">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AF11">
         <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH11">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AI11">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ11" t="s">
         <v>248</v>
@@ -2411,7 +2411,7 @@
         <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
         <v>90</v>
@@ -2438,76 +2438,76 @@
         <v>247</v>
       </c>
       <c r="L12">
-        <v>2.18</v>
+        <v>5.5</v>
       </c>
       <c r="M12">
-        <v>3.12</v>
+        <v>4.1</v>
       </c>
       <c r="N12">
-        <v>2.93</v>
+        <v>1.44</v>
       </c>
       <c r="O12">
-        <v>1.79</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>10.5</v>
+        <v>15.25</v>
       </c>
       <c r="Q12">
-        <v>2.16</v>
+        <v>1.36</v>
       </c>
       <c r="R12">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S12">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="T12">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="U12">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V12">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z12">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AA12">
-        <v>3.08</v>
+        <v>4.05</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC12">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AD12">
-        <v>3.58</v>
+        <v>2.59</v>
       </c>
       <c r="AE12">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AF12">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH12">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="AI12">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AJ12" t="s">
         <v>248</v>
@@ -2554,76 +2554,76 @@
         <v>247</v>
       </c>
       <c r="L13">
-        <v>2.79</v>
+        <v>4.6</v>
       </c>
       <c r="M13">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="N13">
-        <v>2.29</v>
+        <v>1.68</v>
       </c>
       <c r="O13">
+        <v>2.85</v>
+      </c>
+      <c r="P13">
+        <v>7.5</v>
+      </c>
+      <c r="Q13">
+        <v>1.58</v>
+      </c>
+      <c r="R13">
+        <v>1.46</v>
+      </c>
+      <c r="S13">
+        <v>2.5</v>
+      </c>
+      <c r="T13">
+        <v>3.1</v>
+      </c>
+      <c r="U13">
+        <v>1.31</v>
+      </c>
+      <c r="V13">
+        <v>8.75</v>
+      </c>
+      <c r="W13">
+        <v>1.06</v>
+      </c>
+      <c r="X13">
+        <v>1.08</v>
+      </c>
+      <c r="Y13">
+        <v>7.5</v>
+      </c>
+      <c r="Z13">
+        <v>1.4</v>
+      </c>
+      <c r="AA13">
+        <v>2.7</v>
+      </c>
+      <c r="AB13">
+        <v>2.13</v>
+      </c>
+      <c r="AC13">
+        <v>1.63</v>
+      </c>
+      <c r="AD13">
+        <v>4</v>
+      </c>
+      <c r="AE13">
+        <v>1.21</v>
+      </c>
+      <c r="AF13">
         <v>2.1</v>
       </c>
-      <c r="P13">
+      <c r="AG13">
+        <v>1.65</v>
+      </c>
+      <c r="AH13">
         <v>8.25</v>
       </c>
-      <c r="Q13">
-        <v>1.9</v>
-      </c>
-      <c r="R13">
-        <v>1.41</v>
-      </c>
-      <c r="S13">
-        <v>2.65</v>
-      </c>
-      <c r="T13">
-        <v>2.85</v>
-      </c>
-      <c r="U13">
-        <v>1.37</v>
-      </c>
-      <c r="V13">
-        <v>7.5</v>
-      </c>
-      <c r="W13">
-        <v>1.08</v>
-      </c>
-      <c r="X13">
+      <c r="AI13">
         <v>1.06</v>
-      </c>
-      <c r="Y13">
-        <v>8.25</v>
-      </c>
-      <c r="Z13">
-        <v>1.32</v>
-      </c>
-      <c r="AA13">
-        <v>3.1</v>
-      </c>
-      <c r="AB13">
-        <v>1.96</v>
-      </c>
-      <c r="AC13">
-        <v>1.74</v>
-      </c>
-      <c r="AD13">
-        <v>3.4</v>
-      </c>
-      <c r="AE13">
-        <v>1.27</v>
-      </c>
-      <c r="AF13">
-        <v>1.78</v>
-      </c>
-      <c r="AG13">
-        <v>1.9</v>
-      </c>
-      <c r="AH13">
-        <v>6.5</v>
-      </c>
-      <c r="AI13">
-        <v>1.09</v>
       </c>
       <c r="AJ13" t="s">
         <v>248</v>
@@ -2643,7 +2643,7 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
         <v>90</v>
@@ -2670,76 +2670,76 @@
         <v>247</v>
       </c>
       <c r="L14">
-        <v>2.47</v>
+        <v>2.16</v>
       </c>
       <c r="M14">
-        <v>3.23</v>
+        <v>3.32</v>
       </c>
       <c r="N14">
-        <v>2.47</v>
+        <v>3.08</v>
       </c>
       <c r="O14">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="P14">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="Q14">
-        <v>1.83</v>
+        <v>2.22</v>
       </c>
       <c r="R14">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S14">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="T14">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="U14">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V14">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="Z14">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AA14">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="AB14">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AC14">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AD14">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AE14">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AF14">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH14">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AI14">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AJ14" t="s">
         <v>248</v>
@@ -2759,7 +2759,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
         <v>90</v>
@@ -2786,76 +2786,76 @@
         <v>247</v>
       </c>
       <c r="L15">
-        <v>2.19</v>
+        <v>2.47</v>
       </c>
       <c r="M15">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
       <c r="N15">
-        <v>2.91</v>
+        <v>2.47</v>
       </c>
       <c r="O15">
+        <v>2.05</v>
+      </c>
+      <c r="P15">
+        <v>10</v>
+      </c>
+      <c r="Q15">
+        <v>1.83</v>
+      </c>
+      <c r="R15">
+        <v>1.33</v>
+      </c>
+      <c r="S15">
+        <v>3.25</v>
+      </c>
+      <c r="T15">
+        <v>2.63</v>
+      </c>
+      <c r="U15">
+        <v>1.44</v>
+      </c>
+      <c r="V15">
+        <v>6.5</v>
+      </c>
+      <c r="W15">
+        <v>1.11</v>
+      </c>
+      <c r="X15">
+        <v>1.05</v>
+      </c>
+      <c r="Y15">
+        <v>9.5</v>
+      </c>
+      <c r="Z15">
+        <v>1.25</v>
+      </c>
+      <c r="AA15">
+        <v>3.7</v>
+      </c>
+      <c r="AB15">
         <v>1.73</v>
       </c>
-      <c r="P15">
-        <v>7.75</v>
-      </c>
-      <c r="Q15">
-        <v>2.38</v>
-      </c>
-      <c r="R15">
-        <v>1.44</v>
-      </c>
-      <c r="S15">
-        <v>2.63</v>
-      </c>
-      <c r="T15">
-        <v>3.25</v>
-      </c>
-      <c r="U15">
-        <v>1.33</v>
-      </c>
-      <c r="V15">
-        <v>9</v>
-      </c>
-      <c r="W15">
-        <v>1.07</v>
-      </c>
-      <c r="X15">
-        <v>1.08</v>
-      </c>
-      <c r="Y15">
-        <v>7.5</v>
-      </c>
-      <c r="Z15">
-        <v>1.4</v>
-      </c>
-      <c r="AA15">
-        <v>2.9</v>
-      </c>
-      <c r="AB15">
-        <v>2.02</v>
-      </c>
       <c r="AC15">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AD15">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AE15">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AF15">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AH15">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AI15">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AJ15" t="s">
         <v>248</v>
@@ -2902,37 +2902,37 @@
         <v>247</v>
       </c>
       <c r="L16">
-        <v>3.99</v>
+        <v>2.79</v>
       </c>
       <c r="M16">
-        <v>3.36</v>
+        <v>3.08</v>
       </c>
       <c r="N16">
-        <v>1.75</v>
+        <v>2.29</v>
       </c>
       <c r="O16">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="P16">
-        <v>8.75</v>
+        <v>8.25</v>
       </c>
       <c r="Q16">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="R16">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S16">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="T16">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U16">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W16">
         <v>1.08</v>
@@ -2941,34 +2941,34 @@
         <v>1.06</v>
       </c>
       <c r="Y16">
-        <v>8.5</v>
+        <v>8.25</v>
       </c>
       <c r="Z16">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AA16">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AB16">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AC16">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AD16">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AE16">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF16">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH16">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AI16">
         <v>1.09</v>
@@ -3134,76 +3134,76 @@
         <v>247</v>
       </c>
       <c r="L18">
-        <v>1.57</v>
+        <v>2.36</v>
       </c>
       <c r="M18">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="N18">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="O18">
+        <v>1.8</v>
+      </c>
+      <c r="P18">
+        <v>7.8</v>
+      </c>
+      <c r="Q18">
+        <v>2.38</v>
+      </c>
+      <c r="R18">
         <v>1.44</v>
       </c>
-      <c r="P18">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q18">
-        <v>3.4</v>
-      </c>
-      <c r="R18">
-        <v>1.39</v>
-      </c>
       <c r="S18">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="T18">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V18">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W18">
+        <v>1.06</v>
+      </c>
+      <c r="X18">
         <v>1.02</v>
       </c>
-      <c r="X18">
-        <v>1.06</v>
-      </c>
       <c r="Y18">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="Z18">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AA18">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="AB18">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC18">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD18">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AE18">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AF18">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AG18">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH18">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AI18">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ18" t="s">
         <v>248</v>
@@ -3250,73 +3250,73 @@
         <v>247</v>
       </c>
       <c r="L19">
-        <v>3.25</v>
+        <v>1.57</v>
       </c>
       <c r="M19">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="N19">
-        <v>2.21</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="P19">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q19">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="R19">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S19">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="T19">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U19">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V19">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="Z19">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AA19">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="AB19">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AC19">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AD19">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AE19">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AF19">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH19">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="AI19">
         <v>1.04</v>
@@ -3366,76 +3366,76 @@
         <v>247</v>
       </c>
       <c r="L20">
-        <v>2.36</v>
+        <v>3.25</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N20">
+        <v>2.21</v>
+      </c>
+      <c r="O20">
+        <v>1.91</v>
+      </c>
+      <c r="P20">
+        <v>7.9</v>
+      </c>
+      <c r="Q20">
+        <v>2.1</v>
+      </c>
+      <c r="R20">
+        <v>1.42</v>
+      </c>
+      <c r="S20">
+        <v>2.62</v>
+      </c>
+      <c r="T20">
         <v>2.9</v>
       </c>
-      <c r="O20">
-        <v>1.8</v>
-      </c>
-      <c r="P20">
-        <v>7.8</v>
-      </c>
-      <c r="Q20">
-        <v>2.38</v>
-      </c>
-      <c r="R20">
-        <v>1.44</v>
-      </c>
-      <c r="S20">
-        <v>2.6</v>
-      </c>
-      <c r="T20">
-        <v>3</v>
-      </c>
       <c r="U20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V20">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="W20">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="Z20">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AA20">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="AB20">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC20">
         <v>1.7</v>
       </c>
       <c r="AD20">
-        <v>3.58</v>
+        <v>3.05</v>
       </c>
       <c r="AE20">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AF20">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AG20">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH20">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="AI20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ20" t="s">
         <v>248</v>
@@ -3803,7 +3803,7 @@
         <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
         <v>90</v>
@@ -3830,76 +3830,76 @@
         <v>247</v>
       </c>
       <c r="L24">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="M24">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="N24">
-        <v>4.2</v>
+        <v>6.9</v>
       </c>
       <c r="O24">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="P24">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q24">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R24">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S24">
         <v>3.5</v>
       </c>
       <c r="T24">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="U24">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="V24">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="W24">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z24">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AA24">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="AB24">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC24">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AD24">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="AE24">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AG24">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AH24">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="AI24">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AJ24" t="s">
         <v>248</v>
@@ -3919,7 +3919,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
         <v>90</v>
@@ -3946,76 +3946,76 @@
         <v>247</v>
       </c>
       <c r="L25">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="M25">
-        <v>4.57</v>
+        <v>4.1</v>
       </c>
       <c r="N25">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="O25">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="P25">
-        <v>8.9</v>
+        <v>14</v>
       </c>
       <c r="Q25">
-        <v>3.52</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S25">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="T25">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="U25">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="W25">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X25">
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>8.9</v>
+        <v>17</v>
       </c>
       <c r="Z25">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AA25">
-        <v>3.28</v>
+        <v>5.2</v>
       </c>
       <c r="AB25">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AC25">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="AD25">
-        <v>3.08</v>
+        <v>2.27</v>
       </c>
       <c r="AE25">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AF25">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="AH25">
-        <v>5.75</v>
+        <v>3.8</v>
       </c>
       <c r="AI25">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="AJ25" t="s">
         <v>248</v>
@@ -4035,7 +4035,7 @@
         <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
         <v>90</v>
@@ -4062,76 +4062,76 @@
         <v>247</v>
       </c>
       <c r="L26">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="M26">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N26">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="O26">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="P26">
-        <v>11</v>
+        <v>8.9</v>
       </c>
       <c r="Q26">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="R26">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S26">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="T26">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="U26">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="V26">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>11</v>
+        <v>8.9</v>
       </c>
       <c r="Z26">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AA26">
-        <v>4.33</v>
+        <v>3.28</v>
       </c>
       <c r="AB26">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AC26">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AD26">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="AE26">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AF26">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AG26">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AH26">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AI26">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AJ26" t="s">
         <v>248</v>
@@ -4178,76 +4178,76 @@
         <v>247</v>
       </c>
       <c r="L27">
-        <v>1.19</v>
+        <v>1.95</v>
       </c>
       <c r="M27">
-        <v>6.83</v>
+        <v>3.36</v>
       </c>
       <c r="N27">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="O27">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="P27">
-        <v>24</v>
+        <v>7.25</v>
       </c>
       <c r="Q27">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R27">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="S27">
-        <v>4.5</v>
+        <v>2.61</v>
       </c>
       <c r="T27">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="U27">
-        <v>2.08</v>
+        <v>1.31</v>
       </c>
       <c r="V27">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="W27">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y27">
-        <v>20</v>
+        <v>7.5</v>
       </c>
       <c r="Z27">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>2.85</v>
       </c>
       <c r="AB27">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="AC27">
-        <v>3.34</v>
+        <v>1.57</v>
       </c>
       <c r="AD27">
-        <v>1.7</v>
+        <v>4.45</v>
       </c>
       <c r="AE27">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="AF27">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG27">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AH27">
-        <v>2.55</v>
+        <v>8.5</v>
       </c>
       <c r="AI27">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="AJ27" t="s">
         <v>248</v>
@@ -4294,76 +4294,76 @@
         <v>247</v>
       </c>
       <c r="L28">
-        <v>1.95</v>
+        <v>1.19</v>
       </c>
       <c r="M28">
-        <v>3.36</v>
+        <v>6.83</v>
       </c>
       <c r="N28">
+        <v>9.4</v>
+      </c>
+      <c r="O28">
+        <v>1.22</v>
+      </c>
+      <c r="P28">
+        <v>24</v>
+      </c>
+      <c r="Q28">
         <v>4</v>
       </c>
-      <c r="O28">
-        <v>1.44</v>
-      </c>
-      <c r="P28">
-        <v>7.25</v>
-      </c>
-      <c r="Q28">
-        <v>3.5</v>
-      </c>
       <c r="R28">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="S28">
-        <v>2.61</v>
+        <v>4.5</v>
       </c>
       <c r="T28">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="U28">
-        <v>1.31</v>
+        <v>2.08</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="X28">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>7.5</v>
+        <v>20</v>
       </c>
       <c r="Z28">
-        <v>1.43</v>
+        <v>1.03</v>
       </c>
       <c r="AA28">
-        <v>2.85</v>
+        <v>8</v>
       </c>
       <c r="AB28">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="AC28">
-        <v>1.57</v>
+        <v>3.34</v>
       </c>
       <c r="AD28">
-        <v>4.45</v>
+        <v>1.7</v>
       </c>
       <c r="AE28">
-        <v>1.18</v>
+        <v>2</v>
       </c>
       <c r="AF28">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AH28">
-        <v>8.5</v>
+        <v>2.55</v>
       </c>
       <c r="AI28">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="AJ28" t="s">
         <v>248</v>
@@ -4383,7 +4383,7 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
         <v>90</v>
@@ -4731,7 +4731,7 @@
         <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D32" t="s">
         <v>90</v>
@@ -4758,76 +4758,76 @@
         <v>247</v>
       </c>
       <c r="L32">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH32">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="s">
         <v>248</v>
@@ -4847,7 +4847,7 @@
         <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
         <v>90</v>
@@ -4874,76 +4874,76 @@
         <v>247</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ33" t="s">
         <v>248</v>
@@ -4963,7 +4963,7 @@
         <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
         <v>90</v>
@@ -4990,76 +4990,76 @@
         <v>247</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AI34">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ34" t="s">
         <v>248</v>
@@ -5427,7 +5427,7 @@
         <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D38" t="s">
         <v>90</v>
@@ -5454,76 +5454,76 @@
         <v>247</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH38">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ38" t="s">
         <v>248</v>
@@ -5543,7 +5543,7 @@
         <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D39" t="s">
         <v>90</v>
@@ -5570,76 +5570,76 @@
         <v>247</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH39">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI39">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ39" t="s">
         <v>248</v>
@@ -5659,7 +5659,7 @@
         <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D40" t="s">
         <v>90</v>
@@ -5686,76 +5686,76 @@
         <v>247</v>
       </c>
       <c r="L40">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M40">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH40">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AI40">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="s">
         <v>248</v>
@@ -6123,7 +6123,7 @@
         <v>51</v>
       </c>
       <c r="C44" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D44" t="s">
         <v>90</v>
@@ -6150,76 +6150,76 @@
         <v>247</v>
       </c>
       <c r="L44">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M44">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N44">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH44">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AI44">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="s">
         <v>248</v>
@@ -6471,7 +6471,7 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D47" t="s">
         <v>90</v>
@@ -6498,76 +6498,76 @@
         <v>247</v>
       </c>
       <c r="L47">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M47">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N47">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S47">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T47">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U47">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V47">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W47">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y47">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z47">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA47">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC47">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD47">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE47">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AF47">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG47">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH47">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI47">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="s">
         <v>248</v>
@@ -6846,13 +6846,13 @@
         <v>247</v>
       </c>
       <c r="L50">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M50">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="N50">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="O50">
         <v>1.25</v>
@@ -6864,19 +6864,19 @@
         <v>4</v>
       </c>
       <c r="R50">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S50">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T50">
         <v>2.2</v>
       </c>
       <c r="U50">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V50">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="W50">
         <v>1.17</v>
@@ -6888,34 +6888,34 @@
         <v>14</v>
       </c>
       <c r="Z50">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AA50">
         <v>5</v>
       </c>
       <c r="AB50">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC50">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD50">
         <v>2.25</v>
       </c>
       <c r="AE50">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AF50">
         <v>1.8</v>
       </c>
       <c r="AG50">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH50">
         <v>4</v>
       </c>
       <c r="AI50">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AJ50" t="s">
         <v>248</v>
@@ -6962,25 +6962,25 @@
         <v>247</v>
       </c>
       <c r="L51">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M51">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="N51">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="O51">
         <v>3</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q51">
         <v>1.4</v>
       </c>
       <c r="R51">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S51">
         <v>3.3</v>
@@ -6989,19 +6989,19 @@
         <v>2.3</v>
       </c>
       <c r="U51">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="V51">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="W51">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="Z51">
         <v>1.19</v>
@@ -7010,22 +7010,22 @@
         <v>4</v>
       </c>
       <c r="AB51">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AC51">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD51">
         <v>2.4</v>
       </c>
       <c r="AE51">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AF51">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AG51">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH51">
         <v>4.2</v>
@@ -7051,7 +7051,7 @@
         <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D52" t="s">
         <v>90</v>
@@ -7167,7 +7167,7 @@
         <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D53" t="s">
         <v>90</v>
@@ -7310,13 +7310,13 @@
         <v>247</v>
       </c>
       <c r="L54">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="M54">
-        <v>3.28</v>
+        <v>3.01</v>
       </c>
       <c r="N54">
-        <v>4.33</v>
+        <v>3.66</v>
       </c>
       <c r="O54">
         <v>1.53</v>
@@ -7328,58 +7328,58 @@
         <v>3.25</v>
       </c>
       <c r="R54">
+        <v>1.5</v>
+      </c>
+      <c r="S54">
+        <v>2.4</v>
+      </c>
+      <c r="T54">
+        <v>3.3</v>
+      </c>
+      <c r="U54">
+        <v>1.29</v>
+      </c>
+      <c r="V54">
+        <v>8.5</v>
+      </c>
+      <c r="W54">
+        <v>1.04</v>
+      </c>
+      <c r="X54">
+        <v>1.05</v>
+      </c>
+      <c r="Y54">
+        <v>6.5</v>
+      </c>
+      <c r="Z54">
         <v>1.44</v>
       </c>
-      <c r="S54">
-        <v>2.6</v>
-      </c>
-      <c r="T54">
-        <v>3</v>
-      </c>
-      <c r="U54">
-        <v>1.33</v>
-      </c>
-      <c r="V54">
-        <v>8</v>
-      </c>
-      <c r="W54">
-        <v>1.05</v>
-      </c>
-      <c r="X54">
-        <v>1.03</v>
-      </c>
-      <c r="Y54">
-        <v>7.5</v>
-      </c>
-      <c r="Z54">
-        <v>1.38</v>
-      </c>
       <c r="AA54">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="AB54">
         <v>2.35</v>
       </c>
       <c r="AC54">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AD54">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AE54">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF54">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG54">
         <v>1.73</v>
       </c>
       <c r="AH54">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AI54">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ54" t="s">
         <v>248</v>
@@ -7637,10 +7637,10 @@
         <v>90</v>
       </c>
       <c r="E57" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F57" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -7747,7 +7747,7 @@
         <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D58" t="s">
         <v>90</v>
@@ -7774,76 +7774,76 @@
         <v>247</v>
       </c>
       <c r="L58">
-        <v>2.42</v>
+        <v>3.8</v>
       </c>
       <c r="M58">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N58">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="O58">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="P58">
-        <v>6.75</v>
+        <v>9.5</v>
       </c>
       <c r="Q58">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="R58">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S58">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="T58">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="U58">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="V58">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="W58">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X58">
         <v>1.05</v>
       </c>
       <c r="Y58">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="Z58">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AA58">
-        <v>2.71</v>
+        <v>3.4</v>
       </c>
       <c r="AB58">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AC58">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AD58">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="AE58">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AF58">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AG58">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH58">
-        <v>9</v>
+        <v>5.9</v>
       </c>
       <c r="AI58">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AJ58" t="s">
         <v>248</v>
@@ -7863,7 +7863,7 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D59" t="s">
         <v>90</v>
@@ -7890,76 +7890,76 @@
         <v>247</v>
       </c>
       <c r="L59">
-        <v>1.91</v>
+        <v>1.32</v>
       </c>
       <c r="M59">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="N59">
-        <v>3</v>
+        <v>11.27</v>
       </c>
       <c r="O59">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q59">
-        <v>2.3</v>
+        <v>6</v>
       </c>
       <c r="R59">
+        <v>1.4</v>
+      </c>
+      <c r="S59">
+        <v>2.7</v>
+      </c>
+      <c r="T59">
+        <v>2.8</v>
+      </c>
+      <c r="U59">
+        <v>1.35</v>
+      </c>
+      <c r="V59">
+        <v>6.75</v>
+      </c>
+      <c r="W59">
+        <v>1.04</v>
+      </c>
+      <c r="X59">
+        <v>1.02</v>
+      </c>
+      <c r="Y59">
+        <v>11</v>
+      </c>
+      <c r="Z59">
+        <v>1.35</v>
+      </c>
+      <c r="AA59">
+        <v>3.1</v>
+      </c>
+      <c r="AB59">
+        <v>2.07</v>
+      </c>
+      <c r="AC59">
+        <v>1.75</v>
+      </c>
+      <c r="AD59">
+        <v>3.4</v>
+      </c>
+      <c r="AE59">
         <v>1.25</v>
       </c>
-      <c r="S59">
-        <v>3.6</v>
-      </c>
-      <c r="T59">
-        <v>2.1</v>
-      </c>
-      <c r="U59">
-        <v>1.65</v>
-      </c>
-      <c r="V59">
-        <v>4.5</v>
-      </c>
-      <c r="W59">
-        <v>1.17</v>
-      </c>
-      <c r="X59">
-        <v>1</v>
-      </c>
-      <c r="Y59">
-        <v>12</v>
-      </c>
-      <c r="Z59">
-        <v>1.12</v>
-      </c>
-      <c r="AA59">
-        <v>4.75</v>
-      </c>
-      <c r="AB59">
-        <v>1.42</v>
-      </c>
-      <c r="AC59">
-        <v>2.5</v>
-      </c>
-      <c r="AD59">
-        <v>2.16</v>
-      </c>
-      <c r="AE59">
-        <v>1.61</v>
-      </c>
       <c r="AF59">
-        <v>1.5</v>
+        <v>2.62</v>
       </c>
       <c r="AG59">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH59">
-        <v>3.58</v>
+        <v>6.75</v>
       </c>
       <c r="AI59">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AJ59" t="s">
         <v>248</v>
@@ -7979,7 +7979,7 @@
         <v>57</v>
       </c>
       <c r="C60" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D60" t="s">
         <v>90</v>
@@ -8006,76 +8006,76 @@
         <v>247</v>
       </c>
       <c r="L60">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="M60">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="N60">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="O60">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="P60">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="Q60">
+        <v>1.91</v>
+      </c>
+      <c r="R60">
+        <v>1.47</v>
+      </c>
+      <c r="S60">
         <v>2.4</v>
       </c>
-      <c r="R60">
-        <v>1.63</v>
-      </c>
-      <c r="S60">
-        <v>2.2</v>
-      </c>
       <c r="T60">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="U60">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V60">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W60">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X60">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Y60">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="Z60">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AA60">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="AB60">
-        <v>2.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC60">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AD60">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="AE60">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF60">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AG60">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AH60">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ60" t="s">
         <v>248</v>
@@ -8095,7 +8095,7 @@
         <v>57</v>
       </c>
       <c r="C61" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D61" t="s">
         <v>90</v>
@@ -8122,76 +8122,76 @@
         <v>247</v>
       </c>
       <c r="L61">
+        <v>2.2</v>
+      </c>
+      <c r="M61">
+        <v>2.87</v>
+      </c>
+      <c r="N61">
+        <v>3.2</v>
+      </c>
+      <c r="O61">
+        <v>1.88</v>
+      </c>
+      <c r="P61">
+        <v>5.75</v>
+      </c>
+      <c r="Q61">
+        <v>2.4</v>
+      </c>
+      <c r="R61">
+        <v>1.63</v>
+      </c>
+      <c r="S61">
+        <v>2.2</v>
+      </c>
+      <c r="T61">
         <v>3.7</v>
       </c>
-      <c r="M61">
-        <v>3.5</v>
-      </c>
-      <c r="N61">
-        <v>1.84</v>
-      </c>
-      <c r="O61">
-        <v>2.6</v>
-      </c>
-      <c r="P61">
-        <v>0</v>
-      </c>
-      <c r="Q61">
+      <c r="U61">
+        <v>1.25</v>
+      </c>
+      <c r="V61">
+        <v>10</v>
+      </c>
+      <c r="W61">
+        <v>1.04</v>
+      </c>
+      <c r="X61">
+        <v>1.13</v>
+      </c>
+      <c r="Y61">
+        <v>6.25</v>
+      </c>
+      <c r="Z61">
         <v>1.57</v>
       </c>
-      <c r="R61">
-        <v>1.33</v>
-      </c>
-      <c r="S61">
-        <v>3.25</v>
-      </c>
-      <c r="T61">
-        <v>2.5</v>
-      </c>
-      <c r="U61">
-        <v>1.5</v>
-      </c>
-      <c r="V61">
+      <c r="AA61">
+        <v>2.25</v>
+      </c>
+      <c r="AB61">
+        <v>2.83</v>
+      </c>
+      <c r="AC61">
+        <v>1.41</v>
+      </c>
+      <c r="AD61">
         <v>5.5</v>
       </c>
-      <c r="W61">
+      <c r="AE61">
         <v>1.13</v>
       </c>
-      <c r="X61">
-        <v>0</v>
-      </c>
-      <c r="Y61">
-        <v>0</v>
-      </c>
-      <c r="Z61">
-        <v>0</v>
-      </c>
-      <c r="AA61">
-        <v>0</v>
-      </c>
-      <c r="AB61">
-        <v>1.65</v>
-      </c>
-      <c r="AC61">
-        <v>2.1</v>
-      </c>
-      <c r="AD61">
-        <v>0</v>
-      </c>
-      <c r="AE61">
-        <v>0</v>
-      </c>
       <c r="AF61">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AG61">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AH61">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI61">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ61" t="s">
         <v>248</v>
@@ -8211,7 +8211,7 @@
         <v>57</v>
       </c>
       <c r="C62" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D62" t="s">
         <v>90</v>
@@ -8238,64 +8238,64 @@
         <v>247</v>
       </c>
       <c r="L62">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="M62">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N62">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="O62">
+        <v>2.6</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>1.57</v>
+      </c>
+      <c r="R62">
+        <v>1.33</v>
+      </c>
+      <c r="S62">
+        <v>3.25</v>
+      </c>
+      <c r="T62">
         <v>2.5</v>
       </c>
-      <c r="P62">
-        <v>9.5</v>
-      </c>
-      <c r="Q62">
-        <v>1.62</v>
-      </c>
-      <c r="R62">
-        <v>1.36</v>
-      </c>
-      <c r="S62">
-        <v>3</v>
-      </c>
-      <c r="T62">
-        <v>2.75</v>
-      </c>
       <c r="U62">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V62">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W62">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X62">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y62">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z62">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA62">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB62">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC62">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD62">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE62">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF62">
         <v>1.73</v>
@@ -8304,10 +8304,10 @@
         <v>2</v>
       </c>
       <c r="AH62">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AI62">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="s">
         <v>248</v>
@@ -8327,7 +8327,7 @@
         <v>57</v>
       </c>
       <c r="C63" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D63" t="s">
         <v>90</v>
@@ -8354,76 +8354,76 @@
         <v>247</v>
       </c>
       <c r="L63">
+        <v>2.37</v>
+      </c>
+      <c r="M63">
+        <v>3.69</v>
+      </c>
+      <c r="N63">
+        <v>2.49</v>
+      </c>
+      <c r="O63">
+        <v>1.73</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>2.2</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+      <c r="AA63">
+        <v>0</v>
+      </c>
+      <c r="AB63">
+        <v>1.5</v>
+      </c>
+      <c r="AC63">
         <v>2.5</v>
       </c>
-      <c r="M63">
-        <v>3.11</v>
-      </c>
-      <c r="N63">
-        <v>2.5</v>
-      </c>
-      <c r="O63">
-        <v>1.8</v>
-      </c>
-      <c r="P63">
-        <v>6.9</v>
-      </c>
-      <c r="Q63">
-        <v>2.5</v>
-      </c>
-      <c r="R63">
-        <v>1.5</v>
-      </c>
-      <c r="S63">
-        <v>2.4</v>
-      </c>
-      <c r="T63">
-        <v>3.2</v>
-      </c>
-      <c r="U63">
-        <v>1.3</v>
-      </c>
-      <c r="V63">
-        <v>8.5</v>
-      </c>
-      <c r="W63">
-        <v>1.04</v>
-      </c>
-      <c r="X63">
-        <v>1.04</v>
-      </c>
-      <c r="Y63">
-        <v>6.75</v>
-      </c>
-      <c r="Z63">
-        <v>1.4</v>
-      </c>
-      <c r="AA63">
-        <v>2.56</v>
-      </c>
-      <c r="AB63">
-        <v>2.35</v>
-      </c>
-      <c r="AC63">
-        <v>1.53</v>
-      </c>
       <c r="AD63">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE63">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF63">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG63">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH63">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AI63">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ63" t="s">
         <v>248</v>
@@ -8443,7 +8443,7 @@
         <v>57</v>
       </c>
       <c r="C64" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D64" t="s">
         <v>90</v>
@@ -8470,76 +8470,76 @@
         <v>247</v>
       </c>
       <c r="L64">
-        <v>2.37</v>
+        <v>1.91</v>
       </c>
       <c r="M64">
-        <v>3.69</v>
+        <v>3.9</v>
       </c>
       <c r="N64">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="O64">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="P64">
         <v>0</v>
       </c>
       <c r="Q64">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB64">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AC64">
         <v>2.5</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH64">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AI64">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AJ64" t="s">
         <v>248</v>
@@ -8559,7 +8559,7 @@
         <v>57</v>
       </c>
       <c r="C65" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D65" t="s">
         <v>90</v>
@@ -8586,76 +8586,76 @@
         <v>247</v>
       </c>
       <c r="L65">
-        <v>1.32</v>
+        <v>1.82</v>
       </c>
       <c r="M65">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="N65">
-        <v>11.27</v>
+        <v>4.06</v>
       </c>
       <c r="O65">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="P65">
-        <v>8.5</v>
+        <v>6.9</v>
       </c>
       <c r="Q65">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="R65">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S65">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="T65">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U65">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V65">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="W65">
+        <v>1.05</v>
+      </c>
+      <c r="X65">
         <v>1.04</v>
       </c>
-      <c r="X65">
-        <v>1.02</v>
-      </c>
       <c r="Y65">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z65">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AA65">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AB65">
-        <v>2.07</v>
+        <v>2.26</v>
       </c>
       <c r="AC65">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AD65">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AE65">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AF65">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="AG65">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AH65">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="AI65">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AJ65" t="s">
         <v>248</v>
@@ -8702,13 +8702,13 @@
         <v>247</v>
       </c>
       <c r="L66">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="M66">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="N66">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="O66">
         <v>1.75</v>
@@ -8723,19 +8723,19 @@
         <v>1.22</v>
       </c>
       <c r="S66">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="T66">
         <v>2.11</v>
       </c>
       <c r="U66">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V66">
         <v>4.2</v>
       </c>
       <c r="W66">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X66">
         <v>1.02</v>
@@ -8756,10 +8756,10 @@
         <v>2.7</v>
       </c>
       <c r="AD66">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AE66">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF66">
         <v>1.4</v>
@@ -8818,46 +8818,46 @@
         <v>247</v>
       </c>
       <c r="L67">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="M67">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N67">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O67">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="P67">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q67">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R67">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S67">
         <v>2.4</v>
       </c>
       <c r="T67">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U67">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="V67">
-        <v>9.300000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="W67">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y67">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="Z67">
         <v>1.48</v>
@@ -8866,28 +8866,28 @@
         <v>2.5</v>
       </c>
       <c r="AB67">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC67">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AD67">
         <v>4.5</v>
       </c>
       <c r="AE67">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF67">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG67">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AH67">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="AI67">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ67" t="s">
         <v>248</v>
@@ -8934,22 +8934,22 @@
         <v>247</v>
       </c>
       <c r="L68">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="M68">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="N68">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="O68">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="P68">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q68">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R68">
         <v>1.48</v>
@@ -8958,22 +8958,22 @@
         <v>2.4</v>
       </c>
       <c r="T68">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U68">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V68">
-        <v>9.75</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W68">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X68">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z68">
         <v>1.48</v>
@@ -8982,28 +8982,28 @@
         <v>2.5</v>
       </c>
       <c r="AB68">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AC68">
         <v>1.5</v>
       </c>
       <c r="AD68">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AE68">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF68">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG68">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH68">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="AI68">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ68" t="s">
         <v>248</v>
@@ -9029,10 +9029,10 @@
         <v>90</v>
       </c>
       <c r="E69" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F69" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -9050,76 +9050,76 @@
         <v>247</v>
       </c>
       <c r="L69">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M69">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N69">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P69">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q69">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R69">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S69">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T69">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U69">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V69">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W69">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X69">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y69">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Z69">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA69">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB69">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC69">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD69">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AE69">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF69">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG69">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH69">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI69">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ69" t="s">
         <v>248</v>
@@ -9145,10 +9145,10 @@
         <v>90</v>
       </c>
       <c r="E70" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="F70" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -9166,76 +9166,76 @@
         <v>247</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH70">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI70">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ70" t="s">
         <v>248</v>
@@ -9255,7 +9255,7 @@
         <v>61</v>
       </c>
       <c r="C71" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D71" t="s">
         <v>90</v>
@@ -9282,76 +9282,76 @@
         <v>247</v>
       </c>
       <c r="L71">
-        <v>3.34</v>
+        <v>1.74</v>
       </c>
       <c r="M71">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N71">
-        <v>2.3</v>
+        <v>5.35</v>
       </c>
       <c r="O71">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="P71">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="Q71">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="R71">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S71">
         <v>2.4</v>
       </c>
       <c r="T71">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U71">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V71">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W71">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X71">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z71">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AA71">
         <v>2.6</v>
       </c>
       <c r="AB71">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AC71">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD71">
-        <v>4.33</v>
+        <v>4.58</v>
       </c>
       <c r="AE71">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF71">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="AG71">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AH71">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AI71">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AJ71" t="s">
         <v>248</v>
@@ -9371,7 +9371,7 @@
         <v>61</v>
       </c>
       <c r="C72" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D72" t="s">
         <v>90</v>
@@ -9398,76 +9398,76 @@
         <v>247</v>
       </c>
       <c r="L72">
-        <v>1.74</v>
+        <v>3.34</v>
       </c>
       <c r="M72">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N72">
-        <v>5.35</v>
+        <v>2.3</v>
       </c>
       <c r="O72">
+        <v>2.4</v>
+      </c>
+      <c r="P72">
+        <v>6.75</v>
+      </c>
+      <c r="Q72">
+        <v>1.8</v>
+      </c>
+      <c r="R72">
         <v>1.5</v>
-      </c>
-      <c r="P72">
-        <v>7</v>
-      </c>
-      <c r="Q72">
-        <v>3.4</v>
-      </c>
-      <c r="R72">
-        <v>1.45</v>
       </c>
       <c r="S72">
         <v>2.4</v>
       </c>
       <c r="T72">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U72">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V72">
+        <v>10</v>
+      </c>
+      <c r="W72">
+        <v>1.02</v>
+      </c>
+      <c r="X72">
+        <v>1.05</v>
+      </c>
+      <c r="Y72">
         <v>8.5</v>
       </c>
-      <c r="W72">
-        <v>1.06</v>
-      </c>
-      <c r="X72">
-        <v>1.03</v>
-      </c>
-      <c r="Y72">
-        <v>7.5</v>
-      </c>
       <c r="Z72">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AA72">
         <v>2.6</v>
       </c>
       <c r="AB72">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="AC72">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD72">
-        <v>4.58</v>
+        <v>4.33</v>
       </c>
       <c r="AE72">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF72">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="AG72">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AH72">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AI72">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ72" t="s">
         <v>248</v>
@@ -9487,7 +9487,7 @@
         <v>62</v>
       </c>
       <c r="C73" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D73" t="s">
         <v>90</v>
@@ -9514,22 +9514,22 @@
         <v>247</v>
       </c>
       <c r="L73">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="M73">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="N73">
-        <v>4.3</v>
+        <v>3.48</v>
       </c>
       <c r="O73">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="P73">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="Q73">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="R73">
         <v>1.48</v>
@@ -9538,49 +9538,49 @@
         <v>2.47</v>
       </c>
       <c r="T73">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U73">
         <v>1.3</v>
       </c>
       <c r="V73">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="W73">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X73">
         <v>1.08</v>
       </c>
       <c r="Y73">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Z73">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AA73">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB73">
         <v>2.25</v>
       </c>
       <c r="AC73">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AD73">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AE73">
         <v>1.2</v>
       </c>
       <c r="AF73">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AG73">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AH73">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AI73">
         <v>1.05</v>
@@ -9603,7 +9603,7 @@
         <v>62</v>
       </c>
       <c r="C74" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D74" t="s">
         <v>90</v>
@@ -9630,76 +9630,76 @@
         <v>247</v>
       </c>
       <c r="L74">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="M74">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="N74">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="O74">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="P74">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="Q74">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="R74">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S74">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="T74">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="U74">
         <v>1.3</v>
       </c>
       <c r="V74">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="W74">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X74">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y74">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Z74">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AA74">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AB74">
         <v>2.25</v>
       </c>
       <c r="AC74">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD74">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AE74">
         <v>1.2</v>
       </c>
       <c r="AF74">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AG74">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AH74">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="AI74">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ74" t="s">
         <v>248</v>
@@ -9746,40 +9746,40 @@
         <v>247</v>
       </c>
       <c r="L75">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="M75">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N75">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="O75">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="P75">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q75">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="R75">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S75">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T75">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U75">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="V75">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="W75">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X75">
         <v>1.09</v>
@@ -9791,31 +9791,31 @@
         <v>1.5</v>
       </c>
       <c r="AA75">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AB75">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AC75">
         <v>1.48</v>
       </c>
       <c r="AD75">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AE75">
         <v>1.15</v>
       </c>
       <c r="AF75">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AG75">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AH75">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="AI75">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ75" t="s">
         <v>248</v>
@@ -9835,16 +9835,16 @@
         <v>63</v>
       </c>
       <c r="C76" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D76" t="s">
         <v>90</v>
       </c>
       <c r="E76" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="F76" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -9862,76 +9862,76 @@
         <v>247</v>
       </c>
       <c r="L76">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="M76">
         <v>3.1</v>
       </c>
       <c r="N76">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="O76">
-        <v>2.2</v>
+        <v>1.63</v>
       </c>
       <c r="P76">
-        <v>7.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q76">
-        <v>1.83</v>
+        <v>2.87</v>
       </c>
       <c r="R76">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S76">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="T76">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="U76">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V76">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W76">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X76">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y76">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Z76">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AA76">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="AB76">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="AC76">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AD76">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AE76">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AF76">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AG76">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AH76">
-        <v>7</v>
+        <v>9.1</v>
       </c>
       <c r="AI76">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AJ76" t="s">
         <v>248</v>
@@ -9951,16 +9951,16 @@
         <v>63</v>
       </c>
       <c r="C77" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D77" t="s">
         <v>90</v>
       </c>
       <c r="E77" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="F77" t="s">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -9978,76 +9978,76 @@
         <v>247</v>
       </c>
       <c r="L77">
+        <v>2.8</v>
+      </c>
+      <c r="M77">
+        <v>3.1</v>
+      </c>
+      <c r="N77">
+        <v>2.55</v>
+      </c>
+      <c r="O77">
         <v>2.2</v>
       </c>
-      <c r="M77">
-        <v>2.9</v>
-      </c>
-      <c r="N77">
-        <v>3.2</v>
-      </c>
-      <c r="O77">
-        <v>1.88</v>
-      </c>
       <c r="P77">
-        <v>6</v>
+        <v>7.75</v>
       </c>
       <c r="Q77">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="R77">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S77">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="T77">
+        <v>3</v>
+      </c>
+      <c r="U77">
+        <v>1.36</v>
+      </c>
+      <c r="V77">
+        <v>9</v>
+      </c>
+      <c r="W77">
+        <v>1.07</v>
+      </c>
+      <c r="X77">
+        <v>1.07</v>
+      </c>
+      <c r="Y77">
+        <v>8</v>
+      </c>
+      <c r="Z77">
+        <v>1.35</v>
+      </c>
+      <c r="AA77">
+        <v>3.1</v>
+      </c>
+      <c r="AB77">
+        <v>2.08</v>
+      </c>
+      <c r="AC77">
+        <v>1.73</v>
+      </c>
+      <c r="AD77">
         <v>3.6</v>
       </c>
-      <c r="U77">
-        <v>1.25</v>
-      </c>
-      <c r="V77">
-        <v>10</v>
-      </c>
-      <c r="W77">
-        <v>1.02</v>
-      </c>
-      <c r="X77">
+      <c r="AE77">
+        <v>1.28</v>
+      </c>
+      <c r="AF77">
+        <v>1.8</v>
+      </c>
+      <c r="AG77">
+        <v>1.95</v>
+      </c>
+      <c r="AH77">
+        <v>7</v>
+      </c>
+      <c r="AI77">
         <v>1.09</v>
-      </c>
-      <c r="Y77">
-        <v>6</v>
-      </c>
-      <c r="Z77">
-        <v>1.5</v>
-      </c>
-      <c r="AA77">
-        <v>2.39</v>
-      </c>
-      <c r="AB77">
-        <v>2.37</v>
-      </c>
-      <c r="AC77">
-        <v>1.48</v>
-      </c>
-      <c r="AD77">
-        <v>4.8</v>
-      </c>
-      <c r="AE77">
-        <v>1.15</v>
-      </c>
-      <c r="AF77">
-        <v>2.1</v>
-      </c>
-      <c r="AG77">
-        <v>1.65</v>
-      </c>
-      <c r="AH77">
-        <v>9.1</v>
-      </c>
-      <c r="AI77">
-        <v>1.02</v>
       </c>
       <c r="AJ77" t="s">
         <v>248</v>
@@ -10067,7 +10067,7 @@
         <v>64</v>
       </c>
       <c r="C78" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D78" t="s">
         <v>90</v>
@@ -10183,7 +10183,7 @@
         <v>65</v>
       </c>
       <c r="C79" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D79" t="s">
         <v>90</v>
@@ -10299,16 +10299,16 @@
         <v>66</v>
       </c>
       <c r="C80" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D80" t="s">
         <v>90</v>
       </c>
       <c r="E80" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="F80" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -10326,76 +10326,76 @@
         <v>247</v>
       </c>
       <c r="L80">
-        <v>1.91</v>
+        <v>2.89</v>
       </c>
       <c r="M80">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="N80">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="O80">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="P80">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R80">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S80">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T80">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U80">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V80">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W80">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X80">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y80">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z80">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA80">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB80">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC80">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AD80">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF80">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG80">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH80">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI80">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ80" t="s">
         <v>248</v>
@@ -10415,16 +10415,16 @@
         <v>66</v>
       </c>
       <c r="C81" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D81" t="s">
         <v>90</v>
       </c>
       <c r="E81" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="F81" t="s">
-        <v>243</v>
+        <v>202</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -10442,76 +10442,76 @@
         <v>247</v>
       </c>
       <c r="L81">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="M81">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="N81">
-        <v>2.76</v>
+        <v>4.2</v>
       </c>
       <c r="O81">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q81">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB81">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC81">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH81">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI81">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ81" t="s">
         <v>248</v>
@@ -10531,7 +10531,7 @@
         <v>67</v>
       </c>
       <c r="C82" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D82" t="s">
         <v>90</v>
@@ -10647,7 +10647,7 @@
         <v>68</v>
       </c>
       <c r="C83" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D83" t="s">
         <v>90</v>
@@ -10763,7 +10763,7 @@
         <v>68</v>
       </c>
       <c r="C84" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D84" t="s">
         <v>90</v>

--- a/jogos_2025-07-20.xlsx
+++ b/jogos_2025-07-20.xlsx
@@ -232,12 +232,12 @@
     <t>Japan J1 League</t>
   </si>
   <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
@@ -250,12 +250,12 @@
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
@@ -265,10 +265,13 @@
     <t>Argentina Primera División</t>
   </si>
   <si>
+    <t>Chile Primera División</t>
+  </si>
+  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
-    <t>Chile Primera División</t>
+    <t>USA MLS Next Pro</t>
   </si>
   <si>
     <t>Brazil Serie B</t>
@@ -277,9 +280,6 @@
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
@@ -310,42 +310,42 @@
     <t>Shimizu S-Pulse</t>
   </si>
   <si>
+    <t>Gamba Osaka</t>
+  </si>
+  <si>
     <t>Albirex Niigata</t>
   </si>
   <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
+    <t>Yokohama F. Marinos</t>
+  </si>
+  <si>
+    <t>Fagiano Okayama</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
-    <t>Fagiano Okayama</t>
-  </si>
-  <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
-    <t>Gamba Osaka</t>
-  </si>
-  <si>
-    <t>Yokohama F. Marinos</t>
-  </si>
-  <si>
     <t>Varberg</t>
   </si>
   <si>
+    <t>Heilongjiang Lava Spring</t>
+  </si>
+  <si>
     <t>Shenzhen Juniors</t>
   </si>
   <si>
     <t>Nanjing City</t>
   </si>
   <si>
-    <t>Heilongjiang Lava Spring</t>
-  </si>
-  <si>
     <t>Sirius</t>
   </si>
   <si>
@@ -355,15 +355,15 @@
     <t>Vålerenga</t>
   </si>
   <si>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
     <t>Kalmar</t>
   </si>
   <si>
     <t>SJK</t>
   </si>
   <si>
-    <t>Kyzyl-Zhar</t>
-  </si>
-  <si>
     <t>Internacional</t>
   </si>
   <si>
@@ -379,60 +379,60 @@
     <t>Halmstad</t>
   </si>
   <si>
+    <t>Lanús</t>
+  </si>
+  <si>
+    <t>Barracas Central</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Independiente</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>Atlético Tucumán</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>Newell's Old Boys</t>
+  </si>
+  <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
+  </si>
+  <si>
     <t>Platense</t>
   </si>
   <si>
+    <t>Boca Juniors</t>
+  </si>
+  <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Tigre</t>
+  </si>
+  <si>
     <t>Sandefjord</t>
   </si>
   <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
-    <t>Independiente</t>
-  </si>
-  <si>
-    <t>Barracas Central</t>
-  </si>
-  <si>
-    <t>Lanús</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Tigre</t>
-  </si>
-  <si>
-    <t>San Lorenzo</t>
-  </si>
-  <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
-    <t>Newell's Old Boys</t>
-  </si>
-  <si>
-    <t>Estudiantes</t>
-  </si>
-  <si>
-    <t>Boca Juniors</t>
-  </si>
-  <si>
-    <t>Atlético Tucumán</t>
-  </si>
-  <si>
-    <t>Defensa y Justicia</t>
-  </si>
-  <si>
-    <t>Instituto</t>
-  </si>
-  <si>
-    <t>Godoy Cruz</t>
-  </si>
-  <si>
     <t>HJK</t>
   </si>
   <si>
@@ -445,36 +445,36 @@
     <t>Kuressaare</t>
   </si>
   <si>
+    <t>Audax Italiano</t>
+  </si>
+  <si>
     <t>Copiapó</t>
   </si>
   <si>
-    <t>Audax Italiano</t>
-  </si>
-  <si>
     <t>HamKam</t>
   </si>
   <si>
+    <t>Toronto II</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>New England II</t>
+  </si>
+  <si>
+    <t>Vitória</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Valour FC</t>
+  </si>
+  <si>
     <t>Ñublense</t>
   </si>
   <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Vitória</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Valour FC</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
-    <t>New England II</t>
-  </si>
-  <si>
     <t>Magallanes</t>
   </si>
   <si>
@@ -487,18 +487,18 @@
     <t>Confiança</t>
   </si>
   <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
     <t>Palmeiras</t>
   </si>
   <si>
-    <t>Sport Recife</t>
+    <t>América Mineiro</t>
   </si>
   <si>
     <t>Deportes Temuco</t>
   </si>
   <si>
-    <t>América Mineiro</t>
-  </si>
-  <si>
     <t>Ypiranga Erechim</t>
   </si>
   <si>
@@ -517,12 +517,12 @@
     <t>Real Monarchs</t>
   </si>
   <si>
+    <t>Colorado Rapids II</t>
+  </si>
+  <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
-    <t>Colorado Rapids II</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
@@ -544,42 +544,42 @@
     <t>Yokohama</t>
   </si>
   <si>
+    <t>Kawasaki Frontale</t>
+  </si>
+  <si>
     <t>Sanfrecce Hiroshima</t>
   </si>
   <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
+    <t>Nagoya Grampus</t>
+  </si>
+  <si>
+    <t>Vissel Kobe</t>
+  </si>
+  <si>
     <t>Ulsan</t>
   </si>
   <si>
-    <t>Cheonan City</t>
-  </si>
-  <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
-    <t>Vissel Kobe</t>
-  </si>
-  <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Kawasaki Frontale</t>
-  </si>
-  <si>
-    <t>Nagoya Grampus</t>
-  </si>
-  <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
+    <t>Shaanxi Union</t>
+  </si>
+  <si>
     <t>Shanghai Jiading</t>
   </si>
   <si>
     <t>Guangxi Baoyun</t>
   </si>
   <si>
-    <t>Shaanxi Union</t>
-  </si>
-  <si>
     <t>IFK Göteborg</t>
   </si>
   <si>
@@ -589,15 +589,15 @@
     <t>Haugesund</t>
   </si>
   <si>
+    <t>Atyrau</t>
+  </si>
+  <si>
     <t>Brage</t>
   </si>
   <si>
     <t>Gnistan</t>
   </si>
   <si>
-    <t>Atyrau</t>
-  </si>
-  <si>
     <t>Ceará</t>
   </si>
   <si>
@@ -613,60 +613,60 @@
     <t>Häcken</t>
   </si>
   <si>
+    <t>Rosario Central</t>
+  </si>
+  <si>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>River Plate</t>
+  </si>
+  <si>
+    <t>Talleres Córdoba</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Central Córdoba SdE</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Racing Club</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Banfield</t>
+  </si>
+  <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
+    <t>Sarmiento</t>
+  </si>
+  <si>
     <t>Vélez Sarsfield</t>
   </si>
   <si>
+    <t>Unión Santa Fe</t>
+  </si>
+  <si>
+    <t>Gimnasia La Plata</t>
+  </si>
+  <si>
+    <t>Huracán</t>
+  </si>
+  <si>
+    <t>Argentinos Juniors</t>
+  </si>
+  <si>
     <t>Kristiansund</t>
   </si>
   <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Talleres Córdoba</t>
-  </si>
-  <si>
-    <t>Independiente Rivadavia</t>
-  </si>
-  <si>
-    <t>Rosario Central</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Argentinos Juniors</t>
-  </si>
-  <si>
-    <t>Gimnasia La Plata</t>
-  </si>
-  <si>
-    <t>Racing Club</t>
-  </si>
-  <si>
-    <t>Banfield</t>
-  </si>
-  <si>
-    <t>Huracán</t>
-  </si>
-  <si>
-    <t>Unión Santa Fe</t>
-  </si>
-  <si>
-    <t>Central Córdoba SdE</t>
-  </si>
-  <si>
-    <t>Aldosivi</t>
-  </si>
-  <si>
-    <t>River Plate</t>
-  </si>
-  <si>
-    <t>Sarmiento</t>
-  </si>
-  <si>
     <t>Oulu</t>
   </si>
   <si>
@@ -679,36 +679,36 @@
     <t>Vaprus</t>
   </si>
   <si>
+    <t>Universidad Católica</t>
+  </si>
+  <si>
     <t>Curicó Unido</t>
   </si>
   <si>
-    <t>Universidad Católica</t>
-  </si>
-  <si>
     <t>Fredrikstad</t>
   </si>
   <si>
+    <t>Chicago Fire II</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
+    <t>Orlando City II</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
+    <t>Cavalry FC</t>
+  </si>
+  <si>
     <t>Universidad Chile</t>
   </si>
   <si>
-    <t>Juventude</t>
-  </si>
-  <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
-    <t>Botafogo SP</t>
-  </si>
-  <si>
-    <t>Cavalry FC</t>
-  </si>
-  <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
-    <t>Orlando City II</t>
-  </si>
-  <si>
     <t>Univ. Concepción</t>
   </si>
   <si>
@@ -721,18 +721,18 @@
     <t>Tombense</t>
   </si>
   <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
     <t>Atlético Mineiro</t>
   </si>
   <si>
-    <t>Botafogo</t>
+    <t>Chapecoense</t>
   </si>
   <si>
     <t>Santiago Morning</t>
   </si>
   <si>
-    <t>Chapecoense</t>
-  </si>
-  <si>
     <t>São Bernardo</t>
   </si>
   <si>
@@ -751,10 +751,10 @@
     <t>Austin II</t>
   </si>
   <si>
+    <t>Tacoma Defiance</t>
+  </si>
+  <si>
     <t>Los Angeles II</t>
-  </si>
-  <si>
-    <t>Tacoma Defiance</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1278,13 +1278,13 @@
         <v>247</v>
       </c>
       <c r="L2">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="M2">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="N2">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O2">
         <v>1.5</v>
@@ -1296,7 +1296,7 @@
         <v>3</v>
       </c>
       <c r="R2">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S2">
         <v>2.62</v>
@@ -1305,43 +1305,43 @@
         <v>2.8</v>
       </c>
       <c r="U2">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V2">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA2">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AB2">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="AC2">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AD2">
         <v>3.4</v>
       </c>
       <c r="AE2">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF2">
         <v>1.95</v>
       </c>
       <c r="AG2">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH2">
         <v>6.5</v>
@@ -1394,13 +1394,13 @@
         <v>247</v>
       </c>
       <c r="L3">
-        <v>4.6</v>
+        <v>2.95</v>
       </c>
       <c r="M3">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N3">
-        <v>1.61</v>
+        <v>2.02</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1510,13 +1510,13 @@
         <v>247</v>
       </c>
       <c r="L4">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="M4">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N4">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="O4">
         <v>1.44</v>
@@ -1531,19 +1531,19 @@
         <v>1.19</v>
       </c>
       <c r="S4">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="T4">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U4">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="V4">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="W4">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
         <v>1</v>
@@ -1555,31 +1555,31 @@
         <v>1.13</v>
       </c>
       <c r="AA4">
-        <v>5.55</v>
+        <v>5.6</v>
       </c>
       <c r="AB4">
         <v>1.5</v>
       </c>
       <c r="AC4">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD4">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AE4">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AF4">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH4">
         <v>3.58</v>
       </c>
       <c r="AI4">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AJ4" t="s">
         <v>248</v>
@@ -1626,19 +1626,19 @@
         <v>247</v>
       </c>
       <c r="L5">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N5">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="O5">
         <v>1.29</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q5">
         <v>3.5</v>
@@ -1650,7 +1650,7 @@
         <v>4</v>
       </c>
       <c r="T5">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="U5">
         <v>1.73</v>
@@ -1668,7 +1668,7 @@
         <v>17</v>
       </c>
       <c r="Z5">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AA5">
         <v>5.75</v>
@@ -1677,7 +1677,7 @@
         <v>1.36</v>
       </c>
       <c r="AC5">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD5">
         <v>1.95</v>
@@ -1692,7 +1692,7 @@
         <v>2.3</v>
       </c>
       <c r="AH5">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AI5">
         <v>1.33</v>
@@ -2090,76 +2090,76 @@
         <v>247</v>
       </c>
       <c r="L9">
-        <v>3.99</v>
+        <v>2.47</v>
       </c>
       <c r="M9">
-        <v>3.36</v>
+        <v>3.23</v>
       </c>
       <c r="N9">
-        <v>1.75</v>
+        <v>2.47</v>
       </c>
       <c r="O9">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="P9">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="R9">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S9">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T9">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U9">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z9">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AA9">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="AB9">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="AC9">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="AD9">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AE9">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AF9">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AG9">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AH9">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AI9">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AJ9" t="s">
         <v>248</v>
@@ -2179,7 +2179,7 @@
         <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
         <v>90</v>
@@ -2206,76 +2206,76 @@
         <v>247</v>
       </c>
       <c r="L10">
-        <v>2.19</v>
+        <v>3.99</v>
       </c>
       <c r="M10">
-        <v>3.13</v>
+        <v>3.36</v>
       </c>
       <c r="N10">
-        <v>2.91</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="P10">
-        <v>7.75</v>
+        <v>8.75</v>
       </c>
       <c r="Q10">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="R10">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S10">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T10">
+        <v>2.75</v>
+      </c>
+      <c r="U10">
+        <v>1.4</v>
+      </c>
+      <c r="V10">
+        <v>8</v>
+      </c>
+      <c r="W10">
+        <v>1.08</v>
+      </c>
+      <c r="X10">
+        <v>1.06</v>
+      </c>
+      <c r="Y10">
+        <v>8.5</v>
+      </c>
+      <c r="Z10">
+        <v>1.33</v>
+      </c>
+      <c r="AA10">
         <v>3.25</v>
       </c>
-      <c r="U10">
-        <v>1.33</v>
-      </c>
-      <c r="V10">
-        <v>9</v>
-      </c>
-      <c r="W10">
-        <v>1.07</v>
-      </c>
-      <c r="X10">
-        <v>1.08</v>
-      </c>
-      <c r="Y10">
-        <v>7.5</v>
-      </c>
-      <c r="Z10">
-        <v>1.4</v>
-      </c>
-      <c r="AA10">
-        <v>2.9</v>
-      </c>
       <c r="AB10">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AC10">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD10">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AE10">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AF10">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG10">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI10">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AJ10" t="s">
         <v>248</v>
@@ -2295,7 +2295,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
         <v>90</v>
@@ -2322,76 +2322,76 @@
         <v>247</v>
       </c>
       <c r="L11">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="M11">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="N11">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="O11">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="P11">
-        <v>10.5</v>
+        <v>9.1</v>
       </c>
       <c r="Q11">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R11">
+        <v>1.36</v>
+      </c>
+      <c r="S11">
+        <v>2.9</v>
+      </c>
+      <c r="T11">
+        <v>2.8</v>
+      </c>
+      <c r="U11">
         <v>1.4</v>
       </c>
-      <c r="S11">
-        <v>2.8</v>
-      </c>
-      <c r="T11">
-        <v>2.9</v>
-      </c>
-      <c r="U11">
-        <v>1.36</v>
-      </c>
       <c r="V11">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="Z11">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AA11">
-        <v>3.08</v>
+        <v>3.22</v>
       </c>
       <c r="AB11">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC11">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AD11">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="AE11">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AF11">
         <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH11">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="AI11">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AJ11" t="s">
         <v>248</v>
@@ -2411,7 +2411,7 @@
         <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
         <v>90</v>
@@ -2527,7 +2527,7 @@
         <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
         <v>90</v>
@@ -2554,76 +2554,76 @@
         <v>247</v>
       </c>
       <c r="L13">
-        <v>4.6</v>
+        <v>2.18</v>
       </c>
       <c r="M13">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="N13">
-        <v>1.68</v>
+        <v>2.93</v>
       </c>
       <c r="O13">
-        <v>2.85</v>
+        <v>1.79</v>
       </c>
       <c r="P13">
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q13">
-        <v>1.58</v>
+        <v>2.16</v>
       </c>
       <c r="R13">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S13">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="T13">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U13">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V13">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="Z13">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AA13">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AB13">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="AC13">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AD13">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AE13">
         <v>1.21</v>
       </c>
       <c r="AF13">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG13">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AH13">
-        <v>8.25</v>
+        <v>7.6</v>
       </c>
       <c r="AI13">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ13" t="s">
         <v>248</v>
@@ -2643,7 +2643,7 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
         <v>90</v>
@@ -2670,76 +2670,76 @@
         <v>247</v>
       </c>
       <c r="L14">
-        <v>2.16</v>
+        <v>2.79</v>
       </c>
       <c r="M14">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="N14">
-        <v>3.08</v>
+        <v>2.29</v>
       </c>
       <c r="O14">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="P14">
-        <v>9.1</v>
+        <v>8.25</v>
       </c>
       <c r="Q14">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="R14">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S14">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="T14">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U14">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W14">
         <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>9.1</v>
+        <v>8.25</v>
       </c>
       <c r="Z14">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AA14">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AB14">
+        <v>1.96</v>
+      </c>
+      <c r="AC14">
+        <v>1.74</v>
+      </c>
+      <c r="AD14">
+        <v>3.4</v>
+      </c>
+      <c r="AE14">
+        <v>1.27</v>
+      </c>
+      <c r="AF14">
+        <v>1.78</v>
+      </c>
+      <c r="AG14">
         <v>1.9</v>
       </c>
-      <c r="AC14">
-        <v>1.81</v>
-      </c>
-      <c r="AD14">
-        <v>3.2</v>
-      </c>
-      <c r="AE14">
-        <v>1.26</v>
-      </c>
-      <c r="AF14">
-        <v>1.75</v>
-      </c>
-      <c r="AG14">
-        <v>2</v>
-      </c>
       <c r="AH14">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="AI14">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AJ14" t="s">
         <v>248</v>
@@ -2786,76 +2786,76 @@
         <v>247</v>
       </c>
       <c r="L15">
-        <v>2.47</v>
+        <v>4.6</v>
       </c>
       <c r="M15">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="N15">
-        <v>2.47</v>
+        <v>1.68</v>
       </c>
       <c r="O15">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="P15">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Q15">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="R15">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="S15">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="T15">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="U15">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="V15">
-        <v>6.5</v>
+        <v>8.75</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z15">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AA15">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AB15">
-        <v>1.73</v>
+        <v>2.13</v>
       </c>
       <c r="AC15">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AD15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE15">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AF15">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AH15">
-        <v>5.5</v>
+        <v>8.25</v>
       </c>
       <c r="AI15">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AJ15" t="s">
         <v>248</v>
@@ -2875,7 +2875,7 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>90</v>
@@ -2902,76 +2902,76 @@
         <v>247</v>
       </c>
       <c r="L16">
-        <v>2.79</v>
+        <v>2.19</v>
       </c>
       <c r="M16">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="N16">
-        <v>2.29</v>
+        <v>2.91</v>
       </c>
       <c r="O16">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="P16">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="Q16">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="R16">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S16">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="T16">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V16">
+        <v>9</v>
+      </c>
+      <c r="W16">
+        <v>1.07</v>
+      </c>
+      <c r="X16">
+        <v>1.08</v>
+      </c>
+      <c r="Y16">
         <v>7.5</v>
       </c>
-      <c r="W16">
-        <v>1.08</v>
-      </c>
-      <c r="X16">
-        <v>1.06</v>
-      </c>
-      <c r="Y16">
-        <v>8.25</v>
-      </c>
       <c r="Z16">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AA16">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AB16">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AC16">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AD16">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AE16">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF16">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG16">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH16">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AI16">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AJ16" t="s">
         <v>248</v>
@@ -3134,40 +3134,40 @@
         <v>247</v>
       </c>
       <c r="L18">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="M18">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N18">
         <v>2.9</v>
       </c>
       <c r="O18">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="P18">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q18">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="R18">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S18">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V18">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
         <v>1.02</v>
@@ -3176,34 +3176,34 @@
         <v>8</v>
       </c>
       <c r="Z18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA18">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="AB18">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AC18">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AD18">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AE18">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF18">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AG18">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AH18">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="AI18">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AJ18" t="s">
         <v>248</v>
@@ -3250,76 +3250,76 @@
         <v>247</v>
       </c>
       <c r="L19">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="M19">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="O19">
+        <v>1.8</v>
+      </c>
+      <c r="P19">
+        <v>7.8</v>
+      </c>
+      <c r="Q19">
+        <v>2.38</v>
+      </c>
+      <c r="R19">
         <v>1.44</v>
       </c>
-      <c r="P19">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q19">
-        <v>3.4</v>
-      </c>
-      <c r="R19">
-        <v>1.39</v>
-      </c>
       <c r="S19">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="T19">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U19">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V19">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W19">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="Z19">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AA19">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="AB19">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC19">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD19">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AE19">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AF19">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AG19">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH19">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="AI19">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AJ19" t="s">
         <v>248</v>
@@ -3366,76 +3366,76 @@
         <v>247</v>
       </c>
       <c r="L20">
+        <v>1.6</v>
+      </c>
+      <c r="M20">
+        <v>3.35</v>
+      </c>
+      <c r="N20">
+        <v>5.4</v>
+      </c>
+      <c r="O20">
+        <v>1.44</v>
+      </c>
+      <c r="P20">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Q20">
+        <v>3.4</v>
+      </c>
+      <c r="R20">
+        <v>1.38</v>
+      </c>
+      <c r="S20">
+        <v>2.8</v>
+      </c>
+      <c r="T20">
+        <v>2.8</v>
+      </c>
+      <c r="U20">
+        <v>1.38</v>
+      </c>
+      <c r="V20">
+        <v>6.5</v>
+      </c>
+      <c r="W20">
+        <v>1.08</v>
+      </c>
+      <c r="X20">
+        <v>1.06</v>
+      </c>
+      <c r="Y20">
+        <v>9.5</v>
+      </c>
+      <c r="Z20">
+        <v>1.3</v>
+      </c>
+      <c r="AA20">
         <v>3.25</v>
       </c>
-      <c r="M20">
-        <v>3.15</v>
-      </c>
-      <c r="N20">
-        <v>2.21</v>
-      </c>
-      <c r="O20">
-        <v>1.91</v>
-      </c>
-      <c r="P20">
-        <v>7.9</v>
-      </c>
-      <c r="Q20">
-        <v>2.1</v>
-      </c>
-      <c r="R20">
-        <v>1.42</v>
-      </c>
-      <c r="S20">
-        <v>2.62</v>
-      </c>
-      <c r="T20">
-        <v>2.9</v>
-      </c>
-      <c r="U20">
-        <v>1.36</v>
-      </c>
-      <c r="V20">
-        <v>7.7</v>
-      </c>
-      <c r="W20">
-        <v>1.07</v>
-      </c>
-      <c r="X20">
-        <v>1.02</v>
-      </c>
-      <c r="Y20">
-        <v>7.9</v>
-      </c>
-      <c r="Z20">
-        <v>1.25</v>
-      </c>
-      <c r="AA20">
-        <v>3</v>
-      </c>
       <c r="AB20">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="AC20">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AD20">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="AE20">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AF20">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG20">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH20">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AI20">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AJ20" t="s">
         <v>248</v>
@@ -3803,7 +3803,7 @@
         <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
         <v>90</v>
@@ -3830,76 +3830,76 @@
         <v>247</v>
       </c>
       <c r="L24">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="M24">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="N24">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="O24">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="P24">
-        <v>11</v>
+        <v>8.9</v>
       </c>
       <c r="Q24">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="R24">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S24">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="T24">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="U24">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V24">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W24">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z24">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AA24">
-        <v>4.33</v>
+        <v>3.22</v>
       </c>
       <c r="AB24">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AC24">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AD24">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="AE24">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AF24">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG24">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AH24">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AI24">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AJ24" t="s">
         <v>248</v>
@@ -3919,7 +3919,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
         <v>90</v>
@@ -3946,76 +3946,76 @@
         <v>247</v>
       </c>
       <c r="L25">
+        <v>1.33</v>
+      </c>
+      <c r="M25">
+        <v>4.5</v>
+      </c>
+      <c r="N25">
+        <v>6.9</v>
+      </c>
+      <c r="O25">
+        <v>1.29</v>
+      </c>
+      <c r="P25">
+        <v>11</v>
+      </c>
+      <c r="Q25">
+        <v>3.75</v>
+      </c>
+      <c r="R25">
+        <v>1.29</v>
+      </c>
+      <c r="S25">
+        <v>3.5</v>
+      </c>
+      <c r="T25">
+        <v>2.38</v>
+      </c>
+      <c r="U25">
+        <v>1.53</v>
+      </c>
+      <c r="V25">
+        <v>5.5</v>
+      </c>
+      <c r="W25">
+        <v>1.14</v>
+      </c>
+      <c r="X25">
+        <v>1.04</v>
+      </c>
+      <c r="Y25">
+        <v>11</v>
+      </c>
+      <c r="Z25">
+        <v>1.22</v>
+      </c>
+      <c r="AA25">
+        <v>4.33</v>
+      </c>
+      <c r="AB25">
         <v>1.6</v>
       </c>
-      <c r="M25">
-        <v>4.1</v>
-      </c>
-      <c r="N25">
-        <v>4.4</v>
-      </c>
-      <c r="O25">
-        <v>1.44</v>
-      </c>
-      <c r="P25">
-        <v>14</v>
-      </c>
-      <c r="Q25">
-        <v>2.75</v>
-      </c>
-      <c r="R25">
-        <v>1.25</v>
-      </c>
-      <c r="S25">
-        <v>3.8</v>
-      </c>
-      <c r="T25">
-        <v>2.2</v>
-      </c>
-      <c r="U25">
-        <v>1.65</v>
-      </c>
-      <c r="V25">
-        <v>4.4</v>
-      </c>
-      <c r="W25">
-        <v>1.17</v>
-      </c>
-      <c r="X25">
-        <v>1.02</v>
-      </c>
-      <c r="Y25">
-        <v>17</v>
-      </c>
-      <c r="Z25">
-        <v>1.13</v>
-      </c>
-      <c r="AA25">
-        <v>5.2</v>
-      </c>
-      <c r="AB25">
-        <v>1.53</v>
-      </c>
       <c r="AC25">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="AD25">
-        <v>2.27</v>
+        <v>2.65</v>
       </c>
       <c r="AE25">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AF25">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AG25">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AH25">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AI25">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AJ25" t="s">
         <v>248</v>
@@ -4062,76 +4062,76 @@
         <v>247</v>
       </c>
       <c r="L26">
+        <v>1.61</v>
+      </c>
+      <c r="M26">
+        <v>3.85</v>
+      </c>
+      <c r="N26">
+        <v>4.2</v>
+      </c>
+      <c r="O26">
         <v>1.44</v>
       </c>
-      <c r="M26">
-        <v>4</v>
-      </c>
-      <c r="N26">
-        <v>6.5</v>
-      </c>
-      <c r="O26">
-        <v>1.39</v>
-      </c>
       <c r="P26">
-        <v>8.9</v>
+        <v>14</v>
       </c>
       <c r="Q26">
-        <v>3.52</v>
+        <v>2.75</v>
       </c>
       <c r="R26">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="S26">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="T26">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="U26">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="W26">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>8.9</v>
+        <v>17</v>
       </c>
       <c r="Z26">
+        <v>1.13</v>
+      </c>
+      <c r="AA26">
+        <v>5</v>
+      </c>
+      <c r="AB26">
+        <v>1.5</v>
+      </c>
+      <c r="AC26">
+        <v>2.4</v>
+      </c>
+      <c r="AD26">
+        <v>2.2</v>
+      </c>
+      <c r="AE26">
+        <v>1.55</v>
+      </c>
+      <c r="AF26">
+        <v>1.53</v>
+      </c>
+      <c r="AG26">
+        <v>2.45</v>
+      </c>
+      <c r="AH26">
+        <v>3.8</v>
+      </c>
+      <c r="AI26">
         <v>1.25</v>
-      </c>
-      <c r="AA26">
-        <v>3.28</v>
-      </c>
-      <c r="AB26">
-        <v>1.87</v>
-      </c>
-      <c r="AC26">
-        <v>1.85</v>
-      </c>
-      <c r="AD26">
-        <v>3.08</v>
-      </c>
-      <c r="AE26">
-        <v>1.28</v>
-      </c>
-      <c r="AF26">
-        <v>1.98</v>
-      </c>
-      <c r="AG26">
-        <v>1.7</v>
-      </c>
-      <c r="AH26">
-        <v>5.75</v>
-      </c>
-      <c r="AI26">
-        <v>1.07</v>
       </c>
       <c r="AJ26" t="s">
         <v>248</v>
@@ -4178,13 +4178,13 @@
         <v>247</v>
       </c>
       <c r="L27">
-        <v>1.95</v>
+        <v>1.56</v>
       </c>
       <c r="M27">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="O27">
         <v>1.44</v>
@@ -4196,55 +4196,55 @@
         <v>3.5</v>
       </c>
       <c r="R27">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S27">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="T27">
         <v>3.2</v>
       </c>
       <c r="U27">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
         <v>1.07</v>
       </c>
       <c r="Y27">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Z27">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AA27">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AB27">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC27">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AD27">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AE27">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF27">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AG27">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AH27">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AI27">
         <v>1.04</v>
@@ -4294,13 +4294,13 @@
         <v>247</v>
       </c>
       <c r="L28">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="M28">
-        <v>6.83</v>
+        <v>6.7</v>
       </c>
       <c r="N28">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="O28">
         <v>1.22</v>
@@ -4312,22 +4312,22 @@
         <v>4</v>
       </c>
       <c r="R28">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S28">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T28">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="U28">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="V28">
         <v>3.3</v>
       </c>
       <c r="W28">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -4339,31 +4339,31 @@
         <v>1.03</v>
       </c>
       <c r="AA28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB28">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AC28">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD28">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AE28">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF28">
         <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH28">
         <v>2.55</v>
       </c>
       <c r="AI28">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AJ28" t="s">
         <v>248</v>
@@ -4410,13 +4410,13 @@
         <v>247</v>
       </c>
       <c r="L29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="N29">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O29">
         <v>4.33</v>
@@ -4431,13 +4431,13 @@
         <v>1.2</v>
       </c>
       <c r="S29">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T29">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="U29">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V29">
         <v>3.7</v>
@@ -4458,19 +4458,19 @@
         <v>5.95</v>
       </c>
       <c r="AB29">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC29">
         <v>2.75</v>
       </c>
       <c r="AD29">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AE29">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF29">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG29">
         <v>2</v>
@@ -4479,7 +4479,7 @@
         <v>3.2</v>
       </c>
       <c r="AI29">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AJ29" t="s">
         <v>248</v>
@@ -4847,7 +4847,7 @@
         <v>51</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D33" t="s">
         <v>90</v>
@@ -4874,76 +4874,76 @@
         <v>247</v>
       </c>
       <c r="L33">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH33">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI33">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="s">
         <v>248</v>
@@ -4963,7 +4963,7 @@
         <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
         <v>90</v>
@@ -4990,76 +4990,76 @@
         <v>247</v>
       </c>
       <c r="L34">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N34">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O34">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH34">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AI34">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="s">
         <v>248</v>
@@ -5195,7 +5195,7 @@
         <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
         <v>90</v>
@@ -5222,76 +5222,76 @@
         <v>247</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH36">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI36">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ36" t="s">
         <v>248</v>
@@ -5427,7 +5427,7 @@
         <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D38" t="s">
         <v>90</v>
@@ -5454,76 +5454,76 @@
         <v>247</v>
       </c>
       <c r="L38">
-        <v>3.51</v>
+        <v>1.65</v>
       </c>
       <c r="M38">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="N38">
-        <v>1.95</v>
+        <v>4.75</v>
       </c>
       <c r="O38">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="P38">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="Q38">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="R38">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S38">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="T38">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="U38">
+        <v>1.44</v>
+      </c>
+      <c r="V38">
+        <v>7</v>
+      </c>
+      <c r="W38">
+        <v>1.1</v>
+      </c>
+      <c r="X38">
+        <v>1.05</v>
+      </c>
+      <c r="Y38">
+        <v>9.5</v>
+      </c>
+      <c r="Z38">
         <v>1.28</v>
       </c>
-      <c r="V38">
-        <v>9</v>
-      </c>
-      <c r="W38">
-        <v>1</v>
-      </c>
-      <c r="X38">
-        <v>1.02</v>
-      </c>
-      <c r="Y38">
-        <v>7</v>
-      </c>
-      <c r="Z38">
-        <v>1.36</v>
-      </c>
       <c r="AA38">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="AB38">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AC38">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AD38">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AE38">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AF38">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG38">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AH38">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="AI38">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AJ38" t="s">
         <v>248</v>
@@ -5543,7 +5543,7 @@
         <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D39" t="s">
         <v>90</v>
@@ -5570,76 +5570,76 @@
         <v>247</v>
       </c>
       <c r="L39">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M39">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N39">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH39">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AI39">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="s">
         <v>248</v>
@@ -5659,7 +5659,7 @@
         <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D40" t="s">
         <v>90</v>
@@ -5686,76 +5686,76 @@
         <v>247</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH40">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AI40">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ40" t="s">
         <v>248</v>
@@ -6703,7 +6703,7 @@
         <v>51</v>
       </c>
       <c r="C49" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D49" t="s">
         <v>90</v>
@@ -6730,76 +6730,76 @@
         <v>247</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH49">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ49" t="s">
         <v>248</v>
@@ -6819,7 +6819,7 @@
         <v>52</v>
       </c>
       <c r="C50" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D50" t="s">
         <v>90</v>
@@ -6846,13 +6846,13 @@
         <v>247</v>
       </c>
       <c r="L50">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M50">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="N50">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="O50">
         <v>1.25</v>
@@ -6864,7 +6864,7 @@
         <v>4</v>
       </c>
       <c r="R50">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S50">
         <v>3.7</v>
@@ -6876,7 +6876,7 @@
         <v>1.6</v>
       </c>
       <c r="V50">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="W50">
         <v>1.17</v>
@@ -6885,25 +6885,25 @@
         <v>1</v>
       </c>
       <c r="Y50">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z50">
         <v>1.15</v>
       </c>
       <c r="AA50">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AB50">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC50">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AD50">
         <v>2.25</v>
       </c>
       <c r="AE50">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AF50">
         <v>1.8</v>
@@ -6915,7 +6915,7 @@
         <v>4</v>
       </c>
       <c r="AI50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ50" t="s">
         <v>248</v>
@@ -6935,7 +6935,7 @@
         <v>52</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D51" t="s">
         <v>90</v>
@@ -6962,13 +6962,13 @@
         <v>247</v>
       </c>
       <c r="L51">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="M51">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="N51">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="O51">
         <v>3</v>
@@ -6980,49 +6980,49 @@
         <v>1.4</v>
       </c>
       <c r="R51">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S51">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="T51">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="U51">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="V51">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
         <v>1</v>
       </c>
       <c r="Y51">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z51">
         <v>1.19</v>
       </c>
       <c r="AA51">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AB51">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AC51">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD51">
         <v>2.4</v>
       </c>
       <c r="AE51">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF51">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG51">
         <v>2.15</v>
@@ -7078,13 +7078,13 @@
         <v>247</v>
       </c>
       <c r="L52">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="M52">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="N52">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="O52">
         <v>1.53</v>
@@ -7099,10 +7099,10 @@
         <v>1.32</v>
       </c>
       <c r="S52">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T52">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="U52">
         <v>1.66</v>
@@ -7111,7 +7111,7 @@
         <v>5.5</v>
       </c>
       <c r="W52">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X52">
         <v>1.04</v>
@@ -7120,22 +7120,22 @@
         <v>12</v>
       </c>
       <c r="Z52">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AA52">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AB52">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AC52">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AD52">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AE52">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AF52">
         <v>1.67</v>
@@ -7147,7 +7147,7 @@
         <v>3.9</v>
       </c>
       <c r="AI52">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AJ52" t="s">
         <v>248</v>
@@ -7194,13 +7194,13 @@
         <v>247</v>
       </c>
       <c r="L53">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="M53">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="N53">
-        <v>2.01</v>
+        <v>2.23</v>
       </c>
       <c r="O53">
         <v>2.1</v>
@@ -7212,58 +7212,58 @@
         <v>1.8</v>
       </c>
       <c r="R53">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S53">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="T53">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="U53">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V53">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="W53">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>11</v>
+        <v>8.9</v>
       </c>
       <c r="Z53">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AA53">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AB53">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC53">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AD53">
         <v>2.6</v>
       </c>
       <c r="AE53">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF53">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AG53">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH53">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AI53">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ53" t="s">
         <v>248</v>
@@ -7310,73 +7310,73 @@
         <v>247</v>
       </c>
       <c r="L54">
-        <v>1.9</v>
+        <v>2.63</v>
       </c>
       <c r="M54">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="N54">
-        <v>3.66</v>
+        <v>2.63</v>
       </c>
       <c r="O54">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="P54">
-        <v>6.8</v>
+        <v>7.75</v>
       </c>
       <c r="Q54">
+        <v>2</v>
+      </c>
+      <c r="R54">
+        <v>1.44</v>
+      </c>
+      <c r="S54">
+        <v>2.63</v>
+      </c>
+      <c r="T54">
         <v>3.25</v>
       </c>
-      <c r="R54">
-        <v>1.5</v>
-      </c>
-      <c r="S54">
-        <v>2.4</v>
-      </c>
-      <c r="T54">
-        <v>3.3</v>
-      </c>
       <c r="U54">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V54">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W54">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X54">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y54">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z54">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AA54">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="AB54">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AC54">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD54">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="AE54">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF54">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AG54">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH54">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="AI54">
         <v>1.04</v>
@@ -7426,76 +7426,76 @@
         <v>247</v>
       </c>
       <c r="L55">
-        <v>2.63</v>
+        <v>1.71</v>
       </c>
       <c r="M55">
+        <v>3.28</v>
+      </c>
+      <c r="N55">
+        <v>4.33</v>
+      </c>
+      <c r="O55">
+        <v>1.53</v>
+      </c>
+      <c r="P55">
+        <v>6.8</v>
+      </c>
+      <c r="Q55">
         <v>3.25</v>
       </c>
-      <c r="N55">
-        <v>2.63</v>
-      </c>
-      <c r="O55">
-        <v>2</v>
-      </c>
-      <c r="P55">
-        <v>7.75</v>
-      </c>
-      <c r="Q55">
-        <v>2</v>
-      </c>
       <c r="R55">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="S55">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="T55">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U55">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V55">
         <v>9</v>
       </c>
       <c r="W55">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X55">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y55">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z55">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AA55">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="AB55">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AC55">
+        <v>1.53</v>
+      </c>
+      <c r="AD55">
+        <v>4.65</v>
+      </c>
+      <c r="AE55">
+        <v>1.17</v>
+      </c>
+      <c r="AF55">
+        <v>2.1</v>
+      </c>
+      <c r="AG55">
         <v>1.67</v>
       </c>
-      <c r="AD55">
-        <v>3.85</v>
-      </c>
-      <c r="AE55">
-        <v>1.22</v>
-      </c>
-      <c r="AF55">
-        <v>1.83</v>
-      </c>
-      <c r="AG55">
-        <v>1.83</v>
-      </c>
       <c r="AH55">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI55">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AJ55" t="s">
         <v>248</v>
@@ -7637,10 +7637,10 @@
         <v>90</v>
       </c>
       <c r="E57" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F57" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -7747,7 +7747,7 @@
         <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D58" t="s">
         <v>90</v>
@@ -7774,76 +7774,76 @@
         <v>247</v>
       </c>
       <c r="L58">
-        <v>3.8</v>
+        <v>2.12</v>
       </c>
       <c r="M58">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N58">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="O58">
+        <v>1.73</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>2.2</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+      <c r="AA58">
+        <v>0</v>
+      </c>
+      <c r="AB58">
+        <v>1.5</v>
+      </c>
+      <c r="AC58">
         <v>2.5</v>
       </c>
-      <c r="P58">
-        <v>9.5</v>
-      </c>
-      <c r="Q58">
-        <v>1.62</v>
-      </c>
-      <c r="R58">
-        <v>1.36</v>
-      </c>
-      <c r="S58">
-        <v>3</v>
-      </c>
-      <c r="T58">
-        <v>2.75</v>
-      </c>
-      <c r="U58">
-        <v>1.4</v>
-      </c>
-      <c r="V58">
-        <v>7</v>
-      </c>
-      <c r="W58">
-        <v>1.1</v>
-      </c>
-      <c r="X58">
-        <v>1.05</v>
-      </c>
-      <c r="Y58">
-        <v>8.5</v>
-      </c>
-      <c r="Z58">
-        <v>1.28</v>
-      </c>
-      <c r="AA58">
-        <v>3.4</v>
-      </c>
-      <c r="AB58">
-        <v>1.9</v>
-      </c>
-      <c r="AC58">
-        <v>1.9</v>
-      </c>
       <c r="AD58">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE58">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF58">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH58">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AI58">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ58" t="s">
         <v>248</v>
@@ -7890,13 +7890,13 @@
         <v>247</v>
       </c>
       <c r="L59">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M59">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="N59">
-        <v>11.27</v>
+        <v>7.2</v>
       </c>
       <c r="O59">
         <v>1.22</v>
@@ -7908,58 +7908,58 @@
         <v>6</v>
       </c>
       <c r="R59">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S59">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T59">
         <v>2.8</v>
       </c>
       <c r="U59">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="V59">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W59">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y59">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z59">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AA59">
         <v>3.1</v>
       </c>
       <c r="AB59">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AC59">
         <v>1.75</v>
       </c>
       <c r="AD59">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AE59">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AF59">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AG59">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AH59">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="AI59">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AJ59" t="s">
         <v>248</v>
@@ -7979,7 +7979,7 @@
         <v>57</v>
       </c>
       <c r="C60" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D60" t="s">
         <v>90</v>
@@ -8006,76 +8006,76 @@
         <v>247</v>
       </c>
       <c r="L60">
-        <v>2.42</v>
+        <v>1.91</v>
       </c>
       <c r="M60">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N60">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O60">
+        <v>1.62</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
         <v>2.3</v>
       </c>
-      <c r="P60">
-        <v>6.75</v>
-      </c>
-      <c r="Q60">
-        <v>1.91</v>
-      </c>
       <c r="R60">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="S60">
+        <v>3.6</v>
+      </c>
+      <c r="T60">
+        <v>2.1</v>
+      </c>
+      <c r="U60">
+        <v>1.65</v>
+      </c>
+      <c r="V60">
+        <v>4.5</v>
+      </c>
+      <c r="W60">
+        <v>1.17</v>
+      </c>
+      <c r="X60">
+        <v>1</v>
+      </c>
+      <c r="Y60">
+        <v>12</v>
+      </c>
+      <c r="Z60">
+        <v>1.12</v>
+      </c>
+      <c r="AA60">
+        <v>4.75</v>
+      </c>
+      <c r="AB60">
+        <v>1.48</v>
+      </c>
+      <c r="AC60">
+        <v>2.5</v>
+      </c>
+      <c r="AD60">
+        <v>2.1</v>
+      </c>
+      <c r="AE60">
+        <v>1.65</v>
+      </c>
+      <c r="AF60">
+        <v>1.5</v>
+      </c>
+      <c r="AG60">
         <v>2.4</v>
       </c>
-      <c r="T60">
-        <v>3.3</v>
-      </c>
-      <c r="U60">
-        <v>1.29</v>
-      </c>
-      <c r="V60">
-        <v>8.5</v>
-      </c>
-      <c r="W60">
-        <v>1.02</v>
-      </c>
-      <c r="X60">
-        <v>1.05</v>
-      </c>
-      <c r="Y60">
-        <v>6.75</v>
-      </c>
-      <c r="Z60">
-        <v>1.44</v>
-      </c>
-      <c r="AA60">
-        <v>2.71</v>
-      </c>
-      <c r="AB60">
-        <v>2.3</v>
-      </c>
-      <c r="AC60">
-        <v>1.55</v>
-      </c>
-      <c r="AD60">
-        <v>4.25</v>
-      </c>
-      <c r="AE60">
-        <v>1.18</v>
-      </c>
-      <c r="AF60">
-        <v>1.98</v>
-      </c>
-      <c r="AG60">
-        <v>1.8</v>
-      </c>
       <c r="AH60">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="AI60">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AJ60" t="s">
         <v>248</v>
@@ -8095,7 +8095,7 @@
         <v>57</v>
       </c>
       <c r="C61" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D61" t="s">
         <v>90</v>
@@ -8122,76 +8122,76 @@
         <v>247</v>
       </c>
       <c r="L61">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="M61">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="N61">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="O61">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="P61">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="Q61">
+        <v>1.91</v>
+      </c>
+      <c r="R61">
+        <v>1.5</v>
+      </c>
+      <c r="S61">
         <v>2.4</v>
       </c>
-      <c r="R61">
-        <v>1.63</v>
-      </c>
-      <c r="S61">
-        <v>2.2</v>
-      </c>
       <c r="T61">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="U61">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V61">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W61">
         <v>1.04</v>
       </c>
       <c r="X61">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>6.25</v>
+        <v>6.9</v>
       </c>
       <c r="Z61">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AA61">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB61">
-        <v>2.83</v>
+        <v>2.53</v>
       </c>
       <c r="AC61">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AD61">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="AE61">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF61">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AG61">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AH61">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI61">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ61" t="s">
         <v>248</v>
@@ -8238,76 +8238,76 @@
         <v>247</v>
       </c>
       <c r="L62">
-        <v>3.78</v>
+        <v>2.17</v>
       </c>
       <c r="M62">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="N62">
-        <v>1.66</v>
+        <v>3.23</v>
       </c>
       <c r="O62">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q62">
+        <v>2.4</v>
+      </c>
+      <c r="R62">
+        <v>1.63</v>
+      </c>
+      <c r="S62">
+        <v>2.2</v>
+      </c>
+      <c r="T62">
+        <v>3.7</v>
+      </c>
+      <c r="U62">
+        <v>1.25</v>
+      </c>
+      <c r="V62">
+        <v>12.5</v>
+      </c>
+      <c r="W62">
+        <v>1.04</v>
+      </c>
+      <c r="X62">
+        <v>1.13</v>
+      </c>
+      <c r="Y62">
+        <v>6.25</v>
+      </c>
+      <c r="Z62">
         <v>1.57</v>
       </c>
-      <c r="R62">
-        <v>1.33</v>
-      </c>
-      <c r="S62">
-        <v>3.25</v>
-      </c>
-      <c r="T62">
-        <v>2.5</v>
-      </c>
-      <c r="U62">
+      <c r="AA62">
+        <v>2.25</v>
+      </c>
+      <c r="AB62">
+        <v>2.25</v>
+      </c>
+      <c r="AC62">
         <v>1.5</v>
       </c>
-      <c r="V62">
+      <c r="AD62">
         <v>5.5</v>
       </c>
-      <c r="W62">
+      <c r="AE62">
         <v>1.13</v>
       </c>
-      <c r="X62">
-        <v>0</v>
-      </c>
-      <c r="Y62">
-        <v>0</v>
-      </c>
-      <c r="Z62">
-        <v>0</v>
-      </c>
-      <c r="AA62">
-        <v>0</v>
-      </c>
-      <c r="AB62">
-        <v>1.85</v>
-      </c>
-      <c r="AC62">
-        <v>1.95</v>
-      </c>
-      <c r="AD62">
-        <v>0</v>
-      </c>
-      <c r="AE62">
-        <v>0</v>
-      </c>
       <c r="AF62">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AG62">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AH62">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI62">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ62" t="s">
         <v>248</v>
@@ -8354,70 +8354,70 @@
         <v>247</v>
       </c>
       <c r="L63">
-        <v>2.37</v>
+        <v>3.7</v>
       </c>
       <c r="M63">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="N63">
-        <v>2.49</v>
+        <v>1.84</v>
       </c>
       <c r="O63">
+        <v>2.6</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>1.57</v>
+      </c>
+      <c r="R63">
+        <v>1.33</v>
+      </c>
+      <c r="S63">
+        <v>3.25</v>
+      </c>
+      <c r="T63">
+        <v>2.5</v>
+      </c>
+      <c r="U63">
+        <v>1.5</v>
+      </c>
+      <c r="V63">
+        <v>5.5</v>
+      </c>
+      <c r="W63">
+        <v>1.13</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+      <c r="AA63">
+        <v>0</v>
+      </c>
+      <c r="AB63">
+        <v>1.65</v>
+      </c>
+      <c r="AC63">
+        <v>2.1</v>
+      </c>
+      <c r="AD63">
+        <v>0</v>
+      </c>
+      <c r="AE63">
+        <v>0</v>
+      </c>
+      <c r="AF63">
         <v>1.73</v>
       </c>
-      <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="Q63">
-        <v>2.2</v>
-      </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
-        <v>0</v>
-      </c>
-      <c r="T63">
-        <v>0</v>
-      </c>
-      <c r="U63">
-        <v>0</v>
-      </c>
-      <c r="V63">
-        <v>0</v>
-      </c>
-      <c r="W63">
-        <v>0</v>
-      </c>
-      <c r="X63">
-        <v>0</v>
-      </c>
-      <c r="Y63">
-        <v>0</v>
-      </c>
-      <c r="Z63">
-        <v>0</v>
-      </c>
-      <c r="AA63">
-        <v>0</v>
-      </c>
-      <c r="AB63">
-        <v>1.5</v>
-      </c>
-      <c r="AC63">
-        <v>2.5</v>
-      </c>
-      <c r="AD63">
-        <v>0</v>
-      </c>
-      <c r="AE63">
-        <v>0</v>
-      </c>
-      <c r="AF63">
-        <v>0</v>
-      </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH63">
         <v>0</v>
@@ -8443,7 +8443,7 @@
         <v>57</v>
       </c>
       <c r="C64" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D64" t="s">
         <v>90</v>
@@ -8470,76 +8470,76 @@
         <v>247</v>
       </c>
       <c r="L64">
-        <v>1.91</v>
+        <v>3.8</v>
       </c>
       <c r="M64">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N64">
+        <v>2</v>
+      </c>
+      <c r="O64">
+        <v>2.5</v>
+      </c>
+      <c r="P64">
+        <v>9.5</v>
+      </c>
+      <c r="Q64">
+        <v>1.62</v>
+      </c>
+      <c r="R64">
+        <v>1.36</v>
+      </c>
+      <c r="S64">
         <v>3</v>
       </c>
-      <c r="O64">
-        <v>1.62</v>
-      </c>
-      <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <v>2.3</v>
-      </c>
-      <c r="R64">
-        <v>1.25</v>
-      </c>
-      <c r="S64">
-        <v>3.6</v>
-      </c>
       <c r="T64">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="U64">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="V64">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="W64">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X64">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y64">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Z64">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AA64">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB64">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="AC64">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AD64">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="AE64">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AF64">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG64">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AH64">
-        <v>3.58</v>
+        <v>5.9</v>
       </c>
       <c r="AI64">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AJ64" t="s">
         <v>248</v>
@@ -8559,7 +8559,7 @@
         <v>57</v>
       </c>
       <c r="C65" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D65" t="s">
         <v>90</v>
@@ -8586,13 +8586,13 @@
         <v>247</v>
       </c>
       <c r="L65">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="M65">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="N65">
-        <v>4.06</v>
+        <v>2.5</v>
       </c>
       <c r="O65">
         <v>1.8</v>
@@ -8604,58 +8604,58 @@
         <v>2.5</v>
       </c>
       <c r="R65">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S65">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T65">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U65">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V65">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W65">
+        <v>1.04</v>
+      </c>
+      <c r="X65">
         <v>1.05</v>
       </c>
-      <c r="X65">
-        <v>1.04</v>
-      </c>
       <c r="Y65">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="Z65">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AA65">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AB65">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AC65">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AD65">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AE65">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF65">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG65">
         <v>1.73</v>
       </c>
       <c r="AH65">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI65">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AJ65" t="s">
         <v>248</v>
@@ -8702,13 +8702,13 @@
         <v>247</v>
       </c>
       <c r="L66">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="M66">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="N66">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="O66">
         <v>1.75</v>
@@ -8723,43 +8723,43 @@
         <v>1.22</v>
       </c>
       <c r="S66">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T66">
         <v>2.11</v>
       </c>
       <c r="U66">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V66">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="W66">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z66">
         <v>1.08</v>
       </c>
       <c r="AA66">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AB66">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AC66">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AD66">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AE66">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF66">
         <v>1.4</v>
@@ -8771,7 +8771,7 @@
         <v>3.35</v>
       </c>
       <c r="AI66">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AJ66" t="s">
         <v>248</v>
@@ -8821,7 +8821,7 @@
         <v>2.05</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N67">
         <v>3.4</v>
@@ -8836,13 +8836,13 @@
         <v>2.45</v>
       </c>
       <c r="R67">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S67">
         <v>2.4</v>
       </c>
       <c r="T67">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="U67">
         <v>1.27</v>
@@ -8851,25 +8851,25 @@
         <v>9.75</v>
       </c>
       <c r="W67">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X67">
         <v>1.09</v>
       </c>
       <c r="Y67">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="Z67">
         <v>1.48</v>
       </c>
       <c r="AA67">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AB67">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC67">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AD67">
         <v>4.5</v>
@@ -8934,13 +8934,13 @@
         <v>247</v>
       </c>
       <c r="L68">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="M68">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="N68">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="O68">
         <v>1.75</v>
@@ -8970,31 +8970,31 @@
         <v>1.03</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y68">
         <v>7.8</v>
       </c>
       <c r="Z68">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AA68">
         <v>2.5</v>
       </c>
       <c r="AB68">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="AC68">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AD68">
         <v>4.5</v>
       </c>
       <c r="AE68">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF68">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG68">
         <v>1.68</v>
@@ -9003,7 +9003,7 @@
         <v>9.9</v>
       </c>
       <c r="AI68">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ68" t="s">
         <v>248</v>
@@ -9029,10 +9029,10 @@
         <v>90</v>
       </c>
       <c r="E69" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F69" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -9050,76 +9050,76 @@
         <v>247</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH69">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI69">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ69" t="s">
         <v>248</v>
@@ -9145,10 +9145,10 @@
         <v>90</v>
       </c>
       <c r="E70" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F70" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -9166,76 +9166,76 @@
         <v>247</v>
       </c>
       <c r="L70">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M70">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N70">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P70">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q70">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S70">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T70">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U70">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V70">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W70">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X70">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y70">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Z70">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA70">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB70">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC70">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD70">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AE70">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF70">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG70">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH70">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI70">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ70" t="s">
         <v>248</v>
@@ -9282,76 +9282,76 @@
         <v>247</v>
       </c>
       <c r="L71">
-        <v>1.74</v>
+        <v>3.4</v>
       </c>
       <c r="M71">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="N71">
-        <v>5.35</v>
+        <v>2.02</v>
       </c>
       <c r="O71">
+        <v>2.4</v>
+      </c>
+      <c r="P71">
+        <v>6.75</v>
+      </c>
+      <c r="Q71">
+        <v>1.8</v>
+      </c>
+      <c r="R71">
         <v>1.5</v>
-      </c>
-      <c r="P71">
-        <v>7</v>
-      </c>
-      <c r="Q71">
-        <v>3.4</v>
-      </c>
-      <c r="R71">
-        <v>1.45</v>
       </c>
       <c r="S71">
         <v>2.4</v>
       </c>
       <c r="T71">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U71">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V71">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="W71">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y71">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Z71">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AA71">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AB71">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="AC71">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD71">
-        <v>4.58</v>
+        <v>4.33</v>
       </c>
       <c r="AE71">
         <v>1.18</v>
       </c>
       <c r="AF71">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AG71">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AH71">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AI71">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ71" t="s">
         <v>248</v>
@@ -9398,22 +9398,22 @@
         <v>247</v>
       </c>
       <c r="L72">
-        <v>3.34</v>
+        <v>1.64</v>
       </c>
       <c r="M72">
         <v>3.1</v>
       </c>
       <c r="N72">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="O72">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="P72">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="Q72">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="R72">
         <v>1.5</v>
@@ -9422,52 +9422,52 @@
         <v>2.4</v>
       </c>
       <c r="T72">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U72">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V72">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W72">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X72">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y72">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z72">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AA72">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AB72">
         <v>2.45</v>
       </c>
       <c r="AC72">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AD72">
-        <v>4.33</v>
+        <v>4.58</v>
       </c>
       <c r="AE72">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF72">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AG72">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AH72">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AI72">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AJ72" t="s">
         <v>248</v>
@@ -9487,7 +9487,7 @@
         <v>62</v>
       </c>
       <c r="C73" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D73" t="s">
         <v>90</v>
@@ -9514,22 +9514,22 @@
         <v>247</v>
       </c>
       <c r="L73">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="M73">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="N73">
-        <v>3.48</v>
+        <v>5.1</v>
       </c>
       <c r="O73">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="P73">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="Q73">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="R73">
         <v>1.48</v>
@@ -9538,13 +9538,13 @@
         <v>2.47</v>
       </c>
       <c r="T73">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U73">
         <v>1.3</v>
       </c>
       <c r="V73">
-        <v>8</v>
+        <v>9.25</v>
       </c>
       <c r="W73">
         <v>1.04</v>
@@ -9553,34 +9553,34 @@
         <v>1.08</v>
       </c>
       <c r="Y73">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Z73">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AA73">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB73">
         <v>2.25</v>
       </c>
       <c r="AC73">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AD73">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AE73">
         <v>1.2</v>
       </c>
       <c r="AF73">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AG73">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AH73">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AI73">
         <v>1.05</v>
@@ -9603,7 +9603,7 @@
         <v>62</v>
       </c>
       <c r="C74" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D74" t="s">
         <v>90</v>
@@ -9630,76 +9630,76 @@
         <v>247</v>
       </c>
       <c r="L74">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="M74">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="N74">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="O74">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="P74">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="Q74">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="R74">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="S74">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="T74">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U74">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V74">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="W74">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X74">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y74">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Z74">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AA74">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AB74">
         <v>2.25</v>
       </c>
       <c r="AC74">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD74">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AE74">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF74">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AG74">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AH74">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AI74">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AJ74" t="s">
         <v>248</v>
@@ -9746,13 +9746,13 @@
         <v>247</v>
       </c>
       <c r="L75">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="M75">
         <v>2.9</v>
       </c>
       <c r="N75">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O75">
         <v>1.88</v>
@@ -9764,10 +9764,10 @@
         <v>2.35</v>
       </c>
       <c r="R75">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S75">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="T75">
         <v>3.6</v>
@@ -9776,7 +9776,7 @@
         <v>1.25</v>
       </c>
       <c r="V75">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W75">
         <v>1.02</v>
@@ -9794,7 +9794,7 @@
         <v>2.4</v>
       </c>
       <c r="AB75">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC75">
         <v>1.48</v>
@@ -9862,13 +9862,13 @@
         <v>247</v>
       </c>
       <c r="L76">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="M76">
         <v>3.1</v>
       </c>
       <c r="N76">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O76">
         <v>1.63</v>
@@ -9889,7 +9889,7 @@
         <v>3.35</v>
       </c>
       <c r="U76">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V76">
         <v>8.699999999999999</v>
@@ -9898,40 +9898,40 @@
         <v>1.03</v>
       </c>
       <c r="X76">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y76">
         <v>6.5</v>
       </c>
       <c r="Z76">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AA76">
         <v>2.52</v>
       </c>
       <c r="AB76">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AC76">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AD76">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AE76">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF76">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AG76">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH76">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="AI76">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AJ76" t="s">
         <v>248</v>
@@ -9957,10 +9957,10 @@
         <v>90</v>
       </c>
       <c r="E77" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F77" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -10097,10 +10097,10 @@
         <v>1.6</v>
       </c>
       <c r="M78">
-        <v>3.75</v>
+        <v>3.41</v>
       </c>
       <c r="N78">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="O78">
         <v>1.44</v>
@@ -10112,58 +10112,58 @@
         <v>3.25</v>
       </c>
       <c r="R78">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S78">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T78">
         <v>3</v>
       </c>
       <c r="U78">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V78">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W78">
         <v>1.05</v>
       </c>
       <c r="X78">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y78">
         <v>8</v>
       </c>
       <c r="Z78">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AA78">
         <v>3</v>
       </c>
       <c r="AB78">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AC78">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AD78">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AE78">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF78">
         <v>2.1</v>
       </c>
       <c r="AG78">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH78">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI78">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AJ78" t="s">
         <v>248</v>
@@ -10183,7 +10183,7 @@
         <v>65</v>
       </c>
       <c r="C79" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D79" t="s">
         <v>90</v>
@@ -10237,7 +10237,7 @@
         <v>1.92</v>
       </c>
       <c r="U79">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="V79">
         <v>3.6</v>
@@ -10270,13 +10270,13 @@
         <v>1.91</v>
       </c>
       <c r="AF79">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AG79">
         <v>2.71</v>
       </c>
       <c r="AH79">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AI79">
         <v>1.38</v>
@@ -10299,16 +10299,16 @@
         <v>66</v>
       </c>
       <c r="C80" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D80" t="s">
         <v>90</v>
       </c>
       <c r="E80" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="F80" t="s">
-        <v>243</v>
+        <v>202</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -10326,76 +10326,76 @@
         <v>247</v>
       </c>
       <c r="L80">
-        <v>2.89</v>
+        <v>1.91</v>
       </c>
       <c r="M80">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N80">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="O80">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q80">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB80">
+        <v>2.3</v>
+      </c>
+      <c r="AC80">
+        <v>1.55</v>
+      </c>
+      <c r="AD80">
+        <v>4.5</v>
+      </c>
+      <c r="AE80">
+        <v>1.2</v>
+      </c>
+      <c r="AF80">
         <v>2.05</v>
       </c>
-      <c r="AC80">
-        <v>1.75</v>
-      </c>
-      <c r="AD80">
-        <v>0</v>
-      </c>
-      <c r="AE80">
-        <v>0</v>
-      </c>
-      <c r="AF80">
-        <v>0</v>
-      </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH80">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI80">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ80" t="s">
         <v>248</v>
@@ -10415,16 +10415,16 @@
         <v>66</v>
       </c>
       <c r="C81" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D81" t="s">
         <v>90</v>
       </c>
       <c r="E81" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="F81" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -10442,76 +10442,76 @@
         <v>247</v>
       </c>
       <c r="L81">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="M81">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="N81">
-        <v>4.2</v>
+        <v>2.76</v>
       </c>
       <c r="O81">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="P81">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="Q81">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R81">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S81">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T81">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U81">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V81">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W81">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X81">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y81">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z81">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA81">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB81">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC81">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AD81">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE81">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF81">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG81">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH81">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI81">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ81" t="s">
         <v>248</v>
@@ -10531,7 +10531,7 @@
         <v>67</v>
       </c>
       <c r="C82" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D82" t="s">
         <v>90</v>
@@ -10558,13 +10558,13 @@
         <v>247</v>
       </c>
       <c r="L82">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="M82">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="N82">
-        <v>2.8</v>
+        <v>3.07</v>
       </c>
       <c r="O82">
         <v>1.73</v>
@@ -10576,58 +10576,58 @@
         <v>2.2</v>
       </c>
       <c r="R82">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S82">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="T82">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="U82">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="V82">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="W82">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z82">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AA82">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AB82">
+        <v>1.73</v>
+      </c>
+      <c r="AC82">
+        <v>2</v>
+      </c>
+      <c r="AD82">
+        <v>2.76</v>
+      </c>
+      <c r="AE82">
+        <v>1.38</v>
+      </c>
+      <c r="AF82">
         <v>1.6</v>
       </c>
-      <c r="AC82">
+      <c r="AG82">
         <v>2.2</v>
       </c>
-      <c r="AD82">
-        <v>2.43</v>
-      </c>
-      <c r="AE82">
-        <v>1.48</v>
-      </c>
-      <c r="AF82">
-        <v>1.53</v>
-      </c>
-      <c r="AG82">
-        <v>2.38</v>
-      </c>
       <c r="AH82">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AI82">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AJ82" t="s">
         <v>248</v>
@@ -10647,7 +10647,7 @@
         <v>68</v>
       </c>
       <c r="C83" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D83" t="s">
         <v>90</v>
@@ -10674,22 +10674,22 @@
         <v>247</v>
       </c>
       <c r="L83">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="M83">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N83">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="O83">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="P83">
         <v>0</v>
       </c>
       <c r="Q83">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="R83">
         <v>1.22</v>
@@ -10698,16 +10698,16 @@
         <v>3.8</v>
       </c>
       <c r="T83">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U83">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="V83">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="W83">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X83">
         <v>0</v>
@@ -10716,34 +10716,34 @@
         <v>0</v>
       </c>
       <c r="Z83">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AA83">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AB83">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AC83">
+        <v>2.61</v>
+      </c>
+      <c r="AD83">
+        <v>2.05</v>
+      </c>
+      <c r="AE83">
+        <v>1.7</v>
+      </c>
+      <c r="AF83">
+        <v>1.38</v>
+      </c>
+      <c r="AG83">
         <v>2.8</v>
       </c>
-      <c r="AD83">
-        <v>1.96</v>
-      </c>
-      <c r="AE83">
-        <v>1.74</v>
-      </c>
-      <c r="AF83">
-        <v>1.42</v>
-      </c>
-      <c r="AG83">
-        <v>2.62</v>
-      </c>
       <c r="AH83">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AI83">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AJ83" t="s">
         <v>248</v>
@@ -10763,7 +10763,7 @@
         <v>68</v>
       </c>
       <c r="C84" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D84" t="s">
         <v>90</v>
@@ -10790,40 +10790,40 @@
         <v>247</v>
       </c>
       <c r="L84">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="M84">
+        <v>3.8</v>
+      </c>
+      <c r="N84">
         <v>3.6</v>
       </c>
-      <c r="N84">
-        <v>2.55</v>
-      </c>
       <c r="O84">
+        <v>1.53</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>2.5</v>
+      </c>
+      <c r="R84">
+        <v>1.22</v>
+      </c>
+      <c r="S84">
+        <v>3.8</v>
+      </c>
+      <c r="T84">
+        <v>2</v>
+      </c>
+      <c r="U84">
         <v>1.73</v>
       </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
-      <c r="Q84">
-        <v>2.05</v>
-      </c>
-      <c r="R84">
-        <v>1.25</v>
-      </c>
-      <c r="S84">
-        <v>3.6</v>
-      </c>
-      <c r="T84">
-        <v>2.1</v>
-      </c>
-      <c r="U84">
-        <v>1.65</v>
-      </c>
       <c r="V84">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="W84">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X84">
         <v>0</v>
@@ -10832,34 +10832,34 @@
         <v>0</v>
       </c>
       <c r="Z84">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AA84">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AB84">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AC84">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="AD84">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE84">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AF84">
         <v>1.42</v>
       </c>
       <c r="AG84">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AH84">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="AI84">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AJ84" t="s">
         <v>248</v>

--- a/jogos_2025-07-20.xlsx
+++ b/jogos_2025-07-20.xlsx
@@ -232,12 +232,12 @@
     <t>Japan J1 League</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
@@ -256,12 +256,12 @@
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
@@ -271,12 +271,12 @@
     <t>Chile Primera B</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -292,12 +292,12 @@
     <t>Sacramento Republic</t>
   </si>
   <si>
+    <t>APIA Leichhardt Tigers</t>
+  </si>
+  <si>
     <t>Central Coast II</t>
   </si>
   <si>
-    <t>APIA Leichhardt Tigers</t>
-  </si>
-  <si>
     <t>Sydney Olympic</t>
   </si>
   <si>
@@ -310,30 +310,30 @@
     <t>Shimizu S-Pulse</t>
   </si>
   <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
+  </si>
+  <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
+    <t>Fagiano Okayama</t>
+  </si>
+  <si>
+    <t>Yokohama F. Marinos</t>
+  </si>
+  <si>
     <t>Gamba Osaka</t>
   </si>
   <si>
     <t>Albirex Niigata</t>
   </si>
   <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
-    <t>Yokohama F. Marinos</t>
-  </si>
-  <si>
-    <t>Fagiano Okayama</t>
-  </si>
-  <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
     <t>Varberg</t>
   </si>
   <si>
@@ -346,105 +346,105 @@
     <t>Nanjing City</t>
   </si>
   <si>
+    <t>Mjällby</t>
+  </si>
+  <si>
     <t>Sirius</t>
   </si>
   <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
     <t>Vålerenga</t>
   </si>
   <si>
     <t>Kyzyl-Zhar</t>
   </si>
   <si>
+    <t>SJK</t>
+  </si>
+  <si>
     <t>Kalmar</t>
   </si>
   <si>
-    <t>SJK</t>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Nõmme Kalju</t>
   </si>
   <si>
     <t>Internacional</t>
   </si>
   <si>
-    <t>Nõmme Kalju</t>
-  </si>
-  <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
     <t>Hammarby</t>
   </si>
   <si>
     <t>Halmstad</t>
   </si>
   <si>
+    <t>Platense</t>
+  </si>
+  <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>Tigre</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Independiente</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
+  </si>
+  <si>
+    <t>Newell's Old Boys</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
+    <t>Atlético Tucumán</t>
+  </si>
+  <si>
     <t>Lanús</t>
   </si>
   <si>
     <t>Barracas Central</t>
   </si>
   <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
     <t>Instituto</t>
   </si>
   <si>
-    <t>Independiente</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Atlético Tucumán</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
-    <t>Newell's Old Boys</t>
-  </si>
-  <si>
-    <t>Defensa y Justicia</t>
-  </si>
-  <si>
-    <t>Godoy Cruz</t>
-  </si>
-  <si>
-    <t>Platense</t>
-  </si>
-  <si>
     <t>Boca Juniors</t>
   </si>
   <si>
-    <t>San Lorenzo</t>
-  </si>
-  <si>
-    <t>Estudiantes</t>
-  </si>
-  <si>
-    <t>Tigre</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
     <t>HJK</t>
   </si>
   <si>
     <t>Jaro</t>
   </si>
   <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
     <t>Paide</t>
   </si>
   <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
     <t>Audax Italiano</t>
   </si>
   <si>
@@ -454,30 +454,30 @@
     <t>HamKam</t>
   </si>
   <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Ñublense</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>New England II</t>
+  </si>
+  <si>
+    <t>Valour FC</t>
+  </si>
+  <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>New England II</t>
-  </si>
-  <si>
     <t>Vitória</t>
   </si>
   <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Valour FC</t>
-  </si>
-  <si>
-    <t>Ñublense</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
@@ -493,18 +493,18 @@
     <t>Palmeiras</t>
   </si>
   <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
     <t>América Mineiro</t>
   </si>
   <si>
-    <t>Deportes Temuco</t>
+    <t>Brusque</t>
   </si>
   <si>
     <t>Ypiranga Erechim</t>
   </si>
   <si>
-    <t>Brusque</t>
-  </si>
-  <si>
     <t>Flamengo</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>Lexington</t>
   </si>
   <si>
+    <t>Sydney United</t>
+  </si>
+  <si>
     <t>St. George Saints</t>
   </si>
   <si>
-    <t>Sydney United</t>
-  </si>
-  <si>
     <t>Mt Druitt Town</t>
   </si>
   <si>
@@ -544,30 +544,30 @@
     <t>Yokohama</t>
   </si>
   <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
+    <t>Incheon United</t>
+  </si>
+  <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
+    <t>Vissel Kobe</t>
+  </si>
+  <si>
+    <t>Nagoya Grampus</t>
+  </si>
+  <si>
     <t>Kawasaki Frontale</t>
   </si>
   <si>
     <t>Sanfrecce Hiroshima</t>
   </si>
   <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Incheon United</t>
-  </si>
-  <si>
-    <t>Cheonan City</t>
-  </si>
-  <si>
-    <t>Nagoya Grampus</t>
-  </si>
-  <si>
-    <t>Vissel Kobe</t>
-  </si>
-  <si>
-    <t>Ulsan</t>
-  </si>
-  <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
@@ -580,105 +580,105 @@
     <t>Guangxi Baoyun</t>
   </si>
   <si>
+    <t>AIK</t>
+  </si>
+  <si>
     <t>IFK Göteborg</t>
   </si>
   <si>
-    <t>AIK</t>
-  </si>
-  <si>
     <t>Haugesund</t>
   </si>
   <si>
     <t>Atyrau</t>
   </si>
   <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
     <t>Brage</t>
   </si>
   <si>
-    <t>Gnistan</t>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
+    <t>Tallinna Kalev</t>
   </si>
   <si>
     <t>Ceará</t>
   </si>
   <si>
-    <t>Tallinna Kalev</t>
-  </si>
-  <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
     <t>Häcken</t>
   </si>
   <si>
+    <t>Vélez Sarsfield</t>
+  </si>
+  <si>
+    <t>Gimnasia La Plata</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Argentinos Juniors</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Huracán</t>
+  </si>
+  <si>
+    <t>Talleres Córdoba</t>
+  </si>
+  <si>
+    <t>Sarmiento</t>
+  </si>
+  <si>
+    <t>Banfield</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
+    <t>Central Córdoba SdE</t>
+  </si>
+  <si>
     <t>Rosario Central</t>
   </si>
   <si>
     <t>Independiente Rivadavia</t>
   </si>
   <si>
+    <t>Racing Club</t>
+  </si>
+  <si>
     <t>River Plate</t>
   </si>
   <si>
-    <t>Talleres Córdoba</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Central Córdoba SdE</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Racing Club</t>
-  </si>
-  <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Banfield</t>
-  </si>
-  <si>
-    <t>Aldosivi</t>
-  </si>
-  <si>
-    <t>Sarmiento</t>
-  </si>
-  <si>
-    <t>Vélez Sarsfield</t>
-  </si>
-  <si>
     <t>Unión Santa Fe</t>
   </si>
   <si>
-    <t>Gimnasia La Plata</t>
-  </si>
-  <si>
-    <t>Huracán</t>
-  </si>
-  <si>
-    <t>Argentinos Juniors</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
     <t>Oulu</t>
   </si>
   <si>
     <t>Ilves</t>
   </si>
   <si>
+    <t>Vaprus</t>
+  </si>
+  <si>
     <t>Trans</t>
   </si>
   <si>
-    <t>Vaprus</t>
-  </si>
-  <si>
     <t>Universidad Católica</t>
   </si>
   <si>
@@ -688,30 +688,30 @@
     <t>Fredrikstad</t>
   </si>
   <si>
+    <t>Univ. Concepción</t>
+  </si>
+  <si>
+    <t>Universidad Chile</t>
+  </si>
+  <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
+    <t>Orlando City II</t>
+  </si>
+  <si>
+    <t>Cavalry FC</t>
+  </si>
+  <si>
     <t>Chicago Fire II</t>
   </si>
   <si>
-    <t>Juventude</t>
-  </si>
-  <si>
-    <t>Orlando City II</t>
-  </si>
-  <si>
     <t>Bragantino</t>
   </si>
   <si>
-    <t>Botafogo SP</t>
-  </si>
-  <si>
-    <t>Cavalry FC</t>
-  </si>
-  <si>
-    <t>Universidad Chile</t>
-  </si>
-  <si>
-    <t>Univ. Concepción</t>
-  </si>
-  <si>
     <t>Valur</t>
   </si>
   <si>
@@ -727,16 +727,16 @@
     <t>Atlético Mineiro</t>
   </si>
   <si>
+    <t>Santiago Morning</t>
+  </si>
+  <si>
     <t>Chapecoense</t>
   </si>
   <si>
-    <t>Santiago Morning</t>
+    <t>Retrô</t>
   </si>
   <si>
     <t>São Bernardo</t>
-  </si>
-  <si>
-    <t>Retrô</t>
   </si>
   <si>
     <t>Fluminense</t>
@@ -1296,58 +1296,58 @@
         <v>3</v>
       </c>
       <c r="R2">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S2">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="T2">
         <v>2.8</v>
       </c>
       <c r="U2">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V2">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W2">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z2">
         <v>1.33</v>
       </c>
       <c r="AA2">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AB2">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC2">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AD2">
         <v>3.4</v>
       </c>
       <c r="AE2">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF2">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH2">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="AI2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AJ2" t="s">
         <v>248</v>
@@ -1394,76 +1394,76 @@
         <v>247</v>
       </c>
       <c r="L3">
-        <v>2.95</v>
+        <v>1.52</v>
       </c>
       <c r="M3">
-        <v>3.6</v>
+        <v>4.27</v>
       </c>
       <c r="N3">
-        <v>2.02</v>
+        <v>4.77</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>18.25</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AB3">
+        <v>1.47</v>
+      </c>
+      <c r="AC3">
+        <v>2.35</v>
+      </c>
+      <c r="AD3">
+        <v>2.35</v>
+      </c>
+      <c r="AE3">
+        <v>1.54</v>
+      </c>
+      <c r="AF3">
         <v>1.6</v>
       </c>
-      <c r="AC3">
-        <v>2.3</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ3" t="s">
         <v>248</v>
@@ -1510,76 +1510,76 @@
         <v>247</v>
       </c>
       <c r="L4">
-        <v>1.61</v>
+        <v>4.27</v>
       </c>
       <c r="M4">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="N4">
-        <v>4.1</v>
+        <v>1.62</v>
       </c>
       <c r="O4">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>18.25</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
         <v>1.6</v>
       </c>
-      <c r="V4">
-        <v>4.75</v>
-      </c>
-      <c r="W4">
-        <v>1.15</v>
-      </c>
-      <c r="X4">
-        <v>1</v>
-      </c>
-      <c r="Y4">
-        <v>12</v>
-      </c>
-      <c r="Z4">
-        <v>1.13</v>
-      </c>
-      <c r="AA4">
-        <v>5.6</v>
-      </c>
-      <c r="AB4">
-        <v>1.5</v>
-      </c>
       <c r="AC4">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD4">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="s">
         <v>248</v>
@@ -1626,13 +1626,13 @@
         <v>247</v>
       </c>
       <c r="L5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M5">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="N5">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="O5">
         <v>1.29</v>
@@ -1644,58 +1644,58 @@
         <v>3.5</v>
       </c>
       <c r="R5">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S5">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="T5">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="U5">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="V5">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="W5">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z5">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AA5">
-        <v>5.75</v>
+        <v>4.95</v>
       </c>
       <c r="AB5">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AC5">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="AD5">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AE5">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AF5">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH5">
-        <v>2.97</v>
+        <v>3.42</v>
       </c>
       <c r="AI5">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AJ5" t="s">
         <v>248</v>
@@ -2063,7 +2063,7 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
         <v>90</v>
@@ -2090,76 +2090,76 @@
         <v>247</v>
       </c>
       <c r="L9">
-        <v>2.47</v>
+        <v>2.19</v>
       </c>
       <c r="M9">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="N9">
-        <v>2.47</v>
+        <v>2.91</v>
       </c>
       <c r="O9">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="P9">
-        <v>10</v>
+        <v>7.75</v>
       </c>
       <c r="Q9">
+        <v>2.38</v>
+      </c>
+      <c r="R9">
+        <v>1.44</v>
+      </c>
+      <c r="S9">
+        <v>2.63</v>
+      </c>
+      <c r="T9">
+        <v>3.25</v>
+      </c>
+      <c r="U9">
+        <v>1.33</v>
+      </c>
+      <c r="V9">
+        <v>9</v>
+      </c>
+      <c r="W9">
+        <v>1.07</v>
+      </c>
+      <c r="X9">
+        <v>1.08</v>
+      </c>
+      <c r="Y9">
+        <v>7.5</v>
+      </c>
+      <c r="Z9">
+        <v>1.4</v>
+      </c>
+      <c r="AA9">
+        <v>2.9</v>
+      </c>
+      <c r="AB9">
+        <v>2.02</v>
+      </c>
+      <c r="AC9">
+        <v>1.7</v>
+      </c>
+      <c r="AD9">
+        <v>4.2</v>
+      </c>
+      <c r="AE9">
+        <v>1.22</v>
+      </c>
+      <c r="AF9">
         <v>1.83</v>
       </c>
-      <c r="R9">
-        <v>1.33</v>
-      </c>
-      <c r="S9">
-        <v>3.25</v>
-      </c>
-      <c r="T9">
-        <v>2.63</v>
-      </c>
-      <c r="U9">
-        <v>1.44</v>
-      </c>
-      <c r="V9">
-        <v>6.5</v>
-      </c>
-      <c r="W9">
-        <v>1.11</v>
-      </c>
-      <c r="X9">
-        <v>1.05</v>
-      </c>
-      <c r="Y9">
-        <v>9.5</v>
-      </c>
-      <c r="Z9">
-        <v>1.25</v>
-      </c>
-      <c r="AA9">
-        <v>3.7</v>
-      </c>
-      <c r="AB9">
-        <v>1.73</v>
-      </c>
-      <c r="AC9">
-        <v>1.98</v>
-      </c>
-      <c r="AD9">
-        <v>3</v>
-      </c>
-      <c r="AE9">
-        <v>1.38</v>
-      </c>
-      <c r="AF9">
-        <v>1.62</v>
-      </c>
       <c r="AG9">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AH9">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AI9">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AJ9" t="s">
         <v>248</v>
@@ -2179,7 +2179,7 @@
         <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
         <v>90</v>
@@ -2206,76 +2206,76 @@
         <v>247</v>
       </c>
       <c r="L10">
-        <v>3.99</v>
+        <v>5.5</v>
       </c>
       <c r="M10">
-        <v>3.36</v>
+        <v>4.1</v>
       </c>
       <c r="N10">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="O10">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>8.75</v>
+        <v>15.25</v>
       </c>
       <c r="Q10">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="R10">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S10">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T10">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="U10">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="Z10">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AA10">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="AB10">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AC10">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AD10">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="AE10">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AF10">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH10">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="AI10">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AJ10" t="s">
         <v>248</v>
@@ -2295,7 +2295,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
         <v>90</v>
@@ -2411,7 +2411,7 @@
         <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
         <v>90</v>
@@ -2438,76 +2438,76 @@
         <v>247</v>
       </c>
       <c r="L12">
-        <v>5.5</v>
+        <v>2.18</v>
       </c>
       <c r="M12">
-        <v>4.1</v>
+        <v>3.12</v>
       </c>
       <c r="N12">
-        <v>1.44</v>
+        <v>2.93</v>
       </c>
       <c r="O12">
-        <v>3.2</v>
+        <v>1.79</v>
       </c>
       <c r="P12">
-        <v>15.25</v>
+        <v>10.5</v>
       </c>
       <c r="Q12">
+        <v>2.16</v>
+      </c>
+      <c r="R12">
+        <v>1.4</v>
+      </c>
+      <c r="S12">
+        <v>2.8</v>
+      </c>
+      <c r="T12">
+        <v>2.9</v>
+      </c>
+      <c r="U12">
         <v>1.36</v>
       </c>
-      <c r="R12">
-        <v>1.3</v>
-      </c>
-      <c r="S12">
-        <v>3.25</v>
-      </c>
-      <c r="T12">
-        <v>2.45</v>
-      </c>
-      <c r="U12">
-        <v>1.5</v>
-      </c>
       <c r="V12">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="W12">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z12">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AA12">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AB12">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AD12">
-        <v>2.59</v>
+        <v>3.58</v>
       </c>
       <c r="AE12">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="AF12">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH12">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="AI12">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AJ12" t="s">
         <v>248</v>
@@ -2527,7 +2527,7 @@
         <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
         <v>90</v>
@@ -2554,76 +2554,76 @@
         <v>247</v>
       </c>
       <c r="L13">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="M13">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="N13">
-        <v>2.93</v>
+        <v>1.68</v>
       </c>
       <c r="O13">
-        <v>1.79</v>
+        <v>2.85</v>
       </c>
       <c r="P13">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q13">
-        <v>2.16</v>
+        <v>1.58</v>
       </c>
       <c r="R13">
+        <v>1.46</v>
+      </c>
+      <c r="S13">
+        <v>2.5</v>
+      </c>
+      <c r="T13">
+        <v>3.1</v>
+      </c>
+      <c r="U13">
+        <v>1.31</v>
+      </c>
+      <c r="V13">
+        <v>8.75</v>
+      </c>
+      <c r="W13">
+        <v>1.06</v>
+      </c>
+      <c r="X13">
+        <v>1.08</v>
+      </c>
+      <c r="Y13">
+        <v>7.5</v>
+      </c>
+      <c r="Z13">
         <v>1.4</v>
       </c>
-      <c r="S13">
-        <v>2.8</v>
-      </c>
-      <c r="T13">
-        <v>2.9</v>
-      </c>
-      <c r="U13">
-        <v>1.36</v>
-      </c>
-      <c r="V13">
-        <v>8.5</v>
-      </c>
-      <c r="W13">
-        <v>1.07</v>
-      </c>
-      <c r="X13">
-        <v>1.03</v>
-      </c>
-      <c r="Y13">
-        <v>9</v>
-      </c>
-      <c r="Z13">
-        <v>1.28</v>
-      </c>
       <c r="AA13">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="AB13">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="AC13">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AD13">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AE13">
         <v>1.21</v>
       </c>
       <c r="AF13">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AG13">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AH13">
-        <v>7.6</v>
+        <v>8.25</v>
       </c>
       <c r="AI13">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AJ13" t="s">
         <v>248</v>
@@ -2786,76 +2786,76 @@
         <v>247</v>
       </c>
       <c r="L15">
-        <v>4.6</v>
+        <v>2.47</v>
       </c>
       <c r="M15">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="N15">
-        <v>1.68</v>
+        <v>2.47</v>
       </c>
       <c r="O15">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="P15">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="R15">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="S15">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="T15">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="U15">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="V15">
-        <v>8.75</v>
+        <v>6.5</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z15">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AA15">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="AB15">
-        <v>2.13</v>
+        <v>1.76</v>
       </c>
       <c r="AC15">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="AD15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE15">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AF15">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AH15">
-        <v>8.25</v>
+        <v>5.5</v>
       </c>
       <c r="AI15">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AJ15" t="s">
         <v>248</v>
@@ -2875,7 +2875,7 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
         <v>90</v>
@@ -2902,76 +2902,76 @@
         <v>247</v>
       </c>
       <c r="L16">
-        <v>2.19</v>
+        <v>3.99</v>
       </c>
       <c r="M16">
-        <v>3.13</v>
+        <v>3.36</v>
       </c>
       <c r="N16">
-        <v>2.91</v>
+        <v>1.75</v>
       </c>
       <c r="O16">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="P16">
-        <v>7.75</v>
+        <v>8.75</v>
       </c>
       <c r="Q16">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="R16">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S16">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T16">
+        <v>2.75</v>
+      </c>
+      <c r="U16">
+        <v>1.4</v>
+      </c>
+      <c r="V16">
+        <v>8</v>
+      </c>
+      <c r="W16">
+        <v>1.08</v>
+      </c>
+      <c r="X16">
+        <v>1.06</v>
+      </c>
+      <c r="Y16">
+        <v>8.5</v>
+      </c>
+      <c r="Z16">
+        <v>1.33</v>
+      </c>
+      <c r="AA16">
         <v>3.25</v>
       </c>
-      <c r="U16">
-        <v>1.33</v>
-      </c>
-      <c r="V16">
-        <v>9</v>
-      </c>
-      <c r="W16">
-        <v>1.07</v>
-      </c>
-      <c r="X16">
-        <v>1.08</v>
-      </c>
-      <c r="Y16">
-        <v>7.5</v>
-      </c>
-      <c r="Z16">
-        <v>1.4</v>
-      </c>
-      <c r="AA16">
-        <v>2.9</v>
-      </c>
       <c r="AB16">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AC16">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AD16">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AE16">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AF16">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG16">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI16">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AJ16" t="s">
         <v>248</v>
@@ -3158,13 +3158,13 @@
         <v>2.62</v>
       </c>
       <c r="T18">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="U18">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V18">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="W18">
         <v>1.07</v>
@@ -3176,16 +3176,16 @@
         <v>8</v>
       </c>
       <c r="Z18">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA18">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AB18">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AC18">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AD18">
         <v>3.9</v>
@@ -3194,10 +3194,10 @@
         <v>1.22</v>
       </c>
       <c r="AF18">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AG18">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AH18">
         <v>8.5</v>
@@ -3268,13 +3268,13 @@
         <v>2.38</v>
       </c>
       <c r="R19">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S19">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U19">
         <v>1.33</v>
@@ -3283,34 +3283,34 @@
         <v>7.5</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="Z19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA19">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AB19">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AC19">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AD19">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AE19">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF19">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG19">
         <v>1.91</v>
@@ -3390,10 +3390,10 @@
         <v>2.8</v>
       </c>
       <c r="T20">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U20">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V20">
         <v>6.5</v>
@@ -3414,10 +3414,10 @@
         <v>3.25</v>
       </c>
       <c r="AB20">
+        <v>1.96</v>
+      </c>
+      <c r="AC20">
         <v>1.75</v>
-      </c>
-      <c r="AC20">
-        <v>1.94</v>
       </c>
       <c r="AD20">
         <v>3.5</v>
@@ -3432,7 +3432,7 @@
         <v>1.75</v>
       </c>
       <c r="AH20">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AI20">
         <v>1.1</v>
@@ -3482,76 +3482,76 @@
         <v>247</v>
       </c>
       <c r="L21">
-        <v>2.49</v>
+        <v>2.03</v>
       </c>
       <c r="M21">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="N21">
+        <v>3.06</v>
+      </c>
+      <c r="O21">
+        <v>1.67</v>
+      </c>
+      <c r="P21">
+        <v>9</v>
+      </c>
+      <c r="Q21">
         <v>2.4</v>
       </c>
-      <c r="O21">
+      <c r="R21">
+        <v>1.44</v>
+      </c>
+      <c r="S21">
+        <v>2.63</v>
+      </c>
+      <c r="T21">
+        <v>3.25</v>
+      </c>
+      <c r="U21">
+        <v>1.33</v>
+      </c>
+      <c r="V21">
+        <v>9</v>
+      </c>
+      <c r="W21">
+        <v>1.07</v>
+      </c>
+      <c r="X21">
+        <v>1.06</v>
+      </c>
+      <c r="Y21">
+        <v>9</v>
+      </c>
+      <c r="Z21">
+        <v>1.38</v>
+      </c>
+      <c r="AA21">
+        <v>3.1</v>
+      </c>
+      <c r="AB21">
+        <v>1.85</v>
+      </c>
+      <c r="AC21">
+        <v>1.85</v>
+      </c>
+      <c r="AD21">
+        <v>3.95</v>
+      </c>
+      <c r="AE21">
+        <v>1.25</v>
+      </c>
+      <c r="AF21">
+        <v>1.95</v>
+      </c>
+      <c r="AG21">
         <v>1.8</v>
       </c>
-      <c r="P21">
-        <v>10</v>
-      </c>
-      <c r="Q21">
-        <v>2.1</v>
-      </c>
-      <c r="R21">
-        <v>1.33</v>
-      </c>
-      <c r="S21">
-        <v>3.25</v>
-      </c>
-      <c r="T21">
-        <v>2.5</v>
-      </c>
-      <c r="U21">
-        <v>1.5</v>
-      </c>
-      <c r="V21">
-        <v>6</v>
-      </c>
-      <c r="W21">
-        <v>1.13</v>
-      </c>
-      <c r="X21">
-        <v>1.05</v>
-      </c>
-      <c r="Y21">
-        <v>10</v>
-      </c>
-      <c r="Z21">
-        <v>1.25</v>
-      </c>
-      <c r="AA21">
-        <v>4</v>
-      </c>
-      <c r="AB21">
-        <v>1.67</v>
-      </c>
-      <c r="AC21">
-        <v>2.07</v>
-      </c>
-      <c r="AD21">
-        <v>2.8</v>
-      </c>
-      <c r="AE21">
-        <v>1.45</v>
-      </c>
-      <c r="AF21">
-        <v>1.57</v>
-      </c>
-      <c r="AG21">
-        <v>2.25</v>
-      </c>
       <c r="AH21">
-        <v>5.25</v>
+        <v>8</v>
       </c>
       <c r="AI21">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AJ21" t="s">
         <v>248</v>
@@ -3598,76 +3598,76 @@
         <v>247</v>
       </c>
       <c r="L22">
-        <v>2.03</v>
+        <v>2.49</v>
       </c>
       <c r="M22">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="N22">
-        <v>3.06</v>
+        <v>2.4</v>
       </c>
       <c r="O22">
+        <v>1.8</v>
+      </c>
+      <c r="P22">
+        <v>10</v>
+      </c>
+      <c r="Q22">
+        <v>2.1</v>
+      </c>
+      <c r="R22">
+        <v>1.33</v>
+      </c>
+      <c r="S22">
+        <v>3.25</v>
+      </c>
+      <c r="T22">
+        <v>2.5</v>
+      </c>
+      <c r="U22">
+        <v>1.5</v>
+      </c>
+      <c r="V22">
+        <v>6</v>
+      </c>
+      <c r="W22">
+        <v>1.13</v>
+      </c>
+      <c r="X22">
+        <v>1.05</v>
+      </c>
+      <c r="Y22">
+        <v>10</v>
+      </c>
+      <c r="Z22">
+        <v>1.25</v>
+      </c>
+      <c r="AA22">
+        <v>4</v>
+      </c>
+      <c r="AB22">
         <v>1.67</v>
       </c>
-      <c r="P22">
-        <v>9</v>
-      </c>
-      <c r="Q22">
-        <v>2.4</v>
-      </c>
-      <c r="R22">
-        <v>1.44</v>
-      </c>
-      <c r="S22">
-        <v>2.63</v>
-      </c>
-      <c r="T22">
-        <v>3.25</v>
-      </c>
-      <c r="U22">
-        <v>1.33</v>
-      </c>
-      <c r="V22">
-        <v>9</v>
-      </c>
-      <c r="W22">
-        <v>1.07</v>
-      </c>
-      <c r="X22">
-        <v>1.06</v>
-      </c>
-      <c r="Y22">
-        <v>9</v>
-      </c>
-      <c r="Z22">
-        <v>1.38</v>
-      </c>
-      <c r="AA22">
-        <v>3.1</v>
-      </c>
-      <c r="AB22">
-        <v>1.85</v>
-      </c>
       <c r="AC22">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AD22">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="AE22">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AF22">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AG22">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH22">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="AI22">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AJ22" t="s">
         <v>248</v>
@@ -3762,10 +3762,10 @@
         <v>5.25</v>
       </c>
       <c r="AB23">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AC23">
-        <v>2.35</v>
+        <v>2.82</v>
       </c>
       <c r="AD23">
         <v>2.1</v>
@@ -3830,13 +3830,13 @@
         <v>247</v>
       </c>
       <c r="L24">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="M24">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="N24">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="O24">
         <v>1.39</v>
@@ -3848,58 +3848,58 @@
         <v>3.52</v>
       </c>
       <c r="R24">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S24">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="T24">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="U24">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V24">
+        <v>8</v>
+      </c>
+      <c r="W24">
+        <v>1.05</v>
+      </c>
+      <c r="X24">
+        <v>1.06</v>
+      </c>
+      <c r="Y24">
+        <v>10</v>
+      </c>
+      <c r="Z24">
+        <v>1.3</v>
+      </c>
+      <c r="AA24">
+        <v>3.3</v>
+      </c>
+      <c r="AB24">
+        <v>1.9</v>
+      </c>
+      <c r="AC24">
+        <v>1.8</v>
+      </c>
+      <c r="AD24">
+        <v>3.4</v>
+      </c>
+      <c r="AE24">
+        <v>1.29</v>
+      </c>
+      <c r="AF24">
+        <v>1.85</v>
+      </c>
+      <c r="AG24">
+        <v>1.91</v>
+      </c>
+      <c r="AH24">
         <v>6.5</v>
       </c>
-      <c r="W24">
-        <v>1.08</v>
-      </c>
-      <c r="X24">
-        <v>1.02</v>
-      </c>
-      <c r="Y24">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z24">
-        <v>1.26</v>
-      </c>
-      <c r="AA24">
-        <v>3.22</v>
-      </c>
-      <c r="AB24">
-        <v>1.88</v>
-      </c>
-      <c r="AC24">
-        <v>1.88</v>
-      </c>
-      <c r="AD24">
-        <v>3.08</v>
-      </c>
-      <c r="AE24">
-        <v>1.28</v>
-      </c>
-      <c r="AF24">
-        <v>2</v>
-      </c>
-      <c r="AG24">
-        <v>1.73</v>
-      </c>
-      <c r="AH24">
-        <v>5.75</v>
-      </c>
       <c r="AI24">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AJ24" t="s">
         <v>248</v>
@@ -3919,7 +3919,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
         <v>90</v>
@@ -3946,76 +3946,76 @@
         <v>247</v>
       </c>
       <c r="L25">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="M25">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="N25">
-        <v>6.9</v>
+        <v>4.2</v>
       </c>
       <c r="O25">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="P25">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q25">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S25">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T25">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="U25">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="V25">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="W25">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AA25">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AB25">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AC25">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="AD25">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="AE25">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AF25">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="AG25">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="AH25">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AI25">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ25" t="s">
         <v>248</v>
@@ -4035,7 +4035,7 @@
         <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
         <v>90</v>
@@ -4062,76 +4062,76 @@
         <v>247</v>
       </c>
       <c r="L26">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="M26">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="N26">
-        <v>4.2</v>
+        <v>6.9</v>
       </c>
       <c r="O26">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="P26">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q26">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R26">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="S26">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="T26">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="U26">
+        <v>1.53</v>
+      </c>
+      <c r="V26">
+        <v>5.5</v>
+      </c>
+      <c r="W26">
+        <v>1.14</v>
+      </c>
+      <c r="X26">
+        <v>1.04</v>
+      </c>
+      <c r="Y26">
+        <v>11</v>
+      </c>
+      <c r="Z26">
+        <v>1.22</v>
+      </c>
+      <c r="AA26">
+        <v>4.33</v>
+      </c>
+      <c r="AB26">
         <v>1.6</v>
       </c>
-      <c r="V26">
-        <v>4.4</v>
-      </c>
-      <c r="W26">
-        <v>1.12</v>
-      </c>
-      <c r="X26">
-        <v>1.03</v>
-      </c>
-      <c r="Y26">
-        <v>17</v>
-      </c>
-      <c r="Z26">
-        <v>1.13</v>
-      </c>
-      <c r="AA26">
+      <c r="AC26">
+        <v>2.1</v>
+      </c>
+      <c r="AD26">
+        <v>2.65</v>
+      </c>
+      <c r="AE26">
+        <v>1.48</v>
+      </c>
+      <c r="AF26">
+        <v>1.91</v>
+      </c>
+      <c r="AG26">
+        <v>1.91</v>
+      </c>
+      <c r="AH26">
         <v>5</v>
       </c>
-      <c r="AB26">
-        <v>1.5</v>
-      </c>
-      <c r="AC26">
-        <v>2.4</v>
-      </c>
-      <c r="AD26">
-        <v>2.2</v>
-      </c>
-      <c r="AE26">
-        <v>1.55</v>
-      </c>
-      <c r="AF26">
-        <v>1.53</v>
-      </c>
-      <c r="AG26">
-        <v>2.45</v>
-      </c>
-      <c r="AH26">
-        <v>3.8</v>
-      </c>
       <c r="AI26">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ26" t="s">
         <v>248</v>
@@ -4178,76 +4178,76 @@
         <v>247</v>
       </c>
       <c r="L27">
-        <v>1.56</v>
+        <v>7</v>
       </c>
       <c r="M27">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="N27">
-        <v>6.4</v>
+        <v>1.25</v>
       </c>
       <c r="O27">
-        <v>1.44</v>
+        <v>4.33</v>
       </c>
       <c r="P27">
-        <v>7.25</v>
+        <v>22</v>
       </c>
       <c r="Q27">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="R27">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="S27">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="T27">
-        <v>3.2</v>
+        <v>1.93</v>
       </c>
       <c r="U27">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="W27">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="X27">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="Z27">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="AA27">
-        <v>2.74</v>
+        <v>6.05</v>
       </c>
       <c r="AB27">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="AC27">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD27">
-        <v>4.33</v>
+        <v>1.95</v>
       </c>
       <c r="AE27">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
       <c r="AF27">
-        <v>2.09</v>
+        <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AH27">
-        <v>9.5</v>
+        <v>3.1</v>
       </c>
       <c r="AI27">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="AJ27" t="s">
         <v>248</v>
@@ -4267,7 +4267,7 @@
         <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
         <v>90</v>
@@ -4312,34 +4312,34 @@
         <v>4</v>
       </c>
       <c r="R28">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S28">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="T28">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="U28">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="V28">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="W28">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Z28">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AB28">
         <v>1.29</v>
@@ -4357,13 +4357,13 @@
         <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AH28">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AI28">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AJ28" t="s">
         <v>248</v>
@@ -4410,76 +4410,76 @@
         <v>247</v>
       </c>
       <c r="L29">
-        <v>7</v>
+        <v>1.56</v>
       </c>
       <c r="M29">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="N29">
-        <v>1.25</v>
+        <v>6.4</v>
       </c>
       <c r="O29">
-        <v>4.33</v>
+        <v>1.44</v>
       </c>
       <c r="P29">
-        <v>22</v>
+        <v>7.25</v>
       </c>
       <c r="Q29">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="R29">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="S29">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="T29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U29">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="V29">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="W29">
+        <v>1.05</v>
+      </c>
+      <c r="X29">
+        <v>1.07</v>
+      </c>
+      <c r="Y29">
+        <v>7.5</v>
+      </c>
+      <c r="Z29">
+        <v>1.38</v>
+      </c>
+      <c r="AA29">
+        <v>2.8</v>
+      </c>
+      <c r="AB29">
+        <v>2.2</v>
+      </c>
+      <c r="AC29">
+        <v>1.59</v>
+      </c>
+      <c r="AD29">
+        <v>4</v>
+      </c>
+      <c r="AE29">
         <v>1.22</v>
       </c>
-      <c r="X29">
-        <v>1.01</v>
-      </c>
-      <c r="Y29">
-        <v>16.5</v>
-      </c>
-      <c r="Z29">
-        <v>1.07</v>
-      </c>
-      <c r="AA29">
-        <v>5.95</v>
-      </c>
-      <c r="AB29">
-        <v>1.4</v>
-      </c>
-      <c r="AC29">
-        <v>2.75</v>
-      </c>
-      <c r="AD29">
-        <v>1.95</v>
-      </c>
-      <c r="AE29">
-        <v>1.73</v>
-      </c>
       <c r="AF29">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AH29">
-        <v>3.2</v>
+        <v>10.5</v>
       </c>
       <c r="AI29">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AJ29" t="s">
         <v>248</v>
@@ -4963,7 +4963,7 @@
         <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D34" t="s">
         <v>90</v>
@@ -4990,76 +4990,76 @@
         <v>247</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI34">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ34" t="s">
         <v>248</v>
@@ -5195,7 +5195,7 @@
         <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D36" t="s">
         <v>90</v>
@@ -5222,76 +5222,76 @@
         <v>247</v>
       </c>
       <c r="L36">
-        <v>3.6</v>
+        <v>1.62</v>
       </c>
       <c r="M36">
-        <v>3.15</v>
+        <v>3.69</v>
       </c>
       <c r="N36">
-        <v>1.93</v>
+        <v>4.3</v>
       </c>
       <c r="O36">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="P36">
-        <v>7.9</v>
+        <v>12.5</v>
       </c>
       <c r="Q36">
-        <v>1.7</v>
+        <v>2.88</v>
       </c>
       <c r="R36">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="S36">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="T36">
-        <v>3.34</v>
+        <v>2.25</v>
       </c>
       <c r="U36">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="V36">
-        <v>9.1</v>
+        <v>5.5</v>
       </c>
       <c r="W36">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Z36">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AA36">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="AB36">
-        <v>2.32</v>
+        <v>1.6</v>
       </c>
       <c r="AC36">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AD36">
-        <v>4</v>
+        <v>2.35</v>
       </c>
       <c r="AE36">
+        <v>1.52</v>
+      </c>
+      <c r="AF36">
+        <v>1.67</v>
+      </c>
+      <c r="AG36">
+        <v>2.1</v>
+      </c>
+      <c r="AH36">
+        <v>4.5</v>
+      </c>
+      <c r="AI36">
         <v>1.2</v>
-      </c>
-      <c r="AF36">
-        <v>1.95</v>
-      </c>
-      <c r="AG36">
-        <v>1.73</v>
-      </c>
-      <c r="AH36">
-        <v>8</v>
-      </c>
-      <c r="AI36">
-        <v>1.05</v>
       </c>
       <c r="AJ36" t="s">
         <v>248</v>
@@ -5311,7 +5311,7 @@
         <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D37" t="s">
         <v>90</v>
@@ -5338,76 +5338,76 @@
         <v>247</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH37">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ37" t="s">
         <v>248</v>
@@ -5427,7 +5427,7 @@
         <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D38" t="s">
         <v>90</v>
@@ -5454,76 +5454,76 @@
         <v>247</v>
       </c>
       <c r="L38">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N38">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH38">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AI38">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="s">
         <v>248</v>
@@ -5659,7 +5659,7 @@
         <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D40" t="s">
         <v>90</v>
@@ -5686,76 +5686,76 @@
         <v>247</v>
       </c>
       <c r="L40">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M40">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N40">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH40">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AI40">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="s">
         <v>248</v>
@@ -5891,7 +5891,7 @@
         <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D42" t="s">
         <v>90</v>
@@ -5918,76 +5918,76 @@
         <v>247</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH42">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI42">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ42" t="s">
         <v>248</v>
@@ -6703,7 +6703,7 @@
         <v>51</v>
       </c>
       <c r="C49" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D49" t="s">
         <v>90</v>
@@ -6730,76 +6730,76 @@
         <v>247</v>
       </c>
       <c r="L49">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M49">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N49">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V49">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE49">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AF49">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH49">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI49">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="s">
         <v>248</v>
@@ -6864,16 +6864,16 @@
         <v>4</v>
       </c>
       <c r="R50">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S50">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T50">
         <v>2.2</v>
       </c>
       <c r="U50">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V50">
         <v>4.75</v>
@@ -6882,31 +6882,31 @@
         <v>1.17</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Z50">
         <v>1.15</v>
       </c>
       <c r="AA50">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AB50">
         <v>1.53</v>
       </c>
       <c r="AC50">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AD50">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AE50">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AF50">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG50">
         <v>2</v>
@@ -6983,31 +6983,31 @@
         <v>1.26</v>
       </c>
       <c r="S51">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="T51">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="U51">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V51">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W51">
         <v>1.08</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="Z51">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AA51">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AB51">
         <v>1.55</v>
@@ -7016,22 +7016,22 @@
         <v>2.2</v>
       </c>
       <c r="AD51">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AE51">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AF51">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG51">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH51">
         <v>4.2</v>
       </c>
       <c r="AI51">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AJ51" t="s">
         <v>248</v>
@@ -7051,7 +7051,7 @@
         <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D52" t="s">
         <v>90</v>
@@ -7078,76 +7078,76 @@
         <v>247</v>
       </c>
       <c r="L52">
+        <v>2.48</v>
+      </c>
+      <c r="M52">
+        <v>3.72</v>
+      </c>
+      <c r="N52">
+        <v>2.23</v>
+      </c>
+      <c r="O52">
         <v>2.1</v>
       </c>
-      <c r="M52">
-        <v>3.59</v>
-      </c>
-      <c r="N52">
-        <v>2.74</v>
-      </c>
-      <c r="O52">
-        <v>1.53</v>
-      </c>
       <c r="P52">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Q52">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="R52">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S52">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="T52">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="U52">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="V52">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W52">
         <v>1.12</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Z52">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AA52">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AB52">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AC52">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AD52">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="AE52">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AF52">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG52">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AH52">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="AI52">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AJ52" t="s">
         <v>248</v>
@@ -7167,7 +7167,7 @@
         <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D53" t="s">
         <v>90</v>
@@ -7194,76 +7194,76 @@
         <v>247</v>
       </c>
       <c r="L53">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="M53">
-        <v>3.72</v>
+        <v>3.59</v>
       </c>
       <c r="N53">
-        <v>2.23</v>
+        <v>2.74</v>
       </c>
       <c r="O53">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="P53">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Q53">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="R53">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S53">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="T53">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="U53">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="V53">
-        <v>6.8</v>
+        <v>6.05</v>
       </c>
       <c r="W53">
+        <v>1.15</v>
+      </c>
+      <c r="X53">
         <v>1.04</v>
       </c>
-      <c r="X53">
-        <v>1.01</v>
-      </c>
       <c r="Y53">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="Z53">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AA53">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AB53">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AC53">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="AD53">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AE53">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AF53">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG53">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AH53">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI53">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AJ53" t="s">
         <v>248</v>
@@ -7444,58 +7444,58 @@
         <v>3.25</v>
       </c>
       <c r="R55">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="S55">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="T55">
         <v>3.3</v>
       </c>
       <c r="U55">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V55">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W55">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X55">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y55">
         <v>6.5</v>
       </c>
       <c r="Z55">
+        <v>1.45</v>
+      </c>
+      <c r="AA55">
+        <v>2.6</v>
+      </c>
+      <c r="AB55">
+        <v>2.3</v>
+      </c>
+      <c r="AC55">
         <v>1.48</v>
       </c>
-      <c r="AA55">
-        <v>2.38</v>
-      </c>
-      <c r="AB55">
-        <v>2.35</v>
-      </c>
-      <c r="AC55">
-        <v>1.53</v>
-      </c>
       <c r="AD55">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="AE55">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF55">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG55">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH55">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI55">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AJ55" t="s">
         <v>248</v>
@@ -7637,10 +7637,10 @@
         <v>90</v>
       </c>
       <c r="E57" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="F57" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -7747,7 +7747,7 @@
         <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D58" t="s">
         <v>90</v>
@@ -7774,76 +7774,76 @@
         <v>247</v>
       </c>
       <c r="L58">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="M58">
-        <v>3.65</v>
+        <v>3.11</v>
       </c>
       <c r="N58">
+        <v>2.5</v>
+      </c>
+      <c r="O58">
+        <v>1.8</v>
+      </c>
+      <c r="P58">
+        <v>6.9</v>
+      </c>
+      <c r="Q58">
+        <v>2.5</v>
+      </c>
+      <c r="R58">
+        <v>1.45</v>
+      </c>
+      <c r="S58">
+        <v>2.55</v>
+      </c>
+      <c r="T58">
+        <v>3</v>
+      </c>
+      <c r="U58">
+        <v>1.33</v>
+      </c>
+      <c r="V58">
+        <v>8.4</v>
+      </c>
+      <c r="W58">
+        <v>1.04</v>
+      </c>
+      <c r="X58">
+        <v>1.04</v>
+      </c>
+      <c r="Y58">
+        <v>7</v>
+      </c>
+      <c r="Z58">
+        <v>1.42</v>
+      </c>
+      <c r="AA58">
         <v>2.75</v>
       </c>
-      <c r="O58">
+      <c r="AB58">
+        <v>2.2</v>
+      </c>
+      <c r="AC58">
+        <v>1.55</v>
+      </c>
+      <c r="AD58">
+        <v>4.2</v>
+      </c>
+      <c r="AE58">
+        <v>1.2</v>
+      </c>
+      <c r="AF58">
+        <v>2</v>
+      </c>
+      <c r="AG58">
         <v>1.73</v>
       </c>
-      <c r="P58">
-        <v>0</v>
-      </c>
-      <c r="Q58">
-        <v>2.2</v>
-      </c>
-      <c r="R58">
-        <v>0</v>
-      </c>
-      <c r="S58">
-        <v>0</v>
-      </c>
-      <c r="T58">
-        <v>0</v>
-      </c>
-      <c r="U58">
-        <v>0</v>
-      </c>
-      <c r="V58">
-        <v>0</v>
-      </c>
-      <c r="W58">
-        <v>0</v>
-      </c>
-      <c r="X58">
-        <v>0</v>
-      </c>
-      <c r="Y58">
-        <v>0</v>
-      </c>
-      <c r="Z58">
-        <v>0</v>
-      </c>
-      <c r="AA58">
-        <v>0</v>
-      </c>
-      <c r="AB58">
-        <v>1.5</v>
-      </c>
-      <c r="AC58">
-        <v>2.5</v>
-      </c>
-      <c r="AD58">
-        <v>0</v>
-      </c>
-      <c r="AE58">
-        <v>0</v>
-      </c>
-      <c r="AF58">
-        <v>0</v>
-      </c>
-      <c r="AG58">
-        <v>0</v>
-      </c>
       <c r="AH58">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI58">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ58" t="s">
         <v>248</v>
@@ -7863,7 +7863,7 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D59" t="s">
         <v>90</v>
@@ -7890,34 +7890,34 @@
         <v>247</v>
       </c>
       <c r="L59">
+        <v>3.8</v>
+      </c>
+      <c r="M59">
+        <v>3.3</v>
+      </c>
+      <c r="N59">
+        <v>2</v>
+      </c>
+      <c r="O59">
+        <v>2.5</v>
+      </c>
+      <c r="P59">
+        <v>9.5</v>
+      </c>
+      <c r="Q59">
+        <v>1.62</v>
+      </c>
+      <c r="R59">
+        <v>1.36</v>
+      </c>
+      <c r="S59">
+        <v>3</v>
+      </c>
+      <c r="T59">
+        <v>2.75</v>
+      </c>
+      <c r="U59">
         <v>1.4</v>
-      </c>
-      <c r="M59">
-        <v>3.75</v>
-      </c>
-      <c r="N59">
-        <v>7.2</v>
-      </c>
-      <c r="O59">
-        <v>1.22</v>
-      </c>
-      <c r="P59">
-        <v>8.5</v>
-      </c>
-      <c r="Q59">
-        <v>6</v>
-      </c>
-      <c r="R59">
-        <v>1.38</v>
-      </c>
-      <c r="S59">
-        <v>2.8</v>
-      </c>
-      <c r="T59">
-        <v>2.8</v>
-      </c>
-      <c r="U59">
-        <v>1.39</v>
       </c>
       <c r="V59">
         <v>7</v>
@@ -7929,34 +7929,34 @@
         <v>1.05</v>
       </c>
       <c r="Y59">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Z59">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AA59">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB59">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC59">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AD59">
         <v>3.2</v>
       </c>
       <c r="AE59">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AF59">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AG59">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="AH59">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AI59">
         <v>1.07</v>
@@ -8006,76 +8006,76 @@
         <v>247</v>
       </c>
       <c r="L60">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="M60">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="N60">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="O60">
+        <v>1.88</v>
+      </c>
+      <c r="P60">
+        <v>5.75</v>
+      </c>
+      <c r="Q60">
+        <v>2.4</v>
+      </c>
+      <c r="R60">
         <v>1.62</v>
       </c>
-      <c r="P60">
-        <v>0</v>
-      </c>
-      <c r="Q60">
+      <c r="S60">
+        <v>2.2</v>
+      </c>
+      <c r="T60">
+        <v>4.3</v>
+      </c>
+      <c r="U60">
+        <v>1.22</v>
+      </c>
+      <c r="V60">
+        <v>10</v>
+      </c>
+      <c r="W60">
+        <v>1.02</v>
+      </c>
+      <c r="X60">
+        <v>1.13</v>
+      </c>
+      <c r="Y60">
+        <v>5.75</v>
+      </c>
+      <c r="Z60">
+        <v>1.6</v>
+      </c>
+      <c r="AA60">
+        <v>2.25</v>
+      </c>
+      <c r="AB60">
+        <v>2.25</v>
+      </c>
+      <c r="AC60">
+        <v>1.5</v>
+      </c>
+      <c r="AD60">
+        <v>5.25</v>
+      </c>
+      <c r="AE60">
+        <v>1.13</v>
+      </c>
+      <c r="AF60">
         <v>2.3</v>
       </c>
-      <c r="R60">
-        <v>1.25</v>
-      </c>
-      <c r="S60">
-        <v>3.6</v>
-      </c>
-      <c r="T60">
-        <v>2.1</v>
-      </c>
-      <c r="U60">
-        <v>1.65</v>
-      </c>
-      <c r="V60">
-        <v>4.5</v>
-      </c>
-      <c r="W60">
-        <v>1.17</v>
-      </c>
-      <c r="X60">
-        <v>1</v>
-      </c>
-      <c r="Y60">
-        <v>12</v>
-      </c>
-      <c r="Z60">
-        <v>1.12</v>
-      </c>
-      <c r="AA60">
-        <v>4.75</v>
-      </c>
-      <c r="AB60">
-        <v>1.48</v>
-      </c>
-      <c r="AC60">
-        <v>2.5</v>
-      </c>
-      <c r="AD60">
-        <v>2.1</v>
-      </c>
-      <c r="AE60">
-        <v>1.65</v>
-      </c>
-      <c r="AF60">
-        <v>1.5</v>
-      </c>
       <c r="AG60">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="AH60">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="AI60">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AJ60" t="s">
         <v>248</v>
@@ -8095,7 +8095,7 @@
         <v>57</v>
       </c>
       <c r="C61" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D61" t="s">
         <v>90</v>
@@ -8122,76 +8122,76 @@
         <v>247</v>
       </c>
       <c r="L61">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="M61">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="N61">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="O61">
-        <v>2.3</v>
+        <v>1.22</v>
       </c>
       <c r="P61">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="Q61">
-        <v>1.91</v>
+        <v>6</v>
       </c>
       <c r="R61">
+        <v>1.37</v>
+      </c>
+      <c r="S61">
+        <v>3.12</v>
+      </c>
+      <c r="T61">
+        <v>2.83</v>
+      </c>
+      <c r="U61">
+        <v>1.43</v>
+      </c>
+      <c r="V61">
+        <v>6</v>
+      </c>
+      <c r="W61">
+        <v>1.09</v>
+      </c>
+      <c r="X61">
+        <v>1.02</v>
+      </c>
+      <c r="Y61">
+        <v>10</v>
+      </c>
+      <c r="Z61">
+        <v>1.25</v>
+      </c>
+      <c r="AA61">
+        <v>3.6</v>
+      </c>
+      <c r="AB61">
+        <v>1.95</v>
+      </c>
+      <c r="AC61">
+        <v>1.75</v>
+      </c>
+      <c r="AD61">
+        <v>3.8</v>
+      </c>
+      <c r="AE61">
+        <v>1.33</v>
+      </c>
+      <c r="AF61">
+        <v>2.4</v>
+      </c>
+      <c r="AG61">
         <v>1.5</v>
       </c>
-      <c r="S61">
-        <v>2.4</v>
-      </c>
-      <c r="T61">
-        <v>3.3</v>
-      </c>
-      <c r="U61">
-        <v>1.29</v>
-      </c>
-      <c r="V61">
-        <v>8</v>
-      </c>
-      <c r="W61">
-        <v>1.04</v>
-      </c>
-      <c r="X61">
-        <v>1.05</v>
-      </c>
-      <c r="Y61">
-        <v>6.9</v>
-      </c>
-      <c r="Z61">
-        <v>1.5</v>
-      </c>
-      <c r="AA61">
-        <v>2.45</v>
-      </c>
-      <c r="AB61">
-        <v>2.53</v>
-      </c>
-      <c r="AC61">
-        <v>1.53</v>
-      </c>
-      <c r="AD61">
-        <v>4.25</v>
-      </c>
-      <c r="AE61">
-        <v>1.18</v>
-      </c>
-      <c r="AF61">
-        <v>2</v>
-      </c>
-      <c r="AG61">
-        <v>1.73</v>
-      </c>
       <c r="AH61">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="AI61">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AJ61" t="s">
         <v>248</v>
@@ -8238,76 +8238,76 @@
         <v>247</v>
       </c>
       <c r="L62">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="M62">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="N62">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="O62">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="P62">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q62">
+        <v>2.3</v>
+      </c>
+      <c r="R62">
+        <v>1.25</v>
+      </c>
+      <c r="S62">
+        <v>3.6</v>
+      </c>
+      <c r="T62">
+        <v>2.2</v>
+      </c>
+      <c r="U62">
+        <v>1.6</v>
+      </c>
+      <c r="V62">
+        <v>4.75</v>
+      </c>
+      <c r="W62">
+        <v>1.15</v>
+      </c>
+      <c r="X62">
+        <v>1</v>
+      </c>
+      <c r="Y62">
+        <v>12</v>
+      </c>
+      <c r="Z62">
+        <v>1.15</v>
+      </c>
+      <c r="AA62">
+        <v>4.75</v>
+      </c>
+      <c r="AB62">
+        <v>1.5</v>
+      </c>
+      <c r="AC62">
         <v>2.4</v>
       </c>
-      <c r="R62">
-        <v>1.63</v>
-      </c>
-      <c r="S62">
-        <v>2.2</v>
-      </c>
-      <c r="T62">
-        <v>3.7</v>
-      </c>
-      <c r="U62">
+      <c r="AD62">
+        <v>2.25</v>
+      </c>
+      <c r="AE62">
+        <v>1.57</v>
+      </c>
+      <c r="AF62">
+        <v>1.5</v>
+      </c>
+      <c r="AG62">
+        <v>2.4</v>
+      </c>
+      <c r="AH62">
+        <v>3.6</v>
+      </c>
+      <c r="AI62">
         <v>1.25</v>
-      </c>
-      <c r="V62">
-        <v>12.5</v>
-      </c>
-      <c r="W62">
-        <v>1.04</v>
-      </c>
-      <c r="X62">
-        <v>1.13</v>
-      </c>
-      <c r="Y62">
-        <v>6.25</v>
-      </c>
-      <c r="Z62">
-        <v>1.57</v>
-      </c>
-      <c r="AA62">
-        <v>2.25</v>
-      </c>
-      <c r="AB62">
-        <v>2.25</v>
-      </c>
-      <c r="AC62">
-        <v>1.5</v>
-      </c>
-      <c r="AD62">
-        <v>5.5</v>
-      </c>
-      <c r="AE62">
-        <v>1.13</v>
-      </c>
-      <c r="AF62">
-        <v>2.3</v>
-      </c>
-      <c r="AG62">
-        <v>1.62</v>
-      </c>
-      <c r="AH62">
-        <v>10</v>
-      </c>
-      <c r="AI62">
-        <v>1.03</v>
       </c>
       <c r="AJ62" t="s">
         <v>248</v>
@@ -8366,64 +8366,64 @@
         <v>2.6</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q63">
         <v>1.57</v>
       </c>
       <c r="R63">
+        <v>1.36</v>
+      </c>
+      <c r="S63">
+        <v>2.9</v>
+      </c>
+      <c r="T63">
+        <v>2.68</v>
+      </c>
+      <c r="U63">
+        <v>1.42</v>
+      </c>
+      <c r="V63">
+        <v>6.5</v>
+      </c>
+      <c r="W63">
+        <v>1.09</v>
+      </c>
+      <c r="X63">
+        <v>1.05</v>
+      </c>
+      <c r="Y63">
+        <v>10</v>
+      </c>
+      <c r="Z63">
+        <v>1.25</v>
+      </c>
+      <c r="AA63">
+        <v>3.5</v>
+      </c>
+      <c r="AB63">
+        <v>1.8</v>
+      </c>
+      <c r="AC63">
+        <v>1.83</v>
+      </c>
+      <c r="AD63">
+        <v>3.1</v>
+      </c>
+      <c r="AE63">
         <v>1.33</v>
       </c>
-      <c r="S63">
-        <v>3.25</v>
-      </c>
-      <c r="T63">
-        <v>2.5</v>
-      </c>
-      <c r="U63">
-        <v>1.5</v>
-      </c>
-      <c r="V63">
+      <c r="AF63">
+        <v>1.75</v>
+      </c>
+      <c r="AG63">
+        <v>1.95</v>
+      </c>
+      <c r="AH63">
         <v>5.5</v>
       </c>
-      <c r="W63">
-        <v>1.13</v>
-      </c>
-      <c r="X63">
-        <v>0</v>
-      </c>
-      <c r="Y63">
-        <v>0</v>
-      </c>
-      <c r="Z63">
-        <v>0</v>
-      </c>
-      <c r="AA63">
-        <v>0</v>
-      </c>
-      <c r="AB63">
-        <v>1.65</v>
-      </c>
-      <c r="AC63">
-        <v>2.1</v>
-      </c>
-      <c r="AD63">
-        <v>0</v>
-      </c>
-      <c r="AE63">
-        <v>0</v>
-      </c>
-      <c r="AF63">
-        <v>1.73</v>
-      </c>
-      <c r="AG63">
-        <v>2</v>
-      </c>
-      <c r="AH63">
-        <v>0</v>
-      </c>
       <c r="AI63">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ63" t="s">
         <v>248</v>
@@ -8443,7 +8443,7 @@
         <v>57</v>
       </c>
       <c r="C64" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D64" t="s">
         <v>90</v>
@@ -8470,76 +8470,76 @@
         <v>247</v>
       </c>
       <c r="L64">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="M64">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="N64">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="O64">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="P64">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q64">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="R64">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T64">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U64">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V64">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W64">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X64">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y64">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z64">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA64">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB64">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC64">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD64">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE64">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF64">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH64">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AI64">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ64" t="s">
         <v>248</v>
@@ -8559,7 +8559,7 @@
         <v>57</v>
       </c>
       <c r="C65" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D65" t="s">
         <v>90</v>
@@ -8586,31 +8586,31 @@
         <v>247</v>
       </c>
       <c r="L65">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="M65">
-        <v>3.11</v>
+        <v>2.96</v>
       </c>
       <c r="N65">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O65">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="P65">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
       <c r="Q65">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="R65">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="S65">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="T65">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U65">
         <v>1.29</v>
@@ -8619,34 +8619,34 @@
         <v>8.5</v>
       </c>
       <c r="W65">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X65">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y65">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="Z65">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AA65">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AB65">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC65">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AD65">
         <v>4.33</v>
       </c>
       <c r="AE65">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF65">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG65">
         <v>1.73</v>
@@ -8655,7 +8655,7 @@
         <v>9</v>
       </c>
       <c r="AI65">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AJ65" t="s">
         <v>248</v>
@@ -8702,13 +8702,13 @@
         <v>247</v>
       </c>
       <c r="L66">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="M66">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N66">
-        <v>2.95</v>
+        <v>3.13</v>
       </c>
       <c r="O66">
         <v>1.75</v>
@@ -8720,13 +8720,13 @@
         <v>2.13</v>
       </c>
       <c r="R66">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S66">
         <v>3.75</v>
       </c>
       <c r="T66">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="U66">
         <v>1.68</v>
@@ -8735,25 +8735,25 @@
         <v>4.33</v>
       </c>
       <c r="W66">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
         <v>15.5</v>
       </c>
       <c r="Z66">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AA66">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AB66">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AC66">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="AD66">
         <v>1.91</v>
@@ -8765,10 +8765,10 @@
         <v>1.4</v>
       </c>
       <c r="AG66">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH66">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AI66">
         <v>1.27</v>
@@ -8818,13 +8818,13 @@
         <v>247</v>
       </c>
       <c r="L67">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="M67">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="N67">
-        <v>3.4</v>
+        <v>3.94</v>
       </c>
       <c r="O67">
         <v>1.78</v>
@@ -8836,34 +8836,34 @@
         <v>2.45</v>
       </c>
       <c r="R67">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="S67">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="T67">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="U67">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="V67">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="W67">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X67">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y67">
-        <v>7.4</v>
+        <v>5.25</v>
       </c>
       <c r="Z67">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AA67">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="AB67">
         <v>2.3</v>
@@ -8872,22 +8872,22 @@
         <v>1.5</v>
       </c>
       <c r="AD67">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="AE67">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AF67">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AG67">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH67">
-        <v>9.4</v>
+        <v>17</v>
       </c>
       <c r="AI67">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AJ67" t="s">
         <v>248</v>
@@ -8934,13 +8934,13 @@
         <v>247</v>
       </c>
       <c r="L68">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="M68">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="N68">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="O68">
         <v>1.75</v>
@@ -8952,34 +8952,34 @@
         <v>2.5</v>
       </c>
       <c r="R68">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="S68">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="T68">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="U68">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="V68">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="W68">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X68">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y68">
-        <v>7.8</v>
+        <v>5.25</v>
       </c>
       <c r="Z68">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AA68">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AB68">
         <v>2.37</v>
@@ -8988,22 +8988,22 @@
         <v>1.48</v>
       </c>
       <c r="AD68">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="AE68">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF68">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AG68">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AH68">
-        <v>9.9</v>
+        <v>12</v>
       </c>
       <c r="AI68">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AJ68" t="s">
         <v>248</v>
@@ -9029,10 +9029,10 @@
         <v>90</v>
       </c>
       <c r="E69" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F69" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -9050,76 +9050,76 @@
         <v>247</v>
       </c>
       <c r="L69">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M69">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N69">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P69">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q69">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R69">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S69">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T69">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U69">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V69">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W69">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X69">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y69">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Z69">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA69">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB69">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC69">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD69">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AE69">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF69">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG69">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH69">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI69">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ69" t="s">
         <v>248</v>
@@ -9145,10 +9145,10 @@
         <v>90</v>
       </c>
       <c r="E70" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F70" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -9166,76 +9166,76 @@
         <v>247</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH70">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI70">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ70" t="s">
         <v>248</v>
@@ -9255,7 +9255,7 @@
         <v>61</v>
       </c>
       <c r="C71" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D71" t="s">
         <v>90</v>
@@ -9309,31 +9309,31 @@
         <v>3.3</v>
       </c>
       <c r="U71">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V71">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="W71">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X71">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y71">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Z71">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AA71">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="AB71">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AC71">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AD71">
         <v>4.33</v>
@@ -9342,16 +9342,16 @@
         <v>1.18</v>
       </c>
       <c r="AF71">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG71">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AH71">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AI71">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ71" t="s">
         <v>248</v>
@@ -9371,7 +9371,7 @@
         <v>61</v>
       </c>
       <c r="C72" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D72" t="s">
         <v>90</v>
@@ -9416,10 +9416,10 @@
         <v>3.4</v>
       </c>
       <c r="R72">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S72">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T72">
         <v>3.2</v>
@@ -9428,34 +9428,34 @@
         <v>1.3</v>
       </c>
       <c r="V72">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W72">
         <v>1.04</v>
       </c>
       <c r="X72">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y72">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Z72">
         <v>1.44</v>
       </c>
       <c r="AA72">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AB72">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AC72">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AD72">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="AE72">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF72">
         <v>2.2</v>
@@ -9467,7 +9467,7 @@
         <v>8.5</v>
       </c>
       <c r="AI72">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AJ72" t="s">
         <v>248</v>
@@ -9487,7 +9487,7 @@
         <v>62</v>
       </c>
       <c r="C73" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D73" t="s">
         <v>90</v>
@@ -9514,73 +9514,73 @@
         <v>247</v>
       </c>
       <c r="L73">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="M73">
-        <v>3.36</v>
+        <v>3.11</v>
       </c>
       <c r="N73">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="O73">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="P73">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="Q73">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="R73">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="S73">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="T73">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U73">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V73">
-        <v>9.25</v>
+        <v>9.6</v>
       </c>
       <c r="W73">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X73">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y73">
         <v>6.5</v>
       </c>
       <c r="Z73">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AA73">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AB73">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AC73">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AD73">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AE73">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF73">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AG73">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH73">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AI73">
         <v>1.05</v>
@@ -9603,7 +9603,7 @@
         <v>62</v>
       </c>
       <c r="C74" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D74" t="s">
         <v>90</v>
@@ -9630,76 +9630,76 @@
         <v>247</v>
       </c>
       <c r="L74">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="M74">
-        <v>3.11</v>
+        <v>3.36</v>
       </c>
       <c r="N74">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="O74">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="P74">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="Q74">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="R74">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S74">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="T74">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U74">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V74">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="W74">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X74">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y74">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="Z74">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AA74">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="AB74">
         <v>2.25</v>
       </c>
       <c r="AC74">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AD74">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AE74">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF74">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG74">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AH74">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI74">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AJ74" t="s">
         <v>248</v>
@@ -9746,52 +9746,52 @@
         <v>247</v>
       </c>
       <c r="L75">
-        <v>2.22</v>
+        <v>1.78</v>
       </c>
       <c r="M75">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N75">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="O75">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="P75">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q75">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="R75">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S75">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T75">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U75">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V75">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W75">
         <v>1.02</v>
       </c>
       <c r="X75">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y75">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Z75">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA75">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB75">
         <v>2.37</v>
@@ -9800,22 +9800,22 @@
         <v>1.48</v>
       </c>
       <c r="AD75">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AE75">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF75">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG75">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH75">
-        <v>9.1</v>
+        <v>12</v>
       </c>
       <c r="AI75">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AJ75" t="s">
         <v>248</v>
@@ -9862,52 +9862,52 @@
         <v>247</v>
       </c>
       <c r="L76">
-        <v>1.78</v>
+        <v>2.37</v>
       </c>
       <c r="M76">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="N76">
-        <v>4.4</v>
+        <v>3.19</v>
       </c>
       <c r="O76">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="P76">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q76">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="R76">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S76">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="T76">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="U76">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V76">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="W76">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X76">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y76">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Z76">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AA76">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="AB76">
         <v>2.37</v>
@@ -9916,22 +9916,22 @@
         <v>1.48</v>
       </c>
       <c r="AD76">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AE76">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF76">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG76">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH76">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI76">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ76" t="s">
         <v>248</v>
@@ -9957,10 +9957,10 @@
         <v>90</v>
       </c>
       <c r="E77" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F77" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -10067,7 +10067,7 @@
         <v>64</v>
       </c>
       <c r="C78" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D78" t="s">
         <v>90</v>
@@ -10112,58 +10112,58 @@
         <v>3.25</v>
       </c>
       <c r="R78">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="S78">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T78">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="U78">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="V78">
+        <v>9</v>
+      </c>
+      <c r="W78">
+        <v>1.03</v>
+      </c>
+      <c r="X78">
+        <v>1.09</v>
+      </c>
+      <c r="Y78">
+        <v>6</v>
+      </c>
+      <c r="Z78">
+        <v>1.44</v>
+      </c>
+      <c r="AA78">
+        <v>2.4</v>
+      </c>
+      <c r="AB78">
+        <v>2.22</v>
+      </c>
+      <c r="AC78">
+        <v>1.58</v>
+      </c>
+      <c r="AD78">
+        <v>4.75</v>
+      </c>
+      <c r="AE78">
+        <v>1.15</v>
+      </c>
+      <c r="AF78">
+        <v>2.25</v>
+      </c>
+      <c r="AG78">
+        <v>1.57</v>
+      </c>
+      <c r="AH78">
         <v>9.300000000000001</v>
       </c>
-      <c r="W78">
-        <v>1.05</v>
-      </c>
-      <c r="X78">
-        <v>1.08</v>
-      </c>
-      <c r="Y78">
-        <v>8</v>
-      </c>
-      <c r="Z78">
-        <v>1.38</v>
-      </c>
-      <c r="AA78">
-        <v>3</v>
-      </c>
-      <c r="AB78">
-        <v>2.1</v>
-      </c>
-      <c r="AC78">
-        <v>1.67</v>
-      </c>
-      <c r="AD78">
-        <v>4.2</v>
-      </c>
-      <c r="AE78">
-        <v>1.2</v>
-      </c>
-      <c r="AF78">
-        <v>2.1</v>
-      </c>
-      <c r="AG78">
-        <v>1.73</v>
-      </c>
-      <c r="AH78">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AI78">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ78" t="s">
         <v>248</v>
@@ -10183,7 +10183,7 @@
         <v>65</v>
       </c>
       <c r="C79" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D79" t="s">
         <v>90</v>
@@ -10228,23 +10228,23 @@
         <v>2.4</v>
       </c>
       <c r="R79">
+        <v>1.22</v>
+      </c>
+      <c r="S79">
+        <v>3.8</v>
+      </c>
+      <c r="T79">
+        <v>2.05</v>
+      </c>
+      <c r="U79">
+        <v>1.7</v>
+      </c>
+      <c r="V79">
+        <v>4.33</v>
+      </c>
+      <c r="W79">
         <v>1.18</v>
       </c>
-      <c r="S79">
-        <v>4.33</v>
-      </c>
-      <c r="T79">
-        <v>1.92</v>
-      </c>
-      <c r="U79">
-        <v>1.81</v>
-      </c>
-      <c r="V79">
-        <v>3.6</v>
-      </c>
-      <c r="W79">
-        <v>1.25</v>
-      </c>
       <c r="X79">
         <v>0</v>
       </c>
@@ -10252,34 +10252,34 @@
         <v>0</v>
       </c>
       <c r="Z79">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AA79">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AB79">
+        <v>1.44</v>
+      </c>
+      <c r="AC79">
+        <v>2.7</v>
+      </c>
+      <c r="AD79">
+        <v>2.12</v>
+      </c>
+      <c r="AE79">
+        <v>1.68</v>
+      </c>
+      <c r="AF79">
+        <v>1.47</v>
+      </c>
+      <c r="AG79">
+        <v>2.57</v>
+      </c>
+      <c r="AH79">
+        <v>3.2</v>
+      </c>
+      <c r="AI79">
         <v>1.3</v>
-      </c>
-      <c r="AC79">
-        <v>3.2</v>
-      </c>
-      <c r="AD79">
-        <v>1.81</v>
-      </c>
-      <c r="AE79">
-        <v>1.91</v>
-      </c>
-      <c r="AF79">
-        <v>1.42</v>
-      </c>
-      <c r="AG79">
-        <v>2.71</v>
-      </c>
-      <c r="AH79">
-        <v>2.8</v>
-      </c>
-      <c r="AI79">
-        <v>1.38</v>
       </c>
       <c r="AJ79" t="s">
         <v>248</v>
@@ -10305,10 +10305,10 @@
         <v>90</v>
       </c>
       <c r="E80" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F80" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="AB81">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC81">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AD81">
         <v>0</v>
@@ -10531,7 +10531,7 @@
         <v>67</v>
       </c>
       <c r="C82" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D82" t="s">
         <v>90</v>
@@ -10558,13 +10558,13 @@
         <v>247</v>
       </c>
       <c r="L82">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="M82">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="N82">
-        <v>3.07</v>
+        <v>3.25</v>
       </c>
       <c r="O82">
         <v>1.73</v>
@@ -10576,58 +10576,58 @@
         <v>2.2</v>
       </c>
       <c r="R82">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S82">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="T82">
-        <v>2.51</v>
+        <v>2.41</v>
       </c>
       <c r="U82">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V82">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W82">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z82">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AA82">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AB82">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC82">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD82">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="AE82">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF82">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG82">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH82">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AI82">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AJ82" t="s">
         <v>248</v>
@@ -10647,7 +10647,7 @@
         <v>68</v>
       </c>
       <c r="C83" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D83" t="s">
         <v>90</v>
@@ -10698,10 +10698,10 @@
         <v>3.8</v>
       </c>
       <c r="T83">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="U83">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V83">
         <v>4.33</v>
@@ -10725,25 +10725,25 @@
         <v>1.42</v>
       </c>
       <c r="AC83">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AD83">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AE83">
         <v>1.7</v>
       </c>
       <c r="AF83">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AG83">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AH83">
         <v>3.3</v>
       </c>
       <c r="AI83">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AJ83" t="s">
         <v>248</v>
@@ -10763,7 +10763,7 @@
         <v>68</v>
       </c>
       <c r="C84" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D84" t="s">
         <v>90</v>
@@ -10808,58 +10808,58 @@
         <v>2.5</v>
       </c>
       <c r="R84">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S84">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="T84">
+        <v>1.85</v>
+      </c>
+      <c r="U84">
+        <v>1.85</v>
+      </c>
+      <c r="V84">
+        <v>3.6</v>
+      </c>
+      <c r="W84">
+        <v>1.25</v>
+      </c>
+      <c r="X84">
+        <v>0</v>
+      </c>
+      <c r="Y84">
+        <v>0</v>
+      </c>
+      <c r="Z84">
+        <v>1.07</v>
+      </c>
+      <c r="AA84">
+        <v>7</v>
+      </c>
+      <c r="AB84">
+        <v>1.29</v>
+      </c>
+      <c r="AC84">
+        <v>3.3</v>
+      </c>
+      <c r="AD84">
+        <v>1.73</v>
+      </c>
+      <c r="AE84">
         <v>2</v>
       </c>
-      <c r="U84">
-        <v>1.73</v>
-      </c>
-      <c r="V84">
-        <v>4</v>
-      </c>
-      <c r="W84">
-        <v>1.2</v>
-      </c>
-      <c r="X84">
-        <v>0</v>
-      </c>
-      <c r="Y84">
-        <v>0</v>
-      </c>
-      <c r="Z84">
-        <v>1.1</v>
-      </c>
-      <c r="AA84">
-        <v>5.75</v>
-      </c>
-      <c r="AB84">
-        <v>1.35</v>
-      </c>
-      <c r="AC84">
-        <v>2.74</v>
-      </c>
-      <c r="AD84">
-        <v>2</v>
-      </c>
-      <c r="AE84">
-        <v>1.74</v>
-      </c>
       <c r="AF84">
+        <v>1.33</v>
+      </c>
+      <c r="AG84">
+        <v>3</v>
+      </c>
+      <c r="AH84">
+        <v>2.62</v>
+      </c>
+      <c r="AI84">
         <v>1.42</v>
-      </c>
-      <c r="AG84">
-        <v>2.62</v>
-      </c>
-      <c r="AH84">
-        <v>3.08</v>
-      </c>
-      <c r="AI84">
-        <v>1.28</v>
       </c>
       <c r="AJ84" t="s">
         <v>248</v>

--- a/jogos_2025-07-20.xlsx
+++ b/jogos_2025-07-20.xlsx
@@ -271,15 +271,15 @@
     <t>Chile Primera B</t>
   </si>
   <si>
+    <t>Canada Canadian Premier League</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Canada Canadian Premier League</t>
-  </si>
-  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
@@ -292,12 +292,12 @@
     <t>Sacramento Republic</t>
   </si>
   <si>
+    <t>Central Coast II</t>
+  </si>
+  <si>
     <t>APIA Leichhardt Tigers</t>
   </si>
   <si>
-    <t>Central Coast II</t>
-  </si>
-  <si>
     <t>Sydney Olympic</t>
   </si>
   <si>
@@ -313,39 +313,39 @@
     <t>FC Seoul</t>
   </si>
   <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
     <t>Gyeongnam</t>
   </si>
   <si>
+    <t>Albirex Niigata</t>
+  </si>
+  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Cheongju</t>
+    <t>Yokohama F. Marinos</t>
   </si>
   <si>
     <t>Fagiano Okayama</t>
   </si>
   <si>
-    <t>Yokohama F. Marinos</t>
-  </si>
-  <si>
     <t>Gamba Osaka</t>
   </si>
   <si>
-    <t>Albirex Niigata</t>
-  </si>
-  <si>
     <t>Varberg</t>
   </si>
   <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
     <t>Shenzhen Juniors</t>
   </si>
   <si>
-    <t>Nanjing City</t>
-  </si>
-  <si>
     <t>Mjällby</t>
   </si>
   <si>
@@ -358,93 +358,93 @@
     <t>Kyzyl-Zhar</t>
   </si>
   <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
     <t>SJK</t>
   </si>
   <si>
-    <t>Kalmar</t>
-  </si>
-  <si>
     <t>Tammeka</t>
   </si>
   <si>
+    <t>Internacional</t>
+  </si>
+  <si>
     <t>Nõmme Kalju</t>
   </si>
   <si>
-    <t>Internacional</t>
-  </si>
-  <si>
     <t>Hammarby</t>
   </si>
   <si>
     <t>Halmstad</t>
   </si>
   <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Boca Juniors</t>
+  </si>
+  <si>
+    <t>Barracas Central</t>
+  </si>
+  <si>
+    <t>Lanús</t>
+  </si>
+  <si>
+    <t>Atlético Tucumán</t>
+  </si>
+  <si>
     <t>Platense</t>
   </si>
   <si>
     <t>San Lorenzo</t>
   </si>
   <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Newell's Old Boys</t>
+  </si>
+  <si>
     <t>Aktobe</t>
   </si>
   <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
+  </si>
+  <si>
+    <t>Independiente</t>
+  </si>
+  <si>
     <t>Tigre</t>
   </si>
   <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Estudiantes</t>
-  </si>
-  <si>
-    <t>Independiente</t>
-  </si>
-  <si>
-    <t>Godoy Cruz</t>
-  </si>
-  <si>
-    <t>Newell's Old Boys</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Defensa y Justicia</t>
-  </si>
-  <si>
-    <t>Atlético Tucumán</t>
-  </si>
-  <si>
-    <t>Lanús</t>
-  </si>
-  <si>
-    <t>Barracas Central</t>
-  </si>
-  <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
-    <t>Instituto</t>
-  </si>
-  <si>
-    <t>Boca Juniors</t>
-  </si>
-  <si>
     <t>HJK</t>
   </si>
   <si>
     <t>Jaro</t>
   </si>
   <si>
+    <t>Paide</t>
+  </si>
+  <si>
     <t>Kuressaare</t>
   </si>
   <si>
-    <t>Paide</t>
-  </si>
-  <si>
     <t>Audax Italiano</t>
   </si>
   <si>
@@ -454,57 +454,57 @@
     <t>HamKam</t>
   </si>
   <si>
+    <t>Ñublense</t>
+  </si>
+  <si>
+    <t>Vitória</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Valour FC</t>
+  </si>
+  <si>
     <t>Magallanes</t>
   </si>
   <si>
-    <t>Ñublense</t>
-  </si>
-  <si>
     <t>Amazonas</t>
   </si>
   <si>
-    <t>Cruzeiro</t>
+    <t>Toronto II</t>
   </si>
   <si>
     <t>New England II</t>
   </si>
   <si>
-    <t>Valour FC</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
-    <t>Vitória</t>
-  </si>
-  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
+    <t>Confiança</t>
+  </si>
+  <si>
     <t>CSA</t>
   </si>
   <si>
-    <t>Confiança</t>
-  </si>
-  <si>
     <t>Sport Recife</t>
   </si>
   <si>
     <t>Palmeiras</t>
   </si>
   <si>
+    <t>América Mineiro</t>
+  </si>
+  <si>
     <t>Deportes Temuco</t>
   </si>
   <si>
-    <t>América Mineiro</t>
+    <t>Ypiranga Erechim</t>
   </si>
   <si>
     <t>Brusque</t>
   </si>
   <si>
-    <t>Ypiranga Erechim</t>
-  </si>
-  <si>
     <t>Flamengo</t>
   </si>
   <si>
@@ -517,21 +517,21 @@
     <t>Real Monarchs</t>
   </si>
   <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
     <t>Colorado Rapids II</t>
   </si>
   <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
     <t>Lexington</t>
   </si>
   <si>
+    <t>St. George Saints</t>
+  </si>
+  <si>
     <t>Sydney United</t>
   </si>
   <si>
-    <t>St. George Saints</t>
-  </si>
-  <si>
     <t>Mt Druitt Town</t>
   </si>
   <si>
@@ -547,39 +547,39 @@
     <t>Ulsan</t>
   </si>
   <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
     <t>Incheon United</t>
   </si>
   <si>
+    <t>Sanfrecce Hiroshima</t>
+  </si>
+  <si>
     <t>Asan Mugunghwa</t>
   </si>
   <si>
-    <t>Cheonan City</t>
+    <t>Nagoya Grampus</t>
   </si>
   <si>
     <t>Vissel Kobe</t>
   </si>
   <si>
-    <t>Nagoya Grampus</t>
-  </si>
-  <si>
     <t>Kawasaki Frontale</t>
   </si>
   <si>
-    <t>Sanfrecce Hiroshima</t>
-  </si>
-  <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
+    <t>Guangxi Baoyun</t>
+  </si>
+  <si>
     <t>Shaanxi Union</t>
   </si>
   <si>
     <t>Shanghai Jiading</t>
   </si>
   <si>
-    <t>Guangxi Baoyun</t>
-  </si>
-  <si>
     <t>AIK</t>
   </si>
   <si>
@@ -592,93 +592,93 @@
     <t>Atyrau</t>
   </si>
   <si>
+    <t>Brage</t>
+  </si>
+  <si>
     <t>Gnistan</t>
   </si>
   <si>
-    <t>Brage</t>
-  </si>
-  <si>
     <t>Tallinna FC Flora</t>
   </si>
   <si>
+    <t>Ceará</t>
+  </si>
+  <si>
     <t>Tallinna Kalev</t>
   </si>
   <si>
-    <t>Ceará</t>
-  </si>
-  <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
     <t>Häcken</t>
   </si>
   <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Racing Club</t>
+  </si>
+  <si>
+    <t>Huracán</t>
+  </si>
+  <si>
+    <t>Unión Santa Fe</t>
+  </si>
+  <si>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>Rosario Central</t>
+  </si>
+  <si>
+    <t>Central Córdoba SdE</t>
+  </si>
+  <si>
     <t>Vélez Sarsfield</t>
   </si>
   <si>
     <t>Gimnasia La Plata</t>
   </si>
   <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>River Plate</t>
+  </si>
+  <si>
+    <t>Banfield</t>
+  </si>
+  <si>
     <t>Tobol</t>
   </si>
   <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
+    <t>Sarmiento</t>
+  </si>
+  <si>
+    <t>Talleres Córdoba</t>
+  </si>
+  <si>
     <t>Argentinos Juniors</t>
   </si>
   <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Huracán</t>
-  </si>
-  <si>
-    <t>Talleres Córdoba</t>
-  </si>
-  <si>
-    <t>Sarmiento</t>
-  </si>
-  <si>
-    <t>Banfield</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Aldosivi</t>
-  </si>
-  <si>
-    <t>Central Córdoba SdE</t>
-  </si>
-  <si>
-    <t>Rosario Central</t>
-  </si>
-  <si>
-    <t>Independiente Rivadavia</t>
-  </si>
-  <si>
-    <t>Racing Club</t>
-  </si>
-  <si>
-    <t>River Plate</t>
-  </si>
-  <si>
-    <t>Unión Santa Fe</t>
-  </si>
-  <si>
     <t>Oulu</t>
   </si>
   <si>
     <t>Ilves</t>
   </si>
   <si>
+    <t>Trans</t>
+  </si>
+  <si>
     <t>Vaprus</t>
   </si>
   <si>
-    <t>Trans</t>
-  </si>
-  <si>
     <t>Universidad Católica</t>
   </si>
   <si>
@@ -688,57 +688,57 @@
     <t>Fredrikstad</t>
   </si>
   <si>
+    <t>Universidad Chile</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
+    <t>Cavalry FC</t>
+  </si>
+  <si>
     <t>Univ. Concepción</t>
   </si>
   <si>
-    <t>Universidad Chile</t>
-  </si>
-  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>Juventude</t>
+    <t>Chicago Fire II</t>
   </si>
   <si>
     <t>Orlando City II</t>
   </si>
   <si>
-    <t>Cavalry FC</t>
-  </si>
-  <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
     <t>Valur</t>
   </si>
   <si>
+    <t>Tombense</t>
+  </si>
+  <si>
     <t>Figueirense</t>
   </si>
   <si>
-    <t>Tombense</t>
-  </si>
-  <si>
     <t>Botafogo</t>
   </si>
   <si>
     <t>Atlético Mineiro</t>
   </si>
   <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
     <t>Santiago Morning</t>
   </si>
   <si>
-    <t>Chapecoense</t>
+    <t>São Bernardo</t>
   </si>
   <si>
     <t>Retrô</t>
   </si>
   <si>
-    <t>São Bernardo</t>
-  </si>
-  <si>
     <t>Fluminense</t>
   </si>
   <si>
@@ -751,10 +751,10 @@
     <t>Austin II</t>
   </si>
   <si>
+    <t>Los Angeles II</t>
+  </si>
+  <si>
     <t>Tacoma Defiance</t>
-  </si>
-  <si>
-    <t>Los Angeles II</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -1394,76 +1394,76 @@
         <v>247</v>
       </c>
       <c r="L3">
-        <v>1.52</v>
+        <v>4.27</v>
       </c>
       <c r="M3">
-        <v>4.27</v>
+        <v>4.15</v>
       </c>
       <c r="N3">
-        <v>4.77</v>
+        <v>1.62</v>
       </c>
       <c r="O3">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>18.25</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AC3">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD3">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="s">
         <v>248</v>
@@ -1510,76 +1510,76 @@
         <v>247</v>
       </c>
       <c r="L4">
+        <v>1.52</v>
+      </c>
+      <c r="M4">
         <v>4.27</v>
       </c>
-      <c r="M4">
-        <v>4.15</v>
-      </c>
       <c r="N4">
-        <v>1.62</v>
+        <v>4.77</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>18.25</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AB4">
+        <v>1.47</v>
+      </c>
+      <c r="AC4">
+        <v>2.35</v>
+      </c>
+      <c r="AD4">
+        <v>2.35</v>
+      </c>
+      <c r="AE4">
+        <v>1.54</v>
+      </c>
+      <c r="AF4">
         <v>1.6</v>
       </c>
-      <c r="AC4">
-        <v>2.3</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ4" t="s">
         <v>248</v>
@@ -2206,76 +2206,76 @@
         <v>247</v>
       </c>
       <c r="L10">
-        <v>5.5</v>
+        <v>2.18</v>
       </c>
       <c r="M10">
-        <v>4.1</v>
+        <v>3.12</v>
       </c>
       <c r="N10">
-        <v>1.44</v>
+        <v>2.93</v>
       </c>
       <c r="O10">
-        <v>3.2</v>
+        <v>1.79</v>
       </c>
       <c r="P10">
-        <v>15.25</v>
+        <v>10.5</v>
       </c>
       <c r="Q10">
+        <v>2.16</v>
+      </c>
+      <c r="R10">
+        <v>1.4</v>
+      </c>
+      <c r="S10">
+        <v>2.8</v>
+      </c>
+      <c r="T10">
+        <v>2.9</v>
+      </c>
+      <c r="U10">
         <v>1.36</v>
       </c>
-      <c r="R10">
-        <v>1.3</v>
-      </c>
-      <c r="S10">
-        <v>3.25</v>
-      </c>
-      <c r="T10">
-        <v>2.45</v>
-      </c>
-      <c r="U10">
-        <v>1.5</v>
-      </c>
       <c r="V10">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z10">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AA10">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AB10">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AD10">
-        <v>2.59</v>
+        <v>3.58</v>
       </c>
       <c r="AE10">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH10">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="AI10">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AJ10" t="s">
         <v>248</v>
@@ -2322,76 +2322,76 @@
         <v>247</v>
       </c>
       <c r="L11">
-        <v>2.16</v>
+        <v>5.5</v>
       </c>
       <c r="M11">
-        <v>3.32</v>
+        <v>4.1</v>
       </c>
       <c r="N11">
-        <v>3.08</v>
+        <v>1.44</v>
       </c>
       <c r="O11">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>9.1</v>
+        <v>15.25</v>
       </c>
       <c r="Q11">
-        <v>2.22</v>
+        <v>1.36</v>
       </c>
       <c r="R11">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S11">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="T11">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="U11">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>9.1</v>
+        <v>13</v>
       </c>
       <c r="Z11">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AA11">
-        <v>3.22</v>
+        <v>4.05</v>
       </c>
       <c r="AB11">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC11">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AD11">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="AE11">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH11">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="AI11">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AJ11" t="s">
         <v>248</v>
@@ -2411,7 +2411,7 @@
         <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
         <v>90</v>
@@ -2438,76 +2438,76 @@
         <v>247</v>
       </c>
       <c r="L12">
-        <v>2.18</v>
+        <v>3.99</v>
       </c>
       <c r="M12">
-        <v>3.12</v>
+        <v>3.36</v>
       </c>
       <c r="N12">
-        <v>2.93</v>
+        <v>1.75</v>
       </c>
       <c r="O12">
-        <v>1.79</v>
+        <v>2.75</v>
       </c>
       <c r="P12">
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q12">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="R12">
         <v>1.4</v>
       </c>
       <c r="S12">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T12">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U12">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V12">
+        <v>8</v>
+      </c>
+      <c r="W12">
+        <v>1.08</v>
+      </c>
+      <c r="X12">
+        <v>1.06</v>
+      </c>
+      <c r="Y12">
         <v>8.5</v>
       </c>
-      <c r="W12">
-        <v>1.07</v>
-      </c>
-      <c r="X12">
-        <v>1.03</v>
-      </c>
-      <c r="Y12">
-        <v>9</v>
-      </c>
       <c r="Z12">
+        <v>1.33</v>
+      </c>
+      <c r="AA12">
+        <v>3.25</v>
+      </c>
+      <c r="AB12">
+        <v>1.94</v>
+      </c>
+      <c r="AC12">
+        <v>1.76</v>
+      </c>
+      <c r="AD12">
+        <v>3.5</v>
+      </c>
+      <c r="AE12">
         <v>1.28</v>
       </c>
-      <c r="AA12">
-        <v>3.08</v>
-      </c>
-      <c r="AB12">
-        <v>1.95</v>
-      </c>
-      <c r="AC12">
-        <v>1.7</v>
-      </c>
-      <c r="AD12">
-        <v>3.58</v>
-      </c>
-      <c r="AE12">
-        <v>1.21</v>
-      </c>
       <c r="AF12">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH12">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AI12">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AJ12" t="s">
         <v>248</v>
@@ -2527,7 +2527,7 @@
         <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
         <v>90</v>
@@ -2554,73 +2554,73 @@
         <v>247</v>
       </c>
       <c r="L13">
-        <v>4.6</v>
+        <v>2.16</v>
       </c>
       <c r="M13">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="N13">
-        <v>1.68</v>
+        <v>3.08</v>
       </c>
       <c r="O13">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="P13">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="Q13">
-        <v>1.58</v>
+        <v>2.22</v>
       </c>
       <c r="R13">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S13">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="T13">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U13">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="V13">
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="Z13">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AA13">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="AB13">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="AC13">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="AD13">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AE13">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AF13">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG13">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AH13">
-        <v>8.25</v>
+        <v>6.2</v>
       </c>
       <c r="AI13">
         <v>1.06</v>
@@ -2786,76 +2786,76 @@
         <v>247</v>
       </c>
       <c r="L15">
-        <v>2.47</v>
+        <v>4.6</v>
       </c>
       <c r="M15">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="N15">
-        <v>2.47</v>
+        <v>1.68</v>
       </c>
       <c r="O15">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="P15">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Q15">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="R15">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="S15">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="T15">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="U15">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="V15">
-        <v>6.5</v>
+        <v>8.75</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z15">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AA15">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AB15">
-        <v>1.76</v>
+        <v>2.13</v>
       </c>
       <c r="AC15">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="AD15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE15">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AF15">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AH15">
-        <v>5.5</v>
+        <v>8.25</v>
       </c>
       <c r="AI15">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AJ15" t="s">
         <v>248</v>
@@ -2902,76 +2902,76 @@
         <v>247</v>
       </c>
       <c r="L16">
-        <v>3.99</v>
+        <v>2.47</v>
       </c>
       <c r="M16">
-        <v>3.36</v>
+        <v>3.23</v>
       </c>
       <c r="N16">
-        <v>1.75</v>
+        <v>2.47</v>
       </c>
       <c r="O16">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="P16">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="R16">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S16">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T16">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U16">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="Z16">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AA16">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="AB16">
+        <v>1.76</v>
+      </c>
+      <c r="AC16">
         <v>1.94</v>
       </c>
-      <c r="AC16">
-        <v>1.76</v>
-      </c>
       <c r="AD16">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AE16">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AF16">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AH16">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AI16">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AJ16" t="s">
         <v>248</v>
@@ -3134,76 +3134,76 @@
         <v>247</v>
       </c>
       <c r="L18">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="M18">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="N18">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="O18">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="P18">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q18">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="R18">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S18">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T18">
-        <v>2.98</v>
+        <v>2.7</v>
       </c>
       <c r="U18">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V18">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="Z18">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA18">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="AB18">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="AC18">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AD18">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AE18">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AF18">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG18">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH18">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="AI18">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AJ18" t="s">
         <v>248</v>
@@ -3250,22 +3250,22 @@
         <v>247</v>
       </c>
       <c r="L19">
-        <v>2.02</v>
+        <v>3.05</v>
       </c>
       <c r="M19">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N19">
-        <v>3.6</v>
+        <v>2.21</v>
       </c>
       <c r="O19">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="P19">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q19">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="R19">
         <v>1.42</v>
@@ -3274,22 +3274,22 @@
         <v>2.62</v>
       </c>
       <c r="T19">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="U19">
         <v>1.33</v>
       </c>
       <c r="V19">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>1.36</v>
@@ -3298,28 +3298,28 @@
         <v>2.9</v>
       </c>
       <c r="AB19">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AC19">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AD19">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AE19">
         <v>1.22</v>
       </c>
       <c r="AF19">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG19">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH19">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="AI19">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AJ19" t="s">
         <v>248</v>
@@ -3366,76 +3366,76 @@
         <v>247</v>
       </c>
       <c r="L20">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="M20">
-        <v>3.35</v>
+        <v>3.03</v>
       </c>
       <c r="N20">
-        <v>5.4</v>
+        <v>3.05</v>
       </c>
       <c r="O20">
+        <v>1.8</v>
+      </c>
+      <c r="P20">
+        <v>7.8</v>
+      </c>
+      <c r="Q20">
+        <v>2.38</v>
+      </c>
+      <c r="R20">
         <v>1.44</v>
       </c>
-      <c r="P20">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q20">
-        <v>3.4</v>
-      </c>
-      <c r="R20">
-        <v>1.38</v>
-      </c>
       <c r="S20">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="T20">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U20">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V20">
-        <v>6.5</v>
+        <v>8.1</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="Z20">
         <v>1.3</v>
       </c>
       <c r="AA20">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AB20">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AC20">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD20">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AE20">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF20">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG20">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH20">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="AI20">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AJ20" t="s">
         <v>248</v>
@@ -3919,7 +3919,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D25" t="s">
         <v>90</v>
@@ -3946,76 +3946,76 @@
         <v>247</v>
       </c>
       <c r="L25">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="M25">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="N25">
-        <v>4.2</v>
+        <v>6.9</v>
       </c>
       <c r="O25">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="P25">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q25">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R25">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S25">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T25">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="U25">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="V25">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="W25">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z25">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AA25">
+        <v>4.33</v>
+      </c>
+      <c r="AB25">
+        <v>1.6</v>
+      </c>
+      <c r="AC25">
+        <v>2.1</v>
+      </c>
+      <c r="AD25">
+        <v>2.65</v>
+      </c>
+      <c r="AE25">
+        <v>1.48</v>
+      </c>
+      <c r="AF25">
+        <v>1.91</v>
+      </c>
+      <c r="AG25">
+        <v>1.91</v>
+      </c>
+      <c r="AH25">
         <v>5</v>
       </c>
-      <c r="AB25">
-        <v>1.45</v>
-      </c>
-      <c r="AC25">
-        <v>2.56</v>
-      </c>
-      <c r="AD25">
-        <v>2.12</v>
-      </c>
-      <c r="AE25">
-        <v>1.64</v>
-      </c>
-      <c r="AF25">
-        <v>1.47</v>
-      </c>
-      <c r="AG25">
-        <v>2.45</v>
-      </c>
-      <c r="AH25">
-        <v>3.8</v>
-      </c>
       <c r="AI25">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AJ25" t="s">
         <v>248</v>
@@ -4035,7 +4035,7 @@
         <v>48</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
         <v>90</v>
@@ -4062,76 +4062,76 @@
         <v>247</v>
       </c>
       <c r="L26">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="M26">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="N26">
-        <v>6.9</v>
+        <v>4.2</v>
       </c>
       <c r="O26">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="P26">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q26">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="R26">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S26">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T26">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="U26">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="V26">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="W26">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z26">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AA26">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AB26">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AC26">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="AD26">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="AE26">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AF26">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="AG26">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="AH26">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AI26">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AJ26" t="s">
         <v>248</v>
@@ -4267,7 +4267,7 @@
         <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D28" t="s">
         <v>90</v>
@@ -4294,76 +4294,76 @@
         <v>247</v>
       </c>
       <c r="L28">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="M28">
-        <v>6.7</v>
+        <v>3.8</v>
       </c>
       <c r="N28">
-        <v>9.5</v>
+        <v>6.4</v>
       </c>
       <c r="O28">
+        <v>1.44</v>
+      </c>
+      <c r="P28">
+        <v>7.25</v>
+      </c>
+      <c r="Q28">
+        <v>3.5</v>
+      </c>
+      <c r="R28">
+        <v>1.44</v>
+      </c>
+      <c r="S28">
+        <v>2.7</v>
+      </c>
+      <c r="T28">
+        <v>3</v>
+      </c>
+      <c r="U28">
+        <v>1.33</v>
+      </c>
+      <c r="V28">
+        <v>8</v>
+      </c>
+      <c r="W28">
+        <v>1.05</v>
+      </c>
+      <c r="X28">
+        <v>1.07</v>
+      </c>
+      <c r="Y28">
+        <v>7.5</v>
+      </c>
+      <c r="Z28">
+        <v>1.38</v>
+      </c>
+      <c r="AA28">
+        <v>2.8</v>
+      </c>
+      <c r="AB28">
+        <v>2.2</v>
+      </c>
+      <c r="AC28">
+        <v>1.59</v>
+      </c>
+      <c r="AD28">
+        <v>4</v>
+      </c>
+      <c r="AE28">
         <v>1.22</v>
       </c>
-      <c r="P28">
-        <v>24</v>
-      </c>
-      <c r="Q28">
-        <v>4</v>
-      </c>
-      <c r="R28">
-        <v>1.18</v>
-      </c>
-      <c r="S28">
-        <v>4.33</v>
-      </c>
-      <c r="T28">
-        <v>1.85</v>
-      </c>
-      <c r="U28">
-        <v>1.81</v>
-      </c>
-      <c r="V28">
-        <v>3.6</v>
-      </c>
-      <c r="W28">
-        <v>1.25</v>
-      </c>
-      <c r="X28">
-        <v>1.01</v>
-      </c>
-      <c r="Y28">
-        <v>23</v>
-      </c>
-      <c r="Z28">
-        <v>1.08</v>
-      </c>
-      <c r="AA28">
-        <v>6.5</v>
-      </c>
-      <c r="AB28">
-        <v>1.29</v>
-      </c>
-      <c r="AC28">
-        <v>3.5</v>
-      </c>
-      <c r="AD28">
-        <v>1.77</v>
-      </c>
-      <c r="AE28">
-        <v>1.93</v>
-      </c>
       <c r="AF28">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AG28">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AH28">
-        <v>2.7</v>
+        <v>10.5</v>
       </c>
       <c r="AI28">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="AJ28" t="s">
         <v>248</v>
@@ -4383,7 +4383,7 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
         <v>90</v>
@@ -4410,76 +4410,76 @@
         <v>247</v>
       </c>
       <c r="L29">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="M29">
-        <v>3.8</v>
+        <v>6.7</v>
       </c>
       <c r="N29">
-        <v>6.4</v>
+        <v>9.5</v>
       </c>
       <c r="O29">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="P29">
-        <v>7.25</v>
+        <v>24</v>
       </c>
       <c r="Q29">
+        <v>4</v>
+      </c>
+      <c r="R29">
+        <v>1.18</v>
+      </c>
+      <c r="S29">
+        <v>4.33</v>
+      </c>
+      <c r="T29">
+        <v>1.85</v>
+      </c>
+      <c r="U29">
+        <v>1.81</v>
+      </c>
+      <c r="V29">
+        <v>3.6</v>
+      </c>
+      <c r="W29">
+        <v>1.25</v>
+      </c>
+      <c r="X29">
+        <v>1.01</v>
+      </c>
+      <c r="Y29">
+        <v>23</v>
+      </c>
+      <c r="Z29">
+        <v>1.08</v>
+      </c>
+      <c r="AA29">
+        <v>6.5</v>
+      </c>
+      <c r="AB29">
+        <v>1.29</v>
+      </c>
+      <c r="AC29">
         <v>3.5</v>
       </c>
-      <c r="R29">
-        <v>1.44</v>
-      </c>
-      <c r="S29">
+      <c r="AD29">
+        <v>1.77</v>
+      </c>
+      <c r="AE29">
+        <v>1.93</v>
+      </c>
+      <c r="AF29">
+        <v>1.62</v>
+      </c>
+      <c r="AG29">
+        <v>2.07</v>
+      </c>
+      <c r="AH29">
         <v>2.7</v>
       </c>
-      <c r="T29">
-        <v>3</v>
-      </c>
-      <c r="U29">
-        <v>1.33</v>
-      </c>
-      <c r="V29">
-        <v>8</v>
-      </c>
-      <c r="W29">
-        <v>1.05</v>
-      </c>
-      <c r="X29">
-        <v>1.07</v>
-      </c>
-      <c r="Y29">
-        <v>7.5</v>
-      </c>
-      <c r="Z29">
-        <v>1.38</v>
-      </c>
-      <c r="AA29">
-        <v>2.8</v>
-      </c>
-      <c r="AB29">
-        <v>2.2</v>
-      </c>
-      <c r="AC29">
-        <v>1.59</v>
-      </c>
-      <c r="AD29">
-        <v>4</v>
-      </c>
-      <c r="AE29">
-        <v>1.22</v>
-      </c>
-      <c r="AF29">
-        <v>2.1</v>
-      </c>
-      <c r="AG29">
-        <v>1.65</v>
-      </c>
-      <c r="AH29">
-        <v>10.5</v>
-      </c>
       <c r="AI29">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="AJ29" t="s">
         <v>248</v>
@@ -4731,7 +4731,7 @@
         <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
         <v>90</v>
@@ -4758,76 +4758,76 @@
         <v>247</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ32" t="s">
         <v>248</v>
@@ -4963,7 +4963,7 @@
         <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
         <v>90</v>
@@ -4990,76 +4990,76 @@
         <v>247</v>
       </c>
       <c r="L34">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M34">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N34">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O34">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH34">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI34">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="s">
         <v>248</v>
@@ -5195,7 +5195,7 @@
         <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D36" t="s">
         <v>90</v>
@@ -5222,76 +5222,76 @@
         <v>247</v>
       </c>
       <c r="L36">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N36">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y36">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z36">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH36">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI36">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="s">
         <v>248</v>
@@ -5311,7 +5311,7 @@
         <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
         <v>90</v>
@@ -5338,76 +5338,76 @@
         <v>247</v>
       </c>
       <c r="L37">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH37">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AI37">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="s">
         <v>248</v>
@@ -5775,7 +5775,7 @@
         <v>51</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D41" t="s">
         <v>90</v>
@@ -5802,76 +5802,76 @@
         <v>247</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH41">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ41" t="s">
         <v>248</v>
@@ -5891,7 +5891,7 @@
         <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D42" t="s">
         <v>90</v>
@@ -5918,76 +5918,76 @@
         <v>247</v>
       </c>
       <c r="L42">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N42">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S42">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T42">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Z42">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA42">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE42">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF42">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG42">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH42">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI42">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="s">
         <v>248</v>
@@ -6123,7 +6123,7 @@
         <v>51</v>
       </c>
       <c r="C44" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D44" t="s">
         <v>90</v>
@@ -6150,76 +6150,76 @@
         <v>247</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH44">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI44">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ44" t="s">
         <v>248</v>
@@ -6239,7 +6239,7 @@
         <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D45" t="s">
         <v>90</v>
@@ -6266,76 +6266,76 @@
         <v>247</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH45">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI45">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ45" t="s">
         <v>248</v>
@@ -7078,76 +7078,76 @@
         <v>247</v>
       </c>
       <c r="L52">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="M52">
-        <v>3.72</v>
+        <v>3.59</v>
       </c>
       <c r="N52">
-        <v>2.23</v>
+        <v>2.74</v>
       </c>
       <c r="O52">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="P52">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Q52">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="R52">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S52">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="T52">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="U52">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="V52">
+        <v>6.05</v>
+      </c>
+      <c r="W52">
+        <v>1.15</v>
+      </c>
+      <c r="X52">
+        <v>1.04</v>
+      </c>
+      <c r="Y52">
+        <v>10</v>
+      </c>
+      <c r="Z52">
+        <v>1.22</v>
+      </c>
+      <c r="AA52">
+        <v>4</v>
+      </c>
+      <c r="AB52">
+        <v>1.44</v>
+      </c>
+      <c r="AC52">
+        <v>2.63</v>
+      </c>
+      <c r="AD52">
+        <v>2</v>
+      </c>
+      <c r="AE52">
+        <v>1.67</v>
+      </c>
+      <c r="AF52">
+        <v>1.67</v>
+      </c>
+      <c r="AG52">
+        <v>2.4</v>
+      </c>
+      <c r="AH52">
         <v>5</v>
       </c>
-      <c r="W52">
-        <v>1.12</v>
-      </c>
-      <c r="X52">
-        <v>1.03</v>
-      </c>
-      <c r="Y52">
-        <v>9</v>
-      </c>
-      <c r="Z52">
-        <v>1.29</v>
-      </c>
-      <c r="AA52">
-        <v>3.5</v>
-      </c>
-      <c r="AB52">
-        <v>1.57</v>
-      </c>
-      <c r="AC52">
-        <v>2.15</v>
-      </c>
-      <c r="AD52">
-        <v>3.25</v>
-      </c>
-      <c r="AE52">
-        <v>1.42</v>
-      </c>
-      <c r="AF52">
-        <v>1.65</v>
-      </c>
-      <c r="AG52">
-        <v>2.01</v>
-      </c>
-      <c r="AH52">
-        <v>5.9</v>
-      </c>
       <c r="AI52">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AJ52" t="s">
         <v>248</v>
@@ -7194,76 +7194,76 @@
         <v>247</v>
       </c>
       <c r="L53">
+        <v>2.48</v>
+      </c>
+      <c r="M53">
+        <v>3.72</v>
+      </c>
+      <c r="N53">
+        <v>2.23</v>
+      </c>
+      <c r="O53">
         <v>2.1</v>
       </c>
-      <c r="M53">
-        <v>3.59</v>
-      </c>
-      <c r="N53">
-        <v>2.74</v>
-      </c>
-      <c r="O53">
-        <v>1.53</v>
-      </c>
       <c r="P53">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Q53">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="R53">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S53">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="T53">
+        <v>2.35</v>
+      </c>
+      <c r="U53">
+        <v>1.5</v>
+      </c>
+      <c r="V53">
+        <v>5</v>
+      </c>
+      <c r="W53">
+        <v>1.12</v>
+      </c>
+      <c r="X53">
+        <v>1.03</v>
+      </c>
+      <c r="Y53">
+        <v>9</v>
+      </c>
+      <c r="Z53">
+        <v>1.29</v>
+      </c>
+      <c r="AA53">
+        <v>3.5</v>
+      </c>
+      <c r="AB53">
+        <v>1.57</v>
+      </c>
+      <c r="AC53">
         <v>2.15</v>
       </c>
-      <c r="U53">
-        <v>1.6</v>
-      </c>
-      <c r="V53">
-        <v>6.05</v>
-      </c>
-      <c r="W53">
-        <v>1.15</v>
-      </c>
-      <c r="X53">
-        <v>1.04</v>
-      </c>
-      <c r="Y53">
-        <v>10</v>
-      </c>
-      <c r="Z53">
-        <v>1.22</v>
-      </c>
-      <c r="AA53">
-        <v>4</v>
-      </c>
-      <c r="AB53">
-        <v>1.44</v>
-      </c>
-      <c r="AC53">
-        <v>2.63</v>
-      </c>
       <c r="AD53">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="AE53">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AF53">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG53">
-        <v>2.4</v>
+        <v>2.01</v>
       </c>
       <c r="AH53">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AI53">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AJ53" t="s">
         <v>248</v>
@@ -7637,10 +7637,10 @@
         <v>90</v>
       </c>
       <c r="E57" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F57" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -7747,7 +7747,7 @@
         <v>57</v>
       </c>
       <c r="C58" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D58" t="s">
         <v>90</v>
@@ -7774,76 +7774,76 @@
         <v>247</v>
       </c>
       <c r="L58">
+        <v>3.8</v>
+      </c>
+      <c r="M58">
+        <v>3.3</v>
+      </c>
+      <c r="N58">
+        <v>2</v>
+      </c>
+      <c r="O58">
         <v>2.5</v>
       </c>
-      <c r="M58">
-        <v>3.11</v>
-      </c>
-      <c r="N58">
-        <v>2.5</v>
-      </c>
-      <c r="O58">
-        <v>1.8</v>
-      </c>
       <c r="P58">
-        <v>6.9</v>
+        <v>9.5</v>
       </c>
       <c r="Q58">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="R58">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="S58">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T58">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U58">
+        <v>1.4</v>
+      </c>
+      <c r="V58">
+        <v>7</v>
+      </c>
+      <c r="W58">
+        <v>1.1</v>
+      </c>
+      <c r="X58">
+        <v>1.05</v>
+      </c>
+      <c r="Y58">
+        <v>8.5</v>
+      </c>
+      <c r="Z58">
+        <v>1.28</v>
+      </c>
+      <c r="AA58">
+        <v>3.4</v>
+      </c>
+      <c r="AB58">
+        <v>1.9</v>
+      </c>
+      <c r="AC58">
+        <v>1.9</v>
+      </c>
+      <c r="AD58">
+        <v>3.2</v>
+      </c>
+      <c r="AE58">
         <v>1.33</v>
       </c>
-      <c r="V58">
-        <v>8.4</v>
-      </c>
-      <c r="W58">
-        <v>1.04</v>
-      </c>
-      <c r="X58">
-        <v>1.04</v>
-      </c>
-      <c r="Y58">
-        <v>7</v>
-      </c>
-      <c r="Z58">
-        <v>1.42</v>
-      </c>
-      <c r="AA58">
-        <v>2.75</v>
-      </c>
-      <c r="AB58">
-        <v>2.2</v>
-      </c>
-      <c r="AC58">
-        <v>1.55</v>
-      </c>
-      <c r="AD58">
-        <v>4.2</v>
-      </c>
-      <c r="AE58">
-        <v>1.2</v>
-      </c>
       <c r="AF58">
+        <v>1.73</v>
+      </c>
+      <c r="AG58">
         <v>2</v>
       </c>
-      <c r="AG58">
-        <v>1.73</v>
-      </c>
       <c r="AH58">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="AI58">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AJ58" t="s">
         <v>248</v>
@@ -7863,7 +7863,7 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D59" t="s">
         <v>90</v>
@@ -7890,76 +7890,76 @@
         <v>247</v>
       </c>
       <c r="L59">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="M59">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="N59">
+        <v>2.4</v>
+      </c>
+      <c r="O59">
+        <v>2.3</v>
+      </c>
+      <c r="P59">
+        <v>6.75</v>
+      </c>
+      <c r="Q59">
+        <v>1.91</v>
+      </c>
+      <c r="R59">
+        <v>1.44</v>
+      </c>
+      <c r="S59">
+        <v>2.62</v>
+      </c>
+      <c r="T59">
+        <v>3.2</v>
+      </c>
+      <c r="U59">
+        <v>1.29</v>
+      </c>
+      <c r="V59">
+        <v>8.5</v>
+      </c>
+      <c r="W59">
+        <v>1.02</v>
+      </c>
+      <c r="X59">
+        <v>1.09</v>
+      </c>
+      <c r="Y59">
+        <v>6.5</v>
+      </c>
+      <c r="Z59">
+        <v>1.5</v>
+      </c>
+      <c r="AA59">
+        <v>2.45</v>
+      </c>
+      <c r="AB59">
+        <v>2.5</v>
+      </c>
+      <c r="AC59">
+        <v>1.46</v>
+      </c>
+      <c r="AD59">
+        <v>4.33</v>
+      </c>
+      <c r="AE59">
+        <v>1.18</v>
+      </c>
+      <c r="AF59">
         <v>2</v>
       </c>
-      <c r="O59">
-        <v>2.5</v>
-      </c>
-      <c r="P59">
-        <v>9.5</v>
-      </c>
-      <c r="Q59">
-        <v>1.62</v>
-      </c>
-      <c r="R59">
-        <v>1.36</v>
-      </c>
-      <c r="S59">
-        <v>3</v>
-      </c>
-      <c r="T59">
-        <v>2.75</v>
-      </c>
-      <c r="U59">
-        <v>1.4</v>
-      </c>
-      <c r="V59">
-        <v>7</v>
-      </c>
-      <c r="W59">
-        <v>1.1</v>
-      </c>
-      <c r="X59">
-        <v>1.05</v>
-      </c>
-      <c r="Y59">
-        <v>8.5</v>
-      </c>
-      <c r="Z59">
-        <v>1.28</v>
-      </c>
-      <c r="AA59">
-        <v>3.4</v>
-      </c>
-      <c r="AB59">
-        <v>1.9</v>
-      </c>
-      <c r="AC59">
-        <v>1.9</v>
-      </c>
-      <c r="AD59">
-        <v>3.2</v>
-      </c>
-      <c r="AE59">
-        <v>1.33</v>
-      </c>
-      <c r="AF59">
+      <c r="AG59">
         <v>1.73</v>
       </c>
-      <c r="AG59">
-        <v>2</v>
-      </c>
       <c r="AH59">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="AI59">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AJ59" t="s">
         <v>248</v>
@@ -7979,7 +7979,7 @@
         <v>57</v>
       </c>
       <c r="C60" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D60" t="s">
         <v>90</v>
@@ -8006,76 +8006,76 @@
         <v>247</v>
       </c>
       <c r="L60">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="M60">
-        <v>2.87</v>
+        <v>3.75</v>
       </c>
       <c r="N60">
-        <v>3.23</v>
+        <v>7.2</v>
       </c>
       <c r="O60">
-        <v>1.88</v>
+        <v>1.22</v>
       </c>
       <c r="P60">
-        <v>5.75</v>
+        <v>8.5</v>
       </c>
       <c r="Q60">
+        <v>6</v>
+      </c>
+      <c r="R60">
+        <v>1.37</v>
+      </c>
+      <c r="S60">
+        <v>3.12</v>
+      </c>
+      <c r="T60">
+        <v>2.83</v>
+      </c>
+      <c r="U60">
+        <v>1.43</v>
+      </c>
+      <c r="V60">
+        <v>6</v>
+      </c>
+      <c r="W60">
+        <v>1.09</v>
+      </c>
+      <c r="X60">
+        <v>1.02</v>
+      </c>
+      <c r="Y60">
+        <v>10</v>
+      </c>
+      <c r="Z60">
+        <v>1.25</v>
+      </c>
+      <c r="AA60">
+        <v>3.6</v>
+      </c>
+      <c r="AB60">
+        <v>1.95</v>
+      </c>
+      <c r="AC60">
+        <v>1.75</v>
+      </c>
+      <c r="AD60">
+        <v>3.8</v>
+      </c>
+      <c r="AE60">
+        <v>1.33</v>
+      </c>
+      <c r="AF60">
         <v>2.4</v>
       </c>
-      <c r="R60">
-        <v>1.62</v>
-      </c>
-      <c r="S60">
-        <v>2.2</v>
-      </c>
-      <c r="T60">
-        <v>4.3</v>
-      </c>
-      <c r="U60">
-        <v>1.22</v>
-      </c>
-      <c r="V60">
-        <v>10</v>
-      </c>
-      <c r="W60">
-        <v>1.02</v>
-      </c>
-      <c r="X60">
-        <v>1.13</v>
-      </c>
-      <c r="Y60">
-        <v>5.75</v>
-      </c>
-      <c r="Z60">
-        <v>1.6</v>
-      </c>
-      <c r="AA60">
-        <v>2.25</v>
-      </c>
-      <c r="AB60">
-        <v>2.25</v>
-      </c>
-      <c r="AC60">
+      <c r="AG60">
         <v>1.5</v>
       </c>
-      <c r="AD60">
-        <v>5.25</v>
-      </c>
-      <c r="AE60">
-        <v>1.13</v>
-      </c>
-      <c r="AF60">
-        <v>2.3</v>
-      </c>
-      <c r="AG60">
-        <v>1.62</v>
-      </c>
       <c r="AH60">
-        <v>13</v>
+        <v>5.5</v>
       </c>
       <c r="AI60">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AJ60" t="s">
         <v>248</v>
@@ -8095,7 +8095,7 @@
         <v>57</v>
       </c>
       <c r="C61" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D61" t="s">
         <v>90</v>
@@ -8122,43 +8122,43 @@
         <v>247</v>
       </c>
       <c r="L61">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="M61">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N61">
-        <v>7.2</v>
+        <v>1.84</v>
       </c>
       <c r="O61">
-        <v>1.22</v>
+        <v>2.6</v>
       </c>
       <c r="P61">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q61">
-        <v>6</v>
+        <v>1.57</v>
       </c>
       <c r="R61">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S61">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="T61">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="U61">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V61">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W61">
         <v>1.09</v>
       </c>
       <c r="X61">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y61">
         <v>10</v>
@@ -8167,31 +8167,31 @@
         <v>1.25</v>
       </c>
       <c r="AA61">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AB61">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC61">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD61">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AE61">
         <v>1.33</v>
       </c>
       <c r="AF61">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AG61">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AH61">
         <v>5.5</v>
       </c>
       <c r="AI61">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ61" t="s">
         <v>248</v>
@@ -8211,7 +8211,7 @@
         <v>57</v>
       </c>
       <c r="C62" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D62" t="s">
         <v>90</v>
@@ -8238,76 +8238,76 @@
         <v>247</v>
       </c>
       <c r="L62">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="M62">
-        <v>3.9</v>
+        <v>3.11</v>
       </c>
       <c r="N62">
+        <v>2.5</v>
+      </c>
+      <c r="O62">
+        <v>1.8</v>
+      </c>
+      <c r="P62">
+        <v>6.9</v>
+      </c>
+      <c r="Q62">
+        <v>2.5</v>
+      </c>
+      <c r="R62">
+        <v>1.45</v>
+      </c>
+      <c r="S62">
+        <v>2.55</v>
+      </c>
+      <c r="T62">
         <v>3</v>
       </c>
-      <c r="O62">
-        <v>1.62</v>
-      </c>
-      <c r="P62">
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <v>2.3</v>
-      </c>
-      <c r="R62">
-        <v>1.25</v>
-      </c>
-      <c r="S62">
-        <v>3.6</v>
-      </c>
-      <c r="T62">
+      <c r="U62">
+        <v>1.33</v>
+      </c>
+      <c r="V62">
+        <v>8.4</v>
+      </c>
+      <c r="W62">
+        <v>1.04</v>
+      </c>
+      <c r="X62">
+        <v>1.04</v>
+      </c>
+      <c r="Y62">
+        <v>7</v>
+      </c>
+      <c r="Z62">
+        <v>1.42</v>
+      </c>
+      <c r="AA62">
+        <v>2.75</v>
+      </c>
+      <c r="AB62">
         <v>2.2</v>
       </c>
-      <c r="U62">
-        <v>1.6</v>
-      </c>
-      <c r="V62">
-        <v>4.75</v>
-      </c>
-      <c r="W62">
-        <v>1.15</v>
-      </c>
-      <c r="X62">
-        <v>1</v>
-      </c>
-      <c r="Y62">
-        <v>12</v>
-      </c>
-      <c r="Z62">
-        <v>1.15</v>
-      </c>
-      <c r="AA62">
-        <v>4.75</v>
-      </c>
-      <c r="AB62">
-        <v>1.5</v>
-      </c>
       <c r="AC62">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="AD62">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="AE62">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AF62">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG62">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AH62">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="AI62">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AJ62" t="s">
         <v>248</v>
@@ -8327,7 +8327,7 @@
         <v>57</v>
       </c>
       <c r="C63" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D63" t="s">
         <v>90</v>
@@ -8354,76 +8354,76 @@
         <v>247</v>
       </c>
       <c r="L63">
-        <v>3.7</v>
+        <v>2.17</v>
       </c>
       <c r="M63">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="N63">
-        <v>1.84</v>
+        <v>3.23</v>
       </c>
       <c r="O63">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="P63">
-        <v>9.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q63">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="R63">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="S63">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="T63">
-        <v>2.68</v>
+        <v>4.3</v>
       </c>
       <c r="U63">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="V63">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="W63">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X63">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Y63">
-        <v>10</v>
+        <v>5.75</v>
       </c>
       <c r="Z63">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AA63">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="AB63">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC63">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AD63">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="AE63">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AF63">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AG63">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AH63">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AI63">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AJ63" t="s">
         <v>248</v>
@@ -8443,7 +8443,7 @@
         <v>57</v>
       </c>
       <c r="C64" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D64" t="s">
         <v>90</v>
@@ -8559,7 +8559,7 @@
         <v>57</v>
       </c>
       <c r="C65" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D65" t="s">
         <v>90</v>
@@ -8586,76 +8586,76 @@
         <v>247</v>
       </c>
       <c r="L65">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="M65">
-        <v>2.96</v>
+        <v>3.9</v>
       </c>
       <c r="N65">
+        <v>3</v>
+      </c>
+      <c r="O65">
+        <v>1.62</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>2.3</v>
+      </c>
+      <c r="R65">
+        <v>1.25</v>
+      </c>
+      <c r="S65">
+        <v>3.6</v>
+      </c>
+      <c r="T65">
+        <v>2.2</v>
+      </c>
+      <c r="U65">
+        <v>1.6</v>
+      </c>
+      <c r="V65">
+        <v>4.75</v>
+      </c>
+      <c r="W65">
+        <v>1.15</v>
+      </c>
+      <c r="X65">
+        <v>1</v>
+      </c>
+      <c r="Y65">
+        <v>12</v>
+      </c>
+      <c r="Z65">
+        <v>1.15</v>
+      </c>
+      <c r="AA65">
+        <v>4.75</v>
+      </c>
+      <c r="AB65">
+        <v>1.5</v>
+      </c>
+      <c r="AC65">
         <v>2.4</v>
       </c>
-      <c r="O65">
-        <v>2.3</v>
-      </c>
-      <c r="P65">
-        <v>6.75</v>
-      </c>
-      <c r="Q65">
-        <v>1.91</v>
-      </c>
-      <c r="R65">
-        <v>1.44</v>
-      </c>
-      <c r="S65">
-        <v>2.62</v>
-      </c>
-      <c r="T65">
-        <v>3.2</v>
-      </c>
-      <c r="U65">
-        <v>1.29</v>
-      </c>
-      <c r="V65">
-        <v>8.5</v>
-      </c>
-      <c r="W65">
-        <v>1.02</v>
-      </c>
-      <c r="X65">
-        <v>1.09</v>
-      </c>
-      <c r="Y65">
-        <v>6.5</v>
-      </c>
-      <c r="Z65">
+      <c r="AD65">
+        <v>2.25</v>
+      </c>
+      <c r="AE65">
+        <v>1.57</v>
+      </c>
+      <c r="AF65">
         <v>1.5</v>
       </c>
-      <c r="AA65">
-        <v>2.45</v>
-      </c>
-      <c r="AB65">
-        <v>2.5</v>
-      </c>
-      <c r="AC65">
-        <v>1.46</v>
-      </c>
-      <c r="AD65">
-        <v>4.33</v>
-      </c>
-      <c r="AE65">
-        <v>1.18</v>
-      </c>
-      <c r="AF65">
-        <v>2</v>
-      </c>
       <c r="AG65">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AH65">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="AI65">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AJ65" t="s">
         <v>248</v>
@@ -8818,22 +8818,22 @@
         <v>247</v>
       </c>
       <c r="L67">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="M67">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="N67">
-        <v>3.94</v>
+        <v>4.7</v>
       </c>
       <c r="O67">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="P67">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q67">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R67">
         <v>1.65</v>
@@ -8842,10 +8842,10 @@
         <v>2.1</v>
       </c>
       <c r="T67">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U67">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V67">
         <v>10</v>
@@ -8860,31 +8860,31 @@
         <v>5.25</v>
       </c>
       <c r="Z67">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AA67">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB67">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC67">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AD67">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="AE67">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF67">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG67">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AH67">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AI67">
         <v>1</v>
@@ -8934,22 +8934,22 @@
         <v>247</v>
       </c>
       <c r="L68">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="M68">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="N68">
-        <v>4.7</v>
+        <v>3.94</v>
       </c>
       <c r="O68">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="P68">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q68">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R68">
         <v>1.65</v>
@@ -8958,10 +8958,10 @@
         <v>2.1</v>
       </c>
       <c r="T68">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U68">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V68">
         <v>10</v>
@@ -8976,31 +8976,31 @@
         <v>5.25</v>
       </c>
       <c r="Z68">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AA68">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB68">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC68">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AD68">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="AE68">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF68">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG68">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AH68">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AI68">
         <v>1</v>
@@ -9029,10 +9029,10 @@
         <v>90</v>
       </c>
       <c r="E69" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F69" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -9145,10 +9145,10 @@
         <v>90</v>
       </c>
       <c r="E70" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="F70" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -9487,7 +9487,7 @@
         <v>62</v>
       </c>
       <c r="C73" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D73" t="s">
         <v>90</v>
@@ -9514,76 +9514,76 @@
         <v>247</v>
       </c>
       <c r="L73">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="M73">
-        <v>3.11</v>
+        <v>3.36</v>
       </c>
       <c r="N73">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="O73">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="P73">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="Q73">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="R73">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S73">
         <v>2.4</v>
       </c>
       <c r="T73">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U73">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V73">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="W73">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X73">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y73">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Z73">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AA73">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AB73">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AC73">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AD73">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AE73">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF73">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AG73">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH73">
-        <v>11</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AI73">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ73" t="s">
         <v>248</v>
@@ -9603,7 +9603,7 @@
         <v>62</v>
       </c>
       <c r="C74" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D74" t="s">
         <v>90</v>
@@ -9630,76 +9630,76 @@
         <v>247</v>
       </c>
       <c r="L74">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="M74">
-        <v>3.36</v>
+        <v>3.11</v>
       </c>
       <c r="N74">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="O74">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="P74">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="Q74">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="R74">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S74">
         <v>2.4</v>
       </c>
       <c r="T74">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U74">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V74">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="W74">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X74">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y74">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Z74">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AA74">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AB74">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AC74">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AD74">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AE74">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF74">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG74">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AH74">
-        <v>8.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="AI74">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ74" t="s">
         <v>248</v>
@@ -9746,34 +9746,34 @@
         <v>247</v>
       </c>
       <c r="L75">
-        <v>1.78</v>
+        <v>2.37</v>
       </c>
       <c r="M75">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="N75">
-        <v>4.4</v>
+        <v>3.19</v>
       </c>
       <c r="O75">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="P75">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q75">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="R75">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S75">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T75">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U75">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V75">
         <v>10</v>
@@ -9782,7 +9782,7 @@
         <v>1.02</v>
       </c>
       <c r="X75">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y75">
         <v>5.75</v>
@@ -9800,22 +9800,22 @@
         <v>1.48</v>
       </c>
       <c r="AD75">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AE75">
         <v>1.13</v>
       </c>
       <c r="AF75">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG75">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH75">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI75">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ75" t="s">
         <v>248</v>
@@ -9835,16 +9835,16 @@
         <v>63</v>
       </c>
       <c r="C76" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D76" t="s">
         <v>90</v>
       </c>
       <c r="E76" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="F76" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -9862,76 +9862,76 @@
         <v>247</v>
       </c>
       <c r="L76">
-        <v>2.37</v>
+        <v>2.8</v>
       </c>
       <c r="M76">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="N76">
-        <v>3.19</v>
+        <v>2.55</v>
       </c>
       <c r="O76">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="P76">
-        <v>6</v>
+        <v>7.75</v>
       </c>
       <c r="Q76">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="R76">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S76">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="T76">
+        <v>3</v>
+      </c>
+      <c r="U76">
+        <v>1.36</v>
+      </c>
+      <c r="V76">
+        <v>9</v>
+      </c>
+      <c r="W76">
+        <v>1.07</v>
+      </c>
+      <c r="X76">
+        <v>1.07</v>
+      </c>
+      <c r="Y76">
+        <v>8</v>
+      </c>
+      <c r="Z76">
+        <v>1.35</v>
+      </c>
+      <c r="AA76">
+        <v>3.1</v>
+      </c>
+      <c r="AB76">
+        <v>2.08</v>
+      </c>
+      <c r="AC76">
+        <v>1.73</v>
+      </c>
+      <c r="AD76">
         <v>3.6</v>
       </c>
-      <c r="U76">
-        <v>1.25</v>
-      </c>
-      <c r="V76">
-        <v>10</v>
-      </c>
-      <c r="W76">
-        <v>1.02</v>
-      </c>
-      <c r="X76">
-        <v>1.1</v>
-      </c>
-      <c r="Y76">
-        <v>5.75</v>
-      </c>
-      <c r="Z76">
-        <v>1.55</v>
-      </c>
-      <c r="AA76">
-        <v>2.3</v>
-      </c>
-      <c r="AB76">
-        <v>2.37</v>
-      </c>
-      <c r="AC76">
-        <v>1.48</v>
-      </c>
-      <c r="AD76">
-        <v>4.8</v>
-      </c>
       <c r="AE76">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AF76">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AG76">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AH76">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AI76">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AJ76" t="s">
         <v>248</v>
@@ -9951,16 +9951,16 @@
         <v>63</v>
       </c>
       <c r="C77" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D77" t="s">
         <v>90</v>
       </c>
       <c r="E77" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="F77" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -9978,76 +9978,76 @@
         <v>247</v>
       </c>
       <c r="L77">
-        <v>2.8</v>
+        <v>1.78</v>
       </c>
       <c r="M77">
         <v>3.1</v>
       </c>
       <c r="N77">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="O77">
+        <v>1.63</v>
+      </c>
+      <c r="P77">
+        <v>6.5</v>
+      </c>
+      <c r="Q77">
+        <v>2.87</v>
+      </c>
+      <c r="R77">
+        <v>1.62</v>
+      </c>
+      <c r="S77">
         <v>2.2</v>
       </c>
-      <c r="P77">
-        <v>7.75</v>
-      </c>
-      <c r="Q77">
-        <v>1.83</v>
-      </c>
-      <c r="R77">
-        <v>1.44</v>
-      </c>
-      <c r="S77">
-        <v>2.63</v>
-      </c>
       <c r="T77">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="U77">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="V77">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W77">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X77">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y77">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="Z77">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AA77">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB77">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="AC77">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AD77">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="AE77">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AF77">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AG77">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AH77">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AI77">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AJ77" t="s">
         <v>248</v>
@@ -10183,7 +10183,7 @@
         <v>65</v>
       </c>
       <c r="C79" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D79" t="s">
         <v>90</v>
@@ -10299,16 +10299,16 @@
         <v>66</v>
       </c>
       <c r="C80" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D80" t="s">
         <v>90</v>
       </c>
       <c r="E80" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="F80" t="s">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -10326,76 +10326,76 @@
         <v>247</v>
       </c>
       <c r="L80">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="M80">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="N80">
-        <v>4.2</v>
+        <v>2.76</v>
       </c>
       <c r="O80">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="P80">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R80">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S80">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T80">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U80">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V80">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W80">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X80">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y80">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z80">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA80">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB80">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AC80">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AD80">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF80">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG80">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH80">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI80">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ80" t="s">
         <v>248</v>
@@ -10415,16 +10415,16 @@
         <v>66</v>
       </c>
       <c r="C81" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D81" t="s">
         <v>90</v>
       </c>
       <c r="E81" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="F81" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -10442,76 +10442,76 @@
         <v>247</v>
       </c>
       <c r="L81">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="M81">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="N81">
-        <v>2.76</v>
+        <v>4.2</v>
       </c>
       <c r="O81">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q81">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB81">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AC81">
+        <v>1.55</v>
+      </c>
+      <c r="AD81">
+        <v>4.5</v>
+      </c>
+      <c r="AE81">
+        <v>1.2</v>
+      </c>
+      <c r="AF81">
+        <v>2.05</v>
+      </c>
+      <c r="AG81">
         <v>1.7</v>
       </c>
-      <c r="AD81">
-        <v>0</v>
-      </c>
-      <c r="AE81">
-        <v>0</v>
-      </c>
-      <c r="AF81">
-        <v>0</v>
-      </c>
-      <c r="AG81">
-        <v>0</v>
-      </c>
       <c r="AH81">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI81">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ81" t="s">
         <v>248</v>
@@ -10531,7 +10531,7 @@
         <v>67</v>
       </c>
       <c r="C82" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D82" t="s">
         <v>90</v>
@@ -10647,7 +10647,7 @@
         <v>68</v>
       </c>
       <c r="C83" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D83" t="s">
         <v>90</v>
@@ -10674,76 +10674,76 @@
         <v>247</v>
       </c>
       <c r="L83">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="M83">
+        <v>3.8</v>
+      </c>
+      <c r="N83">
         <v>3.6</v>
       </c>
-      <c r="N83">
-        <v>2.55</v>
-      </c>
       <c r="O83">
+        <v>1.53</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>2.5</v>
+      </c>
+      <c r="R83">
+        <v>1.18</v>
+      </c>
+      <c r="S83">
+        <v>4.33</v>
+      </c>
+      <c r="T83">
+        <v>1.85</v>
+      </c>
+      <c r="U83">
+        <v>1.85</v>
+      </c>
+      <c r="V83">
+        <v>3.6</v>
+      </c>
+      <c r="W83">
+        <v>1.25</v>
+      </c>
+      <c r="X83">
+        <v>0</v>
+      </c>
+      <c r="Y83">
+        <v>0</v>
+      </c>
+      <c r="Z83">
+        <v>1.07</v>
+      </c>
+      <c r="AA83">
+        <v>7</v>
+      </c>
+      <c r="AB83">
+        <v>1.29</v>
+      </c>
+      <c r="AC83">
+        <v>3.3</v>
+      </c>
+      <c r="AD83">
         <v>1.73</v>
       </c>
-      <c r="P83">
-        <v>0</v>
-      </c>
-      <c r="Q83">
-        <v>2.05</v>
-      </c>
-      <c r="R83">
-        <v>1.22</v>
-      </c>
-      <c r="S83">
-        <v>3.8</v>
-      </c>
-      <c r="T83">
-        <v>2.05</v>
-      </c>
-      <c r="U83">
-        <v>1.7</v>
-      </c>
-      <c r="V83">
-        <v>4.33</v>
-      </c>
-      <c r="W83">
-        <v>1.18</v>
-      </c>
-      <c r="X83">
-        <v>0</v>
-      </c>
-      <c r="Y83">
-        <v>0</v>
-      </c>
-      <c r="Z83">
-        <v>1.11</v>
-      </c>
-      <c r="AA83">
-        <v>5.5</v>
-      </c>
-      <c r="AB83">
+      <c r="AE83">
+        <v>2</v>
+      </c>
+      <c r="AF83">
+        <v>1.33</v>
+      </c>
+      <c r="AG83">
+        <v>3</v>
+      </c>
+      <c r="AH83">
+        <v>2.62</v>
+      </c>
+      <c r="AI83">
         <v>1.42</v>
-      </c>
-      <c r="AC83">
-        <v>2.62</v>
-      </c>
-      <c r="AD83">
-        <v>2.04</v>
-      </c>
-      <c r="AE83">
-        <v>1.7</v>
-      </c>
-      <c r="AF83">
-        <v>1.39</v>
-      </c>
-      <c r="AG83">
-        <v>2.85</v>
-      </c>
-      <c r="AH83">
-        <v>3.3</v>
-      </c>
-      <c r="AI83">
-        <v>1.29</v>
       </c>
       <c r="AJ83" t="s">
         <v>248</v>
@@ -10763,7 +10763,7 @@
         <v>68</v>
       </c>
       <c r="C84" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D84" t="s">
         <v>90</v>
@@ -10790,41 +10790,41 @@
         <v>247</v>
       </c>
       <c r="L84">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="M84">
+        <v>3.6</v>
+      </c>
+      <c r="N84">
+        <v>2.55</v>
+      </c>
+      <c r="O84">
+        <v>1.73</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>2.05</v>
+      </c>
+      <c r="R84">
+        <v>1.22</v>
+      </c>
+      <c r="S84">
         <v>3.8</v>
       </c>
-      <c r="N84">
-        <v>3.6</v>
-      </c>
-      <c r="O84">
-        <v>1.53</v>
-      </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
-      <c r="Q84">
-        <v>2.5</v>
-      </c>
-      <c r="R84">
+      <c r="T84">
+        <v>2.05</v>
+      </c>
+      <c r="U84">
+        <v>1.7</v>
+      </c>
+      <c r="V84">
+        <v>4.33</v>
+      </c>
+      <c r="W84">
         <v>1.18</v>
       </c>
-      <c r="S84">
-        <v>4.33</v>
-      </c>
-      <c r="T84">
-        <v>1.85</v>
-      </c>
-      <c r="U84">
-        <v>1.85</v>
-      </c>
-      <c r="V84">
-        <v>3.6</v>
-      </c>
-      <c r="W84">
-        <v>1.25</v>
-      </c>
       <c r="X84">
         <v>0</v>
       </c>
@@ -10832,34 +10832,34 @@
         <v>0</v>
       </c>
       <c r="Z84">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AA84">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AB84">
+        <v>1.42</v>
+      </c>
+      <c r="AC84">
+        <v>2.62</v>
+      </c>
+      <c r="AD84">
+        <v>2.04</v>
+      </c>
+      <c r="AE84">
+        <v>1.7</v>
+      </c>
+      <c r="AF84">
+        <v>1.39</v>
+      </c>
+      <c r="AG84">
+        <v>2.85</v>
+      </c>
+      <c r="AH84">
+        <v>3.3</v>
+      </c>
+      <c r="AI84">
         <v>1.29</v>
-      </c>
-      <c r="AC84">
-        <v>3.3</v>
-      </c>
-      <c r="AD84">
-        <v>1.73</v>
-      </c>
-      <c r="AE84">
-        <v>2</v>
-      </c>
-      <c r="AF84">
-        <v>1.33</v>
-      </c>
-      <c r="AG84">
-        <v>3</v>
-      </c>
-      <c r="AH84">
-        <v>2.62</v>
-      </c>
-      <c r="AI84">
-        <v>1.42</v>
       </c>
       <c r="AJ84" t="s">
         <v>248</v>

--- a/jogos_2025-07-20.xlsx
+++ b/jogos_2025-07-20.xlsx
@@ -244,12 +244,12 @@
     <t>Japan J1 League</t>
   </si>
   <si>
+    <t>South Korea K League 2</t>
+  </si>
+  <si>
     <t>South Korea K League 1</t>
   </si>
   <si>
-    <t>South Korea K League 2</t>
-  </si>
-  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
@@ -262,18 +262,18 @@
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Finland Veikkausliiga</t>
+    <t>Brazil Serie A</t>
   </si>
   <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
@@ -286,15 +286,15 @@
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
@@ -307,12 +307,12 @@
     <t>Sacramento Republic</t>
   </si>
   <si>
+    <t>APIA Leichhardt Tigers</t>
+  </si>
+  <si>
     <t>Central Coast II</t>
   </si>
   <si>
-    <t>APIA Leichhardt Tigers</t>
-  </si>
-  <si>
     <t>Sydney Olympic</t>
   </si>
   <si>
@@ -325,10 +325,19 @@
     <t>Shimizu S-Pulse</t>
   </si>
   <si>
+    <t>Fagiano Okayama</t>
+  </si>
+  <si>
+    <t>Bucheon 1995</t>
+  </si>
+  <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
     <t>Albirex Niigata</t>
   </si>
   <si>
-    <t>FC Seoul</t>
+    <t>Yokohama F. Marinos</t>
   </si>
   <si>
     <t>Cheongju</t>
@@ -337,30 +346,21 @@
     <t>Gamba Osaka</t>
   </si>
   <si>
-    <t>Fagiano Okayama</t>
-  </si>
-  <si>
     <t>Gyeongnam</t>
   </si>
   <si>
-    <t>Bucheon 1995</t>
-  </si>
-  <si>
-    <t>Yokohama F. Marinos</t>
-  </si>
-  <si>
     <t>Varberg</t>
   </si>
   <si>
+    <t>Shenzhen Juniors</t>
+  </si>
+  <si>
     <t>Nanjing City</t>
   </si>
   <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
-    <t>Shenzhen Juniors</t>
-  </si>
-  <si>
     <t>Mjällby</t>
   </si>
   <si>
@@ -370,90 +370,90 @@
     <t>Vålerenga</t>
   </si>
   <si>
+    <t>SJK</t>
+  </si>
+  <si>
+    <t>Kalmar</t>
+  </si>
+  <si>
     <t>Kyzyl-Zhar</t>
   </si>
   <si>
-    <t>Kalmar</t>
-  </si>
-  <si>
-    <t>SJK</t>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
   </si>
   <si>
     <t>Nõmme Kalju</t>
   </si>
   <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
-    <t>Internacional</t>
-  </si>
-  <si>
     <t>Hammarby</t>
   </si>
   <si>
     <t>Halmstad</t>
   </si>
   <si>
+    <t>Godoy Cruz</t>
+  </si>
+  <si>
     <t>Lanús</t>
   </si>
   <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Tigre</t>
+  </si>
+  <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>Boca Juniors</t>
+  </si>
+  <si>
+    <t>Atlético Tucumán</t>
+  </si>
+  <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Independiente</t>
+  </si>
+  <si>
     <t>Newell's Old Boys</t>
   </si>
   <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Platense</t>
+  </si>
+  <si>
     <t>Tromsø</t>
   </si>
   <si>
-    <t>Instituto</t>
-  </si>
-  <si>
-    <t>Godoy Cruz</t>
+    <t>Barracas Central</t>
   </si>
   <si>
     <t>Defensa y Justicia</t>
   </si>
   <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Atlético Tucumán</t>
-  </si>
-  <si>
-    <t>Estudiantes</t>
-  </si>
-  <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
-    <t>Independiente</t>
-  </si>
-  <si>
-    <t>San Lorenzo</t>
-  </si>
-  <si>
-    <t>Barracas Central</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Platense</t>
-  </si>
-  <si>
-    <t>Boca Juniors</t>
-  </si>
-  <si>
-    <t>Tigre</t>
-  </si>
-  <si>
-    <t>Aktobe</t>
+    <t>HJK</t>
   </si>
   <si>
     <t>Jaro</t>
   </si>
   <si>
-    <t>HJK</t>
-  </si>
-  <si>
     <t>Paide</t>
   </si>
   <si>
@@ -475,45 +475,45 @@
     <t>Gimnasia Mendoza</t>
   </si>
   <si>
+    <t>Patronato</t>
+  </si>
+  <si>
+    <t>Club Atlético Güemes</t>
+  </si>
+  <si>
     <t>Almirante Brown</t>
   </si>
   <si>
-    <t>Patronato</t>
-  </si>
-  <si>
-    <t>Club Atlético Güemes</t>
+    <t>Toronto II</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>Vitória</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
+    <t>Gimnasia Jujuy</t>
+  </si>
+  <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>New England II</t>
   </si>
   <si>
     <t>Valour FC</t>
   </si>
   <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Gimnasia Jujuy</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
+    <t>Ñublense</t>
   </si>
   <si>
     <t>Cruzeiro</t>
   </si>
   <si>
-    <t>Defensores de Belgrano</t>
-  </si>
-  <si>
-    <t>Vitória</t>
-  </si>
-  <si>
-    <t>Ñublense</t>
-  </si>
-  <si>
-    <t>New England II</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
@@ -529,18 +529,18 @@
     <t>Sport Recife</t>
   </si>
   <si>
+    <t>Central Norte</t>
+  </si>
+  <si>
     <t>Nueva Chicago</t>
   </si>
   <si>
-    <t>Central Norte</t>
+    <t>Deportes Temuco</t>
   </si>
   <si>
     <t>América Mineiro</t>
   </si>
   <si>
-    <t>Deportes Temuco</t>
-  </si>
-  <si>
     <t>Ypiranga Erechim</t>
   </si>
   <si>
@@ -568,12 +568,12 @@
     <t>Lexington</t>
   </si>
   <si>
+    <t>Sydney United</t>
+  </si>
+  <si>
     <t>St. George Saints</t>
   </si>
   <si>
-    <t>Sydney United</t>
-  </si>
-  <si>
     <t>Mt Druitt Town</t>
   </si>
   <si>
@@ -586,10 +586,19 @@
     <t>Yokohama</t>
   </si>
   <si>
+    <t>Vissel Kobe</t>
+  </si>
+  <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
+    <t>Ulsan</t>
+  </si>
+  <si>
     <t>Sanfrecce Hiroshima</t>
   </si>
   <si>
-    <t>Ulsan</t>
+    <t>Nagoya Grampus</t>
   </si>
   <si>
     <t>Cheonan City</t>
@@ -598,30 +607,21 @@
     <t>Kawasaki Frontale</t>
   </si>
   <si>
-    <t>Vissel Kobe</t>
-  </si>
-  <si>
     <t>Incheon United</t>
   </si>
   <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Nagoya Grampus</t>
-  </si>
-  <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
+    <t>Shanghai Jiading</t>
+  </si>
+  <si>
     <t>Guangxi Baoyun</t>
   </si>
   <si>
     <t>Shaanxi Union</t>
   </si>
   <si>
-    <t>Shanghai Jiading</t>
-  </si>
-  <si>
     <t>AIK</t>
   </si>
   <si>
@@ -631,90 +631,90 @@
     <t>Haugesund</t>
   </si>
   <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
     <t>Atyrau</t>
   </si>
   <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Gnistan</t>
+    <t>Ceará</t>
+  </si>
+  <si>
+    <t>Tallinna FC Flora</t>
   </si>
   <si>
     <t>Tallinna Kalev</t>
   </si>
   <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
-    <t>Ceará</t>
-  </si>
-  <si>
     <t>Brommapojkarna</t>
   </si>
   <si>
     <t>Häcken</t>
   </si>
   <si>
+    <t>Sarmiento</t>
+  </si>
+  <si>
     <t>Rosario Central</t>
   </si>
   <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Argentinos Juniors</t>
+  </si>
+  <si>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Gimnasia La Plata</t>
+  </si>
+  <si>
+    <t>Unión Santa Fe</t>
+  </si>
+  <si>
+    <t>Central Córdoba SdE</t>
+  </si>
+  <si>
+    <t>Racing Club</t>
+  </si>
+  <si>
+    <t>Talleres Córdoba</t>
+  </si>
+  <si>
     <t>Banfield</t>
   </si>
   <si>
+    <t>River Plate</t>
+  </si>
+  <si>
+    <t>Huracán</t>
+  </si>
+  <si>
+    <t>Vélez Sarsfield</t>
+  </si>
+  <si>
     <t>Bryne</t>
   </si>
   <si>
-    <t>River Plate</t>
-  </si>
-  <si>
-    <t>Sarmiento</t>
+    <t>Independiente Rivadavia</t>
   </si>
   <si>
     <t>Aldosivi</t>
   </si>
   <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Central Córdoba SdE</t>
-  </si>
-  <si>
-    <t>Huracán</t>
-  </si>
-  <si>
-    <t>Racing Club</t>
-  </si>
-  <si>
-    <t>Talleres Córdoba</t>
-  </si>
-  <si>
-    <t>Gimnasia La Plata</t>
-  </si>
-  <si>
-    <t>Independiente Rivadavia</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Vélez Sarsfield</t>
-  </si>
-  <si>
-    <t>Unión Santa Fe</t>
-  </si>
-  <si>
-    <t>Argentinos Juniors</t>
-  </si>
-  <si>
-    <t>Tobol</t>
+    <t>Oulu</t>
   </si>
   <si>
     <t>Ilves</t>
   </si>
   <si>
-    <t>Oulu</t>
-  </si>
-  <si>
     <t>Trans</t>
   </si>
   <si>
@@ -736,45 +736,45 @@
     <t>Temperley</t>
   </si>
   <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
     <t>Club Atlético Mitre</t>
   </si>
   <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>Gimnasia y Tiro</t>
+    <t>Chicago Fire II</t>
+  </si>
+  <si>
+    <t>Univ. Concepción</t>
+  </si>
+  <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
+    <t>Estudiantes Río Cuarto</t>
+  </si>
+  <si>
+    <t>Defensores Unidos</t>
+  </si>
+  <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
+    <t>Orlando City II</t>
   </si>
   <si>
     <t>Cavalry FC</t>
   </si>
   <si>
-    <t>Botafogo SP</t>
-  </si>
-  <si>
-    <t>Defensores Unidos</t>
-  </si>
-  <si>
-    <t>Chicago Fire II</t>
+    <t>Universidad Chile</t>
   </si>
   <si>
     <t>Juventude</t>
   </si>
   <si>
-    <t>Estudiantes Río Cuarto</t>
-  </si>
-  <si>
-    <t>Bragantino</t>
-  </si>
-  <si>
-    <t>Universidad Chile</t>
-  </si>
-  <si>
-    <t>Orlando City II</t>
-  </si>
-  <si>
-    <t>Univ. Concepción</t>
-  </si>
-  <si>
     <t>Valur</t>
   </si>
   <si>
@@ -790,16 +790,16 @@
     <t>Botafogo</t>
   </si>
   <si>
+    <t>Colón</t>
+  </si>
+  <si>
     <t>Chaco For Ever</t>
   </si>
   <si>
-    <t>Colón</t>
+    <t>Santiago Morning</t>
   </si>
   <si>
     <t>Chapecoense</t>
-  </si>
-  <si>
-    <t>Santiago Morning</t>
   </si>
   <si>
     <t>São Bernardo</t>
@@ -1350,13 +1350,13 @@
         <v>270</v>
       </c>
       <c r="L2">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="M2">
-        <v>3.63</v>
+        <v>3.47</v>
       </c>
       <c r="N2">
-        <v>4.93</v>
+        <v>4.33</v>
       </c>
       <c r="O2">
         <v>1.5</v>
@@ -1374,34 +1374,34 @@
         <v>2.7</v>
       </c>
       <c r="T2">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="U2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z2">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AA2">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB2">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC2">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AD2">
         <v>3.6</v>
@@ -1410,16 +1410,16 @@
         <v>1.25</v>
       </c>
       <c r="AF2">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG2">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AH2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="AI2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AJ2" t="s">
         <v>272</v>
@@ -1466,76 +1466,76 @@
         <v>270</v>
       </c>
       <c r="L3">
-        <v>4.15</v>
+        <v>1.53</v>
       </c>
       <c r="M3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="N3">
-        <v>1.62</v>
+        <v>4.9</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>18.25</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB3">
+        <v>1.47</v>
+      </c>
+      <c r="AC3">
+        <v>2.45</v>
+      </c>
+      <c r="AD3">
+        <v>2.35</v>
+      </c>
+      <c r="AE3">
+        <v>1.57</v>
+      </c>
+      <c r="AF3">
         <v>1.6</v>
       </c>
-      <c r="AC3">
-        <v>2.3</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AJ3" t="s">
         <v>272</v>
@@ -1582,76 +1582,76 @@
         <v>270</v>
       </c>
       <c r="L4">
-        <v>1.53</v>
+        <v>4.15</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="N4">
-        <v>4.9</v>
+        <v>1.62</v>
       </c>
       <c r="O4">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>18.25</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AC4">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AD4">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="s">
         <v>272</v>
@@ -2162,76 +2162,76 @@
         <v>270</v>
       </c>
       <c r="L9">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="M9">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="N9">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="O9">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P9">
+        <v>7.5</v>
+      </c>
+      <c r="Q9">
+        <v>1.58</v>
+      </c>
+      <c r="R9">
+        <v>1.46</v>
+      </c>
+      <c r="S9">
+        <v>2.5</v>
+      </c>
+      <c r="T9">
+        <v>3.1</v>
+      </c>
+      <c r="U9">
+        <v>1.31</v>
+      </c>
+      <c r="V9">
         <v>8.75</v>
       </c>
-      <c r="Q9">
-        <v>1.53</v>
-      </c>
-      <c r="R9">
+      <c r="W9">
+        <v>1.06</v>
+      </c>
+      <c r="X9">
+        <v>1.08</v>
+      </c>
+      <c r="Y9">
+        <v>7.5</v>
+      </c>
+      <c r="Z9">
         <v>1.4</v>
       </c>
-      <c r="S9">
-        <v>2.75</v>
-      </c>
-      <c r="T9">
-        <v>2.75</v>
-      </c>
-      <c r="U9">
-        <v>1.4</v>
-      </c>
-      <c r="V9">
-        <v>8</v>
-      </c>
-      <c r="W9">
-        <v>1.08</v>
-      </c>
-      <c r="X9">
+      <c r="AA9">
+        <v>2.7</v>
+      </c>
+      <c r="AB9">
+        <v>2.13</v>
+      </c>
+      <c r="AC9">
+        <v>1.63</v>
+      </c>
+      <c r="AD9">
+        <v>4</v>
+      </c>
+      <c r="AE9">
+        <v>1.21</v>
+      </c>
+      <c r="AF9">
+        <v>2.1</v>
+      </c>
+      <c r="AG9">
+        <v>1.65</v>
+      </c>
+      <c r="AH9">
+        <v>8.25</v>
+      </c>
+      <c r="AI9">
         <v>1.06</v>
-      </c>
-      <c r="Y9">
-        <v>8.5</v>
-      </c>
-      <c r="Z9">
-        <v>1.33</v>
-      </c>
-      <c r="AA9">
-        <v>3.25</v>
-      </c>
-      <c r="AB9">
-        <v>1.94</v>
-      </c>
-      <c r="AC9">
-        <v>1.76</v>
-      </c>
-      <c r="AD9">
-        <v>3.5</v>
-      </c>
-      <c r="AE9">
-        <v>1.28</v>
-      </c>
-      <c r="AF9">
-        <v>1.91</v>
-      </c>
-      <c r="AG9">
-        <v>1.91</v>
-      </c>
-      <c r="AH9">
-        <v>7</v>
-      </c>
-      <c r="AI9">
-        <v>1.09</v>
       </c>
       <c r="AJ9" t="s">
         <v>272</v>
@@ -2278,76 +2278,76 @@
         <v>270</v>
       </c>
       <c r="L10">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="M10">
-        <v>3.13</v>
+        <v>3.32</v>
       </c>
       <c r="N10">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="O10">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="P10">
-        <v>7.75</v>
+        <v>9.1</v>
       </c>
       <c r="Q10">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="R10">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S10">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="T10">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="Z10">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AA10">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="AB10">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AC10">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AD10">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AE10">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF10">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH10">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AI10">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AJ10" t="s">
         <v>272</v>
@@ -2394,76 +2394,76 @@
         <v>270</v>
       </c>
       <c r="L11">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="M11">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="N11">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="O11">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="P11">
-        <v>10.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q11">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="R11">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S11">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="T11">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V11">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="Z11">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AA11">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="AB11">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC11">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD11">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AE11">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH11">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AI11">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AJ11" t="s">
         <v>272</v>
@@ -2510,76 +2510,76 @@
         <v>270</v>
       </c>
       <c r="L12">
-        <v>2.47</v>
+        <v>3.99</v>
       </c>
       <c r="M12">
-        <v>3.23</v>
+        <v>3.36</v>
       </c>
       <c r="N12">
-        <v>2.47</v>
+        <v>1.75</v>
       </c>
       <c r="O12">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="P12">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q12">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="R12">
+        <v>1.4</v>
+      </c>
+      <c r="S12">
+        <v>2.75</v>
+      </c>
+      <c r="T12">
+        <v>2.75</v>
+      </c>
+      <c r="U12">
+        <v>1.4</v>
+      </c>
+      <c r="V12">
+        <v>8</v>
+      </c>
+      <c r="W12">
+        <v>1.08</v>
+      </c>
+      <c r="X12">
+        <v>1.06</v>
+      </c>
+      <c r="Y12">
+        <v>8.5</v>
+      </c>
+      <c r="Z12">
         <v>1.33</v>
       </c>
-      <c r="S12">
+      <c r="AA12">
         <v>3.25</v>
       </c>
-      <c r="T12">
-        <v>2.63</v>
-      </c>
-      <c r="U12">
-        <v>1.44</v>
-      </c>
-      <c r="V12">
-        <v>6.5</v>
-      </c>
-      <c r="W12">
-        <v>1.11</v>
-      </c>
-      <c r="X12">
-        <v>1.05</v>
-      </c>
-      <c r="Y12">
-        <v>9.5</v>
-      </c>
-      <c r="Z12">
-        <v>1.25</v>
-      </c>
-      <c r="AA12">
-        <v>3.7</v>
-      </c>
       <c r="AB12">
+        <v>1.94</v>
+      </c>
+      <c r="AC12">
         <v>1.76</v>
       </c>
-      <c r="AC12">
-        <v>1.94</v>
-      </c>
       <c r="AD12">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AE12">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AF12">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AG12">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH12">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AI12">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AJ12" t="s">
         <v>272</v>
@@ -2626,76 +2626,76 @@
         <v>270</v>
       </c>
       <c r="L13">
-        <v>4.6</v>
+        <v>2.79</v>
       </c>
       <c r="M13">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="N13">
-        <v>1.68</v>
+        <v>2.29</v>
       </c>
       <c r="O13">
+        <v>2.1</v>
+      </c>
+      <c r="P13">
+        <v>8.25</v>
+      </c>
+      <c r="Q13">
+        <v>1.9</v>
+      </c>
+      <c r="R13">
+        <v>1.41</v>
+      </c>
+      <c r="S13">
+        <v>2.65</v>
+      </c>
+      <c r="T13">
         <v>2.85</v>
       </c>
-      <c r="P13">
+      <c r="U13">
+        <v>1.37</v>
+      </c>
+      <c r="V13">
         <v>7.5</v>
       </c>
-      <c r="Q13">
-        <v>1.58</v>
-      </c>
-      <c r="R13">
-        <v>1.46</v>
-      </c>
-      <c r="S13">
-        <v>2.5</v>
-      </c>
-      <c r="T13">
+      <c r="W13">
+        <v>1.08</v>
+      </c>
+      <c r="X13">
+        <v>1.06</v>
+      </c>
+      <c r="Y13">
+        <v>8.25</v>
+      </c>
+      <c r="Z13">
+        <v>1.32</v>
+      </c>
+      <c r="AA13">
         <v>3.1</v>
       </c>
-      <c r="U13">
-        <v>1.31</v>
-      </c>
-      <c r="V13">
-        <v>8.75</v>
-      </c>
-      <c r="W13">
-        <v>1.06</v>
-      </c>
-      <c r="X13">
-        <v>1.08</v>
-      </c>
-      <c r="Y13">
-        <v>7.5</v>
-      </c>
-      <c r="Z13">
-        <v>1.4</v>
-      </c>
-      <c r="AA13">
-        <v>2.7</v>
-      </c>
       <c r="AB13">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="AC13">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AD13">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AE13">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AF13">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AG13">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AH13">
-        <v>8.25</v>
+        <v>6.5</v>
       </c>
       <c r="AI13">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AJ13" t="s">
         <v>272</v>
@@ -2715,7 +2715,7 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
         <v>95</v>
@@ -2742,76 +2742,76 @@
         <v>270</v>
       </c>
       <c r="L14">
-        <v>5.5</v>
+        <v>2.18</v>
       </c>
       <c r="M14">
-        <v>4.1</v>
+        <v>3.12</v>
       </c>
       <c r="N14">
-        <v>1.44</v>
+        <v>2.93</v>
       </c>
       <c r="O14">
-        <v>3.2</v>
+        <v>1.79</v>
       </c>
       <c r="P14">
-        <v>15.25</v>
+        <v>10.5</v>
       </c>
       <c r="Q14">
+        <v>2.16</v>
+      </c>
+      <c r="R14">
+        <v>1.4</v>
+      </c>
+      <c r="S14">
+        <v>2.8</v>
+      </c>
+      <c r="T14">
+        <v>2.9</v>
+      </c>
+      <c r="U14">
         <v>1.36</v>
       </c>
-      <c r="R14">
-        <v>1.3</v>
-      </c>
-      <c r="S14">
-        <v>3.25</v>
-      </c>
-      <c r="T14">
-        <v>2.45</v>
-      </c>
-      <c r="U14">
-        <v>1.5</v>
-      </c>
       <c r="V14">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Z14">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AA14">
-        <v>4.05</v>
+        <v>3.08</v>
       </c>
       <c r="AB14">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AD14">
-        <v>2.59</v>
+        <v>3.58</v>
       </c>
       <c r="AE14">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="AF14">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH14">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="AI14">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AJ14" t="s">
         <v>272</v>
@@ -2831,7 +2831,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
         <v>95</v>
@@ -2858,76 +2858,76 @@
         <v>270</v>
       </c>
       <c r="L15">
-        <v>2.16</v>
+        <v>2.47</v>
       </c>
       <c r="M15">
-        <v>3.32</v>
+        <v>3.23</v>
       </c>
       <c r="N15">
-        <v>3.08</v>
+        <v>2.47</v>
       </c>
       <c r="O15">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="P15">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="R15">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S15">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="T15">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="U15">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="Z15">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AA15">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="AB15">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC15">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AD15">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AE15">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AF15">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH15">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AI15">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AJ15" t="s">
         <v>272</v>
@@ -2947,7 +2947,7 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
         <v>95</v>
@@ -2974,76 +2974,76 @@
         <v>270</v>
       </c>
       <c r="L16">
-        <v>2.79</v>
+        <v>5.5</v>
       </c>
       <c r="M16">
-        <v>3.08</v>
+        <v>4.1</v>
       </c>
       <c r="N16">
-        <v>2.29</v>
+        <v>1.44</v>
       </c>
       <c r="O16">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>8.25</v>
+        <v>15.25</v>
       </c>
       <c r="Q16">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="R16">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="S16">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="T16">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="U16">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="V16">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>8.25</v>
+        <v>13</v>
       </c>
       <c r="Z16">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AA16">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="AB16">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="AC16">
-        <v>1.74</v>
+        <v>2.01</v>
       </c>
       <c r="AD16">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="AE16">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AF16">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH16">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="AI16">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AJ16" t="s">
         <v>272</v>
@@ -3206,76 +3206,76 @@
         <v>270</v>
       </c>
       <c r="L18">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="M18">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="N18">
-        <v>6</v>
+        <v>2.75</v>
       </c>
       <c r="O18">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="P18">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Q18">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="R18">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S18">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="T18">
-        <v>2.6</v>
+        <v>3.09</v>
       </c>
       <c r="U18">
+        <v>1.27</v>
+      </c>
+      <c r="V18">
+        <v>8.5</v>
+      </c>
+      <c r="W18">
+        <v>1.07</v>
+      </c>
+      <c r="X18">
+        <v>1.06</v>
+      </c>
+      <c r="Y18">
+        <v>8</v>
+      </c>
+      <c r="Z18">
         <v>1.42</v>
       </c>
-      <c r="V18">
-        <v>6</v>
-      </c>
-      <c r="W18">
-        <v>1.09</v>
-      </c>
-      <c r="X18">
-        <v>1.05</v>
-      </c>
-      <c r="Y18">
-        <v>11</v>
-      </c>
-      <c r="Z18">
-        <v>1.22</v>
-      </c>
       <c r="AA18">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="AB18">
+        <v>2.25</v>
+      </c>
+      <c r="AC18">
+        <v>1.55</v>
+      </c>
+      <c r="AD18">
+        <v>3.6</v>
+      </c>
+      <c r="AE18">
+        <v>1.24</v>
+      </c>
+      <c r="AF18">
+        <v>1.91</v>
+      </c>
+      <c r="AG18">
         <v>1.85</v>
       </c>
-      <c r="AC18">
-        <v>1.85</v>
-      </c>
-      <c r="AD18">
-        <v>3.15</v>
-      </c>
-      <c r="AE18">
-        <v>1.33</v>
-      </c>
-      <c r="AF18">
-        <v>1.95</v>
-      </c>
-      <c r="AG18">
-        <v>1.75</v>
-      </c>
       <c r="AH18">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="AI18">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AJ18" t="s">
         <v>272</v>
@@ -3322,76 +3322,76 @@
         <v>270</v>
       </c>
       <c r="L19">
-        <v>3.01</v>
+        <v>1.44</v>
       </c>
       <c r="M19">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="N19">
-        <v>2.19</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="P19">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q19">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="R19">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S19">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="T19">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="U19">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V19">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Z19">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA19">
-        <v>3.5</v>
+        <v>2.81</v>
       </c>
       <c r="AB19">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC19">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AD19">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AE19">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF19">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AG19">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH19">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="AI19">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AJ19" t="s">
         <v>272</v>
@@ -3438,76 +3438,76 @@
         <v>270</v>
       </c>
       <c r="L20">
-        <v>2.5</v>
+        <v>3.01</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N20">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="O20">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="P20">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Q20">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="R20">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S20">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="T20">
-        <v>3.09</v>
+        <v>2.8</v>
       </c>
       <c r="U20">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="V20">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
         <v>8</v>
       </c>
       <c r="Z20">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AA20">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="AB20">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AC20">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AD20">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AE20">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AF20">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG20">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH20">
-        <v>8.5</v>
+        <v>6.25</v>
       </c>
       <c r="AI20">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AJ20" t="s">
         <v>272</v>
@@ -3902,76 +3902,76 @@
         <v>270</v>
       </c>
       <c r="L24">
+        <v>1.75</v>
+      </c>
+      <c r="M24">
+        <v>3.95</v>
+      </c>
+      <c r="N24">
+        <v>3.9</v>
+      </c>
+      <c r="O24">
+        <v>1.44</v>
+      </c>
+      <c r="P24">
+        <v>14</v>
+      </c>
+      <c r="Q24">
+        <v>2.75</v>
+      </c>
+      <c r="R24">
+        <v>1.25</v>
+      </c>
+      <c r="S24">
+        <v>3.9</v>
+      </c>
+      <c r="T24">
+        <v>2.15</v>
+      </c>
+      <c r="U24">
         <v>1.64</v>
       </c>
-      <c r="M24">
-        <v>3.55</v>
-      </c>
-      <c r="N24">
-        <v>4.7</v>
-      </c>
-      <c r="O24">
-        <v>1.39</v>
-      </c>
-      <c r="P24">
-        <v>8.9</v>
-      </c>
-      <c r="Q24">
-        <v>3.52</v>
-      </c>
-      <c r="R24">
-        <v>1.42</v>
-      </c>
-      <c r="S24">
-        <v>2.4</v>
-      </c>
-      <c r="T24">
-        <v>2.95</v>
-      </c>
-      <c r="U24">
-        <v>1.29</v>
-      </c>
       <c r="V24">
-        <v>7.3</v>
+        <v>4.8</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AA24">
-        <v>2.83</v>
+        <v>4.9</v>
       </c>
       <c r="AB24">
-        <v>2.09</v>
+        <v>1.48</v>
       </c>
       <c r="AC24">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AD24">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="AE24">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="AF24">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AG24">
-        <v>1.79</v>
+        <v>2.4</v>
       </c>
       <c r="AH24">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="AI24">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AJ24" t="s">
         <v>272</v>
@@ -4134,76 +4134,76 @@
         <v>270</v>
       </c>
       <c r="L26">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="M26">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="N26">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="O26">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="P26">
-        <v>14</v>
+        <v>8.9</v>
       </c>
       <c r="Q26">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="R26">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="S26">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="T26">
-        <v>2.15</v>
+        <v>2.95</v>
       </c>
       <c r="U26">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="V26">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="W26">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="Z26">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AA26">
-        <v>4.9</v>
+        <v>2.83</v>
       </c>
       <c r="AB26">
-        <v>1.48</v>
+        <v>2.09</v>
       </c>
       <c r="AC26">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AD26">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="AE26">
-        <v>1.57</v>
+        <v>1.21</v>
       </c>
       <c r="AF26">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AG26">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="AH26">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="AI26">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AJ26" t="s">
         <v>272</v>
@@ -4250,76 +4250,76 @@
         <v>270</v>
       </c>
       <c r="L27">
-        <v>1.26</v>
+        <v>1.56</v>
       </c>
       <c r="M27">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="N27">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="O27">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="P27">
-        <v>24</v>
+        <v>7.25</v>
       </c>
       <c r="Q27">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R27">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="S27">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="T27">
-        <v>1.7</v>
+        <v>3.18</v>
       </c>
       <c r="U27">
-        <v>1.98</v>
+        <v>1.33</v>
       </c>
       <c r="V27">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>26</v>
+        <v>7.5</v>
       </c>
       <c r="Z27">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="AA27">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="AB27">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="AC27">
-        <v>3.25</v>
+        <v>1.59</v>
       </c>
       <c r="AD27">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="AE27">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>1.6</v>
+        <v>2.23</v>
       </c>
       <c r="AG27">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="AH27">
-        <v>2.7</v>
+        <v>9</v>
       </c>
       <c r="AI27">
-        <v>1.45</v>
+        <v>1.06</v>
       </c>
       <c r="AJ27" t="s">
         <v>272</v>
@@ -4339,7 +4339,7 @@
         <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D28" t="s">
         <v>95</v>
@@ -4482,76 +4482,76 @@
         <v>270</v>
       </c>
       <c r="L29">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="M29">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="N29">
-        <v>5.25</v>
+        <v>7.4</v>
       </c>
       <c r="O29">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="P29">
-        <v>7.25</v>
+        <v>24</v>
       </c>
       <c r="Q29">
+        <v>4</v>
+      </c>
+      <c r="R29">
+        <v>1.14</v>
+      </c>
+      <c r="S29">
+        <v>4.8</v>
+      </c>
+      <c r="T29">
+        <v>1.7</v>
+      </c>
+      <c r="U29">
+        <v>1.98</v>
+      </c>
+      <c r="V29">
         <v>3.5</v>
       </c>
-      <c r="R29">
-        <v>1.5</v>
-      </c>
-      <c r="S29">
+      <c r="W29">
+        <v>1.29</v>
+      </c>
+      <c r="X29">
+        <v>1.01</v>
+      </c>
+      <c r="Y29">
+        <v>26</v>
+      </c>
+      <c r="Z29">
+        <v>1.05</v>
+      </c>
+      <c r="AA29">
+        <v>6.5</v>
+      </c>
+      <c r="AB29">
+        <v>1.28</v>
+      </c>
+      <c r="AC29">
+        <v>3.25</v>
+      </c>
+      <c r="AD29">
+        <v>1.7</v>
+      </c>
+      <c r="AE29">
+        <v>1.95</v>
+      </c>
+      <c r="AF29">
+        <v>1.6</v>
+      </c>
+      <c r="AG29">
+        <v>2.25</v>
+      </c>
+      <c r="AH29">
         <v>2.7</v>
       </c>
-      <c r="T29">
-        <v>3.2</v>
-      </c>
-      <c r="U29">
-        <v>1.36</v>
-      </c>
-      <c r="V29">
-        <v>8</v>
-      </c>
-      <c r="W29">
-        <v>1</v>
-      </c>
-      <c r="X29">
-        <v>1.05</v>
-      </c>
-      <c r="Y29">
-        <v>8.5</v>
-      </c>
-      <c r="Z29">
-        <v>1.35</v>
-      </c>
-      <c r="AA29">
-        <v>2.99</v>
-      </c>
-      <c r="AB29">
-        <v>2.2</v>
-      </c>
-      <c r="AC29">
-        <v>1.58</v>
-      </c>
-      <c r="AD29">
-        <v>3.8</v>
-      </c>
-      <c r="AE29">
-        <v>1.22</v>
-      </c>
-      <c r="AF29">
-        <v>2.23</v>
-      </c>
-      <c r="AG29">
-        <v>1.68</v>
-      </c>
-      <c r="AH29">
-        <v>8.9</v>
-      </c>
       <c r="AI29">
-        <v>1.06</v>
+        <v>1.45</v>
       </c>
       <c r="AJ29" t="s">
         <v>272</v>
@@ -5062,76 +5062,76 @@
         <v>270</v>
       </c>
       <c r="L34">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="M34">
-        <v>3.29</v>
+        <v>3.69</v>
       </c>
       <c r="N34">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="O34">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="P34">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q34">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R34">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S34">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T34">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="U34">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="Z34">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AA34">
-        <v>3.55</v>
+        <v>4.33</v>
       </c>
       <c r="AB34">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC34">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD34">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="AE34">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AF34">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AG34">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH34">
-        <v>6.25</v>
+        <v>4.5</v>
       </c>
       <c r="AI34">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AJ34" t="s">
         <v>272</v>
@@ -5267,7 +5267,7 @@
         <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
         <v>95</v>
@@ -5294,76 +5294,76 @@
         <v>270</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH36">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ36" t="s">
         <v>272</v>
@@ -5383,7 +5383,7 @@
         <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
         <v>95</v>
@@ -5410,76 +5410,76 @@
         <v>270</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH37">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ37" t="s">
         <v>272</v>
@@ -5499,7 +5499,7 @@
         <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D38" t="s">
         <v>95</v>
@@ -5526,76 +5526,76 @@
         <v>270</v>
       </c>
       <c r="L38">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N38">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH38">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI38">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="s">
         <v>272</v>
@@ -6311,7 +6311,7 @@
         <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D45" t="s">
         <v>95</v>
@@ -6338,76 +6338,76 @@
         <v>270</v>
       </c>
       <c r="L45">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M45">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N45">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S45">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T45">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U45">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V45">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W45">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z45">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA45">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB45">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC45">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD45">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE45">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF45">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG45">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH45">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AI45">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="s">
         <v>272</v>
@@ -6543,7 +6543,7 @@
         <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D47" t="s">
         <v>95</v>
@@ -6570,76 +6570,76 @@
         <v>270</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH47">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI47">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ47" t="s">
         <v>272</v>
@@ -6775,7 +6775,7 @@
         <v>51</v>
       </c>
       <c r="C49" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D49" t="s">
         <v>95</v>
@@ -6802,76 +6802,76 @@
         <v>270</v>
       </c>
       <c r="L49">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M49">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N49">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V49">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE49">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF49">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH49">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AI49">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="s">
         <v>272</v>
@@ -6891,7 +6891,7 @@
         <v>52</v>
       </c>
       <c r="C50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D50" t="s">
         <v>95</v>
@@ -6918,76 +6918,76 @@
         <v>270</v>
       </c>
       <c r="L50">
-        <v>5.65</v>
+        <v>1.36</v>
       </c>
       <c r="M50">
-        <v>4.32</v>
+        <v>5.2</v>
       </c>
       <c r="N50">
-        <v>1.58</v>
+        <v>5.9</v>
       </c>
       <c r="O50">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="P50">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Q50">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="R50">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S50">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T50">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="U50">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="V50">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="W50">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X50">
         <v>1</v>
       </c>
       <c r="Y50">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="Z50">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AA50">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AB50">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC50">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AD50">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AE50">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF50">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG50">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH50">
-        <v>4.33</v>
+        <v>4.42</v>
       </c>
       <c r="AI50">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AJ50" t="s">
         <v>272</v>
@@ -7007,7 +7007,7 @@
         <v>52</v>
       </c>
       <c r="C51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D51" t="s">
         <v>95</v>
@@ -7034,76 +7034,76 @@
         <v>270</v>
       </c>
       <c r="L51">
-        <v>1.36</v>
+        <v>5.65</v>
       </c>
       <c r="M51">
-        <v>5.2</v>
+        <v>4.32</v>
       </c>
       <c r="N51">
-        <v>5.9</v>
+        <v>1.58</v>
       </c>
       <c r="O51">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="P51">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Q51">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="R51">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S51">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T51">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="U51">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="V51">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="W51">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X51">
         <v>1</v>
       </c>
       <c r="Y51">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="Z51">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AA51">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AB51">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC51">
+        <v>2.2</v>
+      </c>
+      <c r="AD51">
         <v>2.5</v>
       </c>
-      <c r="AD51">
-        <v>2.45</v>
-      </c>
       <c r="AE51">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AF51">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG51">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH51">
-        <v>4.42</v>
+        <v>4.33</v>
       </c>
       <c r="AI51">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AJ51" t="s">
         <v>272</v>
@@ -7123,7 +7123,7 @@
         <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D52" t="s">
         <v>95</v>
@@ -7239,7 +7239,7 @@
         <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D53" t="s">
         <v>95</v>
@@ -7614,76 +7614,76 @@
         <v>270</v>
       </c>
       <c r="L56">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M56">
         <v>3.6</v>
       </c>
       <c r="N56">
-        <v>7.51</v>
+        <v>7.8</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P56">
         <v>0</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB56">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC56">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH56">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI56">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ56" t="s">
         <v>272</v>
@@ -7825,10 +7825,10 @@
         <v>95</v>
       </c>
       <c r="E58" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F58" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -7965,73 +7965,73 @@
         <v>1.85</v>
       </c>
       <c r="M59">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="N59">
-        <v>4.88</v>
+        <v>4.35</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P59">
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Z59">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AA59">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB59">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AC59">
         <v>1.4</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH59">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ59" t="s">
         <v>272</v>
@@ -8075,16 +8075,16 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L60">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="M60">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="N60">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -8096,58 +8096,58 @@
         <v>0</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB60">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="AC60">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH60">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ60" t="s">
         <v>272</v>
@@ -8191,79 +8191,79 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L61">
         <v>2.02</v>
       </c>
       <c r="M61">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="N61">
+        <v>4.1</v>
+      </c>
+      <c r="O61">
+        <v>1.73</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>3.2</v>
+      </c>
+      <c r="R61">
+        <v>1.72</v>
+      </c>
+      <c r="S61">
+        <v>1.93</v>
+      </c>
+      <c r="T61">
+        <v>4.75</v>
+      </c>
+      <c r="U61">
+        <v>1.14</v>
+      </c>
+      <c r="V61">
+        <v>12</v>
+      </c>
+      <c r="W61">
+        <v>1.01</v>
+      </c>
+      <c r="X61">
+        <v>1.17</v>
+      </c>
+      <c r="Y61">
+        <v>4</v>
+      </c>
+      <c r="Z61">
+        <v>1.91</v>
+      </c>
+      <c r="AA61">
+        <v>1.91</v>
+      </c>
+      <c r="AB61">
         <v>3.5</v>
       </c>
-      <c r="O61">
-        <v>0</v>
-      </c>
-      <c r="P61">
-        <v>0</v>
-      </c>
-      <c r="Q61">
-        <v>0</v>
-      </c>
-      <c r="R61">
-        <v>0</v>
-      </c>
-      <c r="S61">
-        <v>0</v>
-      </c>
-      <c r="T61">
-        <v>0</v>
-      </c>
-      <c r="U61">
-        <v>0</v>
-      </c>
-      <c r="V61">
-        <v>0</v>
-      </c>
-      <c r="W61">
-        <v>0</v>
-      </c>
-      <c r="X61">
-        <v>1.07</v>
-      </c>
-      <c r="Y61">
+      <c r="AC61">
+        <v>1.29</v>
+      </c>
+      <c r="AD61">
         <v>7.5</v>
       </c>
-      <c r="Z61">
-        <v>1.48</v>
-      </c>
-      <c r="AA61">
-        <v>2.55</v>
-      </c>
-      <c r="AB61">
-        <v>2.7</v>
-      </c>
-      <c r="AC61">
-        <v>1.44</v>
-      </c>
-      <c r="AD61">
-        <v>0</v>
-      </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH61">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AI61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ61" t="s">
         <v>272</v>
@@ -8310,76 +8310,76 @@
         <v>270</v>
       </c>
       <c r="L62">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="M62">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="N62">
+        <v>2.8</v>
+      </c>
+      <c r="O62">
+        <v>2.05</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>2.38</v>
+      </c>
+      <c r="R62">
+        <v>1.7</v>
+      </c>
+      <c r="S62">
+        <v>1.97</v>
+      </c>
+      <c r="T62">
+        <v>4.33</v>
+      </c>
+      <c r="U62">
+        <v>1.17</v>
+      </c>
+      <c r="V62">
+        <v>9</v>
+      </c>
+      <c r="W62">
+        <v>1.02</v>
+      </c>
+      <c r="X62">
+        <v>1.17</v>
+      </c>
+      <c r="Y62">
         <v>4.5</v>
       </c>
-      <c r="O62">
-        <v>0</v>
-      </c>
-      <c r="P62">
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <v>0</v>
-      </c>
-      <c r="R62">
-        <v>0</v>
-      </c>
-      <c r="S62">
-        <v>0</v>
-      </c>
-      <c r="T62">
-        <v>0</v>
-      </c>
-      <c r="U62">
-        <v>0</v>
-      </c>
-      <c r="V62">
-        <v>0</v>
-      </c>
-      <c r="W62">
-        <v>0</v>
-      </c>
-      <c r="X62">
-        <v>0</v>
-      </c>
-      <c r="Y62">
-        <v>0</v>
-      </c>
       <c r="Z62">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB62">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AC62">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH62">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AI62">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ62" t="s">
         <v>272</v>
@@ -8426,76 +8426,76 @@
         <v>270</v>
       </c>
       <c r="L63">
-        <v>3.78</v>
+        <v>2.55</v>
       </c>
       <c r="M63">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="N63">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="O63">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="P63">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q63">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="R63">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="S63">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T63">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U63">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V63">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W63">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X63">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y63">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z63">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA63">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AC63">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AD63">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE63">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF63">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG63">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH63">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI63">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ63" t="s">
         <v>272</v>
@@ -8515,7 +8515,7 @@
         <v>60</v>
       </c>
       <c r="C64" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D64" t="s">
         <v>95</v>
@@ -8542,76 +8542,76 @@
         <v>270</v>
       </c>
       <c r="L64">
-        <v>2.34</v>
+        <v>1.97</v>
       </c>
       <c r="M64">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="N64">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="O64">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="P64">
-        <v>5.75</v>
+        <v>6.9</v>
       </c>
       <c r="Q64">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R64">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="S64">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="T64">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U64">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V64">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="W64">
         <v>1.04</v>
       </c>
       <c r="X64">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Y64">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="Z64">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AA64">
-        <v>2.25</v>
+        <v>2.84</v>
       </c>
       <c r="AB64">
-        <v>2.83</v>
+        <v>2.22</v>
       </c>
       <c r="AC64">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AD64">
-        <v>5.89</v>
+        <v>4.1</v>
       </c>
       <c r="AE64">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF64">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AG64">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AH64">
-        <v>12</v>
+        <v>7.7</v>
       </c>
       <c r="AI64">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ64" t="s">
         <v>272</v>
@@ -8631,7 +8631,7 @@
         <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D65" t="s">
         <v>95</v>
@@ -8658,76 +8658,76 @@
         <v>270</v>
       </c>
       <c r="L65">
-        <v>1.23</v>
+        <v>2.75</v>
       </c>
       <c r="M65">
-        <v>4.77</v>
+        <v>2.96</v>
       </c>
       <c r="N65">
-        <v>12.59</v>
+        <v>2.4</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB65">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AC65">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH65">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI65">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ65" t="s">
         <v>272</v>
@@ -8747,7 +8747,7 @@
         <v>60</v>
       </c>
       <c r="C66" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D66" t="s">
         <v>95</v>
@@ -8774,76 +8774,76 @@
         <v>270</v>
       </c>
       <c r="L66">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="M66">
-        <v>3.53</v>
+        <v>2.7</v>
       </c>
       <c r="N66">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="O66">
+        <v>1.83</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>2.63</v>
+      </c>
+      <c r="R66">
         <v>1.73</v>
       </c>
-      <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>2.2</v>
-      </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
       <c r="S66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB66">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="AC66">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH66">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AI66">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ66" t="s">
         <v>272</v>
@@ -8863,7 +8863,7 @@
         <v>60</v>
       </c>
       <c r="C67" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D67" t="s">
         <v>95</v>
@@ -8890,76 +8890,76 @@
         <v>270</v>
       </c>
       <c r="L67">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M67">
-        <v>5.35</v>
+        <v>4.5</v>
       </c>
       <c r="N67">
-        <v>11.93</v>
+        <v>12</v>
       </c>
       <c r="O67">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P67">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R67">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S67">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="T67">
-        <v>2.62</v>
+        <v>3.34</v>
       </c>
       <c r="U67">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V67">
-        <v>7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W67">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
         <v>1.06</v>
       </c>
       <c r="Y67">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Z67">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AA67">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AB67">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AC67">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AD67">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AE67">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AF67">
-        <v>2.3</v>
+        <v>3.18</v>
       </c>
       <c r="AG67">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AH67">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="AI67">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AJ67" t="s">
         <v>272</v>
@@ -8979,7 +8979,7 @@
         <v>60</v>
       </c>
       <c r="C68" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D68" t="s">
         <v>95</v>
@@ -9006,76 +9006,76 @@
         <v>270</v>
       </c>
       <c r="L68">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="M68">
-        <v>2.64</v>
+        <v>2.87</v>
       </c>
       <c r="N68">
-        <v>3.58</v>
+        <v>3.23</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB68">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="AC68">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH68">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI68">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ68" t="s">
         <v>272</v>
@@ -9095,7 +9095,7 @@
         <v>60</v>
       </c>
       <c r="C69" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D69" t="s">
         <v>95</v>
@@ -9122,76 +9122,76 @@
         <v>270</v>
       </c>
       <c r="L69">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="M69">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N69">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O69">
+        <v>1.62</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
         <v>2.3</v>
       </c>
-      <c r="P69">
-        <v>6.75</v>
-      </c>
-      <c r="Q69">
-        <v>1.91</v>
-      </c>
       <c r="R69">
+        <v>1.25</v>
+      </c>
+      <c r="S69">
+        <v>3.6</v>
+      </c>
+      <c r="T69">
+        <v>2.2</v>
+      </c>
+      <c r="U69">
+        <v>1.62</v>
+      </c>
+      <c r="V69">
+        <v>4.75</v>
+      </c>
+      <c r="W69">
+        <v>1.15</v>
+      </c>
+      <c r="X69">
+        <v>1</v>
+      </c>
+      <c r="Y69">
+        <v>12</v>
+      </c>
+      <c r="Z69">
+        <v>1.13</v>
+      </c>
+      <c r="AA69">
+        <v>4.75</v>
+      </c>
+      <c r="AB69">
         <v>1.5</v>
       </c>
-      <c r="S69">
-        <v>2.42</v>
-      </c>
-      <c r="T69">
-        <v>3.3</v>
-      </c>
-      <c r="U69">
-        <v>1.28</v>
-      </c>
-      <c r="V69">
-        <v>8.5</v>
-      </c>
-      <c r="W69">
-        <v>1.06</v>
-      </c>
-      <c r="X69">
-        <v>1.09</v>
-      </c>
-      <c r="Y69">
-        <v>7</v>
-      </c>
-      <c r="Z69">
-        <v>1.44</v>
-      </c>
-      <c r="AA69">
-        <v>2.65</v>
-      </c>
-      <c r="AB69">
+      <c r="AC69">
         <v>2.4</v>
       </c>
-      <c r="AC69">
-        <v>1.55</v>
-      </c>
       <c r="AD69">
-        <v>4.33</v>
+        <v>2.18</v>
       </c>
       <c r="AE69">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="AF69">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="AG69">
-        <v>1.78</v>
+        <v>2.49</v>
       </c>
       <c r="AH69">
-        <v>10</v>
+        <v>3.72</v>
       </c>
       <c r="AI69">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AJ69" t="s">
         <v>272</v>
@@ -9211,7 +9211,7 @@
         <v>60</v>
       </c>
       <c r="C70" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D70" t="s">
         <v>95</v>
@@ -9238,76 +9238,76 @@
         <v>270</v>
       </c>
       <c r="L70">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="M70">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N70">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="O70">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P70">
         <v>9.5</v>
       </c>
       <c r="Q70">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R70">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S70">
         <v>3</v>
       </c>
       <c r="T70">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="U70">
+        <v>1.48</v>
+      </c>
+      <c r="V70">
+        <v>6.5</v>
+      </c>
+      <c r="W70">
+        <v>1.09</v>
+      </c>
+      <c r="X70">
+        <v>1.04</v>
+      </c>
+      <c r="Y70">
+        <v>10</v>
+      </c>
+      <c r="Z70">
+        <v>1.25</v>
+      </c>
+      <c r="AA70">
+        <v>3.6</v>
+      </c>
+      <c r="AB70">
+        <v>1.8</v>
+      </c>
+      <c r="AC70">
+        <v>1.83</v>
+      </c>
+      <c r="AD70">
+        <v>3</v>
+      </c>
+      <c r="AE70">
         <v>1.4</v>
       </c>
-      <c r="V70">
-        <v>7</v>
-      </c>
-      <c r="W70">
-        <v>1.1</v>
-      </c>
-      <c r="X70">
-        <v>1.05</v>
-      </c>
-      <c r="Y70">
-        <v>8.5</v>
-      </c>
-      <c r="Z70">
-        <v>1.28</v>
-      </c>
-      <c r="AA70">
-        <v>3.4</v>
-      </c>
-      <c r="AB70">
-        <v>1.9</v>
-      </c>
-      <c r="AC70">
-        <v>1.9</v>
-      </c>
-      <c r="AD70">
-        <v>3.2</v>
-      </c>
-      <c r="AE70">
-        <v>1.33</v>
-      </c>
       <c r="AF70">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG70">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH70">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AI70">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AJ70" t="s">
         <v>272</v>
@@ -9327,7 +9327,7 @@
         <v>60</v>
       </c>
       <c r="C71" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D71" t="s">
         <v>95</v>
@@ -9354,76 +9354,76 @@
         <v>270</v>
       </c>
       <c r="L71">
-        <v>1.91</v>
+        <v>3.8</v>
       </c>
       <c r="M71">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N71">
+        <v>2</v>
+      </c>
+      <c r="O71">
+        <v>2.5</v>
+      </c>
+      <c r="P71">
+        <v>9.5</v>
+      </c>
+      <c r="Q71">
+        <v>1.62</v>
+      </c>
+      <c r="R71">
+        <v>1.36</v>
+      </c>
+      <c r="S71">
         <v>3</v>
       </c>
-      <c r="O71">
-        <v>1.62</v>
-      </c>
-      <c r="P71">
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <v>2.3</v>
-      </c>
-      <c r="R71">
-        <v>1.25</v>
-      </c>
-      <c r="S71">
-        <v>3.6</v>
-      </c>
       <c r="T71">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="U71">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="V71">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="W71">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X71">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y71">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="Z71">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AA71">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="AB71">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AC71">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="AD71">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="AE71">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AF71">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG71">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AH71">
-        <v>3.6</v>
+        <v>5.9</v>
       </c>
       <c r="AI71">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AJ71" t="s">
         <v>272</v>
@@ -9443,7 +9443,7 @@
         <v>60</v>
       </c>
       <c r="C72" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D72" t="s">
         <v>95</v>
@@ -9470,76 +9470,76 @@
         <v>270</v>
       </c>
       <c r="L72">
-        <v>1.97</v>
+        <v>1.4</v>
       </c>
       <c r="M72">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N72">
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="O72">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="P72">
-        <v>6.9</v>
+        <v>8.5</v>
       </c>
       <c r="Q72">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="R72">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="S72">
-        <v>2.47</v>
+        <v>3.16</v>
       </c>
       <c r="T72">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U72">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="V72">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="W72">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X72">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z72">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AA72">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="AB72">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="AC72">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AD72">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AE72">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AF72">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AG72">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AH72">
-        <v>7.7</v>
+        <v>5.5</v>
       </c>
       <c r="AI72">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AJ72" t="s">
         <v>272</v>
@@ -9720,10 +9720,10 @@
         <v>2.45</v>
       </c>
       <c r="R74">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S74">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T74">
         <v>4.1</v>
@@ -9741,31 +9741,31 @@
         <v>1.08</v>
       </c>
       <c r="Y74">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Z74">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AA74">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AB74">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="AC74">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AD74">
-        <v>6.2</v>
+        <v>6.05</v>
       </c>
       <c r="AE74">
         <v>1.11</v>
       </c>
       <c r="AF74">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG74">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AH74">
         <v>11</v>
@@ -9818,13 +9818,13 @@
         <v>270</v>
       </c>
       <c r="L75">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="M75">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="N75">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="O75">
         <v>1.75</v>
@@ -9836,7 +9836,7 @@
         <v>2.5</v>
       </c>
       <c r="R75">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S75">
         <v>2.2</v>
@@ -9854,28 +9854,28 @@
         <v>1.02</v>
       </c>
       <c r="X75">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Y75">
-        <v>6.05</v>
+        <v>6.15</v>
       </c>
       <c r="Z75">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AA75">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AB75">
-        <v>3.03</v>
+        <v>2.37</v>
       </c>
       <c r="AC75">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AD75">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="AE75">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF75">
         <v>2.5</v>
@@ -9913,10 +9913,10 @@
         <v>95</v>
       </c>
       <c r="E76" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F76" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -10029,10 +10029,10 @@
         <v>95</v>
       </c>
       <c r="E77" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="F77" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -10139,7 +10139,7 @@
         <v>64</v>
       </c>
       <c r="C78" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D78" t="s">
         <v>95</v>
@@ -10166,13 +10166,13 @@
         <v>270</v>
       </c>
       <c r="L78">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="M78">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N78">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O78">
         <v>1.5</v>
@@ -10187,55 +10187,55 @@
         <v>1.5</v>
       </c>
       <c r="S78">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="T78">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="U78">
         <v>1.26</v>
       </c>
       <c r="V78">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W78">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X78">
         <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Z78">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AA78">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="AB78">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AC78">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AD78">
         <v>4.33</v>
       </c>
       <c r="AE78">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF78">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AG78">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AH78">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AI78">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AJ78" t="s">
         <v>272</v>
@@ -10255,7 +10255,7 @@
         <v>64</v>
       </c>
       <c r="C79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D79" t="s">
         <v>95</v>
@@ -10282,13 +10282,13 @@
         <v>270</v>
       </c>
       <c r="L79">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="M79">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="N79">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="O79">
         <v>2.4</v>
@@ -10303,25 +10303,25 @@
         <v>1.5</v>
       </c>
       <c r="S79">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T79">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U79">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V79">
         <v>8.5</v>
       </c>
       <c r="W79">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X79">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y79">
-        <v>7.47</v>
+        <v>7.48</v>
       </c>
       <c r="Z79">
         <v>1.43</v>
@@ -10330,19 +10330,19 @@
         <v>2.62</v>
       </c>
       <c r="AB79">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AC79">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AD79">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="AE79">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF79">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG79">
         <v>1.75</v>
@@ -10351,7 +10351,7 @@
         <v>8.4</v>
       </c>
       <c r="AI79">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ79" t="s">
         <v>272</v>
@@ -10398,76 +10398,76 @@
         <v>270</v>
       </c>
       <c r="L80">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="M80">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="N80">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P80">
         <v>0</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB80">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC80">
         <v>1.36</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH80">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ80" t="s">
         <v>272</v>
@@ -10514,76 +10514,76 @@
         <v>270</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P81">
         <v>0</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH81">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AI81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ81" t="s">
         <v>272</v>
@@ -10603,7 +10603,7 @@
         <v>66</v>
       </c>
       <c r="C82" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D82" t="s">
         <v>95</v>
@@ -10630,76 +10630,76 @@
         <v>270</v>
       </c>
       <c r="L82">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="M82">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N82">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="O82">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="P82">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="Q82">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="R82">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S82">
         <v>2.5</v>
       </c>
       <c r="T82">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U82">
         <v>1.3</v>
       </c>
       <c r="V82">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="W82">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X82">
         <v>1.04</v>
       </c>
       <c r="Y82">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="Z82">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AA82">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB82">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AC82">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AD82">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AE82">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF82">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AG82">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH82">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="AI82">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AJ82" t="s">
         <v>272</v>
@@ -10719,7 +10719,7 @@
         <v>66</v>
       </c>
       <c r="C83" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D83" t="s">
         <v>95</v>
@@ -10746,76 +10746,76 @@
         <v>270</v>
       </c>
       <c r="L83">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="M83">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="N83">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="O83">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="P83">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="Q83">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="R83">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S83">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T83">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U83">
         <v>1.3</v>
       </c>
       <c r="V83">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="W83">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X83">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y83">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="Z83">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AA83">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AB83">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AC83">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AD83">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AE83">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF83">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG83">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH83">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AI83">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AJ83" t="s">
         <v>272</v>
@@ -10883,7 +10883,7 @@
         <v>1.6</v>
       </c>
       <c r="S84">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="T84">
         <v>3.6</v>
@@ -10910,10 +10910,10 @@
         <v>2.3</v>
       </c>
       <c r="AB84">
-        <v>2.52</v>
+        <v>2.37</v>
       </c>
       <c r="AC84">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AD84">
         <v>4.8</v>
@@ -11094,13 +11094,13 @@
         <v>270</v>
       </c>
       <c r="L86">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="M86">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="N86">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O86">
         <v>1.63</v>
@@ -11112,10 +11112,10 @@
         <v>2.87</v>
       </c>
       <c r="R86">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S86">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="T86">
         <v>3.8</v>
@@ -11130,40 +11130,40 @@
         <v>1.02</v>
       </c>
       <c r="X86">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y86">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Z86">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AA86">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AB86">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="AC86">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AD86">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AE86">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF86">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AG86">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH86">
         <v>9.199999999999999</v>
       </c>
       <c r="AI86">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ86" t="s">
         <v>272</v>
@@ -11183,7 +11183,7 @@
         <v>68</v>
       </c>
       <c r="C87" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D87" t="s">
         <v>95</v>
@@ -11210,13 +11210,13 @@
         <v>270</v>
       </c>
       <c r="L87">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="M87">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="N87">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="O87">
         <v>1.44</v>
@@ -11228,7 +11228,7 @@
         <v>3.25</v>
       </c>
       <c r="R87">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S87">
         <v>2.5</v>
@@ -11243,13 +11243,13 @@
         <v>9</v>
       </c>
       <c r="W87">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X87">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y87">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z87">
         <v>1.5</v>
@@ -11258,28 +11258,28 @@
         <v>2.5</v>
       </c>
       <c r="AB87">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="AC87">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AD87">
         <v>4.75</v>
       </c>
       <c r="AE87">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AF87">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AG87">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH87">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI87">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AJ87" t="s">
         <v>272</v>
@@ -11299,7 +11299,7 @@
         <v>69</v>
       </c>
       <c r="C88" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D88" t="s">
         <v>95</v>
@@ -11350,7 +11350,7 @@
         <v>4</v>
       </c>
       <c r="T88">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U88">
         <v>1.8</v>
@@ -11380,13 +11380,13 @@
         <v>2.75</v>
       </c>
       <c r="AD88">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AE88">
         <v>1.85</v>
       </c>
       <c r="AF88">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG88">
         <v>2.57</v>
@@ -11415,16 +11415,16 @@
         <v>70</v>
       </c>
       <c r="C89" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D89" t="s">
         <v>95</v>
       </c>
       <c r="E89" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="F89" t="s">
-        <v>223</v>
+        <v>266</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -11442,76 +11442,76 @@
         <v>270</v>
       </c>
       <c r="L89">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="M89">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N89">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="O89">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="P89">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R89">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S89">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T89">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U89">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V89">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W89">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X89">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y89">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z89">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA89">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB89">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AC89">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AD89">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF89">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG89">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH89">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI89">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ89" t="s">
         <v>272</v>
@@ -11531,16 +11531,16 @@
         <v>70</v>
       </c>
       <c r="C90" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D90" t="s">
         <v>95</v>
       </c>
       <c r="E90" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="F90" t="s">
-        <v>266</v>
+        <v>223</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -11558,76 +11558,76 @@
         <v>270</v>
       </c>
       <c r="L90">
+        <v>1.91</v>
+      </c>
+      <c r="M90">
+        <v>3.3</v>
+      </c>
+      <c r="N90">
+        <v>4.2</v>
+      </c>
+      <c r="O90">
+        <v>1.57</v>
+      </c>
+      <c r="P90">
+        <v>6.75</v>
+      </c>
+      <c r="Q90">
+        <v>3</v>
+      </c>
+      <c r="R90">
+        <v>1.5</v>
+      </c>
+      <c r="S90">
+        <v>2.5</v>
+      </c>
+      <c r="T90">
+        <v>3.4</v>
+      </c>
+      <c r="U90">
+        <v>1.3</v>
+      </c>
+      <c r="V90">
+        <v>10</v>
+      </c>
+      <c r="W90">
+        <v>1.06</v>
+      </c>
+      <c r="X90">
+        <v>1.09</v>
+      </c>
+      <c r="Y90">
+        <v>7</v>
+      </c>
+      <c r="Z90">
+        <v>1.45</v>
+      </c>
+      <c r="AA90">
         <v>2.7</v>
       </c>
-      <c r="M90">
-        <v>3.1</v>
-      </c>
-      <c r="N90">
-        <v>2.5</v>
-      </c>
-      <c r="O90">
-        <v>1.83</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
-        <v>2.25</v>
-      </c>
-      <c r="R90">
-        <v>0</v>
-      </c>
-      <c r="S90">
-        <v>0</v>
-      </c>
-      <c r="T90">
-        <v>0</v>
-      </c>
-      <c r="U90">
-        <v>0</v>
-      </c>
-      <c r="V90">
-        <v>0</v>
-      </c>
-      <c r="W90">
-        <v>0</v>
-      </c>
-      <c r="X90">
-        <v>0</v>
-      </c>
-      <c r="Y90">
-        <v>0</v>
-      </c>
-      <c r="Z90">
-        <v>0</v>
-      </c>
-      <c r="AA90">
-        <v>0</v>
-      </c>
       <c r="AB90">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AC90">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH90">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI90">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ90" t="s">
         <v>272</v>
@@ -11647,7 +11647,7 @@
         <v>71</v>
       </c>
       <c r="C91" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D91" t="s">
         <v>95</v>
@@ -11692,13 +11692,13 @@
         <v>2.2</v>
       </c>
       <c r="R91">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S91">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="T91">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="U91">
         <v>1.5</v>
@@ -11725,13 +11725,13 @@
         <v>1.6</v>
       </c>
       <c r="AC91">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AD91">
         <v>2.46</v>
       </c>
       <c r="AE91">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AF91">
         <v>1.57</v>
@@ -11763,7 +11763,7 @@
         <v>72</v>
       </c>
       <c r="C92" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D92" t="s">
         <v>95</v>
@@ -11838,7 +11838,7 @@
         <v>7</v>
       </c>
       <c r="AB92">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC92">
         <v>3.28</v>
@@ -11859,7 +11859,7 @@
         <v>2.62</v>
       </c>
       <c r="AI92">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AJ92" t="s">
         <v>272</v>
@@ -11879,7 +11879,7 @@
         <v>72</v>
       </c>
       <c r="C93" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D93" t="s">
         <v>95</v>
@@ -11930,16 +11930,16 @@
         <v>3.8</v>
       </c>
       <c r="T93">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="U93">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="V93">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="W93">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X93">
         <v>0</v>
@@ -11954,13 +11954,13 @@
         <v>5.5</v>
       </c>
       <c r="AB93">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AC93">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD93">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AE93">
         <v>1.73</v>
@@ -11972,10 +11972,10 @@
         <v>2.8</v>
       </c>
       <c r="AH93">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AI93">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AJ93" t="s">
         <v>272</v>

--- a/jogos_2025-07-20.xlsx
+++ b/jogos_2025-07-20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="306">
   <si>
     <t>Date</t>
   </si>
@@ -262,18 +262,18 @@
     <t>Norway Eliteserien</t>
   </si>
   <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Finland Veikkausliiga</t>
+    <t>Estonia Meistriliiga</t>
   </si>
   <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Argentina Primera División</t>
   </si>
   <si>
@@ -289,12 +289,12 @@
     <t>Brazil Serie B</t>
   </si>
   <si>
+    <t>Canada Canadian Premier League</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Canada Canadian Premier League</t>
-  </si>
-  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
@@ -325,135 +325,135 @@
     <t>Shimizu S-Pulse</t>
   </si>
   <si>
+    <t>Albirex Niigata</t>
+  </si>
+  <si>
     <t>Gamba Osaka</t>
   </si>
   <si>
+    <t>Yokohama F. Marinos</t>
+  </si>
+  <si>
+    <t>Fagiano Okayama</t>
+  </si>
+  <si>
+    <t>Cheongju</t>
+  </si>
+  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
     <t>FC Seoul</t>
   </si>
   <si>
-    <t>Albirex Niigata</t>
-  </si>
-  <si>
-    <t>Cheongju</t>
-  </si>
-  <si>
-    <t>Fagiano Okayama</t>
-  </si>
-  <si>
-    <t>Yokohama F. Marinos</t>
-  </si>
-  <si>
     <t>Gyeongnam</t>
   </si>
   <si>
     <t>Varberg</t>
   </si>
   <si>
+    <t>Nanjing City</t>
+  </si>
+  <si>
+    <t>Shenzhen Juniors</t>
+  </si>
+  <si>
     <t>Heilongjiang Lava Spring</t>
   </si>
   <si>
-    <t>Shenzhen Juniors</t>
-  </si>
-  <si>
-    <t>Nanjing City</t>
+    <t>Mjällby</t>
   </si>
   <si>
     <t>Sirius</t>
   </si>
   <si>
-    <t>Mjällby</t>
-  </si>
-  <si>
     <t>Vålerenga</t>
   </si>
   <si>
     <t>Kalmar</t>
   </si>
   <si>
+    <t>SJK</t>
+  </si>
+  <si>
     <t>Kyzyl-Zhar</t>
   </si>
   <si>
-    <t>SJK</t>
+    <t>Nõmme Kalju</t>
   </si>
   <si>
     <t>Internacional</t>
   </si>
   <si>
-    <t>Nõmme Kalju</t>
-  </si>
-  <si>
     <t>Tammeka</t>
   </si>
   <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
     <t>Halmstad</t>
   </si>
   <si>
-    <t>Hammarby</t>
+    <t>Zhetysu</t>
+  </si>
+  <si>
+    <t>Platense</t>
+  </si>
+  <si>
+    <t>Lanús</t>
+  </si>
+  <si>
+    <t>Instituto</t>
+  </si>
+  <si>
+    <t>Atlético Tucumán</t>
+  </si>
+  <si>
+    <t>Newell's Old Boys</t>
+  </si>
+  <si>
+    <t>Barracas Central</t>
+  </si>
+  <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
+    <t>Godoy Cruz</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Tigre</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Independiente</t>
+  </si>
+  <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Boca Juniors</t>
   </si>
   <si>
     <t>Defensa y Justicia</t>
   </si>
   <si>
-    <t>Tigre</t>
-  </si>
-  <si>
-    <t>Godoy Cruz</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Belgrano</t>
-  </si>
-  <si>
-    <t>Newell's Old Boys</t>
-  </si>
-  <si>
-    <t>Estudiantes</t>
-  </si>
-  <si>
-    <t>Instituto</t>
-  </si>
-  <si>
-    <t>San Lorenzo</t>
-  </si>
-  <si>
-    <t>Atlético Tucumán</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
-    <t>Independiente</t>
-  </si>
-  <si>
-    <t>Tromsø</t>
-  </si>
-  <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
-    <t>Boca Juniors</t>
-  </si>
-  <si>
-    <t>Lanús</t>
-  </si>
-  <si>
-    <t>Platense</t>
-  </si>
-  <si>
-    <t>Barracas Central</t>
+    <t>Jaro</t>
   </si>
   <si>
     <t>HJK</t>
   </si>
   <si>
-    <t>Jaro</t>
-  </si>
-  <si>
     <t>Kuressaare</t>
   </si>
   <si>
@@ -478,45 +478,45 @@
     <t>Patronato</t>
   </si>
   <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
     <t>Club Atlético Güemes</t>
   </si>
   <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
     <t>Ñublense</t>
   </si>
   <si>
+    <t>Amazonas</t>
+  </si>
+  <si>
+    <t>Valour FC</t>
+  </si>
+  <si>
+    <t>Magallanes</t>
+  </si>
+  <si>
+    <t>New England II</t>
+  </si>
+  <si>
     <t>Vitória</t>
   </si>
   <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Toronto II</t>
+  </si>
+  <si>
+    <t>Gimnasia Jujuy</t>
+  </si>
+  <si>
+    <t>Racing Córdoba</t>
+  </si>
+  <si>
     <t>Defensores de Belgrano</t>
   </si>
   <si>
-    <t>Gimnasia Jujuy</t>
-  </si>
-  <si>
-    <t>Racing Córdoba</t>
-  </si>
-  <si>
-    <t>Amazonas</t>
-  </si>
-  <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
-    <t>Cruzeiro</t>
-  </si>
-  <si>
-    <t>Magallanes</t>
-  </si>
-  <si>
-    <t>Valour FC</t>
-  </si>
-  <si>
-    <t>New England II</t>
-  </si>
-  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
@@ -526,30 +526,30 @@
     <t>Confiança</t>
   </si>
   <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>Palmeiras</t>
+    <t>Central Norte</t>
   </si>
   <si>
     <t>Nueva Chicago</t>
   </si>
   <si>
-    <t>Central Norte</t>
-  </si>
-  <si>
     <t>América Mineiro</t>
   </si>
   <si>
     <t>Deportes Temuco</t>
   </si>
   <si>
+    <t>Brusque</t>
+  </si>
+  <si>
     <t>Ypiranga Erechim</t>
   </si>
   <si>
-    <t>Brusque</t>
-  </si>
-  <si>
     <t>Flamengo</t>
   </si>
   <si>
@@ -589,135 +589,135 @@
     <t>Yokohama</t>
   </si>
   <si>
+    <t>Sanfrecce Hiroshima</t>
+  </si>
+  <si>
     <t>Kawasaki Frontale</t>
   </si>
   <si>
+    <t>Nagoya Grampus</t>
+  </si>
+  <si>
+    <t>Vissel Kobe</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
     <t>Asan Mugunghwa</t>
   </si>
   <si>
     <t>Ulsan</t>
   </si>
   <si>
-    <t>Sanfrecce Hiroshima</t>
-  </si>
-  <si>
-    <t>Cheonan City</t>
-  </si>
-  <si>
-    <t>Vissel Kobe</t>
-  </si>
-  <si>
-    <t>Nagoya Grampus</t>
-  </si>
-  <si>
     <t>Incheon United</t>
   </si>
   <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
+    <t>Guangxi Baoyun</t>
+  </si>
+  <si>
+    <t>Shanghai Jiading</t>
+  </si>
+  <si>
     <t>Shaanxi Union</t>
   </si>
   <si>
-    <t>Shanghai Jiading</t>
-  </si>
-  <si>
-    <t>Guangxi Baoyun</t>
+    <t>AIK</t>
   </si>
   <si>
     <t>IFK Göteborg</t>
   </si>
   <si>
-    <t>AIK</t>
-  </si>
-  <si>
     <t>Haugesund</t>
   </si>
   <si>
     <t>Brage</t>
   </si>
   <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
     <t>Atyrau</t>
   </si>
   <si>
-    <t>Gnistan</t>
+    <t>Tallinna Kalev</t>
   </si>
   <si>
     <t>Ceará</t>
   </si>
   <si>
-    <t>Tallinna Kalev</t>
-  </si>
-  <si>
     <t>Tallinna FC Flora</t>
   </si>
   <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
     <t>Häcken</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
+    <t>Ordabasy</t>
+  </si>
+  <si>
+    <t>Vélez Sarsfield</t>
+  </si>
+  <si>
+    <t>Rosario Central</t>
+  </si>
+  <si>
+    <t>River Plate</t>
+  </si>
+  <si>
+    <t>Central Córdoba SdE</t>
+  </si>
+  <si>
+    <t>Banfield</t>
+  </si>
+  <si>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>Tobol</t>
+  </si>
+  <si>
+    <t>Sarmiento</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Argentinos Juniors</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
+    <t>Gimnasia La Plata</t>
+  </si>
+  <si>
+    <t>Huracán</t>
+  </si>
+  <si>
+    <t>Talleres Córdoba</t>
+  </si>
+  <si>
+    <t>Racing Club</t>
+  </si>
+  <si>
+    <t>Unión Santa Fe</t>
   </si>
   <si>
     <t>Aldosivi</t>
   </si>
   <si>
-    <t>Argentinos Juniors</t>
-  </si>
-  <si>
-    <t>Sarmiento</t>
-  </si>
-  <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Racing Club</t>
-  </si>
-  <si>
-    <t>Banfield</t>
-  </si>
-  <si>
-    <t>Huracán</t>
-  </si>
-  <si>
-    <t>River Plate</t>
-  </si>
-  <si>
-    <t>Gimnasia La Plata</t>
-  </si>
-  <si>
-    <t>Central Córdoba SdE</t>
-  </si>
-  <si>
-    <t>Ordabasy</t>
-  </si>
-  <si>
-    <t>Talleres Córdoba</t>
-  </si>
-  <si>
-    <t>Bryne</t>
-  </si>
-  <si>
-    <t>Tobol</t>
-  </si>
-  <si>
-    <t>Unión Santa Fe</t>
-  </si>
-  <si>
-    <t>Rosario Central</t>
-  </si>
-  <si>
-    <t>Vélez Sarsfield</t>
-  </si>
-  <si>
-    <t>Independiente Rivadavia</t>
+    <t>Ilves</t>
   </si>
   <si>
     <t>Oulu</t>
   </si>
   <si>
-    <t>Ilves</t>
-  </si>
-  <si>
     <t>Vaprus</t>
   </si>
   <si>
@@ -742,45 +742,45 @@
     <t>Deportivo Maipú</t>
   </si>
   <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
     <t>Gimnasia y Tiro</t>
   </si>
   <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
     <t>Universidad Chile</t>
   </si>
   <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
+    <t>Cavalry FC</t>
+  </si>
+  <si>
+    <t>Univ. Concepción</t>
+  </si>
+  <si>
+    <t>Orlando City II</t>
+  </si>
+  <si>
     <t>Bragantino</t>
   </si>
   <si>
+    <t>Juventude</t>
+  </si>
+  <si>
+    <t>Chicago Fire II</t>
+  </si>
+  <si>
+    <t>Defensores Unidos</t>
+  </si>
+  <si>
+    <t>Colegiales</t>
+  </si>
+  <si>
     <t>Estudiantes Río Cuarto</t>
   </si>
   <si>
-    <t>Defensores Unidos</t>
-  </si>
-  <si>
-    <t>Colegiales</t>
-  </si>
-  <si>
-    <t>Botafogo SP</t>
-  </si>
-  <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
-    <t>Juventude</t>
-  </si>
-  <si>
-    <t>Univ. Concepción</t>
-  </si>
-  <si>
-    <t>Cavalry FC</t>
-  </si>
-  <si>
-    <t>Orlando City II</t>
-  </si>
-  <si>
     <t>Valur</t>
   </si>
   <si>
@@ -790,30 +790,30 @@
     <t>Tombense</t>
   </si>
   <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
     <t>Botafogo</t>
   </si>
   <si>
-    <t>Atlético Mineiro</t>
+    <t>Colón</t>
   </si>
   <si>
     <t>Chaco For Ever</t>
   </si>
   <si>
-    <t>Colón</t>
-  </si>
-  <si>
     <t>Chapecoense</t>
   </si>
   <si>
     <t>Santiago Morning</t>
   </si>
   <si>
+    <t>Retrô</t>
+  </si>
+  <si>
     <t>São Bernardo</t>
   </si>
   <si>
-    <t>Retrô</t>
-  </si>
-  <si>
     <t>Fluminense</t>
   </si>
   <si>
@@ -838,6 +838,9 @@
     <t>incomplete</t>
   </si>
   <si>
+    <t>suspended</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
@@ -859,19 +862,31 @@
     <t>['45+3', '57']</t>
   </si>
   <si>
+    <t>['35', '45+2', '90+4']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
+    <t>['12', '68']</t>
+  </si>
+  <si>
     <t>['13', '45+2', '47', '67', '68']</t>
   </si>
   <si>
     <t>['42']</t>
   </si>
   <si>
-    <t>['12', '68']</t>
-  </si>
-  <si>
-    <t>['90+5']</t>
-  </si>
-  <si>
-    <t>['35', '45+2', '90+4']</t>
+    <t>['50', '87']</t>
+  </si>
+  <si>
+    <t>['47', '85']</t>
+  </si>
+  <si>
+    <t>['55', '83']</t>
+  </si>
+  <si>
+    <t>['60', '63', '85']</t>
   </si>
   <si>
     <t>['10', '3']</t>
@@ -889,19 +904,34 @@
     <t>['43', '76']</t>
   </si>
   <si>
+    <t>['2', '48']</t>
+  </si>
+  <si>
     <t>['9']</t>
   </si>
   <si>
+    <t>['30', '64']</t>
+  </si>
+  <si>
+    <t>['20']</t>
+  </si>
+  <si>
     <t>['3', '57', '60']</t>
   </si>
   <si>
-    <t>['2', '48']</t>
-  </si>
-  <si>
-    <t>['20']</t>
-  </si>
-  <si>
-    <t>['30', '64']</t>
+    <t>['50', '90+9']</t>
+  </si>
+  <si>
+    <t>['38']</t>
+  </si>
+  <si>
+    <t>['59']</t>
+  </si>
+  <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['18']</t>
   </si>
 </sst>
 </file>
@@ -1491,10 +1521,10 @@
         <v>1.07</v>
       </c>
       <c r="AJ2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL2" s="3">
         <v>45858</v>
@@ -1607,10 +1637,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AK3" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AL3" s="3">
         <v>45858.08333333334</v>
@@ -1723,10 +1753,10 @@
         <v>1.16</v>
       </c>
       <c r="AJ4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AK4" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="AL4" s="3">
         <v>45858.08333333334</v>
@@ -1839,10 +1869,10 @@
         <v>1.29</v>
       </c>
       <c r="AJ5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AK5" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AL5" s="3">
         <v>45858.16666666666</v>
@@ -1955,10 +1985,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK6" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AL6" s="3">
         <v>45858.25</v>
@@ -2071,10 +2101,10 @@
         <v>1.09</v>
       </c>
       <c r="AJ7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AK7" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="AL7" s="3">
         <v>45858.25</v>
@@ -2187,10 +2217,10 @@
         <v>1.07</v>
       </c>
       <c r="AJ8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AK8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL8" s="3">
         <v>45858.27083333334</v>
@@ -2216,13 +2246,13 @@
         <v>191</v>
       </c>
       <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>2</v>
       </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
       <c r="I9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -2231,82 +2261,82 @@
         <v>272</v>
       </c>
       <c r="L9">
-        <v>2.47</v>
+        <v>3.99</v>
       </c>
       <c r="M9">
-        <v>3.23</v>
+        <v>3.36</v>
       </c>
       <c r="N9">
-        <v>2.47</v>
+        <v>1.75</v>
       </c>
       <c r="O9">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="P9">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="Q9">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="R9">
+        <v>1.4</v>
+      </c>
+      <c r="S9">
+        <v>2.75</v>
+      </c>
+      <c r="T9">
+        <v>2.75</v>
+      </c>
+      <c r="U9">
+        <v>1.4</v>
+      </c>
+      <c r="V9">
+        <v>8</v>
+      </c>
+      <c r="W9">
+        <v>1.08</v>
+      </c>
+      <c r="X9">
+        <v>1.06</v>
+      </c>
+      <c r="Y9">
+        <v>8.5</v>
+      </c>
+      <c r="Z9">
         <v>1.33</v>
       </c>
-      <c r="S9">
+      <c r="AA9">
         <v>3.25</v>
       </c>
-      <c r="T9">
-        <v>2.63</v>
-      </c>
-      <c r="U9">
-        <v>1.44</v>
-      </c>
-      <c r="V9">
-        <v>6.5</v>
-      </c>
-      <c r="W9">
-        <v>1.11</v>
-      </c>
-      <c r="X9">
-        <v>1.05</v>
-      </c>
-      <c r="Y9">
-        <v>9.5</v>
-      </c>
-      <c r="Z9">
-        <v>1.25</v>
-      </c>
-      <c r="AA9">
-        <v>3.7</v>
-      </c>
       <c r="AB9">
+        <v>1.94</v>
+      </c>
+      <c r="AC9">
         <v>1.76</v>
       </c>
-      <c r="AC9">
-        <v>1.94</v>
-      </c>
       <c r="AD9">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AE9">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AF9">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AG9">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH9">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AI9">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AJ9" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AK9" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AL9" s="3">
         <v>45858.29166666666</v>
@@ -2320,7 +2350,7 @@
         <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
         <v>95</v>
@@ -2332,13 +2362,13 @@
         <v>192</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -2347,82 +2377,82 @@
         <v>272</v>
       </c>
       <c r="L10">
-        <v>2.16</v>
+        <v>2.47</v>
       </c>
       <c r="M10">
-        <v>3.32</v>
+        <v>3.23</v>
       </c>
       <c r="N10">
-        <v>3.08</v>
+        <v>2.47</v>
       </c>
       <c r="O10">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="P10">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="R10">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="T10">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="U10">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="Z10">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AA10">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="AB10">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC10">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AD10">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AE10">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AF10">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH10">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AI10">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AJ10" t="s">
         <v>281</v>
       </c>
       <c r="AK10" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AL10" s="3">
         <v>45858.29166666666</v>
@@ -2436,7 +2466,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
         <v>95</v>
@@ -2448,13 +2478,13 @@
         <v>193</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2463,82 +2493,82 @@
         <v>272</v>
       </c>
       <c r="L11">
-        <v>2.19</v>
+        <v>2.79</v>
       </c>
       <c r="M11">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="N11">
-        <v>2.91</v>
+        <v>2.29</v>
       </c>
       <c r="O11">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="P11">
-        <v>7.75</v>
+        <v>8.25</v>
       </c>
       <c r="Q11">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="R11">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S11">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="T11">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="U11">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y11">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="Z11">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AA11">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AB11">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AC11">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AD11">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AE11">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG11">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH11">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AI11">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AJ11" t="s">
         <v>282</v>
       </c>
       <c r="AK11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL11" s="3">
         <v>45858.29166666666</v>
@@ -2564,7 +2594,7 @@
         <v>194</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -2579,82 +2609,82 @@
         <v>272</v>
       </c>
       <c r="L12">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="M12">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="N12">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="O12">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P12">
+        <v>7.5</v>
+      </c>
+      <c r="Q12">
+        <v>1.58</v>
+      </c>
+      <c r="R12">
+        <v>1.46</v>
+      </c>
+      <c r="S12">
+        <v>2.5</v>
+      </c>
+      <c r="T12">
+        <v>3.1</v>
+      </c>
+      <c r="U12">
+        <v>1.31</v>
+      </c>
+      <c r="V12">
         <v>8.75</v>
       </c>
-      <c r="Q12">
-        <v>1.53</v>
-      </c>
-      <c r="R12">
+      <c r="W12">
+        <v>1.06</v>
+      </c>
+      <c r="X12">
+        <v>1.08</v>
+      </c>
+      <c r="Y12">
+        <v>7.5</v>
+      </c>
+      <c r="Z12">
         <v>1.4</v>
       </c>
-      <c r="S12">
-        <v>2.75</v>
-      </c>
-      <c r="T12">
-        <v>2.75</v>
-      </c>
-      <c r="U12">
-        <v>1.4</v>
-      </c>
-      <c r="V12">
-        <v>8</v>
-      </c>
-      <c r="W12">
-        <v>1.08</v>
-      </c>
-      <c r="X12">
+      <c r="AA12">
+        <v>2.7</v>
+      </c>
+      <c r="AB12">
+        <v>2.13</v>
+      </c>
+      <c r="AC12">
+        <v>1.63</v>
+      </c>
+      <c r="AD12">
+        <v>4</v>
+      </c>
+      <c r="AE12">
+        <v>1.21</v>
+      </c>
+      <c r="AF12">
+        <v>2.1</v>
+      </c>
+      <c r="AG12">
+        <v>1.65</v>
+      </c>
+      <c r="AH12">
+        <v>8.25</v>
+      </c>
+      <c r="AI12">
         <v>1.06</v>
       </c>
-      <c r="Y12">
-        <v>8.5</v>
-      </c>
-      <c r="Z12">
-        <v>1.33</v>
-      </c>
-      <c r="AA12">
-        <v>3.25</v>
-      </c>
-      <c r="AB12">
-        <v>1.94</v>
-      </c>
-      <c r="AC12">
-        <v>1.76</v>
-      </c>
-      <c r="AD12">
-        <v>3.5</v>
-      </c>
-      <c r="AE12">
-        <v>1.28</v>
-      </c>
-      <c r="AF12">
-        <v>1.91</v>
-      </c>
-      <c r="AG12">
-        <v>1.91</v>
-      </c>
-      <c r="AH12">
-        <v>7</v>
-      </c>
-      <c r="AI12">
-        <v>1.09</v>
-      </c>
       <c r="AJ12" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="AK12" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AL12" s="3">
         <v>45858.29166666666</v>
@@ -2767,10 +2797,10 @@
         <v>1.03</v>
       </c>
       <c r="AJ13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AK13" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="AL13" s="3">
         <v>45858.29166666666</v>
@@ -2784,7 +2814,7 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
         <v>95</v>
@@ -2796,13 +2826,13 @@
         <v>196</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
         <v>2</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -2811,82 +2841,82 @@
         <v>272</v>
       </c>
       <c r="L14">
-        <v>4.6</v>
+        <v>2.16</v>
       </c>
       <c r="M14">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="N14">
-        <v>1.68</v>
+        <v>3.08</v>
       </c>
       <c r="O14">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="P14">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="Q14">
-        <v>1.58</v>
+        <v>2.22</v>
       </c>
       <c r="R14">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S14">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="T14">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U14">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="V14">
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="Z14">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AA14">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="AB14">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="AC14">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="AD14">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AE14">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AF14">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AH14">
-        <v>8.25</v>
+        <v>6.2</v>
       </c>
       <c r="AI14">
         <v>1.06</v>
       </c>
       <c r="AJ14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AK14" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AL14" s="3">
         <v>45858.29166666666</v>
@@ -2900,7 +2930,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
         <v>95</v>
@@ -2912,13 +2942,13 @@
         <v>197</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2927,82 +2957,82 @@
         <v>272</v>
       </c>
       <c r="L15">
-        <v>2.79</v>
+        <v>2.19</v>
       </c>
       <c r="M15">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="N15">
-        <v>2.29</v>
+        <v>2.91</v>
       </c>
       <c r="O15">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="P15">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="Q15">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="R15">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S15">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="T15">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V15">
+        <v>9</v>
+      </c>
+      <c r="W15">
+        <v>1.07</v>
+      </c>
+      <c r="X15">
+        <v>1.08</v>
+      </c>
+      <c r="Y15">
         <v>7.5</v>
       </c>
-      <c r="W15">
-        <v>1.08</v>
-      </c>
-      <c r="X15">
-        <v>1.06</v>
-      </c>
-      <c r="Y15">
-        <v>8.25</v>
-      </c>
       <c r="Z15">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AA15">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AB15">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AC15">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AD15">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AE15">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG15">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH15">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AI15">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AJ15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AK15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL15" s="3">
         <v>45858.29166666666</v>
@@ -3115,10 +3145,10 @@
         <v>1.12</v>
       </c>
       <c r="AJ16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL16" s="3">
         <v>45858.29166666666</v>
@@ -3147,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -3156,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L17">
         <v>1.61</v>
@@ -3231,10 +3261,10 @@
         <v>1.1</v>
       </c>
       <c r="AJ17" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK17" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="AL17" s="3">
         <v>45858.33333333334</v>
@@ -3260,97 +3290,97 @@
         <v>200</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L18">
-        <v>3.05</v>
+        <v>1.63</v>
       </c>
       <c r="M18">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N18">
-        <v>2.26</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="P18">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q18">
+        <v>3.4</v>
+      </c>
+      <c r="R18">
+        <v>1.44</v>
+      </c>
+      <c r="S18">
+        <v>2.52</v>
+      </c>
+      <c r="T18">
+        <v>3.1</v>
+      </c>
+      <c r="U18">
+        <v>1.3</v>
+      </c>
+      <c r="V18">
+        <v>8</v>
+      </c>
+      <c r="W18">
+        <v>1.01</v>
+      </c>
+      <c r="X18">
+        <v>1.08</v>
+      </c>
+      <c r="Y18">
+        <v>7.5</v>
+      </c>
+      <c r="Z18">
+        <v>1.31</v>
+      </c>
+      <c r="AA18">
+        <v>2.88</v>
+      </c>
+      <c r="AB18">
         <v>2.1</v>
       </c>
-      <c r="R18">
-        <v>1.38</v>
-      </c>
-      <c r="S18">
-        <v>2.72</v>
-      </c>
-      <c r="T18">
-        <v>2.6</v>
-      </c>
-      <c r="U18">
-        <v>1.37</v>
-      </c>
-      <c r="V18">
-        <v>6.5</v>
-      </c>
-      <c r="W18">
-        <v>1.04</v>
-      </c>
-      <c r="X18">
-        <v>1.01</v>
-      </c>
-      <c r="Y18">
-        <v>9.5</v>
-      </c>
-      <c r="Z18">
-        <v>1.25</v>
-      </c>
-      <c r="AA18">
-        <v>3.5</v>
-      </c>
-      <c r="AB18">
-        <v>1.91</v>
-      </c>
       <c r="AC18">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AD18">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="AE18">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AH18">
-        <v>6.15</v>
+        <v>7.5</v>
       </c>
       <c r="AI18">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ18" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="AK18" t="s">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="AL18" s="3">
         <v>45858.35416666666</v>
@@ -3388,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L19">
         <v>2.4</v>
@@ -3463,10 +3493,10 @@
         <v>1.08</v>
       </c>
       <c r="AJ19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL19" s="3">
         <v>45858.35416666666</v>
@@ -3492,7 +3522,7 @@
         <v>202</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -3504,85 +3534,85 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L20">
-        <v>1.63</v>
+        <v>3.05</v>
       </c>
       <c r="M20">
+        <v>3.15</v>
+      </c>
+      <c r="N20">
+        <v>2.26</v>
+      </c>
+      <c r="O20">
+        <v>1.91</v>
+      </c>
+      <c r="P20">
+        <v>7.9</v>
+      </c>
+      <c r="Q20">
+        <v>2.1</v>
+      </c>
+      <c r="R20">
+        <v>1.38</v>
+      </c>
+      <c r="S20">
+        <v>2.72</v>
+      </c>
+      <c r="T20">
+        <v>2.6</v>
+      </c>
+      <c r="U20">
+        <v>1.37</v>
+      </c>
+      <c r="V20">
+        <v>6.5</v>
+      </c>
+      <c r="W20">
+        <v>1.04</v>
+      </c>
+      <c r="X20">
+        <v>1.01</v>
+      </c>
+      <c r="Y20">
+        <v>9.5</v>
+      </c>
+      <c r="Z20">
+        <v>1.25</v>
+      </c>
+      <c r="AA20">
         <v>3.5</v>
       </c>
-      <c r="N20">
-        <v>5</v>
-      </c>
-      <c r="O20">
-        <v>1.44</v>
-      </c>
-      <c r="P20">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="Q20">
-        <v>3.4</v>
-      </c>
-      <c r="R20">
-        <v>1.44</v>
-      </c>
-      <c r="S20">
-        <v>2.52</v>
-      </c>
-      <c r="T20">
+      <c r="AB20">
+        <v>1.91</v>
+      </c>
+      <c r="AC20">
+        <v>1.75</v>
+      </c>
+      <c r="AD20">
         <v>3.1</v>
       </c>
-      <c r="U20">
+      <c r="AE20">
         <v>1.3</v>
       </c>
-      <c r="V20">
-        <v>8</v>
-      </c>
-      <c r="W20">
-        <v>1.01</v>
-      </c>
-      <c r="X20">
-        <v>1.08</v>
-      </c>
-      <c r="Y20">
-        <v>7.5</v>
-      </c>
-      <c r="Z20">
-        <v>1.31</v>
-      </c>
-      <c r="AA20">
-        <v>2.88</v>
-      </c>
-      <c r="AB20">
-        <v>2.1</v>
-      </c>
-      <c r="AC20">
-        <v>1.62</v>
-      </c>
-      <c r="AD20">
-        <v>4.2</v>
-      </c>
-      <c r="AE20">
-        <v>1.2</v>
-      </c>
       <c r="AF20">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AG20">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AH20">
-        <v>7.5</v>
+        <v>6.15</v>
       </c>
       <c r="AI20">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AJ20" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="AK20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL20" s="3">
         <v>45858.35416666666</v>
@@ -3608,7 +3638,7 @@
         <v>203</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -3620,85 +3650,85 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L21">
-        <v>2.49</v>
+        <v>2.03</v>
       </c>
       <c r="M21">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="N21">
+        <v>3.06</v>
+      </c>
+      <c r="O21">
+        <v>1.67</v>
+      </c>
+      <c r="P21">
+        <v>9</v>
+      </c>
+      <c r="Q21">
         <v>2.4</v>
       </c>
-      <c r="O21">
+      <c r="R21">
+        <v>1.44</v>
+      </c>
+      <c r="S21">
+        <v>2.63</v>
+      </c>
+      <c r="T21">
+        <v>3.25</v>
+      </c>
+      <c r="U21">
+        <v>1.33</v>
+      </c>
+      <c r="V21">
+        <v>9</v>
+      </c>
+      <c r="W21">
+        <v>1.07</v>
+      </c>
+      <c r="X21">
+        <v>1.06</v>
+      </c>
+      <c r="Y21">
+        <v>9</v>
+      </c>
+      <c r="Z21">
+        <v>1.38</v>
+      </c>
+      <c r="AA21">
+        <v>3.1</v>
+      </c>
+      <c r="AB21">
+        <v>1.85</v>
+      </c>
+      <c r="AC21">
+        <v>1.85</v>
+      </c>
+      <c r="AD21">
+        <v>3.95</v>
+      </c>
+      <c r="AE21">
+        <v>1.25</v>
+      </c>
+      <c r="AF21">
+        <v>1.95</v>
+      </c>
+      <c r="AG21">
         <v>1.8</v>
       </c>
-      <c r="P21">
-        <v>10</v>
-      </c>
-      <c r="Q21">
-        <v>2.1</v>
-      </c>
-      <c r="R21">
-        <v>1.33</v>
-      </c>
-      <c r="S21">
-        <v>3.25</v>
-      </c>
-      <c r="T21">
-        <v>2.5</v>
-      </c>
-      <c r="U21">
-        <v>1.5</v>
-      </c>
-      <c r="V21">
-        <v>6</v>
-      </c>
-      <c r="W21">
-        <v>1.13</v>
-      </c>
-      <c r="X21">
-        <v>1.05</v>
-      </c>
-      <c r="Y21">
-        <v>10</v>
-      </c>
-      <c r="Z21">
-        <v>1.25</v>
-      </c>
-      <c r="AA21">
-        <v>4</v>
-      </c>
-      <c r="AB21">
-        <v>1.67</v>
-      </c>
-      <c r="AC21">
-        <v>2.07</v>
-      </c>
-      <c r="AD21">
-        <v>2.8</v>
-      </c>
-      <c r="AE21">
-        <v>1.45</v>
-      </c>
-      <c r="AF21">
-        <v>1.57</v>
-      </c>
-      <c r="AG21">
-        <v>2.25</v>
-      </c>
       <c r="AH21">
-        <v>5.25</v>
+        <v>8</v>
       </c>
       <c r="AI21">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AJ21" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="AK21" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL21" s="3">
         <v>45858.375</v>
@@ -3727,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -3736,85 +3766,85 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L22">
-        <v>2.03</v>
+        <v>2.49</v>
       </c>
       <c r="M22">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="N22">
-        <v>3.06</v>
+        <v>2.4</v>
       </c>
       <c r="O22">
+        <v>1.8</v>
+      </c>
+      <c r="P22">
+        <v>10</v>
+      </c>
+      <c r="Q22">
+        <v>2.1</v>
+      </c>
+      <c r="R22">
+        <v>1.33</v>
+      </c>
+      <c r="S22">
+        <v>3.25</v>
+      </c>
+      <c r="T22">
+        <v>2.5</v>
+      </c>
+      <c r="U22">
+        <v>1.5</v>
+      </c>
+      <c r="V22">
+        <v>6</v>
+      </c>
+      <c r="W22">
+        <v>1.13</v>
+      </c>
+      <c r="X22">
+        <v>1.05</v>
+      </c>
+      <c r="Y22">
+        <v>10</v>
+      </c>
+      <c r="Z22">
+        <v>1.25</v>
+      </c>
+      <c r="AA22">
+        <v>4</v>
+      </c>
+      <c r="AB22">
         <v>1.67</v>
       </c>
-      <c r="P22">
-        <v>9</v>
-      </c>
-      <c r="Q22">
-        <v>2.4</v>
-      </c>
-      <c r="R22">
-        <v>1.44</v>
-      </c>
-      <c r="S22">
-        <v>2.63</v>
-      </c>
-      <c r="T22">
-        <v>3.25</v>
-      </c>
-      <c r="U22">
-        <v>1.33</v>
-      </c>
-      <c r="V22">
-        <v>9</v>
-      </c>
-      <c r="W22">
-        <v>1.07</v>
-      </c>
-      <c r="X22">
-        <v>1.06</v>
-      </c>
-      <c r="Y22">
-        <v>9</v>
-      </c>
-      <c r="Z22">
-        <v>1.38</v>
-      </c>
-      <c r="AA22">
-        <v>3.1</v>
-      </c>
-      <c r="AB22">
-        <v>1.85</v>
-      </c>
       <c r="AC22">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AD22">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="AE22">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AF22">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AG22">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH22">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="AI22">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AJ22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK22" t="s">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="AL22" s="3">
         <v>45858.375</v>
@@ -3927,10 +3957,10 @@
         <v>1.25</v>
       </c>
       <c r="AJ23" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK23" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL23" s="3">
         <v>45858.39583333334</v>
@@ -4043,10 +4073,10 @@
         <v>1.18</v>
       </c>
       <c r="AJ24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL24" s="3">
         <v>45858.41666666666</v>
@@ -4072,97 +4102,97 @@
         <v>207</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L25">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="M25">
+        <v>4.1</v>
+      </c>
+      <c r="N25">
         <v>4.2</v>
       </c>
-      <c r="N25">
-        <v>6.9</v>
-      </c>
       <c r="O25">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="P25">
-        <v>8.9</v>
+        <v>14</v>
       </c>
       <c r="Q25">
-        <v>3.52</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="S25">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="T25">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="U25">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="V25">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>8.5</v>
+        <v>15</v>
       </c>
       <c r="Z25">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AA25">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="AB25">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AC25">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AD25">
-        <v>3.85</v>
+        <v>2.27</v>
       </c>
       <c r="AE25">
-        <v>1.22</v>
+        <v>1.63</v>
       </c>
       <c r="AF25">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="AH25">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="AI25">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AJ25" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="AK25" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="AL25" s="3">
         <v>45858.41666666666</v>
@@ -4191,94 +4221,94 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L26">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="M26">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="N26">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="O26">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="P26">
-        <v>14</v>
+        <v>8.9</v>
       </c>
       <c r="Q26">
-        <v>2.75</v>
+        <v>3.52</v>
       </c>
       <c r="R26">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="S26">
-        <v>3.5</v>
+        <v>2.51</v>
       </c>
       <c r="T26">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="U26">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="V26">
-        <v>4.4</v>
+        <v>7.7</v>
       </c>
       <c r="W26">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="Z26">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AA26">
-        <v>4.75</v>
+        <v>2.74</v>
       </c>
       <c r="AB26">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="AC26">
-        <v>2.56</v>
+        <v>1.65</v>
       </c>
       <c r="AD26">
-        <v>2.12</v>
+        <v>3.8</v>
       </c>
       <c r="AE26">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="AF26">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AG26">
-        <v>2.59</v>
+        <v>1.75</v>
       </c>
       <c r="AH26">
-        <v>3.72</v>
+        <v>9</v>
       </c>
       <c r="AI26">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AJ26" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK26" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="AL26" s="3">
         <v>45858.41666666666</v>
@@ -4319,82 +4349,82 @@
         <v>273</v>
       </c>
       <c r="L27">
-        <v>1.67</v>
+        <v>1.16</v>
       </c>
       <c r="M27">
-        <v>3.6</v>
+        <v>6.7</v>
       </c>
       <c r="N27">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="O27">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="P27">
-        <v>7.25</v>
+        <v>24</v>
       </c>
       <c r="Q27">
+        <v>4</v>
+      </c>
+      <c r="R27">
+        <v>1.2</v>
+      </c>
+      <c r="S27">
+        <v>4</v>
+      </c>
+      <c r="T27">
+        <v>1.7</v>
+      </c>
+      <c r="U27">
+        <v>2</v>
+      </c>
+      <c r="V27">
+        <v>3.3</v>
+      </c>
+      <c r="W27">
+        <v>1.27</v>
+      </c>
+      <c r="X27">
+        <v>1.02</v>
+      </c>
+      <c r="Y27">
+        <v>21</v>
+      </c>
+      <c r="Z27">
+        <v>1.06</v>
+      </c>
+      <c r="AA27">
+        <v>5.75</v>
+      </c>
+      <c r="AB27">
+        <v>1.29</v>
+      </c>
+      <c r="AC27">
         <v>3.5</v>
       </c>
-      <c r="R27">
-        <v>1.44</v>
-      </c>
-      <c r="S27">
-        <v>2.6</v>
-      </c>
-      <c r="T27">
-        <v>3.38</v>
-      </c>
-      <c r="U27">
-        <v>1.33</v>
-      </c>
-      <c r="V27">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W27">
-        <v>1.05</v>
-      </c>
-      <c r="X27">
-        <v>1.08</v>
-      </c>
-      <c r="Y27">
-        <v>7.5</v>
-      </c>
-      <c r="Z27">
-        <v>1.36</v>
-      </c>
-      <c r="AA27">
-        <v>2.9</v>
-      </c>
-      <c r="AB27">
-        <v>2.2</v>
-      </c>
-      <c r="AC27">
-        <v>1.65</v>
-      </c>
       <c r="AD27">
-        <v>4</v>
+        <v>1.77</v>
       </c>
       <c r="AE27">
-        <v>1.22</v>
+        <v>1.93</v>
       </c>
       <c r="AF27">
+        <v>1.57</v>
+      </c>
+      <c r="AG27">
         <v>2.1</v>
       </c>
-      <c r="AG27">
-        <v>1.65</v>
-      </c>
       <c r="AH27">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AI27">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AJ27" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK27" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL27" s="3">
         <v>45858.45833333334</v>
@@ -4435,82 +4465,82 @@
         <v>273</v>
       </c>
       <c r="L28">
-        <v>1.16</v>
+        <v>1.55</v>
       </c>
       <c r="M28">
-        <v>6.7</v>
+        <v>3.47</v>
       </c>
       <c r="N28">
-        <v>9.5</v>
+        <v>5.3</v>
       </c>
       <c r="O28">
+        <v>1.44</v>
+      </c>
+      <c r="P28">
+        <v>7.25</v>
+      </c>
+      <c r="Q28">
+        <v>3.5</v>
+      </c>
+      <c r="R28">
+        <v>1.44</v>
+      </c>
+      <c r="S28">
+        <v>2.6</v>
+      </c>
+      <c r="T28">
+        <v>3.38</v>
+      </c>
+      <c r="U28">
+        <v>1.33</v>
+      </c>
+      <c r="V28">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W28">
+        <v>1.05</v>
+      </c>
+      <c r="X28">
+        <v>1.08</v>
+      </c>
+      <c r="Y28">
+        <v>7.5</v>
+      </c>
+      <c r="Z28">
+        <v>1.36</v>
+      </c>
+      <c r="AA28">
+        <v>2.9</v>
+      </c>
+      <c r="AB28">
+        <v>2.2</v>
+      </c>
+      <c r="AC28">
+        <v>1.59</v>
+      </c>
+      <c r="AD28">
+        <v>4</v>
+      </c>
+      <c r="AE28">
         <v>1.22</v>
       </c>
-      <c r="P28">
-        <v>24</v>
-      </c>
-      <c r="Q28">
-        <v>4</v>
-      </c>
-      <c r="R28">
-        <v>1.2</v>
-      </c>
-      <c r="S28">
-        <v>4.5</v>
-      </c>
-      <c r="T28">
-        <v>2.02</v>
-      </c>
-      <c r="U28">
-        <v>1.75</v>
-      </c>
-      <c r="V28">
-        <v>4.2</v>
-      </c>
-      <c r="W28">
-        <v>1.17</v>
-      </c>
-      <c r="X28">
-        <v>1.01</v>
-      </c>
-      <c r="Y28">
-        <v>23</v>
-      </c>
-      <c r="Z28">
-        <v>1.06</v>
-      </c>
-      <c r="AA28">
-        <v>6.15</v>
-      </c>
-      <c r="AB28">
-        <v>1.29</v>
-      </c>
-      <c r="AC28">
-        <v>3.5</v>
-      </c>
-      <c r="AD28">
-        <v>1.77</v>
-      </c>
-      <c r="AE28">
-        <v>1.93</v>
-      </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AG28">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AH28">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AI28">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AJ28" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK28" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL28" s="3">
         <v>45858.45833333334</v>
@@ -4524,7 +4554,7 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D29" t="s">
         <v>95</v>
@@ -4572,31 +4602,31 @@
         <v>1.2</v>
       </c>
       <c r="S29">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T29">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U29">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="V29">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="W29">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X29">
         <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="Z29">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AA29">
-        <v>5.95</v>
+        <v>5.65</v>
       </c>
       <c r="AB29">
         <v>1.4</v>
@@ -4611,22 +4641,22 @@
         <v>1.73</v>
       </c>
       <c r="AF29">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AH29">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AI29">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AJ29" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK29" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL29" s="3">
         <v>45858.45833333334</v>
@@ -4667,82 +4697,82 @@
         <v>273</v>
       </c>
       <c r="L30">
-        <v>3.17</v>
+        <v>1.52</v>
       </c>
       <c r="M30">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N30">
-        <v>1.94</v>
+        <v>4.7</v>
       </c>
       <c r="O30">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="P30">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q30">
+        <v>2.88</v>
+      </c>
+      <c r="R30">
+        <v>1.25</v>
+      </c>
+      <c r="S30">
+        <v>3.75</v>
+      </c>
+      <c r="T30">
+        <v>2.2</v>
+      </c>
+      <c r="U30">
         <v>1.62</v>
       </c>
-      <c r="R30">
-        <v>1.33</v>
-      </c>
-      <c r="S30">
-        <v>3.25</v>
-      </c>
-      <c r="T30">
-        <v>2.63</v>
-      </c>
-      <c r="U30">
-        <v>1.44</v>
-      </c>
       <c r="V30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X30">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Z30">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA30">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="AB30">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AC30">
-        <v>1.94</v>
+        <v>2.34</v>
       </c>
       <c r="AD30">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AE30">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AF30">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH30">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="AI30">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AJ30" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK30" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL30" s="3">
         <v>45858.47916666666</v>
@@ -4783,82 +4813,82 @@
         <v>273</v>
       </c>
       <c r="L31">
-        <v>1.52</v>
+        <v>3.17</v>
       </c>
       <c r="M31">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N31">
-        <v>4.7</v>
+        <v>1.94</v>
       </c>
       <c r="O31">
+        <v>2.38</v>
+      </c>
+      <c r="P31">
+        <v>10</v>
+      </c>
+      <c r="Q31">
+        <v>1.62</v>
+      </c>
+      <c r="R31">
+        <v>1.33</v>
+      </c>
+      <c r="S31">
+        <v>3.25</v>
+      </c>
+      <c r="T31">
+        <v>2.63</v>
+      </c>
+      <c r="U31">
+        <v>1.44</v>
+      </c>
+      <c r="V31">
+        <v>7</v>
+      </c>
+      <c r="W31">
+        <v>1.1</v>
+      </c>
+      <c r="X31">
+        <v>1.05</v>
+      </c>
+      <c r="Y31">
+        <v>10</v>
+      </c>
+      <c r="Z31">
+        <v>1.25</v>
+      </c>
+      <c r="AA31">
+        <v>3.85</v>
+      </c>
+      <c r="AB31">
+        <v>1.76</v>
+      </c>
+      <c r="AC31">
+        <v>1.94</v>
+      </c>
+      <c r="AD31">
+        <v>3</v>
+      </c>
+      <c r="AE31">
         <v>1.4</v>
       </c>
-      <c r="P31">
-        <v>12</v>
-      </c>
-      <c r="Q31">
-        <v>2.88</v>
-      </c>
-      <c r="R31">
-        <v>1.25</v>
-      </c>
-      <c r="S31">
-        <v>3.75</v>
-      </c>
-      <c r="T31">
-        <v>2.2</v>
-      </c>
-      <c r="U31">
-        <v>1.62</v>
-      </c>
-      <c r="V31">
-        <v>5</v>
-      </c>
-      <c r="W31">
-        <v>1.17</v>
-      </c>
-      <c r="X31">
-        <v>1.01</v>
-      </c>
-      <c r="Y31">
-        <v>17</v>
-      </c>
-      <c r="Z31">
-        <v>1.18</v>
-      </c>
-      <c r="AA31">
-        <v>5</v>
-      </c>
-      <c r="AB31">
-        <v>1.6</v>
-      </c>
-      <c r="AC31">
-        <v>2.34</v>
-      </c>
-      <c r="AD31">
-        <v>2.3</v>
-      </c>
-      <c r="AE31">
-        <v>1.54</v>
-      </c>
       <c r="AF31">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG31">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH31">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="AI31">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AJ31" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK31" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL31" s="3">
         <v>45858.47916666666</v>
@@ -4872,7 +4902,7 @@
         <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D32" t="s">
         <v>95</v>
@@ -4899,82 +4929,82 @@
         <v>273</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ32" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK32" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL32" s="3">
         <v>45858.5</v>
@@ -5087,10 +5117,10 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK33" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL33" s="3">
         <v>45858.5</v>
@@ -5203,10 +5233,10 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK34" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL34" s="3">
         <v>45858.5</v>
@@ -5220,7 +5250,7 @@
         <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
         <v>95</v>
@@ -5247,82 +5277,82 @@
         <v>273</v>
       </c>
       <c r="L35">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Q35">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S35">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V35">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W35">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z35">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH35">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI35">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK35" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL35" s="3">
         <v>45858.5</v>
@@ -5435,10 +5465,10 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK36" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL36" s="3">
         <v>45858.5</v>
@@ -5551,10 +5581,10 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK37" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL37" s="3">
         <v>45858.5</v>
@@ -5667,10 +5697,10 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK38" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL38" s="3">
         <v>45858.5</v>
@@ -5684,7 +5714,7 @@
         <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D39" t="s">
         <v>95</v>
@@ -5711,82 +5741,82 @@
         <v>273</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH39">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AI39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ39" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK39" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL39" s="3">
         <v>45858.5</v>
@@ -5899,10 +5929,10 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK40" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL40" s="3">
         <v>45858.5</v>
@@ -5916,7 +5946,7 @@
         <v>51</v>
       </c>
       <c r="C41" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D41" t="s">
         <v>95</v>
@@ -5943,82 +5973,82 @@
         <v>273</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH41">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ41" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK41" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL41" s="3">
         <v>45858.5</v>
@@ -6032,7 +6062,7 @@
         <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D42" t="s">
         <v>95</v>
@@ -6059,82 +6089,82 @@
         <v>273</v>
       </c>
       <c r="L42">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N42">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S42">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T42">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z42">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AA42">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE42">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF42">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG42">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH42">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI42">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK42" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL42" s="3">
         <v>45858.5</v>
@@ -6148,7 +6178,7 @@
         <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D43" t="s">
         <v>95</v>
@@ -6175,82 +6205,82 @@
         <v>273</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH43">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI43">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ43" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK43" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL43" s="3">
         <v>45858.5</v>
@@ -6264,7 +6294,7 @@
         <v>51</v>
       </c>
       <c r="C44" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D44" t="s">
         <v>95</v>
@@ -6291,82 +6321,82 @@
         <v>273</v>
       </c>
       <c r="L44">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M44">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N44">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH44">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AI44">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK44" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL44" s="3">
         <v>45858.5</v>
@@ -6380,7 +6410,7 @@
         <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D45" t="s">
         <v>95</v>
@@ -6407,82 +6437,82 @@
         <v>273</v>
       </c>
       <c r="L45">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M45">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N45">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S45">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T45">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U45">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V45">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="W45">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z45">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA45">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AB45">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC45">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD45">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE45">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF45">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG45">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH45">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AI45">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK45" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL45" s="3">
         <v>45858.5</v>
@@ -6595,10 +6625,10 @@
         <v>0</v>
       </c>
       <c r="AJ46" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK46" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL46" s="3">
         <v>45858.5</v>
@@ -6711,10 +6741,10 @@
         <v>0</v>
       </c>
       <c r="AJ47" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK47" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL47" s="3">
         <v>45858.5</v>
@@ -6827,10 +6857,10 @@
         <v>0</v>
       </c>
       <c r="AJ48" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK48" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL48" s="3">
         <v>45858.5</v>
@@ -6943,10 +6973,10 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK49" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL49" s="3">
         <v>45858.5</v>
@@ -6960,7 +6990,7 @@
         <v>52</v>
       </c>
       <c r="C50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D50" t="s">
         <v>95</v>
@@ -6987,82 +7017,82 @@
         <v>273</v>
       </c>
       <c r="L50">
-        <v>1.28</v>
+        <v>5.7</v>
       </c>
       <c r="M50">
+        <v>4.5</v>
+      </c>
+      <c r="N50">
+        <v>1.53</v>
+      </c>
+      <c r="O50">
+        <v>3</v>
+      </c>
+      <c r="P50">
+        <v>12.5</v>
+      </c>
+      <c r="Q50">
+        <v>1.4</v>
+      </c>
+      <c r="R50">
+        <v>1.23</v>
+      </c>
+      <c r="S50">
+        <v>3.3</v>
+      </c>
+      <c r="T50">
+        <v>2.3</v>
+      </c>
+      <c r="U50">
+        <v>1.55</v>
+      </c>
+      <c r="V50">
         <v>5.2</v>
       </c>
-      <c r="N50">
-        <v>6.9</v>
-      </c>
-      <c r="O50">
-        <v>1.25</v>
-      </c>
-      <c r="P50">
-        <v>14</v>
-      </c>
-      <c r="Q50">
-        <v>4</v>
-      </c>
-      <c r="R50">
-        <v>1.25</v>
-      </c>
-      <c r="S50">
-        <v>3.5</v>
-      </c>
-      <c r="T50">
-        <v>2.2</v>
-      </c>
-      <c r="U50">
-        <v>1.57</v>
-      </c>
-      <c r="V50">
-        <v>4.8</v>
-      </c>
       <c r="W50">
+        <v>1.09</v>
+      </c>
+      <c r="X50">
+        <v>1.03</v>
+      </c>
+      <c r="Y50">
+        <v>9.5</v>
+      </c>
+      <c r="Z50">
         <v>1.17</v>
       </c>
-      <c r="X50">
-        <v>1.02</v>
-      </c>
-      <c r="Y50">
-        <v>10</v>
-      </c>
-      <c r="Z50">
-        <v>1.19</v>
-      </c>
       <c r="AA50">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AB50">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AC50">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AD50">
         <v>2.38</v>
       </c>
       <c r="AE50">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AF50">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG50">
         <v>2.1</v>
       </c>
       <c r="AH50">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AI50">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AJ50" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK50" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL50" s="3">
         <v>45858.52083333334</v>
@@ -7076,7 +7106,7 @@
         <v>52</v>
       </c>
       <c r="C51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D51" t="s">
         <v>95</v>
@@ -7103,64 +7133,64 @@
         <v>273</v>
       </c>
       <c r="L51">
-        <v>3.94</v>
+        <v>1.59</v>
       </c>
       <c r="M51">
-        <v>3.55</v>
+        <v>4.25</v>
       </c>
       <c r="N51">
-        <v>1.71</v>
+        <v>5.61</v>
       </c>
       <c r="O51">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="P51">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Q51">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="R51">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S51">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T51">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U51">
         <v>1.55</v>
       </c>
       <c r="V51">
-        <v>5.65</v>
+        <v>5</v>
       </c>
       <c r="W51">
         <v>1.13</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="Z51">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AA51">
         <v>4.33</v>
       </c>
       <c r="AB51">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC51">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD51">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AE51">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AF51">
         <v>1.67</v>
@@ -7169,16 +7199,16 @@
         <v>2.1</v>
       </c>
       <c r="AH51">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AI51">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AJ51" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK51" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL51" s="3">
         <v>45858.52083333334</v>
@@ -7192,7 +7222,7 @@
         <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D52" t="s">
         <v>95</v>
@@ -7219,13 +7249,13 @@
         <v>273</v>
       </c>
       <c r="L52">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="M52">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="N52">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="O52">
         <v>2.1</v>
@@ -7237,64 +7267,64 @@
         <v>1.8</v>
       </c>
       <c r="R52">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S52">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="T52">
         <v>2.62</v>
       </c>
       <c r="U52">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V52">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="W52">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z52">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AA52">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AB52">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC52">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD52">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AE52">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AF52">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AG52">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH52">
-        <v>5.75</v>
+        <v>4.4</v>
       </c>
       <c r="AI52">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AJ52" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK52" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL52" s="3">
         <v>45858.54166666666</v>
@@ -7308,7 +7338,7 @@
         <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D53" t="s">
         <v>95</v>
@@ -7335,13 +7365,13 @@
         <v>273</v>
       </c>
       <c r="L53">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="M53">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="N53">
-        <v>2.74</v>
+        <v>4.3</v>
       </c>
       <c r="O53">
         <v>1.53</v>
@@ -7371,46 +7401,46 @@
         <v>1.15</v>
       </c>
       <c r="X53">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y53">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z53">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AA53">
         <v>4.6</v>
       </c>
       <c r="AB53">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AC53">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AD53">
+        <v>2.8</v>
+      </c>
+      <c r="AE53">
+        <v>1.33</v>
+      </c>
+      <c r="AF53">
+        <v>1.73</v>
+      </c>
+      <c r="AG53">
         <v>2</v>
       </c>
-      <c r="AE53">
-        <v>1.67</v>
-      </c>
-      <c r="AF53">
-        <v>1.67</v>
-      </c>
-      <c r="AG53">
-        <v>2.15</v>
-      </c>
       <c r="AH53">
-        <v>3.9</v>
+        <v>5.35</v>
       </c>
       <c r="AI53">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AJ53" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK53" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL53" s="3">
         <v>45858.54166666666</v>
@@ -7523,10 +7553,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ54" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK54" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL54" s="3">
         <v>45858.5625</v>
@@ -7585,22 +7615,22 @@
         <v>3.25</v>
       </c>
       <c r="R55">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S55">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T55">
         <v>3.14</v>
       </c>
       <c r="U55">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V55">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W55">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
         <v>1.02</v>
@@ -7609,10 +7639,10 @@
         <v>7.5</v>
       </c>
       <c r="Z55">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AA55">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="AB55">
         <v>2.3</v>
@@ -7624,10 +7654,10 @@
         <v>3.8</v>
       </c>
       <c r="AE55">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF55">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG55">
         <v>1.75</v>
@@ -7636,13 +7666,13 @@
         <v>8</v>
       </c>
       <c r="AI55">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ55" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK55" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL55" s="3">
         <v>45858.5625</v>
@@ -7683,13 +7713,13 @@
         <v>273</v>
       </c>
       <c r="L56">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="M56">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N56">
-        <v>7.6</v>
+        <v>8.9</v>
       </c>
       <c r="O56">
         <v>1.36</v>
@@ -7725,16 +7755,16 @@
         <v>6.55</v>
       </c>
       <c r="Z56">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AA56">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AB56">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AC56">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AD56">
         <v>5.7</v>
@@ -7755,10 +7785,10 @@
         <v>1.01</v>
       </c>
       <c r="AJ56" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK56" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL56" s="3">
         <v>45858.58333333334</v>
@@ -7871,10 +7901,10 @@
         <v>1.1</v>
       </c>
       <c r="AJ57" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK57" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL57" s="3">
         <v>45858.59375</v>
@@ -7894,10 +7924,10 @@
         <v>95</v>
       </c>
       <c r="E58" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="F58" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -7987,10 +8017,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ58" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK58" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL58" s="3">
         <v>45858.60416666666</v>
@@ -8031,13 +8061,13 @@
         <v>273</v>
       </c>
       <c r="L59">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="M59">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="N59">
-        <v>5.56</v>
+        <v>4.3</v>
       </c>
       <c r="O59">
         <v>1.57</v>
@@ -8073,13 +8103,13 @@
         <v>5.5</v>
       </c>
       <c r="Z59">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AA59">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AB59">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AC59">
         <v>1.4</v>
@@ -8103,10 +8133,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ59" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK59" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL59" s="3">
         <v>45858.625</v>
@@ -8147,13 +8177,13 @@
         <v>273</v>
       </c>
       <c r="L60">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="M60">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="N60">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="O60">
         <v>1.73</v>
@@ -8189,16 +8219,16 @@
         <v>5.75</v>
       </c>
       <c r="Z60">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AA60">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AB60">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AC60">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AD60">
         <v>5</v>
@@ -8219,10 +8249,10 @@
         <v>1.02</v>
       </c>
       <c r="AJ60" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK60" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL60" s="3">
         <v>45858.64583333334</v>
@@ -8263,82 +8293,82 @@
         <v>273</v>
       </c>
       <c r="L61">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="M61">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="N61">
-        <v>4.72</v>
+        <v>2.86</v>
       </c>
       <c r="O61">
+        <v>2.05</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>2.38</v>
+      </c>
+      <c r="R61">
         <v>1.73</v>
       </c>
-      <c r="P61">
-        <v>0</v>
-      </c>
-      <c r="Q61">
-        <v>3.2</v>
-      </c>
-      <c r="R61">
-        <v>1.72</v>
-      </c>
       <c r="S61">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="T61">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="U61">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="V61">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X61">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Y61">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Z61">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AA61">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AB61">
-        <v>3.69</v>
+        <v>2.99</v>
       </c>
       <c r="AC61">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AD61">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="AE61">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF61">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AG61">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AH61">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI61">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ61" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK61" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL61" s="3">
         <v>45858.64583333334</v>
@@ -8379,82 +8409,82 @@
         <v>273</v>
       </c>
       <c r="L62">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="M62">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="N62">
+        <v>3.78</v>
+      </c>
+      <c r="O62">
+        <v>1.73</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>3.2</v>
+      </c>
+      <c r="R62">
+        <v>1.72</v>
+      </c>
+      <c r="S62">
+        <v>1.93</v>
+      </c>
+      <c r="T62">
+        <v>4.75</v>
+      </c>
+      <c r="U62">
+        <v>1.14</v>
+      </c>
+      <c r="V62">
+        <v>12</v>
+      </c>
+      <c r="W62">
+        <v>1.01</v>
+      </c>
+      <c r="X62">
+        <v>1.17</v>
+      </c>
+      <c r="Y62">
+        <v>4.3</v>
+      </c>
+      <c r="Z62">
+        <v>1.75</v>
+      </c>
+      <c r="AA62">
+        <v>1.95</v>
+      </c>
+      <c r="AB62">
+        <v>3.48</v>
+      </c>
+      <c r="AC62">
+        <v>1.26</v>
+      </c>
+      <c r="AD62">
+        <v>7.5</v>
+      </c>
+      <c r="AE62">
+        <v>1.06</v>
+      </c>
+      <c r="AF62">
         <v>2.8</v>
       </c>
-      <c r="O62">
-        <v>2.05</v>
-      </c>
-      <c r="P62">
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <v>2.38</v>
-      </c>
-      <c r="R62">
-        <v>1.73</v>
-      </c>
-      <c r="S62">
-        <v>2.09</v>
-      </c>
-      <c r="T62">
-        <v>4.33</v>
-      </c>
-      <c r="U62">
-        <v>1.18</v>
-      </c>
-      <c r="V62">
-        <v>11</v>
-      </c>
-      <c r="W62">
-        <v>1.03</v>
-      </c>
-      <c r="X62">
-        <v>1.12</v>
-      </c>
-      <c r="Y62">
-        <v>4.5</v>
-      </c>
-      <c r="Z62">
-        <v>1.65</v>
-      </c>
-      <c r="AA62">
-        <v>2.1</v>
-      </c>
-      <c r="AB62">
-        <v>3.4</v>
-      </c>
-      <c r="AC62">
-        <v>1.36</v>
-      </c>
-      <c r="AD62">
-        <v>6.75</v>
-      </c>
-      <c r="AE62">
-        <v>1.1</v>
-      </c>
-      <c r="AF62">
-        <v>2.4</v>
-      </c>
       <c r="AG62">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AH62">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI62">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ62" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK62" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL62" s="3">
         <v>45858.64583333334</v>
@@ -8567,10 +8597,10 @@
         <v>1.07</v>
       </c>
       <c r="AJ63" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK63" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL63" s="3">
         <v>45858.66666666666</v>
@@ -8584,7 +8614,7 @@
         <v>60</v>
       </c>
       <c r="C64" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D64" t="s">
         <v>95</v>
@@ -8611,82 +8641,82 @@
         <v>273</v>
       </c>
       <c r="L64">
-        <v>2.54</v>
+        <v>2.17</v>
       </c>
       <c r="M64">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="N64">
-        <v>2.7</v>
+        <v>3.23</v>
       </c>
       <c r="O64">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="P64">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
       <c r="Q64">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="R64">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="S64">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="T64">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U64">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V64">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="W64">
+        <v>1.02</v>
+      </c>
+      <c r="X64">
+        <v>1.13</v>
+      </c>
+      <c r="Y64">
+        <v>5.5</v>
+      </c>
+      <c r="Z64">
+        <v>1.53</v>
+      </c>
+      <c r="AA64">
+        <v>2.22</v>
+      </c>
+      <c r="AB64">
+        <v>2.25</v>
+      </c>
+      <c r="AC64">
+        <v>1.5</v>
+      </c>
+      <c r="AD64">
+        <v>6.42</v>
+      </c>
+      <c r="AE64">
+        <v>1.11</v>
+      </c>
+      <c r="AF64">
+        <v>2.4</v>
+      </c>
+      <c r="AG64">
+        <v>1.6</v>
+      </c>
+      <c r="AH64">
+        <v>12</v>
+      </c>
+      <c r="AI64">
         <v>1.03</v>
       </c>
-      <c r="X64">
-        <v>1.09</v>
-      </c>
-      <c r="Y64">
-        <v>6.7</v>
-      </c>
-      <c r="Z64">
-        <v>1.49</v>
-      </c>
-      <c r="AA64">
-        <v>2.5</v>
-      </c>
-      <c r="AB64">
-        <v>2.5</v>
-      </c>
-      <c r="AC64">
-        <v>1.58</v>
-      </c>
-      <c r="AD64">
-        <v>4.8</v>
-      </c>
-      <c r="AE64">
-        <v>1.18</v>
-      </c>
-      <c r="AF64">
-        <v>2.02</v>
-      </c>
-      <c r="AG64">
-        <v>1.73</v>
-      </c>
-      <c r="AH64">
-        <v>9.25</v>
-      </c>
-      <c r="AI64">
-        <v>1.01</v>
-      </c>
       <c r="AJ64" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK64" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL64" s="3">
         <v>45858.66666666666</v>
@@ -8700,7 +8730,7 @@
         <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D65" t="s">
         <v>95</v>
@@ -8727,82 +8757,82 @@
         <v>273</v>
       </c>
       <c r="L65">
-        <v>2.43</v>
+        <v>3.7</v>
       </c>
       <c r="M65">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="N65">
-        <v>3.3</v>
+        <v>1.84</v>
       </c>
       <c r="O65">
+        <v>2.6</v>
+      </c>
+      <c r="P65">
+        <v>9.5</v>
+      </c>
+      <c r="Q65">
+        <v>1.57</v>
+      </c>
+      <c r="R65">
+        <v>1.36</v>
+      </c>
+      <c r="S65">
+        <v>2.8</v>
+      </c>
+      <c r="T65">
+        <v>2.99</v>
+      </c>
+      <c r="U65">
+        <v>1.34</v>
+      </c>
+      <c r="V65">
+        <v>8</v>
+      </c>
+      <c r="W65">
+        <v>1.06</v>
+      </c>
+      <c r="X65">
+        <v>1.07</v>
+      </c>
+      <c r="Y65">
+        <v>8</v>
+      </c>
+      <c r="Z65">
+        <v>1.3</v>
+      </c>
+      <c r="AA65">
+        <v>2.97</v>
+      </c>
+      <c r="AB65">
+        <v>1.8</v>
+      </c>
+      <c r="AC65">
         <v>1.83</v>
       </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>2.63</v>
-      </c>
-      <c r="R65">
-        <v>1.73</v>
-      </c>
-      <c r="S65">
-        <v>2</v>
-      </c>
-      <c r="T65">
-        <v>4.33</v>
-      </c>
-      <c r="U65">
-        <v>1.18</v>
-      </c>
-      <c r="V65">
-        <v>11</v>
-      </c>
-      <c r="W65">
-        <v>1.01</v>
-      </c>
-      <c r="X65">
-        <v>1.15</v>
-      </c>
-      <c r="Y65">
-        <v>5</v>
-      </c>
-      <c r="Z65">
-        <v>1.66</v>
-      </c>
-      <c r="AA65">
-        <v>2.1</v>
-      </c>
-      <c r="AB65">
-        <v>3.2</v>
-      </c>
-      <c r="AC65">
-        <v>1.28</v>
-      </c>
       <c r="AD65">
-        <v>6.5</v>
+        <v>3.68</v>
       </c>
       <c r="AE65">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AF65">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AG65">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AH65">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AI65">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AJ65" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK65" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL65" s="3">
         <v>45858.66666666666</v>
@@ -8816,7 +8846,7 @@
         <v>60</v>
       </c>
       <c r="C66" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D66" t="s">
         <v>95</v>
@@ -8843,82 +8873,82 @@
         <v>273</v>
       </c>
       <c r="L66">
-        <v>1.28</v>
+        <v>2.5</v>
       </c>
       <c r="M66">
-        <v>4.75</v>
+        <v>3.11</v>
       </c>
       <c r="N66">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="O66">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="Q66">
+        <v>2.5</v>
+      </c>
+      <c r="R66">
+        <v>1.42</v>
+      </c>
+      <c r="S66">
+        <v>2.62</v>
+      </c>
+      <c r="T66">
+        <v>2.9</v>
+      </c>
+      <c r="U66">
+        <v>1.36</v>
+      </c>
+      <c r="V66">
         <v>7</v>
       </c>
-      <c r="R66">
-        <v>1.47</v>
-      </c>
-      <c r="S66">
-        <v>2.49</v>
-      </c>
-      <c r="T66">
-        <v>3.3</v>
-      </c>
-      <c r="U66">
-        <v>1.33</v>
-      </c>
-      <c r="V66">
-        <v>9.6</v>
-      </c>
       <c r="W66">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X66">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Z66">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AA66">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AB66">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC66">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AD66">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AE66">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF66">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="AG66">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AH66">
-        <v>8</v>
+        <v>6.55</v>
       </c>
       <c r="AI66">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AJ66" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK66" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL66" s="3">
         <v>45858.66666666666</v>
@@ -8932,7 +8962,7 @@
         <v>60</v>
       </c>
       <c r="C67" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D67" t="s">
         <v>95</v>
@@ -8959,82 +8989,82 @@
         <v>273</v>
       </c>
       <c r="L67">
-        <v>1.99</v>
+        <v>1.58</v>
       </c>
       <c r="M67">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="N67">
-        <v>4.6</v>
+        <v>4.81</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R67">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="S67">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="T67">
-        <v>4.33</v>
+        <v>2.05</v>
       </c>
       <c r="U67">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="V67">
+        <v>4.5</v>
+      </c>
+      <c r="W67">
+        <v>1.17</v>
+      </c>
+      <c r="X67">
+        <v>1</v>
+      </c>
+      <c r="Y67">
         <v>12</v>
       </c>
-      <c r="W67">
-        <v>1</v>
-      </c>
-      <c r="X67">
-        <v>1.11</v>
-      </c>
-      <c r="Y67">
-        <v>4.75</v>
-      </c>
       <c r="Z67">
-        <v>1.8</v>
+        <v>1.12</v>
       </c>
       <c r="AA67">
-        <v>1.95</v>
+        <v>5.25</v>
       </c>
       <c r="AB67">
-        <v>2.65</v>
+        <v>1.48</v>
       </c>
       <c r="AC67">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="AD67">
-        <v>7</v>
+        <v>2.14</v>
       </c>
       <c r="AE67">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="AF67">
-        <v>2.63</v>
+        <v>1.52</v>
       </c>
       <c r="AG67">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="AH67">
-        <v>14.5</v>
+        <v>3.6</v>
       </c>
       <c r="AI67">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AJ67" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK67" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL67" s="3">
         <v>45858.66666666666</v>
@@ -9048,7 +9078,7 @@
         <v>60</v>
       </c>
       <c r="C68" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D68" t="s">
         <v>95</v>
@@ -9075,82 +9105,82 @@
         <v>273</v>
       </c>
       <c r="L68">
-        <v>2.17</v>
+        <v>2.75</v>
       </c>
       <c r="M68">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="N68">
-        <v>3.23</v>
+        <v>2.4</v>
       </c>
       <c r="O68">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="P68">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="Q68">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="R68">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="S68">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="T68">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U68">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V68">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="W68">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X68">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Y68">
-        <v>5.75</v>
+        <v>6.7</v>
       </c>
       <c r="Z68">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA68">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="AB68">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AC68">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AD68">
-        <v>5.89</v>
+        <v>4.8</v>
       </c>
       <c r="AE68">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF68">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="AG68">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH68">
-        <v>12</v>
+        <v>9.25</v>
       </c>
       <c r="AI68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ68" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK68" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL68" s="3">
         <v>45858.66666666666</v>
@@ -9164,7 +9194,7 @@
         <v>60</v>
       </c>
       <c r="C69" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D69" t="s">
         <v>95</v>
@@ -9191,82 +9221,82 @@
         <v>273</v>
       </c>
       <c r="L69">
-        <v>2.44</v>
+        <v>1.4</v>
       </c>
       <c r="M69">
+        <v>3.75</v>
+      </c>
+      <c r="N69">
+        <v>7.2</v>
+      </c>
+      <c r="O69">
+        <v>1.22</v>
+      </c>
+      <c r="P69">
+        <v>8.5</v>
+      </c>
+      <c r="Q69">
+        <v>6</v>
+      </c>
+      <c r="R69">
+        <v>1.33</v>
+      </c>
+      <c r="S69">
+        <v>3</v>
+      </c>
+      <c r="T69">
+        <v>2.6</v>
+      </c>
+      <c r="U69">
+        <v>1.38</v>
+      </c>
+      <c r="V69">
+        <v>6</v>
+      </c>
+      <c r="W69">
+        <v>1.09</v>
+      </c>
+      <c r="X69">
+        <v>1.02</v>
+      </c>
+      <c r="Y69">
+        <v>12</v>
+      </c>
+      <c r="Z69">
+        <v>1.27</v>
+      </c>
+      <c r="AA69">
         <v>3.48</v>
       </c>
-      <c r="N69">
-        <v>2.42</v>
-      </c>
-      <c r="O69">
-        <v>1.73</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>2.2</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <v>0</v>
-      </c>
-      <c r="T69">
-        <v>0</v>
-      </c>
-      <c r="U69">
-        <v>0</v>
-      </c>
-      <c r="V69">
-        <v>0</v>
-      </c>
-      <c r="W69">
-        <v>0</v>
-      </c>
-      <c r="X69">
-        <v>0</v>
-      </c>
-      <c r="Y69">
-        <v>0</v>
-      </c>
-      <c r="Z69">
-        <v>0</v>
-      </c>
-      <c r="AA69">
-        <v>0</v>
-      </c>
       <c r="AB69">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC69">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH69">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI69">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ69" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK69" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL69" s="3">
         <v>45858.66666666666</v>
@@ -9280,7 +9310,7 @@
         <v>60</v>
       </c>
       <c r="C70" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D70" t="s">
         <v>95</v>
@@ -9307,82 +9337,82 @@
         <v>273</v>
       </c>
       <c r="L70">
-        <v>1.33</v>
+        <v>2.49</v>
       </c>
       <c r="M70">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="N70">
-        <v>10</v>
+        <v>2.4</v>
       </c>
       <c r="O70">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="P70">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q70">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="R70">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S70">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T70">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="U70">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="V70">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="W70">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y70">
         <v>12</v>
       </c>
       <c r="Z70">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AA70">
-        <v>3.48</v>
+        <v>4.5</v>
       </c>
       <c r="AB70">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AC70">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AD70">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AE70">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AF70">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AG70">
-        <v>1.46</v>
+        <v>2.5</v>
       </c>
       <c r="AH70">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AI70">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AJ70" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK70" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL70" s="3">
         <v>45858.66666666666</v>
@@ -9396,7 +9426,7 @@
         <v>60</v>
       </c>
       <c r="C71" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D71" t="s">
         <v>95</v>
@@ -9423,82 +9453,82 @@
         <v>273</v>
       </c>
       <c r="L71">
-        <v>2.5</v>
+        <v>1.29</v>
       </c>
       <c r="M71">
-        <v>3.11</v>
+        <v>4.2</v>
       </c>
       <c r="N71">
-        <v>2.5</v>
+        <v>9.4</v>
       </c>
       <c r="O71">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="P71">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="Q71">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="R71">
+        <v>1.47</v>
+      </c>
+      <c r="S71">
+        <v>2.49</v>
+      </c>
+      <c r="T71">
+        <v>3.3</v>
+      </c>
+      <c r="U71">
+        <v>1.33</v>
+      </c>
+      <c r="V71">
+        <v>9.6</v>
+      </c>
+      <c r="W71">
+        <v>1</v>
+      </c>
+      <c r="X71">
+        <v>1.07</v>
+      </c>
+      <c r="Y71">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Z71">
+        <v>1.43</v>
+      </c>
+      <c r="AA71">
+        <v>2.55</v>
+      </c>
+      <c r="AB71">
+        <v>2.37</v>
+      </c>
+      <c r="AC71">
         <v>1.48</v>
       </c>
-      <c r="S71">
-        <v>2.5</v>
-      </c>
-      <c r="T71">
-        <v>3.2</v>
-      </c>
-      <c r="U71">
-        <v>1.3</v>
-      </c>
-      <c r="V71">
-        <v>8</v>
-      </c>
-      <c r="W71">
-        <v>1.05</v>
-      </c>
-      <c r="X71">
-        <v>1.08</v>
-      </c>
-      <c r="Y71">
-        <v>8</v>
-      </c>
-      <c r="Z71">
-        <v>1.36</v>
-      </c>
-      <c r="AA71">
-        <v>2.9</v>
-      </c>
-      <c r="AB71">
-        <v>2.2</v>
-      </c>
-      <c r="AC71">
-        <v>1.55</v>
-      </c>
       <c r="AD71">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AE71">
         <v>1.2</v>
       </c>
       <c r="AF71">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="AG71">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AH71">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AI71">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AJ71" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK71" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL71" s="3">
         <v>45858.66666666666</v>
@@ -9512,7 +9542,7 @@
         <v>60</v>
       </c>
       <c r="C72" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D72" t="s">
         <v>95</v>
@@ -9539,82 +9569,82 @@
         <v>273</v>
       </c>
       <c r="L72">
-        <v>3.7</v>
+        <v>1.82</v>
       </c>
       <c r="M72">
-        <v>3.5</v>
+        <v>3.07</v>
       </c>
       <c r="N72">
-        <v>1.84</v>
+        <v>4.1</v>
       </c>
       <c r="O72">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P72">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q72">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R72">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="S72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T72">
-        <v>2.62</v>
+        <v>4.33</v>
       </c>
       <c r="U72">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="V72">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="W72">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y72">
-        <v>10</v>
+        <v>4.75</v>
       </c>
       <c r="Z72">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AA72">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="AB72">
-        <v>1.8</v>
+        <v>2.81</v>
       </c>
       <c r="AC72">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="AD72">
-        <v>2.95</v>
+        <v>7</v>
       </c>
       <c r="AE72">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AF72">
-        <v>1.7</v>
+        <v>2.63</v>
       </c>
       <c r="AG72">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AH72">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI72">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AJ72" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK72" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL72" s="3">
         <v>45858.66666666666</v>
@@ -9628,7 +9658,7 @@
         <v>60</v>
       </c>
       <c r="C73" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D73" t="s">
         <v>95</v>
@@ -9655,82 +9685,82 @@
         <v>273</v>
       </c>
       <c r="L73">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="M73">
-        <v>3.9</v>
+        <v>2.51</v>
       </c>
       <c r="N73">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="O73">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="P73">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Q73">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="R73">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="S73">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="T73">
+        <v>4.33</v>
+      </c>
+      <c r="U73">
+        <v>1.18</v>
+      </c>
+      <c r="V73">
+        <v>11</v>
+      </c>
+      <c r="W73">
+        <v>1.01</v>
+      </c>
+      <c r="X73">
+        <v>1.15</v>
+      </c>
+      <c r="Y73">
+        <v>5</v>
+      </c>
+      <c r="Z73">
+        <v>1.6</v>
+      </c>
+      <c r="AA73">
         <v>2.1</v>
       </c>
-      <c r="U73">
-        <v>1.65</v>
-      </c>
-      <c r="V73">
-        <v>4.5</v>
-      </c>
-      <c r="W73">
-        <v>1.17</v>
-      </c>
-      <c r="X73">
-        <v>1</v>
-      </c>
-      <c r="Y73">
+      <c r="AB73">
+        <v>3.04</v>
+      </c>
+      <c r="AC73">
+        <v>1.33</v>
+      </c>
+      <c r="AD73">
+        <v>6.5</v>
+      </c>
+      <c r="AE73">
+        <v>1.1</v>
+      </c>
+      <c r="AF73">
+        <v>2.4</v>
+      </c>
+      <c r="AG73">
+        <v>1.5</v>
+      </c>
+      <c r="AH73">
         <v>12</v>
       </c>
-      <c r="Z73">
-        <v>1.12</v>
-      </c>
-      <c r="AA73">
-        <v>5.25</v>
-      </c>
-      <c r="AB73">
-        <v>1.48</v>
-      </c>
-      <c r="AC73">
-        <v>2.5</v>
-      </c>
-      <c r="AD73">
-        <v>2.1</v>
-      </c>
-      <c r="AE73">
-        <v>1.65</v>
-      </c>
-      <c r="AF73">
-        <v>1.55</v>
-      </c>
-      <c r="AG73">
-        <v>2.3</v>
-      </c>
-      <c r="AH73">
-        <v>3.6</v>
-      </c>
       <c r="AI73">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AJ73" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK73" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL73" s="3">
         <v>45858.66666666666</v>
@@ -9771,13 +9801,13 @@
         <v>273</v>
       </c>
       <c r="L74">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="M74">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N74">
-        <v>3.13</v>
+        <v>3.34</v>
       </c>
       <c r="O74">
         <v>1.75</v>
@@ -9789,7 +9819,7 @@
         <v>2.13</v>
       </c>
       <c r="R74">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S74">
         <v>3.3</v>
@@ -9804,49 +9834,49 @@
         <v>5</v>
       </c>
       <c r="W74">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X74">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y74">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z74">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AA74">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AB74">
+        <v>1.4</v>
+      </c>
+      <c r="AC74">
+        <v>2.25</v>
+      </c>
+      <c r="AD74">
+        <v>2.3</v>
+      </c>
+      <c r="AE74">
         <v>1.53</v>
       </c>
-      <c r="AC74">
-        <v>2.22</v>
-      </c>
-      <c r="AD74">
-        <v>1.91</v>
-      </c>
-      <c r="AE74">
-        <v>1.73</v>
-      </c>
       <c r="AF74">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AG74">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AH74">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AI74">
         <v>1.27</v>
       </c>
       <c r="AJ74" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK74" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL74" s="3">
         <v>45858.67708333334</v>
@@ -9905,19 +9935,19 @@
         <v>2.45</v>
       </c>
       <c r="R75">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="S75">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T75">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="U75">
         <v>1.22</v>
       </c>
       <c r="V75">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W75">
         <v>1.02</v>
@@ -9926,13 +9956,13 @@
         <v>1.11</v>
       </c>
       <c r="Y75">
-        <v>5.6</v>
+        <v>6.25</v>
       </c>
       <c r="Z75">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AA75">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB75">
         <v>2.3</v>
@@ -9941,28 +9971,28 @@
         <v>1.5</v>
       </c>
       <c r="AD75">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AE75">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF75">
         <v>2.3</v>
       </c>
       <c r="AG75">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AH75">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AI75">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ75" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK75" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL75" s="3">
         <v>45858.6875</v>
@@ -10021,28 +10051,28 @@
         <v>2.5</v>
       </c>
       <c r="R76">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="S76">
         <v>2.2</v>
       </c>
       <c r="T76">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="U76">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V76">
         <v>10</v>
       </c>
       <c r="W76">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X76">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y76">
-        <v>6.15</v>
+        <v>6.3</v>
       </c>
       <c r="Z76">
         <v>1.63</v>
@@ -10057,28 +10087,28 @@
         <v>1.48</v>
       </c>
       <c r="AD76">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="AE76">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF76">
         <v>2.5</v>
       </c>
       <c r="AG76">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AH76">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AI76">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ76" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK76" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL76" s="3">
         <v>45858.6875</v>
@@ -10098,10 +10128,10 @@
         <v>95</v>
       </c>
       <c r="E77" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="F77" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -10191,10 +10221,10 @@
         <v>1.03</v>
       </c>
       <c r="AJ77" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK77" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL77" s="3">
         <v>45858.69791666666</v>
@@ -10307,10 +10337,10 @@
         <v>0</v>
       </c>
       <c r="AJ78" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK78" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL78" s="3">
         <v>45858.69791666666</v>
@@ -10324,7 +10354,7 @@
         <v>64</v>
       </c>
       <c r="C79" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D79" t="s">
         <v>95</v>
@@ -10351,82 +10381,82 @@
         <v>273</v>
       </c>
       <c r="L79">
-        <v>3.5</v>
+        <v>1.64</v>
       </c>
       <c r="M79">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N79">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="O79">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="P79">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="Q79">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="R79">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S79">
         <v>2.4</v>
       </c>
       <c r="T79">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U79">
         <v>1.28</v>
       </c>
       <c r="V79">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="W79">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X79">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y79">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Z79">
         <v>1.44</v>
       </c>
       <c r="AA79">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AB79">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC79">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AD79">
-        <v>4.77</v>
+        <v>4.6</v>
       </c>
       <c r="AE79">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF79">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AG79">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AH79">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AI79">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ79" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK79" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL79" s="3">
         <v>45858.72916666666</v>
@@ -10440,7 +10470,7 @@
         <v>64</v>
       </c>
       <c r="C80" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D80" t="s">
         <v>95</v>
@@ -10467,82 +10497,82 @@
         <v>273</v>
       </c>
       <c r="L80">
-        <v>1.71</v>
+        <v>3.4</v>
       </c>
       <c r="M80">
-        <v>3.51</v>
+        <v>3.03</v>
       </c>
       <c r="N80">
-        <v>5</v>
+        <v>2.02</v>
       </c>
       <c r="O80">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="P80">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="Q80">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="R80">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S80">
         <v>2.4</v>
       </c>
       <c r="T80">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U80">
         <v>1.28</v>
       </c>
       <c r="V80">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="W80">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X80">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y80">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="Z80">
         <v>1.44</v>
       </c>
       <c r="AA80">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AB80">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC80">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AD80">
-        <v>4.6</v>
+        <v>4.77</v>
       </c>
       <c r="AE80">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF80">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AG80">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH80">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AI80">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ80" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK80" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL80" s="3">
         <v>45858.72916666666</v>
@@ -10583,82 +10613,82 @@
         <v>273</v>
       </c>
       <c r="L81">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="M81">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="N81">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="O81">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="P81">
         <v>0</v>
       </c>
       <c r="Q81">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="R81">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="S81">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="T81">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="U81">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="V81">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="W81">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X81">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Y81">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="Z81">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AA81">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="AB81">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AC81">
         <v>1.33</v>
       </c>
       <c r="AD81">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AE81">
+        <v>1.1</v>
+      </c>
+      <c r="AF81">
+        <v>2.3</v>
+      </c>
+      <c r="AG81">
+        <v>1.57</v>
+      </c>
+      <c r="AH81">
+        <v>12</v>
+      </c>
+      <c r="AI81">
         <v>1.03</v>
       </c>
-      <c r="AF81">
-        <v>2.4</v>
-      </c>
-      <c r="AG81">
-        <v>1.44</v>
-      </c>
-      <c r="AH81">
-        <v>15</v>
-      </c>
-      <c r="AI81">
-        <v>1.01</v>
-      </c>
       <c r="AJ81" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK81" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL81" s="3">
         <v>45858.75</v>
@@ -10699,82 +10729,82 @@
         <v>273</v>
       </c>
       <c r="L82">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="M82">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="N82">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="O82">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="P82">
         <v>0</v>
       </c>
       <c r="Q82">
+        <v>2.6</v>
+      </c>
+      <c r="R82">
+        <v>1.74</v>
+      </c>
+      <c r="S82">
+        <v>2.02</v>
+      </c>
+      <c r="T82">
+        <v>4.7</v>
+      </c>
+      <c r="U82">
+        <v>1.14</v>
+      </c>
+      <c r="V82">
+        <v>11</v>
+      </c>
+      <c r="W82">
+        <v>1.03</v>
+      </c>
+      <c r="X82">
+        <v>1.1</v>
+      </c>
+      <c r="Y82">
+        <v>5.1</v>
+      </c>
+      <c r="Z82">
+        <v>1.48</v>
+      </c>
+      <c r="AA82">
+        <v>2.37</v>
+      </c>
+      <c r="AB82">
+        <v>2.94</v>
+      </c>
+      <c r="AC82">
+        <v>1.35</v>
+      </c>
+      <c r="AD82">
+        <v>7.5</v>
+      </c>
+      <c r="AE82">
+        <v>1.03</v>
+      </c>
+      <c r="AF82">
         <v>2.4</v>
       </c>
-      <c r="R82">
-        <v>1.65</v>
-      </c>
-      <c r="S82">
-        <v>2.05</v>
-      </c>
-      <c r="T82">
-        <v>3.9</v>
-      </c>
-      <c r="U82">
-        <v>1.17</v>
-      </c>
-      <c r="V82">
-        <v>11.5</v>
-      </c>
-      <c r="W82">
-        <v>1.02</v>
-      </c>
-      <c r="X82">
-        <v>1.17</v>
-      </c>
-      <c r="Y82">
-        <v>4.5</v>
-      </c>
-      <c r="Z82">
-        <v>1.7</v>
-      </c>
-      <c r="AA82">
-        <v>2.05</v>
-      </c>
-      <c r="AB82">
-        <v>3</v>
-      </c>
-      <c r="AC82">
-        <v>1.36</v>
-      </c>
-      <c r="AD82">
-        <v>6.5</v>
-      </c>
-      <c r="AE82">
-        <v>1.1</v>
-      </c>
-      <c r="AF82">
-        <v>2.3</v>
-      </c>
       <c r="AG82">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH82">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI82">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ82" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK82" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL82" s="3">
         <v>45858.75</v>
@@ -10833,10 +10863,10 @@
         <v>3.25</v>
       </c>
       <c r="R83">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S83">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T83">
         <v>3.33</v>
@@ -10854,7 +10884,7 @@
         <v>1.08</v>
       </c>
       <c r="Y83">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Z83">
         <v>1.45</v>
@@ -10869,28 +10899,28 @@
         <v>1.53</v>
       </c>
       <c r="AD83">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AE83">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF83">
         <v>2.12</v>
       </c>
       <c r="AG83">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH83">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI83">
         <v>1.02</v>
       </c>
       <c r="AJ83" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK83" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL83" s="3">
         <v>45858.77083333334</v>
@@ -10949,10 +10979,10 @@
         <v>2.3</v>
       </c>
       <c r="R84">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S84">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="T84">
         <v>3.2</v>
@@ -10961,22 +10991,22 @@
         <v>1.3</v>
       </c>
       <c r="V84">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W84">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X84">
         <v>1.04</v>
       </c>
       <c r="Y84">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="Z84">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AA84">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AB84">
         <v>2.37</v>
@@ -10985,13 +11015,13 @@
         <v>1.48</v>
       </c>
       <c r="AD84">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AE84">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AF84">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG84">
         <v>1.8</v>
@@ -11003,10 +11033,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ84" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK84" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL84" s="3">
         <v>45858.77083333334</v>
@@ -11047,52 +11077,52 @@
         <v>273</v>
       </c>
       <c r="L85">
-        <v>2.37</v>
+        <v>1.97</v>
       </c>
       <c r="M85">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="N85">
-        <v>3.19</v>
+        <v>4.1</v>
       </c>
       <c r="O85">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="P85">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q85">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="R85">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="S85">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="T85">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U85">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V85">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="W85">
         <v>1.02</v>
       </c>
       <c r="X85">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y85">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z85">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AA85">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AB85">
         <v>2.37</v>
@@ -11101,28 +11131,28 @@
         <v>1.48</v>
       </c>
       <c r="AD85">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AE85">
         <v>1.11</v>
       </c>
       <c r="AF85">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AG85">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AH85">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI85">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AJ85" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK85" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL85" s="3">
         <v>45858.79166666666</v>
@@ -11163,52 +11193,52 @@
         <v>273</v>
       </c>
       <c r="L86">
-        <v>1.97</v>
+        <v>2.37</v>
       </c>
       <c r="M86">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="N86">
-        <v>4.1</v>
+        <v>3.19</v>
       </c>
       <c r="O86">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="P86">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q86">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="R86">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S86">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T86">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U86">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V86">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="W86">
         <v>1.02</v>
       </c>
       <c r="X86">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y86">
         <v>5.5</v>
       </c>
       <c r="Z86">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AA86">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AB86">
         <v>2.37</v>
@@ -11217,28 +11247,28 @@
         <v>1.48</v>
       </c>
       <c r="AD86">
-        <v>5.5</v>
+        <v>4.85</v>
       </c>
       <c r="AE86">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF86">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG86">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH86">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AI86">
         <v>1.02</v>
       </c>
       <c r="AJ86" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK86" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL86" s="3">
         <v>45858.79166666666</v>
@@ -11258,10 +11288,10 @@
         <v>95</v>
       </c>
       <c r="E87" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F87" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -11351,10 +11381,10 @@
         <v>1.09</v>
       </c>
       <c r="AJ87" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK87" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL87" s="3">
         <v>45858.79166666666</v>
@@ -11368,7 +11398,7 @@
         <v>68</v>
       </c>
       <c r="C88" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D88" t="s">
         <v>95</v>
@@ -11395,13 +11425,13 @@
         <v>273</v>
       </c>
       <c r="L88">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="M88">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="N88">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="O88">
         <v>1.44</v>
@@ -11443,10 +11473,10 @@
         <v>2.4</v>
       </c>
       <c r="AB88">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AC88">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AD88">
         <v>5</v>
@@ -11467,10 +11497,10 @@
         <v>1.07</v>
       </c>
       <c r="AJ88" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK88" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL88" s="3">
         <v>45858.8125</v>
@@ -11484,7 +11514,7 @@
         <v>69</v>
       </c>
       <c r="C89" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D89" t="s">
         <v>95</v>
@@ -11511,13 +11541,13 @@
         <v>273</v>
       </c>
       <c r="L89">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M89">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="N89">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="O89">
         <v>1.53</v>
@@ -11529,13 +11559,13 @@
         <v>2.4</v>
       </c>
       <c r="R89">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S89">
         <v>4</v>
       </c>
       <c r="T89">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U89">
         <v>1.75</v>
@@ -11565,28 +11595,28 @@
         <v>2.7</v>
       </c>
       <c r="AD89">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AE89">
         <v>1.8</v>
       </c>
       <c r="AF89">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG89">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AH89">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AI89">
         <v>1.33</v>
       </c>
       <c r="AJ89" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK89" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL89" s="3">
         <v>45858.83333333334</v>
@@ -11600,16 +11630,16 @@
         <v>70</v>
       </c>
       <c r="C90" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D90" t="s">
         <v>95</v>
       </c>
       <c r="E90" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="F90" t="s">
-        <v>268</v>
+        <v>228</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -11627,82 +11657,82 @@
         <v>273</v>
       </c>
       <c r="L90">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="M90">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="N90">
-        <v>2.76</v>
+        <v>4.2</v>
       </c>
       <c r="O90">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q90">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB90">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AC90">
+        <v>1.55</v>
+      </c>
+      <c r="AD90">
+        <v>4.5</v>
+      </c>
+      <c r="AE90">
+        <v>1.2</v>
+      </c>
+      <c r="AF90">
+        <v>2.05</v>
+      </c>
+      <c r="AG90">
         <v>1.7</v>
       </c>
-      <c r="AD90">
-        <v>0</v>
-      </c>
-      <c r="AE90">
-        <v>0</v>
-      </c>
-      <c r="AF90">
-        <v>0</v>
-      </c>
-      <c r="AG90">
-        <v>0</v>
-      </c>
       <c r="AH90">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI90">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ90" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK90" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL90" s="3">
         <v>45858.875</v>
@@ -11716,16 +11746,16 @@
         <v>70</v>
       </c>
       <c r="C91" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D91" t="s">
         <v>95</v>
       </c>
       <c r="E91" t="s">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="F91" t="s">
-        <v>225</v>
+        <v>268</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -11743,82 +11773,82 @@
         <v>273</v>
       </c>
       <c r="L91">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="M91">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="N91">
-        <v>4.2</v>
+        <v>2.76</v>
       </c>
       <c r="O91">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="P91">
-        <v>6.75</v>
+        <v>8.25</v>
       </c>
       <c r="Q91">
+        <v>2.25</v>
+      </c>
+      <c r="R91">
+        <v>1.42</v>
+      </c>
+      <c r="S91">
+        <v>2.62</v>
+      </c>
+      <c r="T91">
+        <v>2.9</v>
+      </c>
+      <c r="U91">
+        <v>1.36</v>
+      </c>
+      <c r="V91">
+        <v>7</v>
+      </c>
+      <c r="W91">
+        <v>1.07</v>
+      </c>
+      <c r="X91">
+        <v>1.06</v>
+      </c>
+      <c r="Y91">
+        <v>8.5</v>
+      </c>
+      <c r="Z91">
+        <v>1.36</v>
+      </c>
+      <c r="AA91">
         <v>3</v>
       </c>
-      <c r="R91">
-        <v>1.5</v>
-      </c>
-      <c r="S91">
-        <v>2.5</v>
-      </c>
-      <c r="T91">
-        <v>3.4</v>
-      </c>
-      <c r="U91">
-        <v>1.3</v>
-      </c>
-      <c r="V91">
-        <v>10</v>
-      </c>
-      <c r="W91">
-        <v>1.06</v>
-      </c>
-      <c r="X91">
-        <v>1.09</v>
-      </c>
-      <c r="Y91">
-        <v>7</v>
-      </c>
-      <c r="Z91">
-        <v>1.45</v>
-      </c>
-      <c r="AA91">
-        <v>2.7</v>
-      </c>
       <c r="AB91">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AC91">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AD91">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AE91">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF91">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AG91">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AH91">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI91">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AJ91" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK91" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL91" s="3">
         <v>45858.875</v>
@@ -11832,7 +11862,7 @@
         <v>71</v>
       </c>
       <c r="C92" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D92" t="s">
         <v>95</v>
@@ -11859,13 +11889,13 @@
         <v>273</v>
       </c>
       <c r="L92">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="M92">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="N92">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="O92">
         <v>1.73</v>
@@ -11877,64 +11907,64 @@
         <v>2.2</v>
       </c>
       <c r="R92">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S92">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="T92">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="U92">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="V92">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="W92">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z92">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AA92">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="AB92">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC92">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD92">
-        <v>2.46</v>
+        <v>3.04</v>
       </c>
       <c r="AE92">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF92">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG92">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="AH92">
-        <v>4.4</v>
+        <v>5.05</v>
       </c>
       <c r="AI92">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AJ92" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK92" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL92" s="3">
         <v>45858.9375</v>
@@ -11948,7 +11978,7 @@
         <v>72</v>
       </c>
       <c r="C93" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D93" t="s">
         <v>95</v>
@@ -11993,16 +12023,16 @@
         <v>2.5</v>
       </c>
       <c r="R93">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S93">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="T93">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="U93">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V93">
         <v>3.6</v>
@@ -12017,40 +12047,40 @@
         <v>0</v>
       </c>
       <c r="Z93">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AA93">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB93">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AC93">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD93">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AE93">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AF93">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG93">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AH93">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AI93">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AJ93" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK93" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL93" s="3">
         <v>45858.95833333334</v>
@@ -12064,7 +12094,7 @@
         <v>72</v>
       </c>
       <c r="C94" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D94" t="s">
         <v>95</v>
@@ -12091,13 +12121,13 @@
         <v>273</v>
       </c>
       <c r="L94">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="M94">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N94">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="O94">
         <v>1.73</v>
@@ -12115,7 +12145,7 @@
         <v>3.8</v>
       </c>
       <c r="T94">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="U94">
         <v>1.73</v>
@@ -12133,40 +12163,40 @@
         <v>0</v>
       </c>
       <c r="Z94">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AA94">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AB94">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AC94">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD94">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AE94">
         <v>1.73</v>
       </c>
       <c r="AF94">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AG94">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH94">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AI94">
         <v>1.3</v>
       </c>
       <c r="AJ94" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AK94" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AL94" s="3">
         <v>45858.95833333334</v>
